--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cemil\subiecte\prc\2025-2026\CPNP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8433F-C32C-4CF0-B702-3196612E2784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA1CB48-F5CA-4301-83F1-6555C03219D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="5" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="IDF..." sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="158">
   <si>
     <t>Spatiu ocupat in U</t>
   </si>
@@ -258,141 +259,6 @@
     <t>AVG_In Room</t>
   </si>
   <si>
-    <t>GF01</t>
-  </si>
-  <si>
-    <t>GF02</t>
-  </si>
-  <si>
-    <t>GF03</t>
-  </si>
-  <si>
-    <t>GF04</t>
-  </si>
-  <si>
-    <t>GF05</t>
-  </si>
-  <si>
-    <t>GF06</t>
-  </si>
-  <si>
-    <t>GF07</t>
-  </si>
-  <si>
-    <t>GF08</t>
-  </si>
-  <si>
-    <t>GF09</t>
-  </si>
-  <si>
-    <t>GF10</t>
-  </si>
-  <si>
-    <t>GF11</t>
-  </si>
-  <si>
-    <t>GF12</t>
-  </si>
-  <si>
-    <t>GF13</t>
-  </si>
-  <si>
-    <t>GF14</t>
-  </si>
-  <si>
-    <t>GF15</t>
-  </si>
-  <si>
-    <t>GF16</t>
-  </si>
-  <si>
-    <t>GF17</t>
-  </si>
-  <si>
-    <t>GF18</t>
-  </si>
-  <si>
-    <t>FF01</t>
-  </si>
-  <si>
-    <t>FF02</t>
-  </si>
-  <si>
-    <t>FF03</t>
-  </si>
-  <si>
-    <t>FF04</t>
-  </si>
-  <si>
-    <t>FF05</t>
-  </si>
-  <si>
-    <t>FF06</t>
-  </si>
-  <si>
-    <t>FF07</t>
-  </si>
-  <si>
-    <t>FF08</t>
-  </si>
-  <si>
-    <t>FF09</t>
-  </si>
-  <si>
-    <t>FF10</t>
-  </si>
-  <si>
-    <t>FF11</t>
-  </si>
-  <si>
-    <t>FF12</t>
-  </si>
-  <si>
-    <t>FF13</t>
-  </si>
-  <si>
-    <t>FF14</t>
-  </si>
-  <si>
-    <t>FF15</t>
-  </si>
-  <si>
-    <t>FF16</t>
-  </si>
-  <si>
-    <t>FF17</t>
-  </si>
-  <si>
-    <t>FF18</t>
-  </si>
-  <si>
-    <t>FF19</t>
-  </si>
-  <si>
-    <t>FF20</t>
-  </si>
-  <si>
-    <t>FF21</t>
-  </si>
-  <si>
-    <t>FF22</t>
-  </si>
-  <si>
-    <t>FF23</t>
-  </si>
-  <si>
-    <t>FF24</t>
-  </si>
-  <si>
-    <t>FF25</t>
-  </si>
-  <si>
-    <t>FF26</t>
-  </si>
-  <si>
-    <t>FF27</t>
-  </si>
-  <si>
     <t>MDF</t>
   </si>
   <si>
@@ -457,6 +323,252 @@
   </si>
   <si>
     <t>From detailed calcullus of prototype room/rooms</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>1.28</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>1.33</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>1.37</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <t>2.15</t>
+  </si>
+  <si>
+    <t>2.16</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>2.22</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>2.24/25</t>
+  </si>
+  <si>
+    <t>2.26</t>
+  </si>
+  <si>
+    <t>2.27</t>
+  </si>
+  <si>
+    <t>2.28</t>
+  </si>
+  <si>
+    <t>2.29</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>2.35</t>
+  </si>
+  <si>
+    <t>2.36</t>
+  </si>
+  <si>
+    <t>2.37</t>
+  </si>
+  <si>
+    <t>2.38</t>
+  </si>
+  <si>
+    <t>2.39</t>
+  </si>
+  <si>
+    <t>2.40</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>2.21</t>
+  </si>
+  <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>2.20</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>1.20</t>
+  </si>
+  <si>
+    <t>BATHROOM</t>
+  </si>
+  <si>
+    <t>1.34</t>
+  </si>
+  <si>
+    <t>1.35</t>
   </si>
 </sst>
 </file>
@@ -525,7 +637,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,8 +704,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -922,11 +1046,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -985,11 +1160,70 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1323,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29A6EC-8F37-4E8F-9E44-40C579389B24}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1340,16 +1574,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="F1" s="39" t="s">
         <v>51</v>
@@ -1361,1342 +1595,2307 @@
         <v>53</v>
       </c>
       <c r="I1" s="40" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="46">
-        <v>6</v>
-      </c>
-      <c r="D2" s="46">
-        <v>8</v>
+      <c r="C2" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D2" s="55">
+        <v>8.5</v>
       </c>
       <c r="E2" s="41">
         <f>C2*D2</f>
-        <v>48</v>
+        <v>55.25</v>
       </c>
       <c r="F2" s="41">
         <f>ROUNDUP(E2/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G2" s="46">
         <v>6</v>
       </c>
-      <c r="H2" s="49">
-        <v>12</v>
-      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="49"/>
       <c r="I2" s="42">
         <f>2*F2*(G2+H2+3)</f>
-        <v>210</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="47">
+      <c r="A3" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="D3" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="E3" s="9">
+        <f t="shared" ref="E3:E18" si="0">C3*D3</f>
+        <v>55.25</v>
+      </c>
+      <c r="F3" s="9">
+        <f t="shared" ref="F3:F19" si="1">ROUNDUP(E3/10,0)</f>
         <v>6</v>
       </c>
-      <c r="D3" s="47">
-        <v>8</v>
-      </c>
-      <c r="E3" s="9">
-        <f t="shared" ref="E3:E10" si="0">C3*D3</f>
-        <v>48</v>
-      </c>
-      <c r="F3" s="9">
-        <f t="shared" ref="F3:F10" si="1">ROUNDUP(E3/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="47">
-        <v>11</v>
-      </c>
-      <c r="H3" s="50">
-        <v>12</v>
-      </c>
+      <c r="G3" s="47"/>
+      <c r="H3" s="50"/>
       <c r="I3" s="43">
-        <f t="shared" ref="I3:I10" si="2">2*F3*(G3+H3+3)</f>
-        <v>260</v>
+        <f t="shared" ref="I3:I19" si="2">2*F3*(G3+H3+3)</f>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="47">
-        <v>8</v>
-      </c>
-      <c r="D4" s="47">
-        <v>12</v>
+      <c r="A4" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="55">
+        <v>4</v>
+      </c>
+      <c r="D4" s="55">
+        <v>4</v>
       </c>
       <c r="E4" s="9">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="F4" s="9">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G4" s="47">
-        <v>17</v>
-      </c>
-      <c r="H4" s="50">
-        <v>14</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="43">
         <f t="shared" si="2"/>
-        <v>680</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="A5" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="55">
+        <v>8.5</v>
+      </c>
       <c r="E5" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F5" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="G5" s="54"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="A6" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D6" s="55">
+        <v>8.5</v>
+      </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="47"/>
-      <c r="H6" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="G6" s="55"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="A7" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D7" s="55">
+        <v>8.5</v>
+      </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F7" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="G7" s="55"/>
+      <c r="H7" s="57"/>
       <c r="I7" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="A8" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D8" s="55">
+        <v>8.5</v>
+      </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F8" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="47"/>
-      <c r="H8" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="G8" s="54"/>
+      <c r="H8" s="56"/>
       <c r="I8" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
+      <c r="A9" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D9" s="55">
+        <v>8.5</v>
+      </c>
       <c r="E9" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="F9" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="47"/>
-      <c r="H9" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="G9" s="55"/>
+      <c r="H9" s="57"/>
       <c r="I9" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="9">
+      <c r="A10" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="69"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="D12" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="9">
+        <v>97.75</v>
+      </c>
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="47"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="43">
+        <v>10</v>
+      </c>
+      <c r="G12" s="55"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29">
-        <f>SUM(F2:F10)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="55">
         <v>20</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29">
-        <f>SUM(I2:I10)</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="D13" s="55">
+        <v>16.5</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="0"/>
+        <v>330</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="G13" s="55"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="43">
+        <f t="shared" si="2"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D14" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G14" s="54"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="43">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D15" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G15" s="55"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="43">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D16" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G16" s="55"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="43">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D17" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E17" s="9">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G17" s="54"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="43">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D18" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G18" s="55"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="43">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="55">
+        <v>10</v>
+      </c>
+      <c r="D19" s="55">
+        <v>20</v>
+      </c>
+      <c r="E19" s="9">
+        <f>C19*D19</f>
+        <v>200</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G19" s="55"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="43">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="1">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1">
-        <f>C12*D12</f>
-        <v>48</v>
-      </c>
-      <c r="F12" s="1">
-        <f>ROUNDUP(E12/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G12" s="1">
-        <v>6</v>
-      </c>
-      <c r="H12" s="1">
-        <v>12</v>
-      </c>
-      <c r="I12" s="1">
-        <f>2*F12*(G12+H12+3)</f>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="1">
-        <v>6</v>
-      </c>
-      <c r="D13" s="1">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" ref="E13:E14" si="3">C13*D13</f>
-        <v>48</v>
-      </c>
-      <c r="F13" s="1">
-        <f t="shared" ref="F13:F20" si="4">ROUNDUP(E13/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>12</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" ref="I13:I20" si="5">2*F13*(G13+H13+3)</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="1">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="3"/>
-        <v>96</v>
-      </c>
-      <c r="F14" s="1">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="G14" s="1">
-        <v>17</v>
-      </c>
-      <c r="H14" s="1">
-        <v>15</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="5"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1">
-        <f t="shared" ref="E15:E20" si="6">C15*D15</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29">
+        <f>SUM(F2:F19)</f>
+        <v>142</v>
+      </c>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29">
+        <f>SUM(I2:I19)</f>
+        <v>852</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
-        <v>109</v>
-      </c>
+      <c r="A21" s="29"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
-      <c r="F21" s="29">
-        <f>SUM(F12:F20)</f>
-        <v>20</v>
-      </c>
+      <c r="F21" s="29"/>
       <c r="G21" s="29"/>
       <c r="H21" s="29"/>
-      <c r="I21" s="29">
-        <f>SUM(I12:I20)</f>
-        <v>1170</v>
-      </c>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D22" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" ref="E22:E23" si="3">C22*D22</f>
+        <v>74.75</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" ref="F22:F23" si="4">ROUNDUP(E22/10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G22" s="47"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="43">
+        <f t="shared" ref="I22:I23" si="5">2*F22*(G22+H22+3)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D23" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" si="3"/>
+        <v>74.75</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G23" s="47"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="43">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="63"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="55">
+        <v>10</v>
+      </c>
+      <c r="D26" s="55">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9">
+        <f>C26*D26</f>
+        <v>200</v>
+      </c>
+      <c r="F26" s="9">
+        <f>ROUNDUP(E26/10,0)</f>
+        <v>20</v>
+      </c>
+      <c r="G26" s="47"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="43">
+        <f>2*F26*(G26+H26+3)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="47">
+        <v>9</v>
+      </c>
+      <c r="D27" s="47">
+        <v>10</v>
+      </c>
+      <c r="E27" s="9">
+        <f>C27*D27</f>
+        <v>90</v>
+      </c>
+      <c r="F27" s="9">
+        <f>ROUNDUP(E27/10,0)</f>
+        <v>9</v>
+      </c>
+      <c r="G27" s="47"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="43">
+        <f>2*F27*(G27+H27+3)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="47">
+        <v>9</v>
+      </c>
+      <c r="D28" s="47">
+        <v>10</v>
+      </c>
+      <c r="E28" s="9">
+        <f t="shared" ref="E28:E29" si="6">C28*D28</f>
+        <v>90</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" ref="F28:F44" si="7">ROUNDUP(E28/10,0)</f>
+        <v>9</v>
+      </c>
+      <c r="G28" s="47"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="43">
+        <f t="shared" ref="I28:I44" si="8">2*F28*(G28+H28+3)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D29" s="47">
+        <v>9</v>
+      </c>
+      <c r="E29" s="9">
+        <f t="shared" si="6"/>
+        <v>58.5</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="G29" s="47"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="43">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D30" s="47">
+        <v>9</v>
+      </c>
+      <c r="E30" s="9">
+        <f t="shared" ref="E30:E44" si="9">C30*D30</f>
+        <v>58.5</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="G30" s="47"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="43">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="47">
+        <v>4</v>
+      </c>
+      <c r="D31" s="47">
+        <v>4</v>
+      </c>
+      <c r="E31" s="9">
+        <f t="shared" si="9"/>
+        <v>16</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="G31" s="47"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="43">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D32" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" si="9"/>
+        <v>42.75</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="G32" s="47"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="43">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D33" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" si="9"/>
+        <v>42.75</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="G33" s="47"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="43">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D34" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" si="9"/>
+        <v>42.75</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="G34" s="47"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="43">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D35" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="9"/>
+        <v>42.75</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="G35" s="47"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="43">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D36" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="9"/>
+        <v>42.75</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="G36" s="47"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="43">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="75"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="78"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D39" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E39" s="9">
+        <f t="shared" si="9"/>
+        <v>81.25</v>
+      </c>
+      <c r="F39" s="9">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="G39" s="47"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="43">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D40" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E40" s="9">
+        <f t="shared" si="9"/>
+        <v>68.75</v>
+      </c>
+      <c r="F40" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="G40" s="47"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="43">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D41" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E41" s="9">
+        <f t="shared" si="9"/>
+        <v>68.75</v>
+      </c>
+      <c r="F41" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="G41" s="47"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="43">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D42" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E42" s="9">
+        <f t="shared" si="9"/>
+        <v>68.75</v>
+      </c>
+      <c r="F42" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="G42" s="47"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="43">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D43" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E43" s="9">
+        <f t="shared" si="9"/>
+        <v>68.75</v>
+      </c>
+      <c r="F43" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="G43" s="47"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="43">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D44" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E44" s="9">
+        <f t="shared" si="9"/>
+        <v>68.75</v>
+      </c>
+      <c r="F44" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="G44" s="47"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="43">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29">
+        <f>SUM(F22:F44)</f>
+        <v>137</v>
+      </c>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29">
+        <f>SUM(I22:I44)</f>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D47" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E47" s="9">
+        <f>C47*D47</f>
+        <v>55.25</v>
+      </c>
+      <c r="F47" s="9">
+        <f>ROUNDUP(E47/10,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G47" s="47"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="43">
+        <f>2*F47*(G47+H47+3)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="D48" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="E48" s="9">
+        <f t="shared" ref="E48:E49" si="10">C48*D48</f>
+        <v>55.25</v>
+      </c>
+      <c r="F48" s="9">
+        <f t="shared" ref="F48:F64" si="11">ROUNDUP(E48/10,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G48" s="47"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="43">
+        <f t="shared" ref="I48:I64" si="12">2*F48*(G48+H48+3)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="55">
+        <v>4</v>
+      </c>
+      <c r="D49" s="55">
+        <v>4</v>
+      </c>
+      <c r="E49" s="9">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="F49" s="9">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="G49" s="47"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="43">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D50" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E50" s="9">
+        <f t="shared" ref="E50:E64" si="13">C50*D50</f>
+        <v>46.75</v>
+      </c>
+      <c r="F50" s="9">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="G50" s="47"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="43">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D51" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E51" s="9">
+        <f t="shared" si="13"/>
+        <v>46.75</v>
+      </c>
+      <c r="F51" s="9">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="G51" s="47"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="43">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D52" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E52" s="9">
+        <f t="shared" si="13"/>
+        <v>46.75</v>
+      </c>
+      <c r="F52" s="9">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="G52" s="47"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="43">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D53" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E53" s="9">
+        <f t="shared" si="13"/>
+        <v>46.75</v>
+      </c>
+      <c r="F53" s="9">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="G53" s="47"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="43">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="55">
+        <v>5.5</v>
+      </c>
+      <c r="D54" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="E54" s="9">
+        <f t="shared" si="13"/>
+        <v>46.75</v>
+      </c>
+      <c r="F54" s="9">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="G54" s="47"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="43">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" s="68"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="68"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="69"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="70"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="72"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="D57" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E57" s="9">
+        <f t="shared" si="13"/>
+        <v>97.75</v>
+      </c>
+      <c r="F57" s="9">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="G57" s="47"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="43">
+        <f t="shared" si="12"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="55">
+        <v>20</v>
+      </c>
+      <c r="D58" s="55">
+        <v>16.5</v>
+      </c>
+      <c r="E58" s="9">
+        <f t="shared" si="13"/>
+        <v>330</v>
+      </c>
+      <c r="F58" s="9">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="G58" s="47"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="43">
+        <f t="shared" si="12"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D59" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E59" s="9">
+        <f t="shared" si="13"/>
+        <v>74.75</v>
+      </c>
+      <c r="F59" s="9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G59" s="47"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="43">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D60" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E60" s="9">
+        <f t="shared" si="13"/>
+        <v>74.75</v>
+      </c>
+      <c r="F60" s="9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G60" s="47"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="43">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D61" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E61" s="9">
+        <f t="shared" si="13"/>
+        <v>74.75</v>
+      </c>
+      <c r="F61" s="9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G61" s="47"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="43">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D62" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E62" s="9">
+        <f t="shared" si="13"/>
+        <v>74.75</v>
+      </c>
+      <c r="F62" s="9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G62" s="47"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="43">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D63" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E63" s="9">
+        <f t="shared" si="13"/>
+        <v>74.75</v>
+      </c>
+      <c r="F63" s="9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G63" s="47"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="43">
+        <f t="shared" si="12"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="55">
+        <v>10</v>
+      </c>
+      <c r="D64" s="55">
+        <v>20</v>
+      </c>
+      <c r="E64" s="9">
+        <f t="shared" si="13"/>
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="G64" s="47"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="43">
+        <f t="shared" si="12"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29">
+        <f>SUM(F47:F64)</f>
+        <v>142</v>
+      </c>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29">
+        <f>SUM(I47:I64)</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D67" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E67" s="9">
+        <f t="shared" ref="E67:E70" si="14">C67*D67</f>
+        <v>74.75</v>
+      </c>
+      <c r="F67" s="9">
+        <f t="shared" ref="F67:F70" si="15">ROUNDUP(E67/10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G67" s="47"/>
+      <c r="H67" s="59"/>
+      <c r="I67" s="43">
+        <f t="shared" ref="I67:I70" si="16">2*F67*(G67+H67+3)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="55">
+        <v>6.5</v>
+      </c>
+      <c r="D68" s="55">
+        <v>11.5</v>
+      </c>
+      <c r="E68" s="9">
+        <f>C68*D68</f>
+        <v>74.75</v>
+      </c>
+      <c r="F68" s="9">
+        <f>ROUNDUP(E68/10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G68" s="47"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="43">
+        <f>2*F68*(G68+H68+3)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="68"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="69"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" s="70"/>
+      <c r="C70" s="71"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="71"/>
+      <c r="F70" s="71"/>
+      <c r="G70" s="71"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="72"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="55">
+        <v>10</v>
+      </c>
+      <c r="D71" s="55">
+        <v>20</v>
+      </c>
+      <c r="E71" s="9">
+        <f>C71*D71</f>
+        <v>200</v>
+      </c>
+      <c r="F71" s="9">
+        <f>ROUNDUP(E71/10,0)</f>
+        <v>20</v>
+      </c>
+      <c r="G71" s="47"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="43">
+        <f>2*F71*(G71+H71+3)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="47">
+        <v>5</v>
+      </c>
+      <c r="D72" s="47">
+        <v>14</v>
+      </c>
+      <c r="E72" s="9">
+        <f t="shared" ref="E72:E73" si="17">C72*D72</f>
+        <v>70</v>
+      </c>
+      <c r="F72" s="9">
+        <f t="shared" ref="F72:F88" si="18">ROUNDUP(E72/10,0)</f>
+        <v>7</v>
+      </c>
+      <c r="G72" s="47"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="43">
+        <f t="shared" ref="I72:I88" si="19">2*F72*(G72+H72+3)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="47">
+        <v>9</v>
+      </c>
+      <c r="D73" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="E73" s="9">
+        <f t="shared" si="17"/>
+        <v>58.5</v>
+      </c>
+      <c r="F73" s="9">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+      <c r="G73" s="47"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="43">
+        <f t="shared" si="19"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C74" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D74" s="47">
+        <v>9</v>
+      </c>
+      <c r="E74" s="9">
+        <f>C74*D74</f>
+        <v>58.5</v>
+      </c>
+      <c r="F74" s="9">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+      <c r="G74" s="47"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="43">
+        <f t="shared" si="19"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D75" s="47">
+        <v>9</v>
+      </c>
+      <c r="E75" s="9">
+        <f>C75*D75</f>
+        <v>58.5</v>
+      </c>
+      <c r="F75" s="9">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+      <c r="G75" s="47"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="43">
+        <f t="shared" si="19"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="47">
+        <v>4</v>
+      </c>
+      <c r="D76" s="47">
+        <v>4</v>
+      </c>
+      <c r="E76" s="9">
+        <f>C76*D76</f>
+        <v>16</v>
+      </c>
+      <c r="F76" s="9">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="G76" s="47"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="43">
+        <f t="shared" si="19"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D77" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E77" s="9">
+        <f>C77*D77</f>
+        <v>42.75</v>
+      </c>
+      <c r="F77" s="9">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="G77" s="47"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="43">
+        <f t="shared" si="19"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C78" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D78" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E78" s="9">
+        <f>C78*D78</f>
+        <v>42.75</v>
+      </c>
+      <c r="F78" s="9">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="G78" s="47"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="43">
+        <f t="shared" si="19"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D79" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E79" s="9">
+        <f>C79*D79</f>
+        <v>42.75</v>
+      </c>
+      <c r="F79" s="9">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="G79" s="47"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="43">
+        <f t="shared" si="19"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="D80" s="47">
+        <v>9.5</v>
+      </c>
+      <c r="E80" s="9">
+        <f>C80*D80</f>
+        <v>42.75</v>
+      </c>
+      <c r="F80" s="9">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="G80" s="47"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="43">
+        <f t="shared" si="19"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="75"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="B82" s="76"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="77"/>
+      <c r="E82" s="77"/>
+      <c r="F82" s="77"/>
+      <c r="G82" s="77"/>
+      <c r="H82" s="77"/>
+      <c r="I82" s="78"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="B83" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D83" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E83" s="9">
+        <f t="shared" ref="E83:E88" si="20">C83*D83</f>
+        <v>81.25</v>
+      </c>
+      <c r="F83" s="9">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="G83" s="47"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="43">
+        <f t="shared" si="19"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="47">
+        <v>6.5</v>
+      </c>
+      <c r="D84" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E84" s="9">
+        <f t="shared" si="20"/>
+        <v>81.25</v>
+      </c>
+      <c r="F84" s="9">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="G84" s="47"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="43">
+        <f t="shared" si="19"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D85" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E85" s="9">
+        <f t="shared" si="20"/>
+        <v>68.75</v>
+      </c>
+      <c r="F85" s="9">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="G85" s="47"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="43">
+        <f t="shared" si="19"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D86" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E86" s="9">
+        <f t="shared" si="20"/>
+        <v>68.75</v>
+      </c>
+      <c r="F86" s="9">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="G86" s="47"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="43">
+        <f t="shared" si="19"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D87" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E87" s="9">
+        <f t="shared" si="20"/>
+        <v>68.75</v>
+      </c>
+      <c r="F87" s="9">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="G87" s="47"/>
+      <c r="H87" s="59"/>
+      <c r="I87" s="43">
+        <f t="shared" si="19"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C88" s="47">
+        <v>5.5</v>
+      </c>
+      <c r="D88" s="47">
+        <v>12.5</v>
+      </c>
+      <c r="E88" s="9">
+        <f t="shared" si="20"/>
+        <v>68.75</v>
+      </c>
+      <c r="F88" s="9">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="G88" s="47"/>
+      <c r="H88" s="59"/>
+      <c r="I88" s="43">
+        <f t="shared" si="19"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="29">
+        <f>SUM(F67:F88)</f>
+        <v>129</v>
+      </c>
+      <c r="G89" s="29"/>
+      <c r="H89" s="29"/>
+      <c r="I89" s="29">
+        <f>SUM(I67:I88)</f>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37">
+        <f>F89+F65+F45+F20</f>
+        <v>550</v>
+      </c>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+      <c r="I91" s="37">
+        <f>I89+I65+I45+I20</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H93" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="I93" s="29">
+        <f>ROUNDUP(ROUNDUP($I$91/305,0)*1.1,0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H94" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I94" s="29">
+        <f>ROUNDUP($I$91/2000,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="37">
+        <f>I91/(F91*2)</f>
+        <v>3</v>
+      </c>
+      <c r="E96" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B98" s="44"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="44"/>
+      <c r="G98" s="44"/>
+      <c r="H98" s="44"/>
+    </row>
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="1">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1">
-        <v>8</v>
-      </c>
-      <c r="E22" s="1">
-        <f>C22*D22</f>
-        <v>48</v>
-      </c>
-      <c r="F22" s="1">
-        <f>ROUNDUP(E22/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G22" s="1">
-        <v>6</v>
-      </c>
-      <c r="H22" s="1">
-        <v>11</v>
-      </c>
-      <c r="I22" s="1">
-        <f>2*F22*(G22+H22+3)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    </row>
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="1">
-        <v>6</v>
-      </c>
-      <c r="D23" s="1">
-        <v>8</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" ref="E23:E24" si="7">C23*D23</f>
-        <v>48</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" ref="F23:F34" si="8">ROUNDUP(E23/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>11</v>
-      </c>
-      <c r="I23" s="1">
-        <f t="shared" ref="I23:I34" si="9">2*F23*(G23+H23+3)</f>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1">
-        <v>12</v>
-      </c>
-      <c r="E24" s="1">
-        <f t="shared" si="7"/>
-        <v>96</v>
-      </c>
-      <c r="F24" s="1">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="G24" s="1">
-        <v>17</v>
-      </c>
-      <c r="H24" s="1">
-        <v>15</v>
-      </c>
-      <c r="I24" s="1">
-        <f t="shared" si="9"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    </row>
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1">
-        <f t="shared" ref="E25:E34" si="10">C25*D25</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29">
-        <f>SUM(F22:F34)</f>
-        <v>20</v>
-      </c>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29">
-        <f>SUM(I22:I34)</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="1">
-        <v>6</v>
-      </c>
-      <c r="D36" s="1">
-        <v>8</v>
-      </c>
-      <c r="E36" s="1">
-        <f>C36*D36</f>
-        <v>48</v>
-      </c>
-      <c r="F36" s="1">
-        <f>ROUNDUP(E36/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G36" s="1">
-        <v>11</v>
-      </c>
-      <c r="H36" s="1">
-        <v>12</v>
-      </c>
-      <c r="I36" s="1">
-        <f>2*F36*(G36+H36+3)</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="1">
-        <v>6</v>
-      </c>
-      <c r="D37" s="1">
-        <v>8</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" ref="E37:E49" si="11">C37*D37</f>
-        <v>48</v>
-      </c>
-      <c r="F37" s="1">
-        <f t="shared" ref="F37:F49" si="12">ROUNDUP(E37/10,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G37" s="1">
-        <v>11</v>
-      </c>
-      <c r="H37" s="1">
-        <v>12</v>
-      </c>
-      <c r="I37" s="1">
-        <f t="shared" ref="I37:I49" si="13">2*F37*(G37+H37+3)</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="1">
-        <v>8</v>
-      </c>
-      <c r="D38" s="1">
-        <v>12</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="11"/>
-        <v>96</v>
-      </c>
-      <c r="F38" s="1">
-        <f t="shared" si="12"/>
-        <v>10</v>
-      </c>
-      <c r="G38" s="1">
-        <v>17</v>
-      </c>
-      <c r="H38" s="1">
-        <v>14</v>
-      </c>
-      <c r="I38" s="1">
-        <f t="shared" si="13"/>
-        <v>680</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29">
-        <f>SUM(F36:F49)</f>
-        <v>20</v>
-      </c>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29">
-        <f>SUM(I36:I49)</f>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37">
-        <f>F50+F35+F21+F11</f>
-        <v>80</v>
-      </c>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37">
-        <f>I50+I35+I21+I11</f>
-        <v>4670</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H54" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="I54" s="29">
-        <f>ROUNDUP(ROUNDUP($I$52/305,0)*1.1,0)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H55" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="I55" s="29">
-        <f>ROUNDUP($I$52/2000,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="37">
-        <f>I52/(F52*2)</f>
-        <v>29.1875</v>
-      </c>
-      <c r="E57" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="44"/>
-    </row>
-    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="45" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B81:I82"/>
+    <mergeCell ref="B69:I70"/>
+    <mergeCell ref="B55:I56"/>
+    <mergeCell ref="B37:I38"/>
+    <mergeCell ref="B10:I11"/>
+    <mergeCell ref="B24:I25"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="C57">
+  <conditionalFormatting sqref="C96">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
       <formula>30</formula>
       <formula>60</formula>
@@ -2706,6 +3905,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A14:A19 A26:A36 A59:A64 A39:A44 A71:A88 A67 A68:A70 A22:A23 A24:A25 A37:A38" twoDigitTextYear="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2750,7 +3952,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="60" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
@@ -2769,12 +3971,12 @@
       <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="60" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="10">
         <v>1</v>
       </c>
@@ -2789,10 +3991,10 @@
       <c r="G3" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="53"/>
+      <c r="H3" s="61"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="53"/>
+      <c r="A4" s="61"/>
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -2809,10 +4011,10 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="53"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="53"/>
+      <c r="A5" s="61"/>
       <c r="B5" s="10">
         <v>1</v>
       </c>
@@ -2823,10 +4025,10 @@
       <c r="G5" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="53"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="53"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="10">
         <v>1</v>
       </c>
@@ -2843,10 +4045,10 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="53"/>
+      <c r="H6" s="61"/>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="53"/>
+      <c r="A7" s="61"/>
       <c r="B7" s="10">
         <v>1</v>
       </c>
@@ -2861,10 +4063,10 @@
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="53"/>
+      <c r="H7" s="61"/>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="53"/>
+      <c r="A8" s="61"/>
       <c r="B8" s="24">
         <v>1</v>
       </c>
@@ -2881,10 +4083,10 @@
       <c r="G8" s="5">
         <v>50</v>
       </c>
-      <c r="H8" s="53"/>
+      <c r="H8" s="61"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="53"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -2894,10 +4096,10 @@
       <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="61"/>
     </row>
     <row r="10" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="53"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -2910,10 +4112,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="53"/>
+      <c r="H10" s="61"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="53"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="10">
         <v>1</v>
       </c>
@@ -2924,10 +4126,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="53"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="10">
         <v>1</v>
       </c>
@@ -2938,10 +4140,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="53"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="10">
         <v>1</v>
       </c>
@@ -2952,10 +4154,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="61"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="53"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="10">
         <v>1</v>
       </c>
@@ -2964,10 +4166,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="10">
         <v>1</v>
       </c>
@@ -2978,10 +4180,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="53"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="10">
         <v>1</v>
       </c>
@@ -2992,10 +4194,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="61"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="24">
         <v>7</v>
       </c>
@@ -3004,70 +4206,70 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="61"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="24"/>
       <c r="C18" s="35"/>
       <c r="D18" s="10"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="61"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="24"/>
       <c r="C19" s="35"/>
       <c r="D19" s="10"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="61"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="24"/>
       <c r="C20" s="35"/>
       <c r="D20" s="10"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="61"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="53"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="24"/>
       <c r="C21" s="35"/>
       <c r="D21" s="10"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="61"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="24"/>
       <c r="C22" s="35"/>
       <c r="D22" s="10"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="61"/>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="53"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="24"/>
       <c r="C23" s="36"/>
       <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="61"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
+      <c r="A24" s="61"/>
       <c r="B24" s="10">
         <v>1</v>
       </c>
@@ -3078,10 +4280,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="61"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -3092,10 +4294,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="53"/>
+      <c r="H25" s="61"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="10">
         <v>1</v>
       </c>
@@ -3106,10 +4308,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="53"/>
+      <c r="H26" s="61"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="53"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="10">
         <v>1</v>
       </c>
@@ -3118,10 +4320,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="61"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="53"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="10">
         <v>1</v>
       </c>
@@ -3130,10 +4332,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="53"/>
+      <c r="H28" s="61"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="53"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="10">
         <v>1</v>
       </c>
@@ -3149,10 +4351,10 @@
       <c r="G29" s="5">
         <v>50</v>
       </c>
-      <c r="H29" s="53"/>
+      <c r="H29" s="61"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="53"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -3163,40 +4365,40 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="53"/>
+      <c r="H30" s="61"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="53"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="53"/>
+      <c r="H31" s="61"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="53"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="53"/>
+      <c r="H32" s="61"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="53"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="10"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="53"/>
+      <c r="H33" s="61"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="53"/>
+      <c r="A34" s="61"/>
       <c r="B34" s="10">
         <v>1</v>
       </c>
@@ -3209,10 +4411,10 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="53"/>
+      <c r="H34" s="61"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="53"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="10">
         <v>1</v>
       </c>
@@ -3223,10 +4425,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="53"/>
+      <c r="H35" s="61"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="53"/>
+      <c r="A36" s="61"/>
       <c r="B36" s="10">
         <v>1</v>
       </c>
@@ -3243,10 +4445,10 @@
       <c r="G36" s="5">
         <v>200</v>
       </c>
-      <c r="H36" s="53"/>
+      <c r="H36" s="61"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="53"/>
+      <c r="A37" s="61"/>
       <c r="B37" s="10">
         <v>2</v>
       </c>
@@ -3257,10 +4459,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="53"/>
+      <c r="H37" s="61"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="53"/>
+      <c r="A38" s="61"/>
       <c r="B38" s="10">
         <v>4</v>
       </c>
@@ -3275,10 +4477,10 @@
       <c r="G38" s="5">
         <v>250</v>
       </c>
-      <c r="H38" s="53"/>
+      <c r="H38" s="61"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="53"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="10">
         <v>4</v>
       </c>
@@ -3293,37 +4495,37 @@
       <c r="G39" s="5">
         <v>250</v>
       </c>
-      <c r="H39" s="53"/>
+      <c r="H39" s="61"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="53"/>
+      <c r="A40" s="61"/>
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="53"/>
+      <c r="H40" s="61"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="53"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="10"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="53"/>
+      <c r="H41" s="61"/>
     </row>
     <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="53"/>
+      <c r="A42" s="61"/>
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="53"/>
+      <c r="H42" s="61"/>
     </row>
     <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
@@ -3701,13 +4903,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1b380a0-b262-4a13-9203-497a21b8eee5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anul 4\Sem 2\CPNP\Network-Design-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA1CB48-F5CA-4301-83F1-6555C03219D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9B7D4C-BF45-42C8-98AA-873E2E7D9A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="IDF..." sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -95,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="161">
   <si>
     <t>Spatiu ocupat in U</t>
   </si>
@@ -569,6 +568,15 @@
   </si>
   <si>
     <t>1.35</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -717,7 +725,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1097,11 +1105,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1168,25 +1198,22 @@
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1207,23 +1234,36 @@
     <xf numFmtId="49" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1557,19 +1597,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29A6EC-8F37-4E8F-9E44-40C579389B24}">
-  <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J101"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>50</v>
       </c>
@@ -1597,8 +1637,11 @@
       <c r="I1" s="40" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="79" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>76</v>
       </c>
@@ -1620,13 +1663,18 @@
         <v>6</v>
       </c>
       <c r="G2" s="46"/>
-      <c r="H2" s="49"/>
+      <c r="H2" s="49">
+        <v>13.21</v>
+      </c>
       <c r="I2" s="42">
         <f>2*F2*(G2+H2+3)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>194.52</v>
+      </c>
+      <c r="J2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
         <v>77</v>
       </c>
@@ -1653,36 +1701,26 @@
         <f t="shared" ref="I3:I19" si="2">2*F3*(G3+H3+3)</f>
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="J3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="55">
-        <v>4</v>
-      </c>
-      <c r="D4" s="55">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="43">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="82"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="53" t="s">
         <v>79</v>
       </c>
@@ -1710,7 +1748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="53" t="s">
         <v>80</v>
       </c>
@@ -1738,7 +1776,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="53" t="s">
         <v>81</v>
       </c>
@@ -1766,7 +1804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
         <v>82</v>
       </c>
@@ -1794,7 +1832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>83</v>
       </c>
@@ -1822,35 +1860,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="69"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="68"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="72"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="69"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>86</v>
       </c>
@@ -1878,7 +1916,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="53" t="s">
         <v>87</v>
       </c>
@@ -1906,7 +1944,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>88</v>
       </c>
@@ -1934,7 +1972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>89</v>
       </c>
@@ -1962,7 +2000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>90</v>
       </c>
@@ -1990,7 +2028,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>91</v>
       </c>
@@ -2018,7 +2056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>92</v>
       </c>
@@ -2046,7 +2084,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>93</v>
       </c>
@@ -2074,7 +2112,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
         <v>63</v>
       </c>
@@ -2084,16 +2122,16 @@
       <c r="E20" s="29"/>
       <c r="F20" s="29">
         <f>SUM(F2:F19)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
       <c r="I20" s="29">
         <f>SUM(I2:I19)</f>
-        <v>852</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>998.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -2104,7 +2142,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
         <v>152</v>
       </c>
@@ -2132,7 +2170,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>153</v>
       </c>
@@ -2160,35 +2198,35 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="63"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="73"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
         <v>94</v>
       </c>
@@ -2216,7 +2254,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
         <v>95</v>
       </c>
@@ -2244,7 +2282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="53" t="s">
         <v>96</v>
       </c>
@@ -2272,7 +2310,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="53" t="s">
         <v>97</v>
       </c>
@@ -2300,7 +2338,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
         <v>98</v>
       </c>
@@ -2328,7 +2366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="53" t="s">
         <v>99</v>
       </c>
@@ -2356,7 +2394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="53" t="s">
         <v>100</v>
       </c>
@@ -2384,7 +2422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="53" t="s">
         <v>101</v>
       </c>
@@ -2412,7 +2450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="53" t="s">
         <v>102</v>
       </c>
@@ -2440,7 +2478,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="53" t="s">
         <v>103</v>
       </c>
@@ -2468,7 +2506,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
         <v>104</v>
       </c>
@@ -2496,35 +2534,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="73" t="s">
+      <c r="B37" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="75"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="62"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="76"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="78"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="63"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="65"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="53" t="s">
         <v>105</v>
       </c>
@@ -2552,7 +2590,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="53" t="s">
         <v>106</v>
       </c>
@@ -2580,7 +2618,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="53" t="s">
         <v>107</v>
       </c>
@@ -2608,7 +2646,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="53" t="s">
         <v>108</v>
       </c>
@@ -2636,7 +2674,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="53" t="s">
         <v>109</v>
       </c>
@@ -2664,7 +2702,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="53" t="s">
         <v>110</v>
       </c>
@@ -2692,7 +2730,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>64</v>
       </c>
@@ -2711,7 +2749,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="29"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -2722,7 +2760,7 @@
       <c r="H46" s="29"/>
       <c r="I46" s="29"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="53" t="s">
         <v>111</v>
       </c>
@@ -2750,7 +2788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="53" t="s">
         <v>112</v>
       </c>
@@ -2778,7 +2816,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="53" t="s">
         <v>113</v>
       </c>
@@ -2806,7 +2844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="53" t="s">
         <v>114</v>
       </c>
@@ -2834,7 +2872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="53" t="s">
         <v>115</v>
       </c>
@@ -2862,7 +2900,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="53" t="s">
         <v>116</v>
       </c>
@@ -2890,7 +2928,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
         <v>117</v>
       </c>
@@ -2918,7 +2956,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="53" t="s">
         <v>118</v>
       </c>
@@ -2946,35 +2984,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="69"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="68"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="70"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-      <c r="I56" s="72"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B56" s="69"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="71"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="53" t="s">
         <v>121</v>
       </c>
@@ -3002,7 +3040,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="53" t="s">
         <v>122</v>
       </c>
@@ -3030,7 +3068,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="53" t="s">
         <v>123</v>
       </c>
@@ -3058,7 +3096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="53" t="s">
         <v>124</v>
       </c>
@@ -3086,7 +3124,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="53" t="s">
         <v>125</v>
       </c>
@@ -3114,7 +3152,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="53" t="s">
         <v>126</v>
       </c>
@@ -3142,7 +3180,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="53" t="s">
         <v>127</v>
       </c>
@@ -3170,7 +3208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="53" t="s">
         <v>128</v>
       </c>
@@ -3198,7 +3236,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="29" t="s">
         <v>65</v>
       </c>
@@ -3217,7 +3255,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="29"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29"/>
@@ -3228,7 +3266,7 @@
       <c r="H66" s="29"/>
       <c r="I66" s="29"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="53" t="s">
         <v>148</v>
       </c>
@@ -3242,21 +3280,21 @@
         <v>11.5</v>
       </c>
       <c r="E67" s="9">
-        <f t="shared" ref="E67:E70" si="14">C67*D67</f>
+        <f t="shared" ref="E67" si="14">C67*D67</f>
         <v>74.75</v>
       </c>
       <c r="F67" s="9">
-        <f t="shared" ref="F67:F70" si="15">ROUNDUP(E67/10,0)</f>
+        <f t="shared" ref="F67" si="15">ROUNDUP(E67/10,0)</f>
         <v>8</v>
       </c>
       <c r="G67" s="47"/>
       <c r="H67" s="59"/>
       <c r="I67" s="43">
-        <f t="shared" ref="I67:I70" si="16">2*F67*(G67+H67+3)</f>
+        <f t="shared" ref="I67" si="16">2*F67*(G67+H67+3)</f>
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="53" t="s">
         <v>149</v>
       </c>
@@ -3284,35 +3322,35 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
-      <c r="I69" s="69"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="68"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="70"/>
-      <c r="C70" s="71"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
-      <c r="F70" s="71"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="71"/>
-      <c r="I70" s="72"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B70" s="69"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="71"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="53" t="s">
         <v>129</v>
       </c>
@@ -3340,7 +3378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="53" t="s">
         <v>130</v>
       </c>
@@ -3368,7 +3406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="53" t="s">
         <v>131</v>
       </c>
@@ -3396,7 +3434,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
         <v>132</v>
       </c>
@@ -3410,7 +3448,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="9">
-        <f>C74*D74</f>
+        <f t="shared" ref="E74:E80" si="20">C74*D74</f>
         <v>58.5</v>
       </c>
       <c r="F74" s="9">
@@ -3424,7 +3462,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="53" t="s">
         <v>133</v>
       </c>
@@ -3438,7 +3476,7 @@
         <v>9</v>
       </c>
       <c r="E75" s="9">
-        <f>C75*D75</f>
+        <f t="shared" si="20"/>
         <v>58.5</v>
       </c>
       <c r="F75" s="9">
@@ -3452,7 +3490,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="53" t="s">
         <v>134</v>
       </c>
@@ -3466,7 +3504,7 @@
         <v>4</v>
       </c>
       <c r="E76" s="9">
-        <f>C76*D76</f>
+        <f t="shared" si="20"/>
         <v>16</v>
       </c>
       <c r="F76" s="9">
@@ -3480,7 +3518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="53" t="s">
         <v>135</v>
       </c>
@@ -3494,7 +3532,7 @@
         <v>9.5</v>
       </c>
       <c r="E77" s="9">
-        <f>C77*D77</f>
+        <f t="shared" si="20"/>
         <v>42.75</v>
       </c>
       <c r="F77" s="9">
@@ -3508,7 +3546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="53" t="s">
         <v>136</v>
       </c>
@@ -3522,7 +3560,7 @@
         <v>9.5</v>
       </c>
       <c r="E78" s="9">
-        <f>C78*D78</f>
+        <f t="shared" si="20"/>
         <v>42.75</v>
       </c>
       <c r="F78" s="9">
@@ -3536,7 +3574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="53" t="s">
         <v>137</v>
       </c>
@@ -3550,7 +3588,7 @@
         <v>9.5</v>
       </c>
       <c r="E79" s="9">
-        <f>C79*D79</f>
+        <f t="shared" si="20"/>
         <v>42.75</v>
       </c>
       <c r="F79" s="9">
@@ -3564,7 +3602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="53" t="s">
         <v>138</v>
       </c>
@@ -3578,7 +3616,7 @@
         <v>9.5</v>
       </c>
       <c r="E80" s="9">
-        <f>C80*D80</f>
+        <f t="shared" si="20"/>
         <v>42.75</v>
       </c>
       <c r="F80" s="9">
@@ -3592,35 +3630,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="73" t="s">
+      <c r="B81" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="74"/>
-      <c r="I81" s="75"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C81" s="61"/>
+      <c r="D81" s="61"/>
+      <c r="E81" s="61"/>
+      <c r="F81" s="61"/>
+      <c r="G81" s="61"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="62"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="76"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="77"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="77"/>
-      <c r="G82" s="77"/>
-      <c r="H82" s="77"/>
-      <c r="I82" s="78"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B82" s="63"/>
+      <c r="C82" s="64"/>
+      <c r="D82" s="64"/>
+      <c r="E82" s="64"/>
+      <c r="F82" s="64"/>
+      <c r="G82" s="64"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="65"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="53" t="s">
         <v>141</v>
       </c>
@@ -3634,7 +3672,7 @@
         <v>12.5</v>
       </c>
       <c r="E83" s="9">
-        <f t="shared" ref="E83:E88" si="20">C83*D83</f>
+        <f t="shared" ref="E83:E88" si="21">C83*D83</f>
         <v>81.25</v>
       </c>
       <c r="F83" s="9">
@@ -3648,7 +3686,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="53" t="s">
         <v>142</v>
       </c>
@@ -3662,7 +3700,7 @@
         <v>12.5</v>
       </c>
       <c r="E84" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>81.25</v>
       </c>
       <c r="F84" s="9">
@@ -3676,7 +3714,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="53" t="s">
         <v>143</v>
       </c>
@@ -3690,7 +3728,7 @@
         <v>12.5</v>
       </c>
       <c r="E85" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>68.75</v>
       </c>
       <c r="F85" s="9">
@@ -3704,7 +3742,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="53" t="s">
         <v>144</v>
       </c>
@@ -3718,7 +3756,7 @@
         <v>12.5</v>
       </c>
       <c r="E86" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>68.75</v>
       </c>
       <c r="F86" s="9">
@@ -3732,7 +3770,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="53" t="s">
         <v>145</v>
       </c>
@@ -3746,7 +3784,7 @@
         <v>12.5</v>
       </c>
       <c r="E87" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>68.75</v>
       </c>
       <c r="F87" s="9">
@@ -3760,7 +3798,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="53" t="s">
         <v>146</v>
       </c>
@@ -3774,7 +3812,7 @@
         <v>12.5</v>
       </c>
       <c r="E88" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>68.75</v>
       </c>
       <c r="F88" s="9">
@@ -3788,7 +3826,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="29" t="s">
         <v>66</v>
       </c>
@@ -3807,7 +3845,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="37" t="s">
         <v>67</v>
       </c>
@@ -3817,25 +3855,25 @@
       <c r="E91" s="37"/>
       <c r="F91" s="37">
         <f>F89+F65+F45+F20</f>
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="37"/>
       <c r="I91" s="37">
         <f>I89+I65+I45+I20</f>
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3446.52</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H93" s="29" t="s">
         <v>68</v>
       </c>
       <c r="I93" s="29">
         <f>ROUNDUP(ROUNDUP($I$91/305,0)*1.1,0)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H94" s="29" t="s">
         <v>69</v>
       </c>
@@ -3844,19 +3882,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="37">
         <f>I91/(F91*2)</f>
-        <v>3</v>
+        <v>3.1446350364963505</v>
       </c>
       <c r="E96" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="44" t="s">
         <v>71</v>
       </c>
@@ -3868,17 +3906,17 @@
       <c r="G98" s="44"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="45" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="51" t="s">
         <v>75</v>
       </c>
@@ -3886,7 +3924,8 @@
       <c r="C101" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="B81:I82"/>
     <mergeCell ref="B69:I70"/>
     <mergeCell ref="B55:I56"/>
@@ -3905,27 +3944,28 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A14:A19 A26:A36 A59:A64 A39:A44 A71:A88 A67 A68:A70 A22:A23 A24:A25 A37:A38" twoDigitTextYear="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AA7270-A5B3-4391-AFAC-44F660C9B196}">
   <dimension ref="A1:H64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -3951,8 +3991,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
@@ -3971,12 +4011,12 @@
       <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="77" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="61"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
       <c r="B3" s="10">
         <v>1</v>
       </c>
@@ -3991,10 +4031,10 @@
       <c r="G3" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="61"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
+      <c r="H3" s="78"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="78"/>
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -4011,10 +4051,10 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="61"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
+      <c r="H4" s="78"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="78"/>
       <c r="B5" s="10">
         <v>1</v>
       </c>
@@ -4025,10 +4065,10 @@
       <c r="G5" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="61"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
+      <c r="H5" s="78"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="78"/>
       <c r="B6" s="10">
         <v>1</v>
       </c>
@@ -4045,10 +4085,10 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="61"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="61"/>
+      <c r="H6" s="78"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="78"/>
       <c r="B7" s="10">
         <v>1</v>
       </c>
@@ -4063,10 +4103,10 @@
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="61"/>
-    </row>
-    <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="61"/>
+      <c r="H7" s="78"/>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="78"/>
       <c r="B8" s="24">
         <v>1</v>
       </c>
@@ -4083,10 +4123,10 @@
       <c r="G8" s="5">
         <v>50</v>
       </c>
-      <c r="H8" s="61"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="61"/>
+      <c r="H8" s="78"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="78"/>
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -4096,10 +4136,10 @@
       <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="61"/>
-    </row>
-    <row r="10" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="61"/>
+      <c r="H9" s="78"/>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="78"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -4112,10 +4152,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="61"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="61"/>
+      <c r="H10" s="78"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="78"/>
       <c r="B11" s="10">
         <v>1</v>
       </c>
@@ -4126,10 +4166,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="61"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="61"/>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="78"/>
       <c r="B12" s="10">
         <v>1</v>
       </c>
@@ -4140,10 +4180,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="61"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
+      <c r="H12" s="78"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="78"/>
       <c r="B13" s="10">
         <v>1</v>
       </c>
@@ -4154,10 +4194,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="61"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
+      <c r="H13" s="78"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="78"/>
       <c r="B14" s="10">
         <v>1</v>
       </c>
@@ -4166,10 +4206,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="61"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
+      <c r="H14" s="78"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="78"/>
       <c r="B15" s="10">
         <v>1</v>
       </c>
@@ -4180,10 +4220,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="61"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="61"/>
+      <c r="H15" s="78"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="78"/>
       <c r="B16" s="10">
         <v>1</v>
       </c>
@@ -4194,10 +4234,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="61"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="61"/>
+      <c r="H16" s="78"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="78"/>
       <c r="B17" s="24">
         <v>7</v>
       </c>
@@ -4206,70 +4246,70 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="61"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
+      <c r="H17" s="78"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="78"/>
       <c r="B18" s="24"/>
       <c r="C18" s="35"/>
       <c r="D18" s="10"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="61"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="61"/>
+      <c r="H18" s="78"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="78"/>
       <c r="B19" s="24"/>
       <c r="C19" s="35"/>
       <c r="D19" s="10"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="61"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="61"/>
+      <c r="H19" s="78"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="78"/>
       <c r="B20" s="24"/>
       <c r="C20" s="35"/>
       <c r="D20" s="10"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="61"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="61"/>
+      <c r="H20" s="78"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="78"/>
       <c r="B21" s="24"/>
       <c r="C21" s="35"/>
       <c r="D21" s="10"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="61"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
+      <c r="H21" s="78"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="78"/>
       <c r="B22" s="24"/>
       <c r="C22" s="35"/>
       <c r="D22" s="10"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="61"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="61"/>
+      <c r="H22" s="78"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="78"/>
       <c r="B23" s="24"/>
       <c r="C23" s="36"/>
       <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="61"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="61"/>
+      <c r="H23" s="78"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="78"/>
       <c r="B24" s="10">
         <v>1</v>
       </c>
@@ -4280,10 +4320,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="61"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
+      <c r="H24" s="78"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="78"/>
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -4294,10 +4334,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="61"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
+      <c r="H25" s="78"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="78"/>
       <c r="B26" s="10">
         <v>1</v>
       </c>
@@ -4308,10 +4348,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="61"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
+      <c r="H26" s="78"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="78"/>
       <c r="B27" s="10">
         <v>1</v>
       </c>
@@ -4320,10 +4360,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="61"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
+      <c r="H27" s="78"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="78"/>
       <c r="B28" s="10">
         <v>1</v>
       </c>
@@ -4332,10 +4372,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="61"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
+      <c r="H28" s="78"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="78"/>
       <c r="B29" s="10">
         <v>1</v>
       </c>
@@ -4351,10 +4391,10 @@
       <c r="G29" s="5">
         <v>50</v>
       </c>
-      <c r="H29" s="61"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
+      <c r="H29" s="78"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="78"/>
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -4365,40 +4405,40 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="61"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
+      <c r="H30" s="78"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="78"/>
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="61"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
+      <c r="H31" s="78"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="78"/>
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="61"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
+      <c r="H32" s="78"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="78"/>
       <c r="B33" s="10"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="61"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
+      <c r="H33" s="78"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="78"/>
       <c r="B34" s="10">
         <v>1</v>
       </c>
@@ -4411,10 +4451,10 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="61"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+      <c r="H34" s="78"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="78"/>
       <c r="B35" s="10">
         <v>1</v>
       </c>
@@ -4425,10 +4465,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="61"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
+      <c r="H35" s="78"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="78"/>
       <c r="B36" s="10">
         <v>1</v>
       </c>
@@ -4445,10 +4485,10 @@
       <c r="G36" s="5">
         <v>200</v>
       </c>
-      <c r="H36" s="61"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
+      <c r="H36" s="78"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="78"/>
       <c r="B37" s="10">
         <v>2</v>
       </c>
@@ -4459,10 +4499,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="61"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="61"/>
+      <c r="H37" s="78"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="78"/>
       <c r="B38" s="10">
         <v>4</v>
       </c>
@@ -4477,10 +4517,10 @@
       <c r="G38" s="5">
         <v>250</v>
       </c>
-      <c r="H38" s="61"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="61"/>
+      <c r="H38" s="78"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="78"/>
       <c r="B39" s="10">
         <v>4</v>
       </c>
@@ -4495,39 +4535,39 @@
       <c r="G39" s="5">
         <v>250</v>
       </c>
-      <c r="H39" s="61"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
+      <c r="H39" s="78"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="78"/>
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="61"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
+      <c r="H40" s="78"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="78"/>
       <c r="B41" s="10"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="61"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="61"/>
+      <c r="H41" s="78"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="78"/>
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="61"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H42" s="78"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>3</v>
       </c>
@@ -4548,7 +4588,7 @@
       </c>
       <c r="H43" s="17"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E44" s="19" t="s">
         <v>17</v>
       </c>
@@ -4557,7 +4597,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F45" t="s">
         <v>34</v>
       </c>
@@ -4565,7 +4605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="2" t="s">
         <v>31</v>
       </c>
@@ -4578,7 +4618,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C47" s="6" t="s">
         <v>32</v>
       </c>
@@ -4591,7 +4631,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E49" s="20" t="s">
         <v>3</v>
       </c>
@@ -4604,7 +4644,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="31" t="s">
         <v>45</v>
       </c>
@@ -4615,7 +4655,7 @@
       <c r="F50" s="29"/>
       <c r="G50" s="29"/>
     </row>
-    <row r="51" spans="1:7" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="30" t="s">
         <v>44</v>
       </c>
@@ -4629,12 +4669,12 @@
       <c r="F51" s="29"/>
       <c r="G51" s="29"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E52" s="29"/>
       <c r="F52" s="29"/>
       <c r="G52" s="29"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -4642,17 +4682,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B56" s="18" t="s">
         <v>24</v>
       </c>
@@ -4662,17 +4702,17 @@
       <c r="F56" s="18"/>
       <c r="G56" s="18"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B59" s="28" t="s">
         <v>43</v>
       </c>
@@ -4682,7 +4722,7 @@
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B60" s="28" t="s">
         <v>47</v>
       </c>
@@ -4692,7 +4732,7 @@
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
         <v>27</v>
       </c>
@@ -4702,17 +4742,17 @@
       <c r="F61" s="21"/>
       <c r="G61" s="21"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B64" s="22" t="s">
         <v>49</v>
       </c>
@@ -4734,7 +4774,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B9A1CC-C4FB-41AD-85DB-3839BA2B7BB9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4743,13 +4783,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A71F13F-E947-4C1E-BDE3-9A5BE07FD910}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E4DE2CC379442A4D8483D9D7B1BA3E35" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3cbd871ac436bbcd94953c6f74650012">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b380a0-b262-4a13-9203-497a21b8eee5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f82e0ce2898406bfa558450728792a3e" ns2:_="">
     <xsd:import namespace="a1b380a0-b262-4a13-9203-497a21b8eee5"/>
@@ -4887,22 +4942,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4918,21 +4975,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anul 4\Sem 2\CPNP\Network-Design-Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9B7D4C-BF45-42C8-98AA-873E2E7D9A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1231DD6F-C620-4423-B62A-6F50A9583523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="5" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="159">
   <si>
     <t>Spatiu ocupat in U</t>
   </si>
@@ -570,13 +570,7 @@
     <t>1.35</t>
   </si>
   <si>
-    <t>TYPE</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>Room Type</t>
   </si>
 </sst>
 </file>
@@ -645,7 +639,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,8 +718,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9999FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1110,15 +1116,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1131,7 +1128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1176,28 +1173,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,19 +1231,13 @@
     <xf numFmtId="49" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1255,16 +1246,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1289,6 +1273,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9999FF"/>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1598,93 +1588,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29A6EC-8F37-4E8F-9E44-40C579389B24}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="79" t="s">
+      <c r="J1" s="72" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="46">
         <v>6.5</v>
       </c>
-      <c r="D2" s="55">
+      <c r="D2" s="46">
         <v>8.5</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="9">
         <f>C2*D2</f>
         <v>55.25</v>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="9">
         <f>ROUNDUP(E2/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="49">
-        <v>13.21</v>
-      </c>
-      <c r="I2" s="42">
+      <c r="G2" s="41"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="38">
         <f>2*F2*(G2+H2+3)</f>
-        <v>194.52</v>
-      </c>
-      <c r="J2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="73"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="46">
         <v>8.5</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="46">
         <v>6.5</v>
       </c>
       <c r="E3" s="9">
@@ -1695,42 +1682,41 @@
         <f t="shared" ref="F3:F19" si="1">ROUNDUP(E3/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="43">
+      <c r="G3" s="41"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="38">
         <f t="shared" ref="I3:I19" si="2">2*F3*(G3+H3+3)</f>
         <v>36</v>
       </c>
-      <c r="J3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="J3" s="73"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="82"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="46">
         <v>5.5</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="46">
         <v>8.5</v>
       </c>
       <c r="E5" s="9">
@@ -1741,24 +1727,25 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="43">
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="38">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="J5" s="73"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="46">
         <v>5.5</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="46">
         <v>8.5</v>
       </c>
       <c r="E6" s="9">
@@ -1769,24 +1756,25 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="43">
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="38">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="J6" s="73"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="46">
         <v>5.5</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="46">
         <v>8.5</v>
       </c>
       <c r="E7" s="9">
@@ -1797,24 +1785,25 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G7" s="55"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="43">
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="38">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="J7" s="73"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="46">
         <v>5.5</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="46">
         <v>8.5</v>
       </c>
       <c r="E8" s="9">
@@ -1825,24 +1814,25 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G8" s="54"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="43">
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="38">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+      <c r="J8" s="73"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="46">
         <v>5.5</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="46">
         <v>8.5</v>
       </c>
       <c r="E9" s="9">
@@ -1853,52 +1843,55 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G9" s="55"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="43">
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="38">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="58" t="s">
+      <c r="J9" s="73"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="68"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="58" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="71"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="46">
         <v>8.5</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="46">
         <v>11.5</v>
       </c>
       <c r="E12" s="9">
@@ -1909,24 +1902,25 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="43">
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="38">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="J12" s="73"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="46">
         <v>20</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="46">
         <v>16.5</v>
       </c>
       <c r="E13" s="9">
@@ -1937,24 +1931,25 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="G13" s="55"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="43">
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="38">
         <f t="shared" si="2"/>
         <v>198</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="J13" s="73"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="46">
         <v>6.5</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="46">
         <v>11.5</v>
       </c>
       <c r="E14" s="9">
@@ -1965,24 +1960,25 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G14" s="54"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="43">
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="38">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="J14" s="73"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="46">
         <v>6.5</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="46">
         <v>11.5</v>
       </c>
       <c r="E15" s="9">
@@ -1993,24 +1989,25 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G15" s="55"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="43">
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="38">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="53" t="s">
+      <c r="J15" s="73"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="46">
         <v>6.5</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="46">
         <v>11.5</v>
       </c>
       <c r="E16" s="9">
@@ -2021,24 +2018,25 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G16" s="55"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="43">
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="38">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="J16" s="73"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="46">
         <v>6.5</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="46">
         <v>11.5</v>
       </c>
       <c r="E17" s="9">
@@ -2049,24 +2047,25 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="43">
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="38">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="J17" s="73"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="46">
         <v>6.5</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="46">
         <v>11.5</v>
       </c>
       <c r="E18" s="9">
@@ -2077,24 +2076,25 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G18" s="55"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="43">
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="38">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="J18" s="73"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="46">
         <v>10</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="46">
         <v>20</v>
       </c>
       <c r="E19" s="9">
@@ -2105,14 +2105,15 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="G19" s="55"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="43">
+      <c r="G19" s="46"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="38">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="73"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
         <v>63</v>
       </c>
@@ -2128,10 +2129,10 @@
       <c r="H20" s="29"/>
       <c r="I20" s="29">
         <f>SUM(I2:I19)</f>
-        <v>998.52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="29"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -2142,17 +2143,17 @@
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="46">
         <v>6.5</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="46">
         <v>11.5</v>
       </c>
       <c r="E22" s="9">
@@ -2163,24 +2164,25 @@
         <f t="shared" ref="F22:F23" si="4">ROUNDUP(E22/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G22" s="47"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="43">
+      <c r="G22" s="41"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="38">
         <f t="shared" ref="I22:I23" si="5">2*F22*(G22+H22+3)</f>
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="J22" s="73"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="46">
         <v>6.5</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="46">
         <v>11.5</v>
       </c>
       <c r="E23" s="9">
@@ -2191,52 +2193,55 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G23" s="47"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="43">
+      <c r="G23" s="41"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="38">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="58" t="s">
+      <c r="J23" s="73"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="73"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="58" t="s">
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="62"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="76"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="B25" s="63"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="65"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="46">
         <v>10</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="46">
         <v>20</v>
       </c>
       <c r="E26" s="9">
@@ -2247,24 +2252,25 @@
         <f>ROUNDUP(E26/10,0)</f>
         <v>20</v>
       </c>
-      <c r="G26" s="47"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="43">
+      <c r="G26" s="41"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="38">
         <f>2*F26*(G26+H26+3)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="J26" s="73"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="41">
         <v>9</v>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="41">
         <v>10</v>
       </c>
       <c r="E27" s="9">
@@ -2275,24 +2281,25 @@
         <f>ROUNDUP(E27/10,0)</f>
         <v>9</v>
       </c>
-      <c r="G27" s="47"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="43">
+      <c r="G27" s="41"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="38">
         <f>2*F27*(G27+H27+3)</f>
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="J27" s="73"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="41">
         <v>9</v>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="41">
         <v>10</v>
       </c>
       <c r="E28" s="9">
@@ -2303,24 +2310,25 @@
         <f t="shared" ref="F28:F44" si="7">ROUNDUP(E28/10,0)</f>
         <v>9</v>
       </c>
-      <c r="G28" s="47"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="43">
+      <c r="G28" s="41"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="38">
         <f t="shared" ref="I28:I44" si="8">2*F28*(G28+H28+3)</f>
         <v>54</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="J28" s="73"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="41">
         <v>6.5</v>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="41">
         <v>9</v>
       </c>
       <c r="E29" s="9">
@@ -2331,24 +2339,25 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="G29" s="47"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="43">
+      <c r="G29" s="41"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="38">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+      <c r="J29" s="73"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="41">
         <v>6.5</v>
       </c>
-      <c r="D30" s="47">
+      <c r="D30" s="41">
         <v>9</v>
       </c>
       <c r="E30" s="9">
@@ -2359,52 +2368,41 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="G30" s="47"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="43">
+      <c r="G30" s="41"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="38">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="J30" s="73"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="47">
-        <v>4</v>
-      </c>
-      <c r="D31" s="47">
-        <v>4</v>
-      </c>
-      <c r="E31" s="9">
-        <f t="shared" si="9"/>
-        <v>16</v>
-      </c>
-      <c r="F31" s="9">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G31" s="47"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="43">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="53" t="s">
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="53"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="41">
         <v>4.5</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D32" s="41">
         <v>9.5</v>
       </c>
       <c r="E32" s="9">
@@ -2415,24 +2413,25 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="43">
+      <c r="G32" s="41"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="38">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
+      <c r="J32" s="73"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="53" t="s">
+      <c r="B33" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="41">
         <v>4.5</v>
       </c>
-      <c r="D33" s="47">
+      <c r="D33" s="41">
         <v>9.5</v>
       </c>
       <c r="E33" s="9">
@@ -2443,24 +2442,25 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="G33" s="47"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="43">
+      <c r="G33" s="41"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="38">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="J33" s="73"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="53" t="s">
+      <c r="B34" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="41">
         <v>4.5</v>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="41">
         <v>9.5</v>
       </c>
       <c r="E34" s="9">
@@ -2471,24 +2471,25 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="G34" s="47"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="43">
+      <c r="G34" s="41"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="38">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
+      <c r="J34" s="73"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="41">
         <v>4.5</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="41">
         <v>9.5</v>
       </c>
       <c r="E35" s="9">
@@ -2499,24 +2500,25 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="G35" s="47"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="43">
+      <c r="G35" s="41"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="38">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="J35" s="73"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="41">
         <v>4.5</v>
       </c>
-      <c r="D36" s="47">
+      <c r="D36" s="41">
         <v>9.5</v>
       </c>
       <c r="E36" s="9">
@@ -2527,52 +2529,55 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="G36" s="47"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="43">
+      <c r="G36" s="41"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="38">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="58" t="s">
+      <c r="J36" s="73"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="62"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="s">
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="56"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="63"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="65"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="B38" s="57"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="59"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="53" t="s">
+      <c r="B39" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="41">
         <v>6.5</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="41">
         <v>12.5</v>
       </c>
       <c r="E39" s="9">
@@ -2583,24 +2588,25 @@
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="G39" s="47"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="43">
+      <c r="G39" s="41"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="38">
         <f t="shared" si="8"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
+      <c r="J39" s="73"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="41">
         <v>5.5</v>
       </c>
-      <c r="D40" s="47">
+      <c r="D40" s="41">
         <v>12.5</v>
       </c>
       <c r="E40" s="9">
@@ -2611,24 +2617,25 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G40" s="47"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="43">
+      <c r="G40" s="41"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="38">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
+      <c r="J40" s="73"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="41">
         <v>5.5</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D41" s="41">
         <v>12.5</v>
       </c>
       <c r="E41" s="9">
@@ -2639,24 +2646,25 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G41" s="47"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="43">
+      <c r="G41" s="41"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="38">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="53" t="s">
+      <c r="J41" s="73"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="53" t="s">
+      <c r="B42" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="41">
         <v>5.5</v>
       </c>
-      <c r="D42" s="47">
+      <c r="D42" s="41">
         <v>12.5</v>
       </c>
       <c r="E42" s="9">
@@ -2667,24 +2675,25 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G42" s="47"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="43">
+      <c r="G42" s="41"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="38">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="53" t="s">
+      <c r="J42" s="73"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="53" t="s">
+      <c r="B43" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="41">
         <v>5.5</v>
       </c>
-      <c r="D43" s="47">
+      <c r="D43" s="41">
         <v>12.5</v>
       </c>
       <c r="E43" s="9">
@@ -2695,24 +2704,25 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G43" s="47"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="43">
+      <c r="G43" s="41"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="38">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
+      <c r="J43" s="73"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="41">
         <v>5.5</v>
       </c>
-      <c r="D44" s="47">
+      <c r="D44" s="41">
         <v>12.5</v>
       </c>
       <c r="E44" s="9">
@@ -2723,14 +2733,15 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="G44" s="47"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="43">
+      <c r="G44" s="41"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="38">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" s="73"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
         <v>64</v>
       </c>
@@ -2740,16 +2751,16 @@
       <c r="E45" s="29"/>
       <c r="F45" s="29">
         <f>SUM(F22:F44)</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G45" s="29"/>
       <c r="H45" s="29"/>
       <c r="I45" s="29">
         <f>SUM(I22:I44)</f>
-        <v>822</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="29"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -2760,17 +2771,17 @@
       <c r="H46" s="29"/>
       <c r="I46" s="29"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="55">
+      <c r="C47" s="46">
         <v>6.5</v>
       </c>
-      <c r="D47" s="55">
+      <c r="D47" s="46">
         <v>8.5</v>
       </c>
       <c r="E47" s="9">
@@ -2781,80 +2792,74 @@
         <f>ROUNDUP(E47/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G47" s="47"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="43">
+      <c r="G47" s="41">
+        <v>9.4</v>
+      </c>
+      <c r="H47" s="49"/>
+      <c r="I47" s="38">
         <f>2*F47*(G47+H47+3)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="J47" s="73"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="55">
+      <c r="C48" s="46">
         <v>8.5</v>
       </c>
-      <c r="D48" s="55">
+      <c r="D48" s="46">
         <v>6.5</v>
       </c>
       <c r="E48" s="9">
-        <f t="shared" ref="E48:E49" si="10">C48*D48</f>
+        <f t="shared" ref="E48" si="10">C48*D48</f>
         <v>55.25</v>
       </c>
       <c r="F48" s="9">
         <f t="shared" ref="F48:F64" si="11">ROUNDUP(E48/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G48" s="47"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="43">
+      <c r="G48" s="41">
+        <v>16.11</v>
+      </c>
+      <c r="H48" s="49"/>
+      <c r="I48" s="38">
         <f t="shared" ref="I48:I64" si="12">2*F48*(G48+H48+3)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="53" t="s">
+        <v>229.32</v>
+      </c>
+      <c r="J48" s="73"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="55">
-        <v>4</v>
-      </c>
-      <c r="D49" s="55">
-        <v>4</v>
-      </c>
-      <c r="E49" s="9">
-        <f t="shared" si="10"/>
-        <v>16</v>
-      </c>
-      <c r="F49" s="9">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="G49" s="47"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="43">
-        <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="53" t="s">
+      <c r="C49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="68"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="47" t="s">
+      <c r="B50" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="55">
+      <c r="C50" s="46">
         <v>5.5</v>
       </c>
-      <c r="D50" s="55">
+      <c r="D50" s="46">
         <v>8.5</v>
       </c>
       <c r="E50" s="9">
@@ -2865,24 +2870,27 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="G50" s="47"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="43">
+      <c r="G50" s="41">
+        <v>21.82</v>
+      </c>
+      <c r="H50" s="49"/>
+      <c r="I50" s="38">
         <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
+        <v>248.2</v>
+      </c>
+      <c r="J50" s="73"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="55">
+      <c r="C51" s="46">
         <v>5.5</v>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="46">
         <v>8.5</v>
       </c>
       <c r="E51" s="9">
@@ -2893,24 +2901,27 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="G51" s="47"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="43">
+      <c r="G51" s="41">
+        <v>27.82</v>
+      </c>
+      <c r="H51" s="49"/>
+      <c r="I51" s="38">
         <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="53" t="s">
+        <v>308.2</v>
+      </c>
+      <c r="J51" s="73"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="47" t="s">
+      <c r="B52" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="46">
         <v>5.5</v>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="46">
         <v>8.5</v>
       </c>
       <c r="E52" s="9">
@@ -2921,24 +2932,27 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="G52" s="47"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="43">
+      <c r="G52" s="41">
+        <v>33.53</v>
+      </c>
+      <c r="H52" s="49"/>
+      <c r="I52" s="38">
         <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="53" t="s">
+        <v>365.3</v>
+      </c>
+      <c r="J52" s="73"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="47" t="s">
+      <c r="B53" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="46">
         <v>5.5</v>
       </c>
-      <c r="D53" s="55">
+      <c r="D53" s="46">
         <v>8.5</v>
       </c>
       <c r="E53" s="9">
@@ -2949,24 +2963,27 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="G53" s="47"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="43">
+      <c r="G53" s="41">
+        <v>39.53</v>
+      </c>
+      <c r="H53" s="49"/>
+      <c r="I53" s="38">
         <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="53" t="s">
+        <v>425.3</v>
+      </c>
+      <c r="J53" s="73"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="47" t="s">
+      <c r="B54" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C54" s="55">
+      <c r="C54" s="46">
         <v>5.5</v>
       </c>
-      <c r="D54" s="55">
+      <c r="D54" s="46">
         <v>8.5</v>
       </c>
       <c r="E54" s="9">
@@ -2977,52 +2994,57 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="G54" s="47"/>
-      <c r="H54" s="59"/>
-      <c r="I54" s="43">
+      <c r="G54" s="41">
+        <v>45.24</v>
+      </c>
+      <c r="H54" s="49"/>
+      <c r="I54" s="38">
         <f t="shared" si="12"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="58" t="s">
+        <v>482.40000000000003</v>
+      </c>
+      <c r="J54" s="73"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="66" t="s">
+      <c r="B55" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="68"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="58" t="s">
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="62"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="71"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
+      <c r="B56" s="63"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="64"/>
+      <c r="J56" s="65"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="47" t="s">
+      <c r="B57" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="55">
+      <c r="C57" s="46">
         <v>8.5</v>
       </c>
-      <c r="D57" s="55">
+      <c r="D57" s="46">
         <v>11.5</v>
       </c>
       <c r="E57" s="9">
@@ -3033,24 +3055,27 @@
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="G57" s="47"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="43">
+      <c r="G57" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="49"/>
+      <c r="I57" s="38">
         <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="J57" s="73"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="47" t="s">
+      <c r="B58" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="55">
+      <c r="C58" s="46">
         <v>20</v>
       </c>
-      <c r="D58" s="55">
+      <c r="D58" s="46">
         <v>16.5</v>
       </c>
       <c r="E58" s="9">
@@ -3061,24 +3086,25 @@
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="G58" s="47"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="43">
+      <c r="G58" s="41"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="38">
         <f t="shared" si="12"/>
         <v>198</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
+      <c r="J58" s="73"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="47" t="s">
+      <c r="B59" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C59" s="55">
+      <c r="C59" s="46">
         <v>6.5</v>
       </c>
-      <c r="D59" s="55">
+      <c r="D59" s="46">
         <v>11.5</v>
       </c>
       <c r="E59" s="9">
@@ -3089,24 +3115,27 @@
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="G59" s="47"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="43">
+      <c r="G59" s="41">
+        <v>84.64</v>
+      </c>
+      <c r="H59" s="49"/>
+      <c r="I59" s="38">
         <f t="shared" si="12"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="53" t="s">
+        <v>1402.24</v>
+      </c>
+      <c r="J59" s="73"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="55">
+      <c r="C60" s="46">
         <v>6.5</v>
       </c>
-      <c r="D60" s="55">
+      <c r="D60" s="46">
         <v>11.5</v>
       </c>
       <c r="E60" s="9">
@@ -3117,24 +3146,27 @@
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="G60" s="47"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="43">
+      <c r="G60" s="41">
+        <v>91.78</v>
+      </c>
+      <c r="H60" s="49"/>
+      <c r="I60" s="38">
         <f t="shared" si="12"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="53" t="s">
+        <v>1516.48</v>
+      </c>
+      <c r="J60" s="73"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="B61" s="47" t="s">
+      <c r="B61" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="55">
+      <c r="C61" s="46">
         <v>6.5</v>
       </c>
-      <c r="D61" s="55">
+      <c r="D61" s="46">
         <v>11.5</v>
       </c>
       <c r="E61" s="9">
@@ -3145,24 +3177,27 @@
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="G61" s="47"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="43">
+      <c r="G61" s="41">
+        <v>98.78</v>
+      </c>
+      <c r="H61" s="49"/>
+      <c r="I61" s="38">
         <f t="shared" si="12"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="53" t="s">
+        <v>1628.48</v>
+      </c>
+      <c r="J61" s="73"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="55">
+      <c r="C62" s="46">
         <v>6.5</v>
       </c>
-      <c r="D62" s="55">
+      <c r="D62" s="46">
         <v>11.5</v>
       </c>
       <c r="E62" s="9">
@@ -3173,24 +3208,27 @@
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="G62" s="47"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="43">
+      <c r="G62" s="41">
+        <v>105.92</v>
+      </c>
+      <c r="H62" s="49"/>
+      <c r="I62" s="38">
         <f t="shared" si="12"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="53" t="s">
+        <v>1742.72</v>
+      </c>
+      <c r="J62" s="73"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B63" s="47" t="s">
+      <c r="B63" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="55">
+      <c r="C63" s="46">
         <v>6.5</v>
       </c>
-      <c r="D63" s="55">
+      <c r="D63" s="46">
         <v>11.5</v>
       </c>
       <c r="E63" s="9">
@@ -3201,24 +3239,27 @@
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="G63" s="47"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="43">
+      <c r="G63" s="41">
+        <v>112.92</v>
+      </c>
+      <c r="H63" s="49"/>
+      <c r="I63" s="38">
         <f t="shared" si="12"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="53" t="s">
+        <v>1854.72</v>
+      </c>
+      <c r="J63" s="73"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="47" t="s">
+      <c r="B64" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C64" s="55">
+      <c r="C64" s="46">
         <v>10</v>
       </c>
-      <c r="D64" s="55">
+      <c r="D64" s="46">
         <v>20</v>
       </c>
       <c r="E64" s="9">
@@ -3229,14 +3270,17 @@
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="G64" s="47"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="43">
+      <c r="G64" s="41">
+        <v>17.5</v>
+      </c>
+      <c r="H64" s="49"/>
+      <c r="I64" s="38">
         <f t="shared" si="12"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+        <v>820</v>
+      </c>
+      <c r="J64" s="73"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
         <v>65</v>
       </c>
@@ -3246,16 +3290,16 @@
       <c r="E65" s="29"/>
       <c r="F65" s="29">
         <f>SUM(F47:F64)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G65" s="29"/>
       <c r="H65" s="29"/>
       <c r="I65" s="29">
         <f>SUM(I47:I64)</f>
-        <v>852</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11440.159999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="29"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29"/>
@@ -3266,17 +3310,17 @@
       <c r="H66" s="29"/>
       <c r="I66" s="29"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="53" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="53" t="s">
+      <c r="B67" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C67" s="55">
+      <c r="C67" s="46">
         <v>6.5</v>
       </c>
-      <c r="D67" s="55">
+      <c r="D67" s="46">
         <v>11.5</v>
       </c>
       <c r="E67" s="9">
@@ -3287,24 +3331,27 @@
         <f t="shared" ref="F67" si="15">ROUNDUP(E67/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G67" s="47"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="43">
+      <c r="G67" s="41">
+        <v>32</v>
+      </c>
+      <c r="H67" s="49"/>
+      <c r="I67" s="38">
         <f t="shared" ref="I67" si="16">2*F67*(G67+H67+3)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="53" t="s">
+        <v>560</v>
+      </c>
+      <c r="J67" s="73"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="53" t="s">
+      <c r="B68" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="55">
+      <c r="C68" s="46">
         <v>6.5</v>
       </c>
-      <c r="D68" s="55">
+      <c r="D68" s="46">
         <v>11.5</v>
       </c>
       <c r="E68" s="9">
@@ -3315,52 +3362,57 @@
         <f>ROUNDUP(E68/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G68" s="47"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="43">
+      <c r="G68" s="41">
+        <v>27</v>
+      </c>
+      <c r="H68" s="49"/>
+      <c r="I68" s="38">
         <f>2*F68*(G68+H68+3)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="58" t="s">
+        <v>480</v>
+      </c>
+      <c r="J68" s="73"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="66" t="s">
+      <c r="B69" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="68"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="58" t="s">
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="62"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="69"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="70"/>
-      <c r="E70" s="70"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="70"/>
-      <c r="H70" s="70"/>
-      <c r="I70" s="71"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="53" t="s">
+      <c r="B70" s="63"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="64"/>
+      <c r="J70" s="65"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="53" t="s">
+      <c r="B71" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="55">
+      <c r="C71" s="46">
         <v>10</v>
       </c>
-      <c r="D71" s="55">
+      <c r="D71" s="46">
         <v>20</v>
       </c>
       <c r="E71" s="9">
@@ -3371,24 +3423,27 @@
         <f>ROUNDUP(E71/10,0)</f>
         <v>20</v>
       </c>
-      <c r="G71" s="47"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="43">
+      <c r="G71" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="H71" s="49"/>
+      <c r="I71" s="38">
         <f>2*F71*(G71+H71+3)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="J71" s="73"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="B72" s="53" t="s">
+      <c r="B72" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="47">
+      <c r="C72" s="41">
         <v>5</v>
       </c>
-      <c r="D72" s="47">
+      <c r="D72" s="41">
         <v>14</v>
       </c>
       <c r="E72" s="9">
@@ -3399,24 +3454,27 @@
         <f t="shared" ref="F72:F88" si="18">ROUNDUP(E72/10,0)</f>
         <v>7</v>
       </c>
-      <c r="G72" s="47"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="43">
+      <c r="G72" s="41">
+        <v>56.07</v>
+      </c>
+      <c r="H72" s="49"/>
+      <c r="I72" s="38">
         <f t="shared" ref="I72:I88" si="19">2*F72*(G72+H72+3)</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="53" t="s">
+        <v>826.98</v>
+      </c>
+      <c r="J72" s="73"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="53" t="s">
+      <c r="B73" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C73" s="47">
+      <c r="C73" s="41">
         <v>9</v>
       </c>
-      <c r="D73" s="47">
+      <c r="D73" s="41">
         <v>6.5</v>
       </c>
       <c r="E73" s="9">
@@ -3427,24 +3485,27 @@
         <f t="shared" si="18"/>
         <v>6</v>
       </c>
-      <c r="G73" s="47"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="43">
+      <c r="G73" s="41">
+        <v>12.54</v>
+      </c>
+      <c r="H73" s="49"/>
+      <c r="I73" s="38">
         <f t="shared" si="19"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="53" t="s">
+        <v>186.48</v>
+      </c>
+      <c r="J73" s="73"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="53" t="s">
+      <c r="B74" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C74" s="47">
+      <c r="C74" s="41">
         <v>6.5</v>
       </c>
-      <c r="D74" s="47">
+      <c r="D74" s="41">
         <v>9</v>
       </c>
       <c r="E74" s="9">
@@ -3455,52 +3516,43 @@
         <f t="shared" si="18"/>
         <v>6</v>
       </c>
-      <c r="G74" s="47"/>
-      <c r="H74" s="59"/>
-      <c r="I74" s="43">
+      <c r="G74" s="41">
+        <v>21.88</v>
+      </c>
+      <c r="H74" s="49"/>
+      <c r="I74" s="38">
         <f t="shared" si="19"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="53" t="s">
+        <v>298.56</v>
+      </c>
+      <c r="J74" s="73"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="53" t="s">
+      <c r="B75" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="C75" s="47">
-        <v>6.5</v>
-      </c>
-      <c r="D75" s="47">
-        <v>9</v>
-      </c>
-      <c r="E75" s="9">
-        <f t="shared" si="20"/>
-        <v>58.5</v>
-      </c>
-      <c r="F75" s="9">
-        <f t="shared" si="18"/>
-        <v>6</v>
-      </c>
-      <c r="G75" s="47"/>
-      <c r="H75" s="59"/>
-      <c r="I75" s="43">
-        <f t="shared" si="19"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="53" t="s">
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="53"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="53" t="s">
+      <c r="B76" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C76" s="47">
+      <c r="C76" s="41">
         <v>4</v>
       </c>
-      <c r="D76" s="47">
+      <c r="D76" s="41">
         <v>4</v>
       </c>
       <c r="E76" s="9">
@@ -3511,24 +3563,27 @@
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
-      <c r="G76" s="47"/>
-      <c r="H76" s="59"/>
-      <c r="I76" s="43">
+      <c r="G76" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="H76" s="49"/>
+      <c r="I76" s="38">
         <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="J76" s="73"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="B77" s="53" t="s">
+      <c r="B77" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C77" s="47">
+      <c r="C77" s="41">
         <v>4.5</v>
       </c>
-      <c r="D77" s="47">
+      <c r="D77" s="41">
         <v>9.5</v>
       </c>
       <c r="E77" s="9">
@@ -3539,24 +3594,27 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="G77" s="47"/>
-      <c r="H77" s="59"/>
-      <c r="I77" s="43">
+      <c r="G77" s="41">
+        <v>17</v>
+      </c>
+      <c r="H77" s="49"/>
+      <c r="I77" s="38">
         <f t="shared" si="19"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="J77" s="73"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B78" s="53" t="s">
+      <c r="B78" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C78" s="47">
+      <c r="C78" s="41">
         <v>4.5</v>
       </c>
-      <c r="D78" s="47">
+      <c r="D78" s="41">
         <v>9.5</v>
       </c>
       <c r="E78" s="9">
@@ -3567,24 +3625,27 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="G78" s="47"/>
-      <c r="H78" s="59"/>
-      <c r="I78" s="43">
+      <c r="G78" s="41">
+        <v>22.5</v>
+      </c>
+      <c r="H78" s="49"/>
+      <c r="I78" s="38">
         <f t="shared" si="19"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="J78" s="73"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="53" t="s">
+      <c r="B79" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C79" s="47">
+      <c r="C79" s="41">
         <v>4.5</v>
       </c>
-      <c r="D79" s="47">
+      <c r="D79" s="41">
         <v>9.5</v>
       </c>
       <c r="E79" s="9">
@@ -3595,24 +3656,27 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="G79" s="47"/>
-      <c r="H79" s="59"/>
-      <c r="I79" s="43">
+      <c r="G79" s="41">
+        <v>28</v>
+      </c>
+      <c r="H79" s="49"/>
+      <c r="I79" s="38">
         <f t="shared" si="19"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="J79" s="73"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="B80" s="53" t="s">
+      <c r="B80" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C80" s="47">
+      <c r="C80" s="41">
         <v>4.5</v>
       </c>
-      <c r="D80" s="47">
+      <c r="D80" s="41">
         <v>9.5</v>
       </c>
       <c r="E80" s="9">
@@ -3623,52 +3687,57 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="G80" s="47"/>
-      <c r="H80" s="59"/>
-      <c r="I80" s="43">
+      <c r="G80" s="41">
+        <v>33.5</v>
+      </c>
+      <c r="H80" s="49"/>
+      <c r="I80" s="38">
         <f t="shared" si="19"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="58" t="s">
+        <v>365</v>
+      </c>
+      <c r="J80" s="73"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="60" t="s">
+      <c r="B81" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="62"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="58" t="s">
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
+      <c r="I81" s="55"/>
+      <c r="J81" s="56"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="63"/>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="65"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="53" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="58"/>
+      <c r="F82" s="58"/>
+      <c r="G82" s="58"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="58"/>
+      <c r="J82" s="59"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="B83" s="53" t="s">
+      <c r="B83" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C83" s="47">
+      <c r="C83" s="41">
         <v>6.5</v>
       </c>
-      <c r="D83" s="47">
+      <c r="D83" s="41">
         <v>12.5</v>
       </c>
       <c r="E83" s="9">
@@ -3679,24 +3748,27 @@
         <f t="shared" si="18"/>
         <v>9</v>
       </c>
-      <c r="G83" s="47"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="43">
+      <c r="G83" s="41">
+        <v>10.5</v>
+      </c>
+      <c r="H83" s="49"/>
+      <c r="I83" s="38">
         <f t="shared" si="19"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="J83" s="73"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="B84" s="53" t="s">
+      <c r="B84" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C84" s="47">
+      <c r="C84" s="41">
         <v>6.5</v>
       </c>
-      <c r="D84" s="47">
+      <c r="D84" s="41">
         <v>12.5</v>
       </c>
       <c r="E84" s="9">
@@ -3707,24 +3779,27 @@
         <f t="shared" si="18"/>
         <v>9</v>
       </c>
-      <c r="G84" s="47"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="43">
+      <c r="G84" s="41">
+        <v>17.5</v>
+      </c>
+      <c r="H84" s="49"/>
+      <c r="I84" s="38">
         <f t="shared" si="19"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="53" t="s">
+        <v>369</v>
+      </c>
+      <c r="J84" s="73"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B85" s="53" t="s">
+      <c r="B85" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C85" s="47">
+      <c r="C85" s="41">
         <v>5.5</v>
       </c>
-      <c r="D85" s="47">
+      <c r="D85" s="41">
         <v>12.5</v>
       </c>
       <c r="E85" s="9">
@@ -3735,24 +3810,27 @@
         <f t="shared" si="18"/>
         <v>7</v>
       </c>
-      <c r="G85" s="47"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="43">
+      <c r="G85" s="41">
+        <v>23.5</v>
+      </c>
+      <c r="H85" s="49"/>
+      <c r="I85" s="38">
         <f t="shared" si="19"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="53" t="s">
+        <v>371</v>
+      </c>
+      <c r="J85" s="73"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="B86" s="53" t="s">
+      <c r="B86" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C86" s="47">
+      <c r="C86" s="41">
         <v>5.5</v>
       </c>
-      <c r="D86" s="47">
+      <c r="D86" s="41">
         <v>12.5</v>
       </c>
       <c r="E86" s="9">
@@ -3763,24 +3841,27 @@
         <f t="shared" si="18"/>
         <v>7</v>
       </c>
-      <c r="G86" s="47"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="43">
+      <c r="G86" s="41">
+        <v>29.5</v>
+      </c>
+      <c r="H86" s="49"/>
+      <c r="I86" s="38">
         <f t="shared" si="19"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="J86" s="73"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="B87" s="53" t="s">
+      <c r="B87" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C87" s="47">
+      <c r="C87" s="41">
         <v>5.5</v>
       </c>
-      <c r="D87" s="47">
+      <c r="D87" s="41">
         <v>12.5</v>
       </c>
       <c r="E87" s="9">
@@ -3791,24 +3872,27 @@
         <f t="shared" si="18"/>
         <v>7</v>
       </c>
-      <c r="G87" s="47"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="43">
+      <c r="G87" s="41">
+        <v>35.5</v>
+      </c>
+      <c r="H87" s="49"/>
+      <c r="I87" s="38">
         <f t="shared" si="19"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="J87" s="73"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="B88" s="53" t="s">
+      <c r="B88" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C88" s="47">
+      <c r="C88" s="41">
         <v>5.5</v>
       </c>
-      <c r="D88" s="47">
+      <c r="D88" s="41">
         <v>12.5</v>
       </c>
       <c r="E88" s="9">
@@ -3819,14 +3903,17 @@
         <f t="shared" si="18"/>
         <v>7</v>
       </c>
-      <c r="G88" s="47"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="43">
+      <c r="G88" s="41">
+        <v>41.5</v>
+      </c>
+      <c r="H88" s="49"/>
+      <c r="I88" s="38">
         <f t="shared" si="19"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+      <c r="J88" s="73"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
         <v>66</v>
       </c>
@@ -3836,16 +3923,16 @@
       <c r="E89" s="29"/>
       <c r="F89" s="29">
         <f>SUM(F67:F88)</f>
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G89" s="29"/>
       <c r="H89" s="29"/>
       <c r="I89" s="29">
         <f>SUM(I67:I88)</f>
-        <v>774</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>6280.02</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="37" t="s">
         <v>67</v>
       </c>
@@ -3855,83 +3942,86 @@
       <c r="E91" s="37"/>
       <c r="F91" s="37">
         <f>F89+F65+F45+F20</f>
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="37"/>
       <c r="I91" s="37">
         <f>I89+I65+I45+I20</f>
-        <v>3446.52</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19370.18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H93" s="29" t="s">
         <v>68</v>
       </c>
       <c r="I93" s="29">
         <f>ROUNDUP(ROUNDUP($I$91/305,0)*1.1,0)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H94" s="29" t="s">
         <v>69</v>
       </c>
       <c r="I94" s="29">
         <f>ROUNDUP($I$91/2000,0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="37">
         <f>I91/(F91*2)</f>
-        <v>3.1446350364963505</v>
+        <v>18.002026022304833</v>
       </c>
       <c r="E96" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="44" t="s">
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B98" s="44"/>
-      <c r="C98" s="44"/>
-      <c r="D98" s="44"/>
-      <c r="E98" s="44"/>
-      <c r="F98" s="44"/>
-      <c r="G98" s="44"/>
-      <c r="H98" s="44"/>
-    </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="45" t="s">
+      <c r="B98" s="39"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+    </row>
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="40" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="48" t="s">
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="42" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="51" t="s">
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B81:I82"/>
-    <mergeCell ref="B69:I70"/>
-    <mergeCell ref="B55:I56"/>
-    <mergeCell ref="B37:I38"/>
-    <mergeCell ref="B10:I11"/>
-    <mergeCell ref="B24:I25"/>
+  <mergeCells count="10">
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B69:J70"/>
+    <mergeCell ref="B81:J82"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B75:J75"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C96">
@@ -3944,28 +4034,27 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A14:A19 A26:A36 A59:A64 A39:A44 A71:A88 A67 A68:A70 A22:A23 A24:A25 A37:A38" twoDigitTextYear="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AA7270-A5B3-4391-AFAC-44F660C9B196}">
   <dimension ref="A1:H64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -3991,8 +4080,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="69" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
@@ -4011,12 +4100,12 @@
       <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="69" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="70"/>
       <c r="B3" s="10">
         <v>1</v>
       </c>
@@ -4031,10 +4120,10 @@
       <c r="G3" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="78"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="78"/>
+      <c r="H3" s="70"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="70"/>
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -4051,10 +4140,10 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="78"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="78"/>
+      <c r="H4" s="70"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="70"/>
       <c r="B5" s="10">
         <v>1</v>
       </c>
@@ -4065,10 +4154,10 @@
       <c r="G5" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="78"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="78"/>
+      <c r="H5" s="70"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="70"/>
       <c r="B6" s="10">
         <v>1</v>
       </c>
@@ -4085,10 +4174,10 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="78"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="78"/>
+      <c r="H6" s="70"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="70"/>
       <c r="B7" s="10">
         <v>1</v>
       </c>
@@ -4103,10 +4192,10 @@
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="78"/>
-    </row>
-    <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
+      <c r="H7" s="70"/>
+    </row>
+    <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="70"/>
       <c r="B8" s="24">
         <v>1</v>
       </c>
@@ -4123,10 +4212,10 @@
       <c r="G8" s="5">
         <v>50</v>
       </c>
-      <c r="H8" s="78"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="78"/>
+      <c r="H8" s="70"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="70"/>
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -4136,10 +4225,10 @@
       <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="78"/>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="78"/>
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="70"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -4152,10 +4241,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="78"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="78"/>
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="70"/>
       <c r="B11" s="10">
         <v>1</v>
       </c>
@@ -4166,10 +4255,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="78"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="78"/>
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="70"/>
       <c r="B12" s="10">
         <v>1</v>
       </c>
@@ -4180,10 +4269,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="78"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="78"/>
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="70"/>
       <c r="B13" s="10">
         <v>1</v>
       </c>
@@ -4194,10 +4283,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="78"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="70"/>
       <c r="B14" s="10">
         <v>1</v>
       </c>
@@ -4206,10 +4295,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="78"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="70"/>
       <c r="B15" s="10">
         <v>1</v>
       </c>
@@ -4220,10 +4309,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="78"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="78"/>
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="70"/>
       <c r="B16" s="10">
         <v>1</v>
       </c>
@@ -4234,10 +4323,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="78"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="78"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
       <c r="B17" s="24">
         <v>7</v>
       </c>
@@ -4246,70 +4335,70 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="78"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="78"/>
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
       <c r="B18" s="24"/>
       <c r="C18" s="35"/>
       <c r="D18" s="10"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="78"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="78"/>
+      <c r="H18" s="70"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="70"/>
       <c r="B19" s="24"/>
       <c r="C19" s="35"/>
       <c r="D19" s="10"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="78"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="78"/>
+      <c r="H19" s="70"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="70"/>
       <c r="B20" s="24"/>
       <c r="C20" s="35"/>
       <c r="D20" s="10"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="78"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="78"/>
+      <c r="H20" s="70"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="70"/>
       <c r="B21" s="24"/>
       <c r="C21" s="35"/>
       <c r="D21" s="10"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="78"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
+      <c r="H21" s="70"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="70"/>
       <c r="B22" s="24"/>
       <c r="C22" s="35"/>
       <c r="D22" s="10"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="78"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
+      <c r="H22" s="70"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="70"/>
       <c r="B23" s="24"/>
       <c r="C23" s="36"/>
       <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="78"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="78"/>
+      <c r="H23" s="70"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="70"/>
       <c r="B24" s="10">
         <v>1</v>
       </c>
@@ -4320,10 +4409,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="78"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="78"/>
+      <c r="H24" s="70"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="70"/>
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -4334,10 +4423,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="78"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="78"/>
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="70"/>
       <c r="B26" s="10">
         <v>1</v>
       </c>
@@ -4348,10 +4437,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="78"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="78"/>
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="70"/>
       <c r="B27" s="10">
         <v>1</v>
       </c>
@@ -4360,10 +4449,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="78"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="78"/>
+      <c r="H27" s="70"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="70"/>
       <c r="B28" s="10">
         <v>1</v>
       </c>
@@ -4372,10 +4461,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="78"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="78"/>
+      <c r="H28" s="70"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="70"/>
       <c r="B29" s="10">
         <v>1</v>
       </c>
@@ -4391,10 +4480,10 @@
       <c r="G29" s="5">
         <v>50</v>
       </c>
-      <c r="H29" s="78"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="78"/>
+      <c r="H29" s="70"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="70"/>
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -4405,40 +4494,40 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="78"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="78"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="70"/>
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="78"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="78"/>
+      <c r="H31" s="70"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="70"/>
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="78"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="78"/>
+      <c r="H32" s="70"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="70"/>
       <c r="B33" s="10"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="78"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="78"/>
+      <c r="H33" s="70"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="70"/>
       <c r="B34" s="10">
         <v>1</v>
       </c>
@@ -4451,10 +4540,10 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="78"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="78"/>
+      <c r="H34" s="70"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="70"/>
       <c r="B35" s="10">
         <v>1</v>
       </c>
@@ -4465,10 +4554,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="78"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="78"/>
+      <c r="H35" s="70"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="70"/>
       <c r="B36" s="10">
         <v>1</v>
       </c>
@@ -4485,10 +4574,10 @@
       <c r="G36" s="5">
         <v>200</v>
       </c>
-      <c r="H36" s="78"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="78"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="70"/>
       <c r="B37" s="10">
         <v>2</v>
       </c>
@@ -4499,10 +4588,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="78"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="78"/>
+      <c r="H37" s="70"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="70"/>
       <c r="B38" s="10">
         <v>4</v>
       </c>
@@ -4517,10 +4606,10 @@
       <c r="G38" s="5">
         <v>250</v>
       </c>
-      <c r="H38" s="78"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="78"/>
+      <c r="H38" s="70"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="70"/>
       <c r="B39" s="10">
         <v>4</v>
       </c>
@@ -4535,39 +4624,39 @@
       <c r="G39" s="5">
         <v>250</v>
       </c>
-      <c r="H39" s="78"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="78"/>
+      <c r="H39" s="70"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="70"/>
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="78"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="78"/>
+      <c r="H40" s="70"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="70"/>
       <c r="B41" s="10"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="78"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="78"/>
+      <c r="H41" s="70"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="70"/>
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="78"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="70"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
         <v>3</v>
       </c>
@@ -4588,7 +4677,7 @@
       </c>
       <c r="H43" s="17"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E44" s="19" t="s">
         <v>17</v>
       </c>
@@ -4597,7 +4686,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F45" t="s">
         <v>34</v>
       </c>
@@ -4605,7 +4694,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C46" s="2" t="s">
         <v>31</v>
       </c>
@@ -4618,7 +4707,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C47" s="6" t="s">
         <v>32</v>
       </c>
@@ -4631,7 +4720,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E49" s="20" t="s">
         <v>3</v>
       </c>
@@ -4644,7 +4733,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="31" t="s">
         <v>45</v>
       </c>
@@ -4655,7 +4744,7 @@
       <c r="F50" s="29"/>
       <c r="G50" s="29"/>
     </row>
-    <row r="51" spans="1:7" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="30" t="s">
         <v>44</v>
       </c>
@@ -4669,12 +4758,12 @@
       <c r="F51" s="29"/>
       <c r="G51" s="29"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E52" s="29"/>
       <c r="F52" s="29"/>
       <c r="G52" s="29"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -4682,17 +4771,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B56" s="18" t="s">
         <v>24</v>
       </c>
@@ -4702,17 +4791,17 @@
       <c r="F56" s="18"/>
       <c r="G56" s="18"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B59" s="28" t="s">
         <v>43</v>
       </c>
@@ -4722,7 +4811,7 @@
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B60" s="28" t="s">
         <v>47</v>
       </c>
@@ -4732,7 +4821,7 @@
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B61" s="21" t="s">
         <v>27</v>
       </c>
@@ -4742,17 +4831,17 @@
       <c r="F61" s="21"/>
       <c r="G61" s="21"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B64" s="22" t="s">
         <v>49</v>
       </c>
@@ -4774,7 +4863,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B9A1CC-C4FB-41AD-85DB-3839BA2B7BB9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4783,28 +4872,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A71F13F-E947-4C1E-BDE3-9A5BE07FD910}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E4DE2CC379442A4D8483D9D7B1BA3E35" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3cbd871ac436bbcd94953c6f74650012">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b380a0-b262-4a13-9203-497a21b8eee5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f82e0ce2898406bfa558450728792a3e" ns2:_="">
     <xsd:import namespace="a1b380a0-b262-4a13-9203-497a21b8eee5"/>
@@ -4942,24 +5016,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4975,4 +5047,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1231DD6F-C620-4423-B62A-6F50A9583523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC6BDD-C523-43C3-8A25-2ACF385A89BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
   </bookViews>
@@ -93,8 +93,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="171">
   <si>
     <t>Spatiu ocupat in U</t>
   </si>
@@ -571,6 +593,42 @@
   </si>
   <si>
     <t>Room Type</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1174,25 +1232,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1213,22 +1275,13 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1246,9 +1299,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1587,6 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29A6EC-8F37-4E8F-9E44-40C579389B24}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1595,54 +1666,54 @@
     <col min="4" max="5" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="70" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="73" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="J1" s="71" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="41">
         <v>6.5</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="41">
         <v>8.5</v>
       </c>
       <c r="E2" s="9">
@@ -1653,25 +1724,32 @@
         <f>ROUNDUP(E2/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="43"/>
+      <c r="G2" s="39">
+        <v>9.4</v>
+      </c>
+      <c r="H2" s="42" cm="1">
+        <f t="array" ref="H2">_xlfn.CEILING.MATH(_xlfn.SWITCH(J2, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I2" s="38">
-        <f>2*F2*(G2+H2+3)</f>
-        <v>36</v>
-      </c>
-      <c r="J2" s="73"/>
+        <f>2*F2*(G2+H2+6)</f>
+        <v>352.79999999999995</v>
+      </c>
+      <c r="J2" s="72" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="41">
         <v>8.5</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="41">
         <v>6.5</v>
       </c>
       <c r="E3" s="9">
@@ -1682,41 +1760,48 @@
         <f t="shared" ref="F3:F19" si="1">ROUNDUP(E3/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="43"/>
+      <c r="G3" s="39">
+        <v>16.11</v>
+      </c>
+      <c r="H3" s="42" cm="1">
+        <f t="array" ref="H3">_xlfn.CEILING.MATH(_xlfn.SWITCH(J3, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>5</v>
+      </c>
       <c r="I3" s="38">
-        <f t="shared" ref="I3:I19" si="2">2*F3*(G3+H3+3)</f>
-        <v>36</v>
-      </c>
-      <c r="J3" s="73"/>
+        <f>2*F3*(G3+H3+6)</f>
+        <v>325.32</v>
+      </c>
+      <c r="J3" s="72" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="53"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="41">
         <v>5.5</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="41">
         <v>8.5</v>
       </c>
       <c r="E5" s="9">
@@ -1727,25 +1812,32 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="39">
+        <v>21.82</v>
+      </c>
+      <c r="H5" s="42" cm="1">
+        <f t="array" ref="H5">_xlfn.CEILING.MATH(_xlfn.SWITCH(J5, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I5" s="38">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="J5" s="73"/>
+        <f>2*F5*(G5+H5+6)</f>
+        <v>388.2</v>
+      </c>
+      <c r="J5" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="41">
         <v>5.5</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="41">
         <v>8.5</v>
       </c>
       <c r="E6" s="9">
@@ -1756,25 +1848,32 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="39">
+        <v>27.82</v>
+      </c>
+      <c r="H6" s="42" cm="1">
+        <f t="array" ref="H6">_xlfn.CEILING.MATH(_xlfn.SWITCH(J6, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I6" s="38">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="J6" s="73"/>
+        <f t="shared" ref="I6:I9" si="2">2*F6*(G6+H6+6)</f>
+        <v>448.2</v>
+      </c>
+      <c r="J6" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="41">
         <v>5.5</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="41">
         <v>8.5</v>
       </c>
       <c r="E7" s="9">
@@ -1785,25 +1884,32 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="G7" s="39">
+        <v>33.53</v>
+      </c>
+      <c r="H7" s="42" cm="1">
+        <f t="array" ref="H7">_xlfn.CEILING.MATH(_xlfn.SWITCH(J7, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I7" s="38">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="J7" s="73"/>
+        <v>505.3</v>
+      </c>
+      <c r="J7" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="41">
         <v>5.5</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="41">
         <v>8.5</v>
       </c>
       <c r="E8" s="9">
@@ -1814,25 +1920,32 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="G8" s="39">
+        <v>39.53</v>
+      </c>
+      <c r="H8" s="42" cm="1">
+        <f t="array" ref="H8">_xlfn.CEILING.MATH(_xlfn.SWITCH(J8, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I8" s="38">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="J8" s="73"/>
+        <v>565.29999999999995</v>
+      </c>
+      <c r="J8" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="41">
         <v>5.5</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="41">
         <v>8.5</v>
       </c>
       <c r="E9" s="9">
@@ -1843,55 +1956,62 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
+      <c r="G9" s="39">
+        <v>45.24</v>
+      </c>
+      <c r="H9" s="42" cm="1">
+        <f t="array" ref="H9">_xlfn.CEILING.MATH(_xlfn.SWITCH(J9, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I9" s="38">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="J9" s="73"/>
+        <v>622.4</v>
+      </c>
+      <c r="J9" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="62"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="51"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="41">
         <v>8.5</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="41">
         <v>11.5</v>
       </c>
       <c r="E12" s="9">
@@ -1902,25 +2022,32 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
+      <c r="G12" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="42" cm="1">
+        <f t="array" ref="H12">_xlfn.CEILING.MATH(_xlfn.SWITCH(J12, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I12" s="38">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="J12" s="73"/>
+        <f>2*F12*(G12+H12+6)</f>
+        <v>350</v>
+      </c>
+      <c r="J12" s="72" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="41">
         <v>20</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="41">
         <v>16.5</v>
       </c>
       <c r="E13" s="9">
@@ -1931,25 +2058,32 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
+      <c r="G13" s="39">
+        <v>5</v>
+      </c>
+      <c r="H13" s="42" cm="1">
+        <f t="array" ref="H13">_xlfn.CEILING.MATH(_xlfn.SWITCH(J13, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>22</v>
+      </c>
       <c r="I13" s="38">
-        <f t="shared" si="2"/>
-        <v>198</v>
-      </c>
-      <c r="J13" s="73"/>
+        <f t="shared" ref="I13:I19" si="3">2*F13*(G13+H13+6)</f>
+        <v>2178</v>
+      </c>
+      <c r="J13" s="72" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="41">
         <v>6.5</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="41">
         <v>11.5</v>
       </c>
       <c r="E14" s="9">
@@ -1960,25 +2094,32 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
+      <c r="G14" s="39">
+        <v>84.64</v>
+      </c>
+      <c r="H14" s="42" cm="1">
+        <f t="array" ref="H14">_xlfn.CEILING.MATH(_xlfn.SWITCH(J14, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I14" s="38">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="J14" s="73"/>
+        <f t="shared" si="3"/>
+        <v>1722.24</v>
+      </c>
+      <c r="J14" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="41">
         <v>6.5</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="41">
         <v>11.5</v>
       </c>
       <c r="E15" s="9">
@@ -1989,25 +2130,32 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
+      <c r="G15" s="39">
+        <v>91.78</v>
+      </c>
+      <c r="H15" s="42" cm="1">
+        <f t="array" ref="H15">_xlfn.CEILING.MATH(_xlfn.SWITCH(J15, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I15" s="38">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="J15" s="73"/>
+        <f t="shared" si="3"/>
+        <v>1836.48</v>
+      </c>
+      <c r="J15" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="41">
         <v>6.5</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="41">
         <v>11.5</v>
       </c>
       <c r="E16" s="9">
@@ -2018,25 +2166,32 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
+      <c r="G16" s="39">
+        <v>98.78</v>
+      </c>
+      <c r="H16" s="42" cm="1">
+        <f t="array" ref="H16">_xlfn.CEILING.MATH(_xlfn.SWITCH(J16, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I16" s="38">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="J16" s="73"/>
+        <f t="shared" si="3"/>
+        <v>1948.48</v>
+      </c>
+      <c r="J16" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="41">
         <v>6.5</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="41">
         <v>11.5</v>
       </c>
       <c r="E17" s="9">
@@ -2047,25 +2202,32 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
+      <c r="G17" s="39">
+        <v>105.92</v>
+      </c>
+      <c r="H17" s="42" cm="1">
+        <f t="array" ref="H17">_xlfn.CEILING.MATH(_xlfn.SWITCH(J17, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I17" s="38">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="J17" s="73"/>
+        <f t="shared" si="3"/>
+        <v>2062.7200000000003</v>
+      </c>
+      <c r="J17" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="41">
         <v>6.5</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="41">
         <v>11.5</v>
       </c>
       <c r="E18" s="9">
@@ -2076,25 +2238,32 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
+      <c r="G18" s="39">
+        <v>112.92</v>
+      </c>
+      <c r="H18" s="42" cm="1">
+        <f t="array" ref="H18">_xlfn.CEILING.MATH(_xlfn.SWITCH(J18, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I18" s="38">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="J18" s="73"/>
+        <f t="shared" si="3"/>
+        <v>2174.7200000000003</v>
+      </c>
+      <c r="J18" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="41">
         <v>10</v>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="41">
         <v>20</v>
       </c>
       <c r="E19" s="9">
@@ -2105,13 +2274,20 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="G19" s="46"/>
-      <c r="H19" s="47"/>
+      <c r="G19" s="39">
+        <v>17.5</v>
+      </c>
+      <c r="H19" s="42" cm="1">
+        <f t="array" ref="H19">_xlfn.CEILING.MATH(_xlfn.SWITCH(J19, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I19" s="38">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="J19" s="73"/>
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="J19" s="72" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
@@ -2126,10 +2302,10 @@
         <v>140</v>
       </c>
       <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="29">
         <f>SUM(I2:I19)</f>
-        <v>840</v>
+        <v>16980.16</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -2140,108 +2316,122 @@
       <c r="E21" s="29"/>
       <c r="F21" s="29"/>
       <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="H21" s="67"/>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="41">
         <v>6.5</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="41">
         <v>11.5</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" ref="E22:E23" si="3">C22*D22</f>
+        <f t="shared" ref="E22:E23" si="4">C22*D22</f>
         <v>74.75</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" ref="F22:F23" si="4">ROUNDUP(E22/10,0)</f>
+        <f t="shared" ref="F22:F23" si="5">ROUNDUP(E22/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G22" s="41"/>
-      <c r="H22" s="49"/>
+      <c r="G22" s="39">
+        <v>32</v>
+      </c>
+      <c r="H22" s="68" cm="1">
+        <f t="array" ref="H22">_xlfn.CEILING.MATH(_xlfn.SWITCH(J22, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I22" s="38">
-        <f t="shared" ref="I22:I23" si="5">2*F22*(G22+H22+3)</f>
-        <v>48</v>
-      </c>
-      <c r="J22" s="73"/>
+        <f>2*F22*(G22+H22+6)</f>
+        <v>880</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="46">
+      <c r="C23" s="41">
         <v>6.5</v>
       </c>
-      <c r="D23" s="46">
+      <c r="D23" s="41">
         <v>11.5</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>74.75</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G23" s="41"/>
-      <c r="H23" s="49"/>
+      <c r="G23" s="39">
+        <v>27</v>
+      </c>
+      <c r="H23" s="68" cm="1">
+        <f t="array" ref="H23">_xlfn.CEILING.MATH(_xlfn.SWITCH(J23, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I23" s="38">
-        <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="J23" s="73"/>
+        <f>2*F23*(G23+H23+6)</f>
+        <v>800</v>
+      </c>
+      <c r="J23" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="60" t="s">
+      <c r="B24" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="62"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="48"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="63"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="65"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="51"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="41">
         <v>10</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="41">
         <v>20</v>
       </c>
       <c r="E26" s="9">
@@ -2252,25 +2442,32 @@
         <f>ROUNDUP(E26/10,0)</f>
         <v>20</v>
       </c>
-      <c r="G26" s="41"/>
-      <c r="H26" s="49"/>
+      <c r="G26" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="68" cm="1">
+        <f t="array" ref="H26">_xlfn.CEILING.MATH(_xlfn.SWITCH(J26, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I26" s="38">
-        <f>2*F26*(G26+H26+3)</f>
-        <v>120</v>
-      </c>
-      <c r="J26" s="73"/>
+        <f>2*F26*(G26+H26+6)</f>
+        <v>820</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="39">
         <v>9</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="39">
         <v>10</v>
       </c>
       <c r="E27" s="9">
@@ -2281,83 +2478,104 @@
         <f>ROUNDUP(E27/10,0)</f>
         <v>9</v>
       </c>
-      <c r="G27" s="41"/>
-      <c r="H27" s="47"/>
+      <c r="G27" s="39">
+        <v>45</v>
+      </c>
+      <c r="H27" s="68" cm="1">
+        <f t="array" ref="H27">_xlfn.CEILING.MATH(_xlfn.SWITCH(J27, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>20</v>
+      </c>
       <c r="I27" s="38">
-        <f>2*F27*(G27+H27+3)</f>
-        <v>54</v>
-      </c>
-      <c r="J27" s="73"/>
+        <f t="shared" ref="I27:I30" si="6">2*F27*(G27+H27+6)</f>
+        <v>1278</v>
+      </c>
+      <c r="J27" s="72" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="39">
         <v>9</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="39">
         <v>10</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" ref="E28:E29" si="6">C28*D28</f>
+        <f t="shared" ref="E28:E29" si="7">C28*D28</f>
         <v>90</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" ref="F28:F44" si="7">ROUNDUP(E28/10,0)</f>
+        <f t="shared" ref="F28:F44" si="8">ROUNDUP(E28/10,0)</f>
         <v>9</v>
       </c>
-      <c r="G28" s="41"/>
-      <c r="H28" s="47"/>
+      <c r="G28" s="39">
+        <v>40</v>
+      </c>
+      <c r="H28" s="68" cm="1">
+        <f t="array" ref="H28">_xlfn.CEILING.MATH(_xlfn.SWITCH(J28, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>20</v>
+      </c>
       <c r="I28" s="38">
-        <f t="shared" ref="I28:I44" si="8">2*F28*(G28+H28+3)</f>
-        <v>54</v>
-      </c>
-      <c r="J28" s="73"/>
+        <f t="shared" si="6"/>
+        <v>1188</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="39">
         <v>6.5</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="39">
         <v>9</v>
       </c>
       <c r="E29" s="9">
+        <f t="shared" si="7"/>
+        <v>58.5</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="G29" s="39">
+        <v>12.54</v>
+      </c>
+      <c r="H29" s="68" cm="1">
+        <f t="array" ref="H29">_xlfn.CEILING.MATH(_xlfn.SWITCH(J29, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I29" s="38">
         <f t="shared" si="6"/>
-        <v>58.5</v>
-      </c>
-      <c r="F29" s="9">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="G29" s="41"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="38">
-        <f t="shared" si="8"/>
-        <v>36</v>
-      </c>
-      <c r="J29" s="73"/>
+        <v>438.48</v>
+      </c>
+      <c r="J29" s="72" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="39">
         <v>6.5</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="39">
         <v>9</v>
       </c>
       <c r="E30" s="9">
@@ -2365,44 +2583,51 @@
         <v>58.5</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="G30" s="41"/>
-      <c r="H30" s="47"/>
+      <c r="G30" s="39">
+        <v>21.88</v>
+      </c>
+      <c r="H30" s="68" cm="1">
+        <f t="array" ref="H30">_xlfn.CEILING.MATH(_xlfn.SWITCH(J30, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I30" s="38">
-        <f t="shared" si="8"/>
-        <v>36</v>
-      </c>
-      <c r="J30" s="73"/>
+        <f t="shared" si="6"/>
+        <v>550.55999999999995</v>
+      </c>
+      <c r="J30" s="72" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="53"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="60"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="39">
         <v>4.5</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="39">
         <v>9.5</v>
       </c>
       <c r="E32" s="9">
@@ -2410,28 +2635,35 @@
         <v>42.75</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G32" s="41"/>
-      <c r="H32" s="47"/>
+      <c r="G32" s="39">
+        <v>11.5</v>
+      </c>
+      <c r="H32" s="42" cm="1">
+        <f t="array" ref="H32">_xlfn.CEILING.MATH(_xlfn.SWITCH(J32, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
       <c r="I32" s="38">
-        <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="J32" s="73"/>
+        <f>2*F32*(G32+H32+6)</f>
+        <v>305</v>
+      </c>
+      <c r="J32" s="72" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="41">
+      <c r="C33" s="39">
         <v>4.5</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="39">
         <v>9.5</v>
       </c>
       <c r="E33" s="9">
@@ -2439,28 +2671,35 @@
         <v>42.75</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G33" s="41"/>
-      <c r="H33" s="47"/>
+      <c r="G33" s="39">
+        <v>17</v>
+      </c>
+      <c r="H33" s="42" cm="1">
+        <f t="array" ref="H33">_xlfn.CEILING.MATH(_xlfn.SWITCH(J33, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
       <c r="I33" s="38">
-        <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="J33" s="73"/>
+        <f t="shared" ref="I33:I36" si="10">2*F33*(G33+H33+6)</f>
+        <v>360</v>
+      </c>
+      <c r="J33" s="72" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="39">
         <v>4.5</v>
       </c>
-      <c r="D34" s="41">
+      <c r="D34" s="39">
         <v>9.5</v>
       </c>
       <c r="E34" s="9">
@@ -2468,28 +2707,35 @@
         <v>42.75</v>
       </c>
       <c r="F34" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G34" s="41"/>
-      <c r="H34" s="47"/>
+      <c r="G34" s="39">
+        <v>22.5</v>
+      </c>
+      <c r="H34" s="42" cm="1">
+        <f t="array" ref="H34">_xlfn.CEILING.MATH(_xlfn.SWITCH(J34, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
       <c r="I34" s="38">
-        <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="J34" s="73"/>
+        <f t="shared" si="10"/>
+        <v>415</v>
+      </c>
+      <c r="J34" s="72" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="45" t="s">
+      <c r="B35" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="39">
         <v>4.5</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="39">
         <v>9.5</v>
       </c>
       <c r="E35" s="9">
@@ -2497,28 +2743,35 @@
         <v>42.75</v>
       </c>
       <c r="F35" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G35" s="41"/>
-      <c r="H35" s="47"/>
+      <c r="G35" s="39">
+        <v>28</v>
+      </c>
+      <c r="H35" s="42" cm="1">
+        <f t="array" ref="H35">_xlfn.CEILING.MATH(_xlfn.SWITCH(J35, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
       <c r="I35" s="38">
-        <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="J35" s="73"/>
+        <f t="shared" si="10"/>
+        <v>470</v>
+      </c>
+      <c r="J35" s="72" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="45" t="s">
+      <c r="B36" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="39">
         <v>4.5</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="39">
         <v>9.5</v>
       </c>
       <c r="E36" s="9">
@@ -2526,87 +2779,101 @@
         <v>42.75</v>
       </c>
       <c r="F36" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="47"/>
+      <c r="G36" s="39">
+        <v>33.5</v>
+      </c>
+      <c r="H36" s="42" cm="1">
+        <f t="array" ref="H36">_xlfn.CEILING.MATH(_xlfn.SWITCH(J36, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
       <c r="I36" s="38">
-        <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="J36" s="73"/>
+        <f t="shared" si="10"/>
+        <v>525</v>
+      </c>
+      <c r="J36" s="72" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="56"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="59"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="57"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="41">
-        <v>6.5</v>
-      </c>
-      <c r="D39" s="41">
+      <c r="C39" s="39">
+        <v>6</v>
+      </c>
+      <c r="D39" s="39">
         <v>12.5</v>
       </c>
       <c r="E39" s="9">
         <f t="shared" si="9"/>
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="F39" s="9">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="G39" s="41"/>
-      <c r="H39" s="47"/>
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="G39" s="39">
+        <v>10.5</v>
+      </c>
+      <c r="H39" s="42" cm="1">
+        <f t="array" ref="H39">_xlfn.CEILING.MATH(_xlfn.SWITCH(J39, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I39" s="38">
-        <f t="shared" si="8"/>
-        <v>54</v>
-      </c>
-      <c r="J39" s="73"/>
+        <f>2*F39*(G39+H39+6)</f>
+        <v>552</v>
+      </c>
+      <c r="J39" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="45" t="s">
+      <c r="B40" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="41">
+      <c r="C40" s="39">
         <v>5.5</v>
       </c>
-      <c r="D40" s="41">
+      <c r="D40" s="39">
         <v>12.5</v>
       </c>
       <c r="E40" s="9">
@@ -2614,28 +2881,35 @@
         <v>68.75</v>
       </c>
       <c r="F40" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="G40" s="41"/>
-      <c r="H40" s="47"/>
+      <c r="G40" s="39">
+        <v>17.5</v>
+      </c>
+      <c r="H40" s="42" cm="1">
+        <f t="array" ref="H40">_xlfn.CEILING.MATH(_xlfn.SWITCH(J40, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I40" s="38">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="J40" s="73"/>
+        <f t="shared" ref="I40:I44" si="11">2*F40*(G40+H40+6)</f>
+        <v>581</v>
+      </c>
+      <c r="J40" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="41">
+      <c r="C41" s="39">
         <v>5.5</v>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="39">
         <v>12.5</v>
       </c>
       <c r="E41" s="9">
@@ -2643,28 +2917,35 @@
         <v>68.75</v>
       </c>
       <c r="F41" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="G41" s="41"/>
-      <c r="H41" s="47"/>
+      <c r="G41" s="39">
+        <v>23.5</v>
+      </c>
+      <c r="H41" s="42" cm="1">
+        <f t="array" ref="H41">_xlfn.CEILING.MATH(_xlfn.SWITCH(J41, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I41" s="38">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="J41" s="73"/>
+        <f t="shared" si="11"/>
+        <v>665</v>
+      </c>
+      <c r="J41" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="45" t="s">
+      <c r="A42" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="41">
+      <c r="C42" s="39">
         <v>5.5</v>
       </c>
-      <c r="D42" s="41">
+      <c r="D42" s="39">
         <v>12.5</v>
       </c>
       <c r="E42" s="9">
@@ -2672,28 +2953,35 @@
         <v>68.75</v>
       </c>
       <c r="F42" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="G42" s="41"/>
-      <c r="H42" s="47"/>
+      <c r="G42" s="39">
+        <v>29.5</v>
+      </c>
+      <c r="H42" s="42" cm="1">
+        <f t="array" ref="H42">_xlfn.CEILING.MATH(_xlfn.SWITCH(J42, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I42" s="38">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="J42" s="73"/>
+        <f t="shared" si="11"/>
+        <v>749</v>
+      </c>
+      <c r="J42" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="45" t="s">
+      <c r="A43" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="45" t="s">
+      <c r="B43" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="41">
+      <c r="C43" s="39">
         <v>5.5</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="39">
         <v>12.5</v>
       </c>
       <c r="E43" s="9">
@@ -2701,28 +2989,35 @@
         <v>68.75</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="G43" s="41"/>
-      <c r="H43" s="47"/>
+      <c r="G43" s="39">
+        <v>35.5</v>
+      </c>
+      <c r="H43" s="42" cm="1">
+        <f t="array" ref="H43">_xlfn.CEILING.MATH(_xlfn.SWITCH(J43, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I43" s="38">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="J43" s="73"/>
+        <f t="shared" si="11"/>
+        <v>833</v>
+      </c>
+      <c r="J43" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
+      <c r="A44" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="41">
+      <c r="C44" s="39">
         <v>5.5</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="39">
         <v>12.5</v>
       </c>
       <c r="E44" s="9">
@@ -2730,16 +3025,23 @@
         <v>68.75</v>
       </c>
       <c r="F44" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="G44" s="41"/>
-      <c r="H44" s="47"/>
+      <c r="G44" s="39">
+        <v>41.5</v>
+      </c>
+      <c r="H44" s="42" cm="1">
+        <f t="array" ref="H44">_xlfn.CEILING.MATH(_xlfn.SWITCH(J44, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I44" s="38">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="J44" s="73"/>
+        <f t="shared" si="11"/>
+        <v>917</v>
+      </c>
+      <c r="J44" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
@@ -2751,13 +3053,13 @@
       <c r="E45" s="29"/>
       <c r="F45" s="29">
         <f>SUM(F22:F44)</f>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
+      <c r="H45" s="67"/>
       <c r="I45" s="29">
         <f>SUM(I22:I44)</f>
-        <v>810</v>
+        <v>12327.039999999999</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -2768,20 +3070,20 @@
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
       <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
+      <c r="H46" s="67"/>
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="46">
+      <c r="C47" s="41">
         <v>6.5</v>
       </c>
-      <c r="D47" s="46">
+      <c r="D47" s="41">
         <v>8.5</v>
       </c>
       <c r="E47" s="9">
@@ -2792,493 +3094,570 @@
         <f>ROUNDUP(E47/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G47" s="41">
+      <c r="G47" s="39">
         <v>9.4</v>
       </c>
-      <c r="H47" s="49"/>
+      <c r="H47" s="68" cm="1">
+        <f t="array" ref="H47">_xlfn.CEILING.MATH(_xlfn.SWITCH(J47, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I47" s="38">
-        <f>2*F47*(G47+H47+3)</f>
-        <v>148.80000000000001</v>
-      </c>
-      <c r="J47" s="73"/>
+        <f>2*F47*(G47+H47+6)</f>
+        <v>352.79999999999995</v>
+      </c>
+      <c r="J47" s="72" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="45" t="s">
+      <c r="A48" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B48" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="46">
+      <c r="C48" s="41">
         <v>8.5</v>
       </c>
-      <c r="D48" s="46">
+      <c r="D48" s="41">
         <v>6.5</v>
       </c>
       <c r="E48" s="9">
-        <f t="shared" ref="E48" si="10">C48*D48</f>
+        <f t="shared" ref="E48" si="12">C48*D48</f>
         <v>55.25</v>
       </c>
       <c r="F48" s="9">
-        <f t="shared" ref="F48:F64" si="11">ROUNDUP(E48/10,0)</f>
+        <f t="shared" ref="F48:F64" si="13">ROUNDUP(E48/10,0)</f>
         <v>6</v>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="39">
         <v>16.11</v>
       </c>
-      <c r="H48" s="49"/>
+      <c r="H48" s="68" cm="1">
+        <f t="array" ref="H48">_xlfn.CEILING.MATH(_xlfn.SWITCH(J48, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>5</v>
+      </c>
       <c r="I48" s="38">
-        <f t="shared" ref="I48:I64" si="12">2*F48*(G48+H48+3)</f>
-        <v>229.32</v>
-      </c>
-      <c r="J48" s="73"/>
+        <f>2*F48*(G48+H48+6)</f>
+        <v>325.32</v>
+      </c>
+      <c r="J48" s="72" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="50" t="s">
+      <c r="A49" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="66" t="s">
+      <c r="B49" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="68"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="62"/>
+      <c r="H49" s="62"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="63"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="45" t="s">
+      <c r="A50" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="41" t="s">
+      <c r="B50" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="46">
+      <c r="C50" s="41">
         <v>5.5</v>
       </c>
-      <c r="D50" s="46">
+      <c r="D50" s="41">
         <v>8.5</v>
       </c>
       <c r="E50" s="9">
-        <f t="shared" ref="E50:E64" si="13">C50*D50</f>
+        <f t="shared" ref="E50:E64" si="14">C50*D50</f>
         <v>46.75</v>
       </c>
       <c r="F50" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="39">
         <v>21.82</v>
       </c>
-      <c r="H50" s="49"/>
+      <c r="H50" s="68" cm="1">
+        <f t="array" ref="H50">_xlfn.CEILING.MATH(_xlfn.SWITCH(J50, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
       <c r="I50" s="38">
-        <f t="shared" si="12"/>
-        <v>248.2</v>
-      </c>
-      <c r="J50" s="73"/>
+        <f>2*F50*(G50+H50+6)</f>
+        <v>388.2</v>
+      </c>
+      <c r="J50" s="72" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="45" t="s">
+      <c r="A51" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="46">
+      <c r="C51" s="41">
         <v>5.5</v>
       </c>
-      <c r="D51" s="46">
+      <c r="D51" s="41">
         <v>8.5</v>
       </c>
       <c r="E51" s="9">
+        <f t="shared" si="14"/>
+        <v>46.75</v>
+      </c>
+      <c r="F51" s="9">
         <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="G51" s="39">
+        <v>27.82</v>
+      </c>
+      <c r="H51" s="68" cm="1">
+        <f t="array" ref="H51">_xlfn.CEILING.MATH(_xlfn.SWITCH(J51, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
+      <c r="I51" s="38">
+        <f t="shared" ref="I51:I54" si="15">2*F51*(G51+H51+6)</f>
+        <v>448.2</v>
+      </c>
+      <c r="J51" s="72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="41">
+        <v>5.5</v>
+      </c>
+      <c r="D52" s="41">
+        <v>8.5</v>
+      </c>
+      <c r="E52" s="9">
+        <f t="shared" si="14"/>
         <v>46.75</v>
       </c>
-      <c r="F51" s="9">
-        <f t="shared" si="11"/>
+      <c r="F52" s="9">
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="G51" s="41">
-        <v>27.82</v>
-      </c>
-      <c r="H51" s="49"/>
-      <c r="I51" s="38">
-        <f t="shared" si="12"/>
-        <v>308.2</v>
-      </c>
-      <c r="J51" s="73"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="41" t="s">
+      <c r="G52" s="39">
+        <v>33.53</v>
+      </c>
+      <c r="H52" s="68" cm="1">
+        <f t="array" ref="H52">_xlfn.CEILING.MATH(_xlfn.SWITCH(J52, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
+      <c r="I52" s="38">
+        <f t="shared" si="15"/>
+        <v>505.3</v>
+      </c>
+      <c r="J52" s="72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C52" s="46">
+      <c r="C53" s="41">
         <v>5.5</v>
       </c>
-      <c r="D52" s="46">
+      <c r="D53" s="41">
         <v>8.5</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E53" s="9">
+        <f t="shared" si="14"/>
+        <v>46.75</v>
+      </c>
+      <c r="F53" s="9">
         <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="G53" s="39">
+        <v>39.53</v>
+      </c>
+      <c r="H53" s="68" cm="1">
+        <f t="array" ref="H53">_xlfn.CEILING.MATH(_xlfn.SWITCH(J53, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
+      <c r="I53" s="38">
+        <f t="shared" si="15"/>
+        <v>565.29999999999995</v>
+      </c>
+      <c r="J53" s="72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="41">
+        <v>5.5</v>
+      </c>
+      <c r="D54" s="41">
+        <v>8.5</v>
+      </c>
+      <c r="E54" s="9">
+        <f t="shared" si="14"/>
         <v>46.75</v>
       </c>
-      <c r="F52" s="9">
-        <f t="shared" si="11"/>
+      <c r="F54" s="9">
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="G52" s="41">
-        <v>33.53</v>
-      </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="38">
-        <f t="shared" si="12"/>
-        <v>365.3</v>
-      </c>
-      <c r="J52" s="73"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="41" t="s">
+      <c r="G54" s="39">
+        <v>45.24</v>
+      </c>
+      <c r="H54" s="68" cm="1">
+        <f t="array" ref="H54">_xlfn.CEILING.MATH(_xlfn.SWITCH(J54, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
+      <c r="I54" s="38">
+        <f t="shared" si="15"/>
+        <v>622.4</v>
+      </c>
+      <c r="J54" s="72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="48"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="49"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="51"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="46">
-        <v>5.5</v>
-      </c>
-      <c r="D53" s="46">
+      <c r="C57" s="41">
         <v>8.5</v>
       </c>
-      <c r="E53" s="9">
+      <c r="D57" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="E57" s="9">
+        <f t="shared" si="14"/>
+        <v>97.75</v>
+      </c>
+      <c r="F57" s="9">
         <f t="shared" si="13"/>
-        <v>46.75</v>
-      </c>
-      <c r="F53" s="9">
-        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="G57" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="68" cm="1">
+        <f t="array" ref="H57">_xlfn.CEILING.MATH(_xlfn.SWITCH(J57, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>11</v>
+      </c>
+      <c r="I57" s="38">
+        <f>2*F57*(G57+H57+6)</f>
+        <v>350</v>
+      </c>
+      <c r="J57" s="72" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="41">
+        <v>20</v>
+      </c>
+      <c r="D58" s="41">
+        <v>16.5</v>
+      </c>
+      <c r="E58" s="9">
+        <f t="shared" si="14"/>
+        <v>330</v>
+      </c>
+      <c r="F58" s="9">
+        <f t="shared" si="13"/>
+        <v>33</v>
+      </c>
+      <c r="G58" s="39">
         <v>5</v>
       </c>
-      <c r="G53" s="41">
-        <v>39.53</v>
-      </c>
-      <c r="H53" s="49"/>
-      <c r="I53" s="38">
-        <f t="shared" si="12"/>
-        <v>425.3</v>
-      </c>
-      <c r="J53" s="73"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="41" t="s">
+      <c r="H58" s="68" cm="1">
+        <f t="array" ref="H58">_xlfn.CEILING.MATH(_xlfn.SWITCH(J58, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>22</v>
+      </c>
+      <c r="I58" s="38">
+        <f t="shared" ref="I58:I64" si="16">2*F58*(G58+H58+6)</f>
+        <v>2178</v>
+      </c>
+      <c r="J58" s="72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C54" s="46">
-        <v>5.5</v>
-      </c>
-      <c r="D54" s="46">
-        <v>8.5</v>
-      </c>
-      <c r="E54" s="9">
+      <c r="C59" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="D59" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="E59" s="9">
+        <f t="shared" si="14"/>
+        <v>74.75</v>
+      </c>
+      <c r="F59" s="9">
         <f t="shared" si="13"/>
-        <v>46.75</v>
-      </c>
-      <c r="F54" s="9">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="G54" s="41">
-        <v>45.24</v>
-      </c>
-      <c r="H54" s="49"/>
-      <c r="I54" s="38">
-        <f t="shared" si="12"/>
-        <v>482.40000000000003</v>
-      </c>
-      <c r="J54" s="73"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="62"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" s="63"/>
-      <c r="C56" s="64"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64"/>
-      <c r="J56" s="65"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="39">
+        <v>84.64</v>
+      </c>
+      <c r="H59" s="68" cm="1">
+        <f t="array" ref="H59">_xlfn.CEILING.MATH(_xlfn.SWITCH(J59, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I59" s="38">
+        <f t="shared" si="16"/>
+        <v>1722.24</v>
+      </c>
+      <c r="J59" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="46">
-        <v>8.5</v>
-      </c>
-      <c r="D57" s="46">
+      <c r="C60" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="D60" s="41">
         <v>11.5</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E60" s="9">
+        <f t="shared" si="14"/>
+        <v>74.75</v>
+      </c>
+      <c r="F60" s="9">
         <f t="shared" si="13"/>
-        <v>97.75</v>
-      </c>
-      <c r="F57" s="9">
-        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G60" s="39">
+        <v>91.78</v>
+      </c>
+      <c r="H60" s="68" cm="1">
+        <f t="array" ref="H60">_xlfn.CEILING.MATH(_xlfn.SWITCH(J60, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I60" s="38">
+        <f t="shared" si="16"/>
+        <v>1836.48</v>
+      </c>
+      <c r="J60" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="D61" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="E61" s="9">
+        <f t="shared" si="14"/>
+        <v>74.75</v>
+      </c>
+      <c r="F61" s="9">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="G61" s="39">
+        <v>98.78</v>
+      </c>
+      <c r="H61" s="68" cm="1">
+        <f t="array" ref="H61">_xlfn.CEILING.MATH(_xlfn.SWITCH(J61, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I61" s="38">
+        <f t="shared" si="16"/>
+        <v>1948.48</v>
+      </c>
+      <c r="J61" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="D62" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="E62" s="9">
+        <f t="shared" si="14"/>
+        <v>74.75</v>
+      </c>
+      <c r="F62" s="9">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="G62" s="39">
+        <v>105.92</v>
+      </c>
+      <c r="H62" s="68" cm="1">
+        <f t="array" ref="H62">_xlfn.CEILING.MATH(_xlfn.SWITCH(J62, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I62" s="38">
+        <f t="shared" si="16"/>
+        <v>2062.7200000000003</v>
+      </c>
+      <c r="J62" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="D63" s="41">
+        <v>11.5</v>
+      </c>
+      <c r="E63" s="9">
+        <f t="shared" si="14"/>
+        <v>74.75</v>
+      </c>
+      <c r="F63" s="9">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="G63" s="39">
+        <v>112.92</v>
+      </c>
+      <c r="H63" s="68" cm="1">
+        <f t="array" ref="H63">_xlfn.CEILING.MATH(_xlfn.SWITCH(J63, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I63" s="38">
+        <f t="shared" si="16"/>
+        <v>2174.7200000000003</v>
+      </c>
+      <c r="J63" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="41">
         <v>10</v>
       </c>
-      <c r="G57" s="41">
-        <v>0.5</v>
-      </c>
-      <c r="H57" s="49"/>
-      <c r="I57" s="38">
-        <f t="shared" si="12"/>
-        <v>70</v>
-      </c>
-      <c r="J57" s="73"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="B58" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="46">
+      <c r="D64" s="41">
         <v>20</v>
       </c>
-      <c r="D58" s="46">
-        <v>16.5</v>
-      </c>
-      <c r="E58" s="9">
+      <c r="E64" s="9">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
         <f t="shared" si="13"/>
-        <v>330</v>
-      </c>
-      <c r="F58" s="9">
-        <f t="shared" si="11"/>
-        <v>33</v>
-      </c>
-      <c r="G58" s="41"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="38">
-        <f t="shared" si="12"/>
-        <v>198</v>
-      </c>
-      <c r="J58" s="73"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="B59" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="46">
-        <v>6.5</v>
-      </c>
-      <c r="D59" s="46">
-        <v>11.5</v>
-      </c>
-      <c r="E59" s="9">
-        <f t="shared" si="13"/>
-        <v>74.75</v>
-      </c>
-      <c r="F59" s="9">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="G59" s="41">
-        <v>84.64</v>
-      </c>
-      <c r="H59" s="49"/>
-      <c r="I59" s="38">
-        <f t="shared" si="12"/>
-        <v>1402.24</v>
-      </c>
-      <c r="J59" s="73"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="B60" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C60" s="46">
-        <v>6.5</v>
-      </c>
-      <c r="D60" s="46">
-        <v>11.5</v>
-      </c>
-      <c r="E60" s="9">
-        <f t="shared" si="13"/>
-        <v>74.75</v>
-      </c>
-      <c r="F60" s="9">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="G60" s="41">
-        <v>91.78</v>
-      </c>
-      <c r="H60" s="49"/>
-      <c r="I60" s="38">
-        <f t="shared" si="12"/>
-        <v>1516.48</v>
-      </c>
-      <c r="J60" s="73"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C61" s="46">
-        <v>6.5</v>
-      </c>
-      <c r="D61" s="46">
-        <v>11.5</v>
-      </c>
-      <c r="E61" s="9">
-        <f t="shared" si="13"/>
-        <v>74.75</v>
-      </c>
-      <c r="F61" s="9">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="G61" s="41">
-        <v>98.78</v>
-      </c>
-      <c r="H61" s="49"/>
-      <c r="I61" s="38">
-        <f t="shared" si="12"/>
-        <v>1628.48</v>
-      </c>
-      <c r="J61" s="73"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="46">
-        <v>6.5</v>
-      </c>
-      <c r="D62" s="46">
-        <v>11.5</v>
-      </c>
-      <c r="E62" s="9">
-        <f t="shared" si="13"/>
-        <v>74.75</v>
-      </c>
-      <c r="F62" s="9">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="G62" s="41">
-        <v>105.92</v>
-      </c>
-      <c r="H62" s="49"/>
-      <c r="I62" s="38">
-        <f t="shared" si="12"/>
-        <v>1742.72</v>
-      </c>
-      <c r="J62" s="73"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C63" s="46">
-        <v>6.5</v>
-      </c>
-      <c r="D63" s="46">
-        <v>11.5</v>
-      </c>
-      <c r="E63" s="9">
-        <f t="shared" si="13"/>
-        <v>74.75</v>
-      </c>
-      <c r="F63" s="9">
-        <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="G63" s="41">
-        <v>112.92</v>
-      </c>
-      <c r="H63" s="49"/>
-      <c r="I63" s="38">
-        <f t="shared" si="12"/>
-        <v>1854.72</v>
-      </c>
-      <c r="J63" s="73"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="46">
-        <v>10</v>
-      </c>
-      <c r="D64" s="46">
         <v>20</v>
       </c>
-      <c r="E64" s="9">
-        <f t="shared" si="13"/>
-        <v>200</v>
-      </c>
-      <c r="F64" s="9">
-        <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="G64" s="41">
+      <c r="G64" s="39">
         <v>17.5</v>
       </c>
-      <c r="H64" s="49"/>
+      <c r="H64" s="68" cm="1">
+        <f t="array" ref="H64">_xlfn.CEILING.MATH(_xlfn.SWITCH(J64, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I64" s="38">
-        <f t="shared" si="12"/>
-        <v>820</v>
-      </c>
-      <c r="J64" s="73"/>
+        <f t="shared" si="16"/>
+        <v>1500</v>
+      </c>
+      <c r="J64" s="72" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
@@ -3293,10 +3672,10 @@
         <v>140</v>
       </c>
       <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
+      <c r="H65" s="67"/>
       <c r="I65" s="29">
         <f>SUM(I47:I64)</f>
-        <v>11440.159999999998</v>
+        <v>16980.16</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -3307,51 +3686,56 @@
       <c r="E66" s="29"/>
       <c r="F66" s="29"/>
       <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
+      <c r="H66" s="67"/>
       <c r="I66" s="29"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="45" t="s">
+      <c r="A67" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C67" s="46">
+      <c r="C67" s="41">
         <v>6.5</v>
       </c>
-      <c r="D67" s="46">
+      <c r="D67" s="41">
         <v>11.5</v>
       </c>
       <c r="E67" s="9">
-        <f t="shared" ref="E67" si="14">C67*D67</f>
+        <f t="shared" ref="E67" si="17">C67*D67</f>
         <v>74.75</v>
       </c>
       <c r="F67" s="9">
-        <f t="shared" ref="F67" si="15">ROUNDUP(E67/10,0)</f>
+        <f t="shared" ref="F67" si="18">ROUNDUP(E67/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G67" s="41">
+      <c r="G67" s="39">
         <v>32</v>
       </c>
-      <c r="H67" s="49"/>
+      <c r="H67" s="68" cm="1">
+        <f t="array" ref="H67">_xlfn.CEILING.MATH(_xlfn.SWITCH(J67, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I67" s="38">
-        <f t="shared" ref="I67" si="16">2*F67*(G67+H67+3)</f>
-        <v>560</v>
-      </c>
-      <c r="J67" s="73"/>
+        <f>2*F67*(G67+H67+6)</f>
+        <v>880</v>
+      </c>
+      <c r="J67" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="45" t="s">
+      <c r="B68" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="46">
+      <c r="C68" s="41">
         <v>6.5</v>
       </c>
-      <c r="D68" s="46">
+      <c r="D68" s="41">
         <v>11.5</v>
       </c>
       <c r="E68" s="9">
@@ -3362,57 +3746,62 @@
         <f>ROUNDUP(E68/10,0)</f>
         <v>8</v>
       </c>
-      <c r="G68" s="41">
+      <c r="G68" s="39">
         <v>27</v>
       </c>
-      <c r="H68" s="49"/>
+      <c r="H68" s="68" cm="1">
+        <f t="array" ref="H68">_xlfn.CEILING.MATH(_xlfn.SWITCH(J68, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
       <c r="I68" s="38">
-        <f>2*F68*(G68+H68+3)</f>
-        <v>480</v>
-      </c>
-      <c r="J68" s="73"/>
+        <f>2*F68*(G68+H68+6)</f>
+        <v>800</v>
+      </c>
+      <c r="J68" s="72" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="48" t="s">
+      <c r="A69" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="60" t="s">
+      <c r="B69" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="62"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="48"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="63"/>
-      <c r="C70" s="64"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="64"/>
-      <c r="J70" s="65"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="51"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="45" t="s">
+      <c r="A71" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="46">
+      <c r="C71" s="41">
         <v>10</v>
       </c>
-      <c r="D71" s="46">
+      <c r="D71" s="41">
         <v>20</v>
       </c>
       <c r="E71" s="9">
@@ -3423,495 +3812,570 @@
         <f>ROUNDUP(E71/10,0)</f>
         <v>20</v>
       </c>
-      <c r="G71" s="41">
+      <c r="G71" s="39">
         <v>0.5</v>
       </c>
-      <c r="H71" s="49"/>
+      <c r="H71" s="68" cm="1">
+        <f t="array" ref="H71">_xlfn.CEILING.MATH(_xlfn.SWITCH(J71, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>14</v>
+      </c>
       <c r="I71" s="38">
-        <f>2*F71*(G71+H71+3)</f>
+        <f>2*F71*(G71+H71+6)</f>
+        <v>820</v>
+      </c>
+      <c r="J71" s="72" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="39">
+        <v>5</v>
+      </c>
+      <c r="D72" s="39">
+        <v>14</v>
+      </c>
+      <c r="E72" s="9">
+        <f t="shared" ref="E72:E73" si="19">C72*D72</f>
+        <v>70</v>
+      </c>
+      <c r="F72" s="9">
+        <f t="shared" ref="F72:F88" si="20">ROUNDUP(E72/10,0)</f>
+        <v>7</v>
+      </c>
+      <c r="G72" s="39">
+        <v>56.07</v>
+      </c>
+      <c r="H72" s="68" cm="1">
+        <f t="array" ref="H72">_xlfn.CEILING.MATH(_xlfn.SWITCH(J72, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>17</v>
+      </c>
+      <c r="I72" s="38">
+        <f t="shared" ref="I72:I74" si="21">2*F72*(G72+H72+6)</f>
+        <v>1106.98</v>
+      </c>
+      <c r="J72" s="72" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="39">
+        <v>9</v>
+      </c>
+      <c r="D73" s="39">
+        <v>6.5</v>
+      </c>
+      <c r="E73" s="9">
+        <f t="shared" si="19"/>
+        <v>58.5</v>
+      </c>
+      <c r="F73" s="9">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="G73" s="39">
+        <v>12.54</v>
+      </c>
+      <c r="H73" s="68" cm="1">
+        <f t="array" ref="H73">_xlfn.CEILING.MATH(_xlfn.SWITCH(J73, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I73" s="38">
+        <f t="shared" si="21"/>
+        <v>438.48</v>
+      </c>
+      <c r="J73" s="72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C74" s="39">
+        <v>6.5</v>
+      </c>
+      <c r="D74" s="39">
+        <v>9</v>
+      </c>
+      <c r="E74" s="9">
+        <f t="shared" ref="E74:E80" si="22">C74*D74</f>
+        <v>58.5</v>
+      </c>
+      <c r="F74" s="9">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="G74" s="39">
+        <v>21.88</v>
+      </c>
+      <c r="H74" s="68" cm="1">
+        <f t="array" ref="H74">_xlfn.CEILING.MATH(_xlfn.SWITCH(J74, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I74" s="38">
+        <f t="shared" si="21"/>
+        <v>550.55999999999995</v>
+      </c>
+      <c r="J74" s="72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="60"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="39">
+        <v>4</v>
+      </c>
+      <c r="D76" s="39">
+        <v>4</v>
+      </c>
+      <c r="E76" s="9">
+        <f t="shared" si="22"/>
+        <v>16</v>
+      </c>
+      <c r="F76" s="9">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="G76" s="39">
+        <v>11.5</v>
+      </c>
+      <c r="H76" s="68" cm="1">
+        <f t="array" ref="H76">_xlfn.CEILING.MATH(_xlfn.SWITCH(J76, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
+      <c r="I76" s="38">
+        <f>2*F76*(G76+H76+6)</f>
+        <v>122</v>
+      </c>
+      <c r="J76" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" s="39">
+        <v>4.5</v>
+      </c>
+      <c r="D77" s="39">
+        <v>9.5</v>
+      </c>
+      <c r="E77" s="9">
+        <f t="shared" si="22"/>
+        <v>42.75</v>
+      </c>
+      <c r="F77" s="9">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="G77" s="39">
+        <v>17</v>
+      </c>
+      <c r="H77" s="68" cm="1">
+        <f t="array" ref="H77">_xlfn.CEILING.MATH(_xlfn.SWITCH(J77, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
+      <c r="I77" s="38">
+        <f t="shared" ref="I77:I80" si="23">2*F77*(G77+H77+6)</f>
+        <v>360</v>
+      </c>
+      <c r="J77" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C78" s="39">
+        <v>4.5</v>
+      </c>
+      <c r="D78" s="39">
+        <v>9.5</v>
+      </c>
+      <c r="E78" s="9">
+        <f t="shared" si="22"/>
+        <v>42.75</v>
+      </c>
+      <c r="F78" s="9">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="G78" s="39">
+        <v>22.5</v>
+      </c>
+      <c r="H78" s="68" cm="1">
+        <f t="array" ref="H78">_xlfn.CEILING.MATH(_xlfn.SWITCH(J78, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
+      <c r="I78" s="38">
+        <f t="shared" si="23"/>
+        <v>415</v>
+      </c>
+      <c r="J78" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="39">
+        <v>4.5</v>
+      </c>
+      <c r="D79" s="39">
+        <v>9.5</v>
+      </c>
+      <c r="E79" s="9">
+        <f t="shared" si="22"/>
+        <v>42.75</v>
+      </c>
+      <c r="F79" s="9">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="G79" s="39">
+        <v>28</v>
+      </c>
+      <c r="H79" s="68" cm="1">
+        <f t="array" ref="H79">_xlfn.CEILING.MATH(_xlfn.SWITCH(J79, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
+      <c r="I79" s="38">
+        <f t="shared" si="23"/>
+        <v>470</v>
+      </c>
+      <c r="J79" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="39">
+        <v>4.5</v>
+      </c>
+      <c r="D80" s="39">
+        <v>9.5</v>
+      </c>
+      <c r="E80" s="9">
+        <f t="shared" si="22"/>
+        <v>42.75</v>
+      </c>
+      <c r="F80" s="9">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="G80" s="39">
+        <v>33.5</v>
+      </c>
+      <c r="H80" s="68" cm="1">
+        <f t="array" ref="H80">_xlfn.CEILING.MATH(_xlfn.SWITCH(J80, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>13</v>
+      </c>
+      <c r="I80" s="38">
+        <f t="shared" si="23"/>
+        <v>525</v>
+      </c>
+      <c r="J80" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="53"/>
+      <c r="D81" s="53"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="53"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="54"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="J71" s="73"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B72" s="45" t="s">
+      <c r="B82" s="55"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="57"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="B83" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="41">
-        <v>5</v>
-      </c>
-      <c r="D72" s="41">
-        <v>14</v>
-      </c>
-      <c r="E72" s="9">
-        <f t="shared" ref="E72:E73" si="17">C72*D72</f>
-        <v>70</v>
-      </c>
-      <c r="F72" s="9">
-        <f t="shared" ref="F72:F88" si="18">ROUNDUP(E72/10,0)</f>
+      <c r="C83" s="39">
+        <v>6.5</v>
+      </c>
+      <c r="D83" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E83" s="9">
+        <f t="shared" ref="E83:E88" si="24">C83*D83</f>
+        <v>81.25</v>
+      </c>
+      <c r="F83" s="9">
+        <f t="shared" si="20"/>
+        <v>9</v>
+      </c>
+      <c r="G83" s="39">
+        <v>10.5</v>
+      </c>
+      <c r="H83" s="68" cm="1">
+        <f t="array" ref="H83">_xlfn.CEILING.MATH(_xlfn.SWITCH(J83, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I83" s="38">
+        <f>2*F83*(G83+H83+6)</f>
+        <v>621</v>
+      </c>
+      <c r="J83" s="72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="39">
+        <v>6.5</v>
+      </c>
+      <c r="D84" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E84" s="9">
+        <f t="shared" si="24"/>
+        <v>81.25</v>
+      </c>
+      <c r="F84" s="9">
+        <f t="shared" si="20"/>
+        <v>9</v>
+      </c>
+      <c r="G84" s="39">
+        <v>17.5</v>
+      </c>
+      <c r="H84" s="68" cm="1">
+        <f t="array" ref="H84">_xlfn.CEILING.MATH(_xlfn.SWITCH(J84, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I84" s="38">
+        <f t="shared" ref="I84:I88" si="25">2*F84*(G84+H84+6)</f>
+        <v>747</v>
+      </c>
+      <c r="J84" s="72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" s="39">
+        <v>5.5</v>
+      </c>
+      <c r="D85" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E85" s="9">
+        <f t="shared" si="24"/>
+        <v>68.75</v>
+      </c>
+      <c r="F85" s="9">
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
-      <c r="G72" s="41">
-        <v>56.07</v>
-      </c>
-      <c r="H72" s="49"/>
-      <c r="I72" s="38">
-        <f t="shared" ref="I72:I88" si="19">2*F72*(G72+H72+3)</f>
-        <v>826.98</v>
-      </c>
-      <c r="J72" s="73"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B73" s="45" t="s">
+      <c r="G85" s="39">
+        <v>23.5</v>
+      </c>
+      <c r="H85" s="68" cm="1">
+        <f t="array" ref="H85">_xlfn.CEILING.MATH(_xlfn.SWITCH(J85, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I85" s="38">
+        <f t="shared" si="25"/>
+        <v>665</v>
+      </c>
+      <c r="J85" s="72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C73" s="41">
-        <v>9</v>
-      </c>
-      <c r="D73" s="41">
-        <v>6.5</v>
-      </c>
-      <c r="E73" s="9">
-        <f t="shared" si="17"/>
-        <v>58.5</v>
-      </c>
-      <c r="F73" s="9">
-        <f t="shared" si="18"/>
-        <v>6</v>
-      </c>
-      <c r="G73" s="41">
-        <v>12.54</v>
-      </c>
-      <c r="H73" s="49"/>
-      <c r="I73" s="38">
-        <f t="shared" si="19"/>
-        <v>186.48</v>
-      </c>
-      <c r="J73" s="73"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B74" s="45" t="s">
+      <c r="C86" s="39">
+        <v>5.5</v>
+      </c>
+      <c r="D86" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E86" s="9">
+        <f t="shared" si="24"/>
+        <v>68.75</v>
+      </c>
+      <c r="F86" s="9">
+        <f t="shared" si="20"/>
+        <v>7</v>
+      </c>
+      <c r="G86" s="39">
+        <v>29.5</v>
+      </c>
+      <c r="H86" s="68" cm="1">
+        <f t="array" ref="H86">_xlfn.CEILING.MATH(_xlfn.SWITCH(J86, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I86" s="38">
+        <f t="shared" si="25"/>
+        <v>749</v>
+      </c>
+      <c r="J86" s="72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C74" s="41">
-        <v>6.5</v>
-      </c>
-      <c r="D74" s="41">
-        <v>9</v>
-      </c>
-      <c r="E74" s="9">
-        <f t="shared" ref="E74:E80" si="20">C74*D74</f>
-        <v>58.5</v>
-      </c>
-      <c r="F74" s="9">
-        <f t="shared" si="18"/>
-        <v>6</v>
-      </c>
-      <c r="G74" s="41">
-        <v>21.88</v>
-      </c>
-      <c r="H74" s="49"/>
-      <c r="I74" s="38">
-        <f t="shared" si="19"/>
-        <v>298.56</v>
-      </c>
-      <c r="J74" s="73"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="B75" s="51" t="s">
+      <c r="C87" s="39">
+        <v>5.5</v>
+      </c>
+      <c r="D87" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E87" s="9">
+        <f t="shared" si="24"/>
+        <v>68.75</v>
+      </c>
+      <c r="F87" s="9">
+        <f t="shared" si="20"/>
+        <v>7</v>
+      </c>
+      <c r="G87" s="39">
+        <v>35.5</v>
+      </c>
+      <c r="H87" s="68" cm="1">
+        <f t="array" ref="H87">_xlfn.CEILING.MATH(_xlfn.SWITCH(J87, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
+      <c r="I87" s="38">
+        <f t="shared" si="25"/>
+        <v>833</v>
+      </c>
+      <c r="J87" s="72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="53"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B76" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C76" s="41">
-        <v>4</v>
-      </c>
-      <c r="D76" s="41">
-        <v>4</v>
-      </c>
-      <c r="E76" s="9">
+      <c r="C88" s="39">
+        <v>5.5</v>
+      </c>
+      <c r="D88" s="39">
+        <v>12.5</v>
+      </c>
+      <c r="E88" s="9">
+        <f t="shared" si="24"/>
+        <v>68.75</v>
+      </c>
+      <c r="F88" s="9">
         <f t="shared" si="20"/>
-        <v>16</v>
-      </c>
-      <c r="F76" s="9">
-        <f t="shared" si="18"/>
-        <v>2</v>
-      </c>
-      <c r="G76" s="41">
-        <v>11.5</v>
-      </c>
-      <c r="H76" s="49"/>
-      <c r="I76" s="38">
-        <f t="shared" si="19"/>
-        <v>58</v>
-      </c>
-      <c r="J76" s="73"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B77" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" s="41">
-        <v>4.5</v>
-      </c>
-      <c r="D77" s="41">
-        <v>9.5</v>
-      </c>
-      <c r="E77" s="9">
-        <f t="shared" si="20"/>
-        <v>42.75</v>
-      </c>
-      <c r="F77" s="9">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="G77" s="41">
-        <v>17</v>
-      </c>
-      <c r="H77" s="49"/>
-      <c r="I77" s="38">
-        <f t="shared" si="19"/>
-        <v>200</v>
-      </c>
-      <c r="J77" s="73"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B78" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C78" s="41">
-        <v>4.5</v>
-      </c>
-      <c r="D78" s="41">
-        <v>9.5</v>
-      </c>
-      <c r="E78" s="9">
-        <f t="shared" si="20"/>
-        <v>42.75</v>
-      </c>
-      <c r="F78" s="9">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="G78" s="41">
-        <v>22.5</v>
-      </c>
-      <c r="H78" s="49"/>
-      <c r="I78" s="38">
-        <f t="shared" si="19"/>
-        <v>255</v>
-      </c>
-      <c r="J78" s="73"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="B79" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C79" s="41">
-        <v>4.5</v>
-      </c>
-      <c r="D79" s="41">
-        <v>9.5</v>
-      </c>
-      <c r="E79" s="9">
-        <f t="shared" si="20"/>
-        <v>42.75</v>
-      </c>
-      <c r="F79" s="9">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="G79" s="41">
-        <v>28</v>
-      </c>
-      <c r="H79" s="49"/>
-      <c r="I79" s="38">
-        <f t="shared" si="19"/>
-        <v>310</v>
-      </c>
-      <c r="J79" s="73"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="B80" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C80" s="41">
-        <v>4.5</v>
-      </c>
-      <c r="D80" s="41">
-        <v>9.5</v>
-      </c>
-      <c r="E80" s="9">
-        <f t="shared" si="20"/>
-        <v>42.75</v>
-      </c>
-      <c r="F80" s="9">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="G80" s="41">
-        <v>33.5</v>
-      </c>
-      <c r="H80" s="49"/>
-      <c r="I80" s="38">
-        <f t="shared" si="19"/>
-        <v>365</v>
-      </c>
-      <c r="J80" s="73"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="B81" s="54" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="55"/>
-      <c r="G81" s="55"/>
-      <c r="H81" s="55"/>
-      <c r="I81" s="55"/>
-      <c r="J81" s="56"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58"/>
-      <c r="J82" s="59"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B83" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="41">
-        <v>6.5</v>
-      </c>
-      <c r="D83" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E83" s="9">
-        <f t="shared" ref="E83:E88" si="21">C83*D83</f>
-        <v>81.25</v>
-      </c>
-      <c r="F83" s="9">
-        <f t="shared" si="18"/>
-        <v>9</v>
-      </c>
-      <c r="G83" s="41">
-        <v>10.5</v>
-      </c>
-      <c r="H83" s="49"/>
-      <c r="I83" s="38">
-        <f t="shared" si="19"/>
-        <v>243</v>
-      </c>
-      <c r="J83" s="73"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="B84" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C84" s="41">
-        <v>6.5</v>
-      </c>
-      <c r="D84" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E84" s="9">
-        <f t="shared" si="21"/>
-        <v>81.25</v>
-      </c>
-      <c r="F84" s="9">
-        <f t="shared" si="18"/>
-        <v>9</v>
-      </c>
-      <c r="G84" s="41">
-        <v>17.5</v>
-      </c>
-      <c r="H84" s="49"/>
-      <c r="I84" s="38">
-        <f t="shared" si="19"/>
-        <v>369</v>
-      </c>
-      <c r="J84" s="73"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C85" s="41">
-        <v>5.5</v>
-      </c>
-      <c r="D85" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E85" s="9">
-        <f t="shared" si="21"/>
-        <v>68.75</v>
-      </c>
-      <c r="F85" s="9">
-        <f t="shared" si="18"/>
         <v>7</v>
       </c>
-      <c r="G85" s="41">
-        <v>23.5</v>
-      </c>
-      <c r="H85" s="49"/>
-      <c r="I85" s="38">
-        <f t="shared" si="19"/>
-        <v>371</v>
-      </c>
-      <c r="J85" s="73"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="B86" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C86" s="41">
-        <v>5.5</v>
-      </c>
-      <c r="D86" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E86" s="9">
-        <f t="shared" si="21"/>
-        <v>68.75</v>
-      </c>
-      <c r="F86" s="9">
-        <f t="shared" si="18"/>
-        <v>7</v>
-      </c>
-      <c r="G86" s="41">
-        <v>29.5</v>
-      </c>
-      <c r="H86" s="49"/>
-      <c r="I86" s="38">
-        <f t="shared" si="19"/>
-        <v>455</v>
-      </c>
-      <c r="J86" s="73"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="B87" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C87" s="41">
-        <v>5.5</v>
-      </c>
-      <c r="D87" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E87" s="9">
-        <f t="shared" si="21"/>
-        <v>68.75</v>
-      </c>
-      <c r="F87" s="9">
-        <f t="shared" si="18"/>
-        <v>7</v>
-      </c>
-      <c r="G87" s="41">
-        <v>35.5</v>
-      </c>
-      <c r="H87" s="49"/>
-      <c r="I87" s="38">
-        <f t="shared" si="19"/>
-        <v>539</v>
-      </c>
-      <c r="J87" s="73"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="B88" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C88" s="41">
-        <v>5.5</v>
-      </c>
-      <c r="D88" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="E88" s="9">
-        <f t="shared" si="21"/>
-        <v>68.75</v>
-      </c>
-      <c r="F88" s="9">
-        <f t="shared" si="18"/>
-        <v>7</v>
-      </c>
-      <c r="G88" s="41">
+      <c r="G88" s="39">
         <v>41.5</v>
       </c>
-      <c r="H88" s="49"/>
+      <c r="H88" s="68" cm="1">
+        <f t="array" ref="H88">_xlfn.CEILING.MATH(_xlfn.SWITCH(J88, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
+        <v>18</v>
+      </c>
       <c r="I88" s="38">
-        <f t="shared" si="19"/>
-        <v>623</v>
-      </c>
-      <c r="J88" s="73"/>
+        <f t="shared" si="25"/>
+        <v>917</v>
+      </c>
+      <c r="J88" s="72" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
@@ -3926,10 +4390,10 @@
         <v>123</v>
       </c>
       <c r="G89" s="29"/>
-      <c r="H89" s="29"/>
+      <c r="H89" s="67"/>
       <c r="I89" s="29">
         <f>SUM(I67:I88)</f>
-        <v>6280.02</v>
+        <v>11020.02</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -3942,31 +4406,31 @@
       <c r="E91" s="37"/>
       <c r="F91" s="37">
         <f>F89+F65+F45+F20</f>
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
+      <c r="H91" s="69"/>
       <c r="I91" s="37">
         <f>I89+I65+I45+I20</f>
-        <v>19370.18</v>
+        <v>57307.380000000005</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H93" s="29" t="s">
+      <c r="H93" s="67" t="s">
         <v>68</v>
       </c>
       <c r="I93" s="29">
         <f>ROUNDUP(ROUNDUP($I$91/305,0)*1.1,0)</f>
-        <v>71</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H94" s="29" t="s">
+      <c r="H94" s="67" t="s">
         <v>69</v>
       </c>
       <c r="I94" s="29">
         <f>ROUNDUP($I$91/2000,0)</f>
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -3975,43 +4439,51 @@
       </c>
       <c r="C96" s="37">
         <f>I91/(F91*2)</f>
-        <v>18.002026022304833</v>
+        <v>53.358826815642459</v>
       </c>
       <c r="E96" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="39" t="s">
+      <c r="A98" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B98" s="39"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
+      <c r="B98" s="74"/>
+      <c r="C98" s="74"/>
+      <c r="D98" s="74"/>
+      <c r="E98" s="74"/>
+      <c r="F98" s="74"/>
+      <c r="G98" s="74"/>
+      <c r="H98" s="74"/>
     </row>
     <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" s="40" t="s">
+      <c r="A99" s="75" t="s">
         <v>72</v>
       </c>
+      <c r="B99" s="75"/>
     </row>
     <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="42" t="s">
+      <c r="A100" s="76" t="s">
         <v>73</v>
       </c>
+      <c r="B100" s="76"/>
     </row>
     <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="44" t="s">
+      <c r="A101" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="B101" s="44"/>
-      <c r="C101" s="44"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
+    <mergeCell ref="A98:H98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="B55:J56"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B81:J82"/>
@@ -4043,6 +4515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AA7270-A5B3-4391-AFAC-44F660C9B196}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4081,7 +4554,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
@@ -4100,12 +4573,12 @@
       <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="64" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="70"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="10">
         <v>1</v>
       </c>
@@ -4120,10 +4593,10 @@
       <c r="G3" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="70"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -4140,10 +4613,10 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="70"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="70"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="10">
         <v>1</v>
       </c>
@@ -4154,10 +4627,10 @@
       <c r="G5" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="70"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="70"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="10">
         <v>1</v>
       </c>
@@ -4174,10 +4647,10 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="70"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="70"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="10">
         <v>1</v>
       </c>
@@ -4192,10 +4665,10 @@
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="70"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="70"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="24">
         <v>1</v>
       </c>
@@ -4212,10 +4685,10 @@
       <c r="G8" s="5">
         <v>50</v>
       </c>
-      <c r="H8" s="70"/>
+      <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="70"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -4225,10 +4698,10 @@
       <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="70"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="70"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -4241,10 +4714,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="70"/>
+      <c r="H10" s="65"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="70"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="10">
         <v>1</v>
       </c>
@@ -4255,10 +4728,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="70"/>
+      <c r="H11" s="65"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="70"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="10">
         <v>1</v>
       </c>
@@ -4269,10 +4742,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="70"/>
+      <c r="H12" s="65"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="70"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="10">
         <v>1</v>
       </c>
@@ -4283,10 +4756,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="70"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="10">
         <v>1</v>
       </c>
@@ -4295,10 +4768,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="70"/>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="70"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="10">
         <v>1</v>
       </c>
@@ -4309,10 +4782,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="70"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="70"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="10">
         <v>1</v>
       </c>
@@ -4323,10 +4796,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="70"/>
+      <c r="H16" s="65"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="24">
         <v>7</v>
       </c>
@@ -4335,70 +4808,70 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="65"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="70"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="24"/>
       <c r="C18" s="35"/>
       <c r="D18" s="10"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="70"/>
+      <c r="H18" s="65"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="70"/>
+      <c r="A19" s="65"/>
       <c r="B19" s="24"/>
       <c r="C19" s="35"/>
       <c r="D19" s="10"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="70"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="24"/>
       <c r="C20" s="35"/>
       <c r="D20" s="10"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="70"/>
+      <c r="H20" s="65"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="70"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="24"/>
       <c r="C21" s="35"/>
       <c r="D21" s="10"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="65"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="70"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="24"/>
       <c r="C22" s="35"/>
       <c r="D22" s="10"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="70"/>
+      <c r="H22" s="65"/>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="70"/>
+      <c r="A23" s="65"/>
       <c r="B23" s="24"/>
       <c r="C23" s="36"/>
       <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="70"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="10">
         <v>1</v>
       </c>
@@ -4409,10 +4882,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="65"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="70"/>
+      <c r="A25" s="65"/>
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -4423,10 +4896,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="70"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="70"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="10">
         <v>1</v>
       </c>
@@ -4437,10 +4910,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="70"/>
+      <c r="H26" s="65"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="70"/>
+      <c r="A27" s="65"/>
       <c r="B27" s="10">
         <v>1</v>
       </c>
@@ -4449,10 +4922,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="70"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="70"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="10">
         <v>1</v>
       </c>
@@ -4461,10 +4934,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="70"/>
+      <c r="H28" s="65"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="70"/>
+      <c r="A29" s="65"/>
       <c r="B29" s="10">
         <v>1</v>
       </c>
@@ -4480,10 +4953,10 @@
       <c r="G29" s="5">
         <v>50</v>
       </c>
-      <c r="H29" s="70"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="70"/>
+      <c r="A30" s="65"/>
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -4494,40 +4967,40 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="70"/>
+      <c r="H30" s="65"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="70"/>
+      <c r="A31" s="65"/>
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="70"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="70"/>
+      <c r="A32" s="65"/>
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="70"/>
+      <c r="H32" s="65"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="70"/>
+      <c r="A33" s="65"/>
       <c r="B33" s="10"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="70"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="70"/>
+      <c r="A34" s="65"/>
       <c r="B34" s="10">
         <v>1</v>
       </c>
@@ -4540,10 +5013,10 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="70"/>
+      <c r="H34" s="65"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="70"/>
+      <c r="A35" s="65"/>
       <c r="B35" s="10">
         <v>1</v>
       </c>
@@ -4554,10 +5027,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="70"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="70"/>
+      <c r="A36" s="65"/>
       <c r="B36" s="10">
         <v>1</v>
       </c>
@@ -4574,10 +5047,10 @@
       <c r="G36" s="5">
         <v>200</v>
       </c>
-      <c r="H36" s="70"/>
+      <c r="H36" s="65"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="70"/>
+      <c r="A37" s="65"/>
       <c r="B37" s="10">
         <v>2</v>
       </c>
@@ -4588,10 +5061,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="70"/>
+      <c r="H37" s="65"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="70"/>
+      <c r="A38" s="65"/>
       <c r="B38" s="10">
         <v>4</v>
       </c>
@@ -4606,10 +5079,10 @@
       <c r="G38" s="5">
         <v>250</v>
       </c>
-      <c r="H38" s="70"/>
+      <c r="H38" s="65"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="70"/>
+      <c r="A39" s="65"/>
       <c r="B39" s="10">
         <v>4</v>
       </c>
@@ -4624,37 +5097,37 @@
       <c r="G39" s="5">
         <v>250</v>
       </c>
-      <c r="H39" s="70"/>
+      <c r="H39" s="65"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="70"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="70"/>
+      <c r="H40" s="65"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="70"/>
+      <c r="A41" s="65"/>
       <c r="B41" s="10"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="70"/>
+      <c r="H41" s="65"/>
     </row>
     <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="70"/>
+      <c r="A42" s="65"/>
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="70"/>
+      <c r="H42" s="65"/>
     </row>
     <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
@@ -4862,6 +5335,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B9A1CC-C4FB-41AD-85DB-3839BA2B7BB9}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -4871,6 +5345,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A71F13F-E947-4C1E-BDE3-9A5BE07FD910}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -4879,6 +5354,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E4DE2CC379442A4D8483D9D7B1BA3E35" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3cbd871ac436bbcd94953c6f74650012">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b380a0-b262-4a13-9203-497a21b8eee5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f82e0ce2898406bfa558450728792a3e" ns2:_="">
     <xsd:import namespace="a1b380a0-b262-4a13-9203-497a21b8eee5"/>
@@ -5016,22 +5506,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5047,21 +5539,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC6BDD-C523-43C3-8A25-2ACF385A89BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD9531D-7E98-4B24-81D9-CBBB9097B79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7CA0D7A-53D0-40E5-91E0-784DA3F57821}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="170">
   <si>
     <t>Spatiu ocupat in U</t>
   </si>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>From your design</t>
-  </si>
-  <si>
-    <t>should be between 30 and 60</t>
   </si>
   <si>
     <t>From detailed calcullus of prototype room/rooms</t>
@@ -1186,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1239,6 +1236,26 @@
     <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1299,25 +1316,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1666,9 +1666,9 @@
     <col min="4" max="5" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="50" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" style="73" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="53" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1693,19 +1693,19 @@
       <c r="G1" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="46" t="s">
         <v>53</v>
       </c>
       <c r="I1" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="71" t="s">
-        <v>158</v>
+      <c r="J1" s="51" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>54</v>
@@ -1735,13 +1735,13 @@
         <f>2*F2*(G2+H2+6)</f>
         <v>352.79999999999995</v>
       </c>
-      <c r="J2" s="72" t="s">
-        <v>159</v>
+      <c r="J2" s="52" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="40" t="s">
         <v>54</v>
@@ -1771,29 +1771,29 @@
         <f>2*F3*(G3+H3+6)</f>
         <v>325.32</v>
       </c>
-      <c r="J3" s="72" t="s">
-        <v>160</v>
+      <c r="J3" s="52" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>54</v>
@@ -1823,13 +1823,13 @@
         <f>2*F5*(G5+H5+6)</f>
         <v>388.2</v>
       </c>
-      <c r="J5" s="72" t="s">
-        <v>161</v>
+      <c r="J5" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="40" t="s">
         <v>54</v>
@@ -1859,13 +1859,13 @@
         <f t="shared" ref="I6:I9" si="2">2*F6*(G6+H6+6)</f>
         <v>448.2</v>
       </c>
-      <c r="J6" s="72" t="s">
-        <v>161</v>
+      <c r="J6" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="40" t="s">
         <v>54</v>
@@ -1895,13 +1895,13 @@
         <f t="shared" si="2"/>
         <v>505.3</v>
       </c>
-      <c r="J7" s="72" t="s">
-        <v>161</v>
+      <c r="J7" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>54</v>
@@ -1931,13 +1931,13 @@
         <f t="shared" si="2"/>
         <v>565.29999999999995</v>
       </c>
-      <c r="J8" s="72" t="s">
-        <v>161</v>
+      <c r="J8" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>54</v>
@@ -1967,43 +1967,43 @@
         <f t="shared" si="2"/>
         <v>622.4</v>
       </c>
-      <c r="J9" s="72" t="s">
-        <v>161</v>
+      <c r="J9" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="48"/>
+        <v>83</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="51"/>
+        <v>84</v>
+      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>54</v>
@@ -2033,13 +2033,13 @@
         <f>2*F12*(G12+H12+6)</f>
         <v>350</v>
       </c>
-      <c r="J12" s="72" t="s">
-        <v>162</v>
+      <c r="J12" s="52" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="40" t="s">
         <v>54</v>
@@ -2069,13 +2069,13 @@
         <f t="shared" ref="I13:I19" si="3">2*F13*(G13+H13+6)</f>
         <v>2178</v>
       </c>
-      <c r="J13" s="72" t="s">
-        <v>163</v>
+      <c r="J13" s="52" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="40" t="s">
         <v>54</v>
@@ -2105,13 +2105,13 @@
         <f t="shared" si="3"/>
         <v>1722.24</v>
       </c>
-      <c r="J14" s="72" t="s">
-        <v>164</v>
+      <c r="J14" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>54</v>
@@ -2141,13 +2141,13 @@
         <f t="shared" si="3"/>
         <v>1836.48</v>
       </c>
-      <c r="J15" s="72" t="s">
-        <v>164</v>
+      <c r="J15" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" s="40" t="s">
         <v>54</v>
@@ -2177,13 +2177,13 @@
         <f t="shared" si="3"/>
         <v>1948.48</v>
       </c>
-      <c r="J16" s="72" t="s">
-        <v>164</v>
+      <c r="J16" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="40" t="s">
         <v>54</v>
@@ -2213,13 +2213,13 @@
         <f t="shared" si="3"/>
         <v>2062.7200000000003</v>
       </c>
-      <c r="J17" s="72" t="s">
-        <v>164</v>
+      <c r="J17" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>54</v>
@@ -2249,13 +2249,13 @@
         <f t="shared" si="3"/>
         <v>2174.7200000000003</v>
       </c>
-      <c r="J18" s="72" t="s">
-        <v>164</v>
+      <c r="J18" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>54</v>
@@ -2285,8 +2285,8 @@
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="J19" s="72" t="s">
-        <v>165</v>
+      <c r="J19" s="52" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -2302,7 +2302,7 @@
         <v>140</v>
       </c>
       <c r="G20" s="29"/>
-      <c r="H20" s="67"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="29">
         <f>SUM(I2:I19)</f>
         <v>16980.16</v>
@@ -2316,12 +2316,12 @@
       <c r="E21" s="29"/>
       <c r="F21" s="29"/>
       <c r="G21" s="29"/>
-      <c r="H21" s="67"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B22" s="40" t="s">
         <v>55</v>
@@ -2343,7 +2343,7 @@
       <c r="G22" s="39">
         <v>32</v>
       </c>
-      <c r="H22" s="68" cm="1">
+      <c r="H22" s="48" cm="1">
         <f t="array" ref="H22">_xlfn.CEILING.MATH(_xlfn.SWITCH(J22, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -2351,13 +2351,13 @@
         <f>2*F22*(G22+H22+6)</f>
         <v>880</v>
       </c>
-      <c r="J22" s="72" t="s">
-        <v>164</v>
+      <c r="J22" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B23" s="40" t="s">
         <v>55</v>
@@ -2379,7 +2379,7 @@
       <c r="G23" s="39">
         <v>27</v>
       </c>
-      <c r="H23" s="68" cm="1">
+      <c r="H23" s="48" cm="1">
         <f t="array" ref="H23">_xlfn.CEILING.MATH(_xlfn.SWITCH(J23, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -2387,43 +2387,43 @@
         <f>2*F23*(G23+H23+6)</f>
         <v>800</v>
       </c>
-      <c r="J23" s="72" t="s">
-        <v>164</v>
+      <c r="J23" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="48"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="60"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="51"/>
+        <v>150</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="63"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" s="40" t="s">
         <v>55</v>
@@ -2445,7 +2445,7 @@
       <c r="G26" s="39">
         <v>0.5</v>
       </c>
-      <c r="H26" s="68" cm="1">
+      <c r="H26" s="48" cm="1">
         <f t="array" ref="H26">_xlfn.CEILING.MATH(_xlfn.SWITCH(J26, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>14</v>
       </c>
@@ -2453,13 +2453,13 @@
         <f>2*F26*(G26+H26+6)</f>
         <v>820</v>
       </c>
-      <c r="J26" s="72" t="s">
-        <v>165</v>
+      <c r="J26" s="52" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="40" t="s">
         <v>55</v>
@@ -2481,7 +2481,7 @@
       <c r="G27" s="39">
         <v>45</v>
       </c>
-      <c r="H27" s="68" cm="1">
+      <c r="H27" s="48" cm="1">
         <f t="array" ref="H27">_xlfn.CEILING.MATH(_xlfn.SWITCH(J27, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>20</v>
       </c>
@@ -2489,13 +2489,13 @@
         <f t="shared" ref="I27:I30" si="6">2*F27*(G27+H27+6)</f>
         <v>1278</v>
       </c>
-      <c r="J27" s="72" t="s">
-        <v>166</v>
+      <c r="J27" s="52" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="40" t="s">
         <v>55</v>
@@ -2517,7 +2517,7 @@
       <c r="G28" s="39">
         <v>40</v>
       </c>
-      <c r="H28" s="68" cm="1">
+      <c r="H28" s="48" cm="1">
         <f t="array" ref="H28">_xlfn.CEILING.MATH(_xlfn.SWITCH(J28, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>20</v>
       </c>
@@ -2525,13 +2525,13 @@
         <f t="shared" si="6"/>
         <v>1188</v>
       </c>
-      <c r="J28" s="72" t="s">
-        <v>166</v>
+      <c r="J28" s="52" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="40" t="s">
         <v>55</v>
@@ -2553,7 +2553,7 @@
       <c r="G29" s="39">
         <v>12.54</v>
       </c>
-      <c r="H29" s="68" cm="1">
+      <c r="H29" s="48" cm="1">
         <f t="array" ref="H29">_xlfn.CEILING.MATH(_xlfn.SWITCH(J29, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -2561,13 +2561,13 @@
         <f t="shared" si="6"/>
         <v>438.48</v>
       </c>
-      <c r="J29" s="72" t="s">
-        <v>167</v>
+      <c r="J29" s="52" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" s="40" t="s">
         <v>55</v>
@@ -2589,7 +2589,7 @@
       <c r="G30" s="39">
         <v>21.88</v>
       </c>
-      <c r="H30" s="68" cm="1">
+      <c r="H30" s="48" cm="1">
         <f t="array" ref="H30">_xlfn.CEILING.MATH(_xlfn.SWITCH(J30, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -2597,29 +2597,29 @@
         <f t="shared" si="6"/>
         <v>550.55999999999995</v>
       </c>
-      <c r="J30" s="72" t="s">
-        <v>167</v>
+      <c r="J30" s="52" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="60"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" s="40" t="s">
         <v>55</v>
@@ -2649,13 +2649,13 @@
         <f>2*F32*(G32+H32+6)</f>
         <v>305</v>
       </c>
-      <c r="J32" s="72" t="s">
-        <v>168</v>
+      <c r="J32" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="40" t="s">
         <v>55</v>
@@ -2685,13 +2685,13 @@
         <f t="shared" ref="I33:I36" si="10">2*F33*(G33+H33+6)</f>
         <v>360</v>
       </c>
-      <c r="J33" s="72" t="s">
-        <v>168</v>
+      <c r="J33" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="40" t="s">
         <v>55</v>
@@ -2721,13 +2721,13 @@
         <f t="shared" si="10"/>
         <v>415</v>
       </c>
-      <c r="J34" s="72" t="s">
-        <v>168</v>
+      <c r="J34" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="40" t="s">
         <v>55</v>
@@ -2757,13 +2757,13 @@
         <f t="shared" si="10"/>
         <v>470</v>
       </c>
-      <c r="J35" s="72" t="s">
-        <v>168</v>
+      <c r="J35" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="40" t="s">
         <v>55</v>
@@ -2793,43 +2793,43 @@
         <f t="shared" si="10"/>
         <v>525</v>
       </c>
-      <c r="J36" s="72" t="s">
-        <v>168</v>
+      <c r="J36" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B37" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="54"/>
+      <c r="B37" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="66"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="57"/>
+        <v>156</v>
+      </c>
+      <c r="B38" s="67"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="69"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" s="40" t="s">
         <v>55</v>
@@ -2859,13 +2859,13 @@
         <f>2*F39*(G39+H39+6)</f>
         <v>552</v>
       </c>
-      <c r="J39" s="72" t="s">
-        <v>169</v>
+      <c r="J39" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" s="40" t="s">
         <v>55</v>
@@ -2895,13 +2895,13 @@
         <f t="shared" ref="I40:I44" si="11">2*F40*(G40+H40+6)</f>
         <v>581</v>
       </c>
-      <c r="J40" s="72" t="s">
-        <v>169</v>
+      <c r="J40" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="40" t="s">
         <v>55</v>
@@ -2931,13 +2931,13 @@
         <f t="shared" si="11"/>
         <v>665</v>
       </c>
-      <c r="J41" s="72" t="s">
-        <v>169</v>
+      <c r="J41" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" s="40" t="s">
         <v>55</v>
@@ -2967,13 +2967,13 @@
         <f t="shared" si="11"/>
         <v>749</v>
       </c>
-      <c r="J42" s="72" t="s">
-        <v>169</v>
+      <c r="J42" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="40" t="s">
         <v>55</v>
@@ -3003,13 +3003,13 @@
         <f t="shared" si="11"/>
         <v>833</v>
       </c>
-      <c r="J43" s="72" t="s">
-        <v>169</v>
+      <c r="J43" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B44" s="40" t="s">
         <v>55</v>
@@ -3039,8 +3039,8 @@
         <f t="shared" si="11"/>
         <v>917</v>
       </c>
-      <c r="J44" s="72" t="s">
-        <v>169</v>
+      <c r="J44" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -3056,7 +3056,7 @@
         <v>134</v>
       </c>
       <c r="G45" s="29"/>
-      <c r="H45" s="67"/>
+      <c r="H45" s="47"/>
       <c r="I45" s="29">
         <f>SUM(I22:I44)</f>
         <v>12327.039999999999</v>
@@ -3070,12 +3070,12 @@
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
       <c r="G46" s="29"/>
-      <c r="H46" s="67"/>
+      <c r="H46" s="47"/>
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B47" s="39" t="s">
         <v>56</v>
@@ -3097,7 +3097,7 @@
       <c r="G47" s="39">
         <v>9.4</v>
       </c>
-      <c r="H47" s="68" cm="1">
+      <c r="H47" s="48" cm="1">
         <f t="array" ref="H47">_xlfn.CEILING.MATH(_xlfn.SWITCH(J47, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>14</v>
       </c>
@@ -3105,13 +3105,13 @@
         <f>2*F47*(G47+H47+6)</f>
         <v>352.79999999999995</v>
       </c>
-      <c r="J47" s="72" t="s">
-        <v>159</v>
+      <c r="J47" s="52" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B48" s="39" t="s">
         <v>56</v>
@@ -3133,7 +3133,7 @@
       <c r="G48" s="39">
         <v>16.11</v>
       </c>
-      <c r="H48" s="68" cm="1">
+      <c r="H48" s="48" cm="1">
         <f t="array" ref="H48">_xlfn.CEILING.MATH(_xlfn.SWITCH(J48, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>5</v>
       </c>
@@ -3141,29 +3141,29 @@
         <f>2*F48*(G48+H48+6)</f>
         <v>325.32</v>
       </c>
-      <c r="J48" s="72" t="s">
-        <v>160</v>
+      <c r="J48" s="52" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="63"/>
+      <c r="C49" s="74"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="75"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B50" s="39" t="s">
         <v>56</v>
@@ -3185,7 +3185,7 @@
       <c r="G50" s="39">
         <v>21.82</v>
       </c>
-      <c r="H50" s="68" cm="1">
+      <c r="H50" s="48" cm="1">
         <f t="array" ref="H50">_xlfn.CEILING.MATH(_xlfn.SWITCH(J50, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3193,13 +3193,13 @@
         <f>2*F50*(G50+H50+6)</f>
         <v>388.2</v>
       </c>
-      <c r="J50" s="72" t="s">
-        <v>161</v>
+      <c r="J50" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B51" s="39" t="s">
         <v>56</v>
@@ -3221,7 +3221,7 @@
       <c r="G51" s="39">
         <v>27.82</v>
       </c>
-      <c r="H51" s="68" cm="1">
+      <c r="H51" s="48" cm="1">
         <f t="array" ref="H51">_xlfn.CEILING.MATH(_xlfn.SWITCH(J51, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3229,13 +3229,13 @@
         <f t="shared" ref="I51:I54" si="15">2*F51*(G51+H51+6)</f>
         <v>448.2</v>
       </c>
-      <c r="J51" s="72" t="s">
-        <v>161</v>
+      <c r="J51" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B52" s="39" t="s">
         <v>56</v>
@@ -3257,7 +3257,7 @@
       <c r="G52" s="39">
         <v>33.53</v>
       </c>
-      <c r="H52" s="68" cm="1">
+      <c r="H52" s="48" cm="1">
         <f t="array" ref="H52">_xlfn.CEILING.MATH(_xlfn.SWITCH(J52, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3265,13 +3265,13 @@
         <f t="shared" si="15"/>
         <v>505.3</v>
       </c>
-      <c r="J52" s="72" t="s">
-        <v>161</v>
+      <c r="J52" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B53" s="39" t="s">
         <v>56</v>
@@ -3293,7 +3293,7 @@
       <c r="G53" s="39">
         <v>39.53</v>
       </c>
-      <c r="H53" s="68" cm="1">
+      <c r="H53" s="48" cm="1">
         <f t="array" ref="H53">_xlfn.CEILING.MATH(_xlfn.SWITCH(J53, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3301,13 +3301,13 @@
         <f t="shared" si="15"/>
         <v>565.29999999999995</v>
       </c>
-      <c r="J53" s="72" t="s">
-        <v>161</v>
+      <c r="J53" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B54" s="39" t="s">
         <v>56</v>
@@ -3329,7 +3329,7 @@
       <c r="G54" s="39">
         <v>45.24</v>
       </c>
-      <c r="H54" s="68" cm="1">
+      <c r="H54" s="48" cm="1">
         <f t="array" ref="H54">_xlfn.CEILING.MATH(_xlfn.SWITCH(J54, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3337,43 +3337,43 @@
         <f t="shared" si="15"/>
         <v>622.4</v>
       </c>
-      <c r="J54" s="72" t="s">
-        <v>161</v>
+      <c r="J54" s="52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="47"/>
-      <c r="J55" s="48"/>
+        <v>118</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="60"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" s="49"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="51"/>
+        <v>119</v>
+      </c>
+      <c r="B56" s="61"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B57" s="39" t="s">
         <v>56</v>
@@ -3395,7 +3395,7 @@
       <c r="G57" s="39">
         <v>0.5</v>
       </c>
-      <c r="H57" s="68" cm="1">
+      <c r="H57" s="48" cm="1">
         <f t="array" ref="H57">_xlfn.CEILING.MATH(_xlfn.SWITCH(J57, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>11</v>
       </c>
@@ -3403,13 +3403,13 @@
         <f>2*F57*(G57+H57+6)</f>
         <v>350</v>
       </c>
-      <c r="J57" s="72" t="s">
-        <v>162</v>
+      <c r="J57" s="52" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B58" s="39" t="s">
         <v>56</v>
@@ -3431,7 +3431,7 @@
       <c r="G58" s="39">
         <v>5</v>
       </c>
-      <c r="H58" s="68" cm="1">
+      <c r="H58" s="48" cm="1">
         <f t="array" ref="H58">_xlfn.CEILING.MATH(_xlfn.SWITCH(J58, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>22</v>
       </c>
@@ -3439,13 +3439,13 @@
         <f t="shared" ref="I58:I64" si="16">2*F58*(G58+H58+6)</f>
         <v>2178</v>
       </c>
-      <c r="J58" s="72" t="s">
-        <v>163</v>
+      <c r="J58" s="52" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B59" s="39" t="s">
         <v>56</v>
@@ -3467,7 +3467,7 @@
       <c r="G59" s="39">
         <v>84.64</v>
       </c>
-      <c r="H59" s="68" cm="1">
+      <c r="H59" s="48" cm="1">
         <f t="array" ref="H59">_xlfn.CEILING.MATH(_xlfn.SWITCH(J59, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3475,13 +3475,13 @@
         <f t="shared" si="16"/>
         <v>1722.24</v>
       </c>
-      <c r="J59" s="72" t="s">
-        <v>164</v>
+      <c r="J59" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B60" s="39" t="s">
         <v>56</v>
@@ -3503,7 +3503,7 @@
       <c r="G60" s="39">
         <v>91.78</v>
       </c>
-      <c r="H60" s="68" cm="1">
+      <c r="H60" s="48" cm="1">
         <f t="array" ref="H60">_xlfn.CEILING.MATH(_xlfn.SWITCH(J60, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3511,13 +3511,13 @@
         <f t="shared" si="16"/>
         <v>1836.48</v>
       </c>
-      <c r="J60" s="72" t="s">
-        <v>164</v>
+      <c r="J60" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B61" s="39" t="s">
         <v>56</v>
@@ -3539,7 +3539,7 @@
       <c r="G61" s="39">
         <v>98.78</v>
       </c>
-      <c r="H61" s="68" cm="1">
+      <c r="H61" s="48" cm="1">
         <f t="array" ref="H61">_xlfn.CEILING.MATH(_xlfn.SWITCH(J61, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3547,13 +3547,13 @@
         <f t="shared" si="16"/>
         <v>1948.48</v>
       </c>
-      <c r="J61" s="72" t="s">
-        <v>164</v>
+      <c r="J61" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B62" s="39" t="s">
         <v>56</v>
@@ -3575,7 +3575,7 @@
       <c r="G62" s="39">
         <v>105.92</v>
       </c>
-      <c r="H62" s="68" cm="1">
+      <c r="H62" s="48" cm="1">
         <f t="array" ref="H62">_xlfn.CEILING.MATH(_xlfn.SWITCH(J62, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3583,13 +3583,13 @@
         <f t="shared" si="16"/>
         <v>2062.7200000000003</v>
       </c>
-      <c r="J62" s="72" t="s">
-        <v>164</v>
+      <c r="J62" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B63" s="39" t="s">
         <v>56</v>
@@ -3611,7 +3611,7 @@
       <c r="G63" s="39">
         <v>112.92</v>
       </c>
-      <c r="H63" s="68" cm="1">
+      <c r="H63" s="48" cm="1">
         <f t="array" ref="H63">_xlfn.CEILING.MATH(_xlfn.SWITCH(J63, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3619,13 +3619,13 @@
         <f t="shared" si="16"/>
         <v>2174.7200000000003</v>
       </c>
-      <c r="J63" s="72" t="s">
-        <v>164</v>
+      <c r="J63" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B64" s="39" t="s">
         <v>56</v>
@@ -3647,7 +3647,7 @@
       <c r="G64" s="39">
         <v>17.5</v>
       </c>
-      <c r="H64" s="68" cm="1">
+      <c r="H64" s="48" cm="1">
         <f t="array" ref="H64">_xlfn.CEILING.MATH(_xlfn.SWITCH(J64, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>14</v>
       </c>
@@ -3655,8 +3655,8 @@
         <f t="shared" si="16"/>
         <v>1500</v>
       </c>
-      <c r="J64" s="72" t="s">
-        <v>165</v>
+      <c r="J64" s="52" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -3672,7 +3672,7 @@
         <v>140</v>
       </c>
       <c r="G65" s="29"/>
-      <c r="H65" s="67"/>
+      <c r="H65" s="47"/>
       <c r="I65" s="29">
         <f>SUM(I47:I64)</f>
         <v>16980.16</v>
@@ -3686,12 +3686,12 @@
       <c r="E66" s="29"/>
       <c r="F66" s="29"/>
       <c r="G66" s="29"/>
-      <c r="H66" s="67"/>
+      <c r="H66" s="47"/>
       <c r="I66" s="29"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B67" s="40" t="s">
         <v>57</v>
@@ -3713,7 +3713,7 @@
       <c r="G67" s="39">
         <v>32</v>
       </c>
-      <c r="H67" s="68" cm="1">
+      <c r="H67" s="48" cm="1">
         <f t="array" ref="H67">_xlfn.CEILING.MATH(_xlfn.SWITCH(J67, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3721,13 +3721,13 @@
         <f>2*F67*(G67+H67+6)</f>
         <v>880</v>
       </c>
-      <c r="J67" s="72" t="s">
-        <v>164</v>
+      <c r="J67" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B68" s="40" t="s">
         <v>57</v>
@@ -3749,7 +3749,7 @@
       <c r="G68" s="39">
         <v>27</v>
       </c>
-      <c r="H68" s="68" cm="1">
+      <c r="H68" s="48" cm="1">
         <f t="array" ref="H68">_xlfn.CEILING.MATH(_xlfn.SWITCH(J68, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3757,43 +3757,43 @@
         <f>2*F68*(G68+H68+6)</f>
         <v>800</v>
       </c>
-      <c r="J68" s="72" t="s">
-        <v>164</v>
+      <c r="J68" s="52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B69" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="48"/>
+        <v>149</v>
+      </c>
+      <c r="B69" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
+      <c r="J69" s="60"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="B70" s="49"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="51"/>
+        <v>146</v>
+      </c>
+      <c r="B70" s="61"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
+      <c r="I70" s="62"/>
+      <c r="J70" s="63"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B71" s="40" t="s">
         <v>57</v>
@@ -3815,7 +3815,7 @@
       <c r="G71" s="39">
         <v>0.5</v>
       </c>
-      <c r="H71" s="68" cm="1">
+      <c r="H71" s="48" cm="1">
         <f t="array" ref="H71">_xlfn.CEILING.MATH(_xlfn.SWITCH(J71, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>14</v>
       </c>
@@ -3823,13 +3823,13 @@
         <f>2*F71*(G71+H71+6)</f>
         <v>820</v>
       </c>
-      <c r="J71" s="72" t="s">
-        <v>165</v>
+      <c r="J71" s="52" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B72" s="40" t="s">
         <v>57</v>
@@ -3851,7 +3851,7 @@
       <c r="G72" s="39">
         <v>56.07</v>
       </c>
-      <c r="H72" s="68" cm="1">
+      <c r="H72" s="48" cm="1">
         <f t="array" ref="H72">_xlfn.CEILING.MATH(_xlfn.SWITCH(J72, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>17</v>
       </c>
@@ -3859,13 +3859,13 @@
         <f t="shared" ref="I72:I74" si="21">2*F72*(G72+H72+6)</f>
         <v>1106.98</v>
       </c>
-      <c r="J72" s="72" t="s">
-        <v>170</v>
+      <c r="J72" s="52" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B73" s="40" t="s">
         <v>57</v>
@@ -3887,7 +3887,7 @@
       <c r="G73" s="39">
         <v>12.54</v>
       </c>
-      <c r="H73" s="68" cm="1">
+      <c r="H73" s="48" cm="1">
         <f t="array" ref="H73">_xlfn.CEILING.MATH(_xlfn.SWITCH(J73, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -3895,13 +3895,13 @@
         <f t="shared" si="21"/>
         <v>438.48</v>
       </c>
-      <c r="J73" s="72" t="s">
-        <v>167</v>
+      <c r="J73" s="52" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B74" s="40" t="s">
         <v>57</v>
@@ -3923,7 +3923,7 @@
       <c r="G74" s="39">
         <v>21.88</v>
       </c>
-      <c r="H74" s="68" cm="1">
+      <c r="H74" s="48" cm="1">
         <f t="array" ref="H74">_xlfn.CEILING.MATH(_xlfn.SWITCH(J74, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -3931,29 +3931,29 @@
         <f t="shared" si="21"/>
         <v>550.55999999999995</v>
       </c>
-      <c r="J74" s="72" t="s">
-        <v>167</v>
+      <c r="J74" s="52" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="B75" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="C75" s="59"/>
-      <c r="D75" s="59"/>
-      <c r="E75" s="59"/>
-      <c r="F75" s="59"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="59"/>
-      <c r="I75" s="59"/>
-      <c r="J75" s="60"/>
+      <c r="C75" s="71"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="71"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="72"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B76" s="40" t="s">
         <v>57</v>
@@ -3975,7 +3975,7 @@
       <c r="G76" s="39">
         <v>11.5</v>
       </c>
-      <c r="H76" s="68" cm="1">
+      <c r="H76" s="48" cm="1">
         <f t="array" ref="H76">_xlfn.CEILING.MATH(_xlfn.SWITCH(J76, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>13</v>
       </c>
@@ -3983,13 +3983,13 @@
         <f>2*F76*(G76+H76+6)</f>
         <v>122</v>
       </c>
-      <c r="J76" s="72" t="s">
-        <v>168</v>
+      <c r="J76" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B77" s="40" t="s">
         <v>57</v>
@@ -4011,7 +4011,7 @@
       <c r="G77" s="39">
         <v>17</v>
       </c>
-      <c r="H77" s="68" cm="1">
+      <c r="H77" s="48" cm="1">
         <f t="array" ref="H77">_xlfn.CEILING.MATH(_xlfn.SWITCH(J77, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>13</v>
       </c>
@@ -4019,13 +4019,13 @@
         <f t="shared" ref="I77:I80" si="23">2*F77*(G77+H77+6)</f>
         <v>360</v>
       </c>
-      <c r="J77" s="72" t="s">
-        <v>168</v>
+      <c r="J77" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B78" s="40" t="s">
         <v>57</v>
@@ -4047,7 +4047,7 @@
       <c r="G78" s="39">
         <v>22.5</v>
       </c>
-      <c r="H78" s="68" cm="1">
+      <c r="H78" s="48" cm="1">
         <f t="array" ref="H78">_xlfn.CEILING.MATH(_xlfn.SWITCH(J78, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>13</v>
       </c>
@@ -4055,13 +4055,13 @@
         <f t="shared" si="23"/>
         <v>415</v>
       </c>
-      <c r="J78" s="72" t="s">
-        <v>168</v>
+      <c r="J78" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B79" s="40" t="s">
         <v>57</v>
@@ -4083,7 +4083,7 @@
       <c r="G79" s="39">
         <v>28</v>
       </c>
-      <c r="H79" s="68" cm="1">
+      <c r="H79" s="48" cm="1">
         <f t="array" ref="H79">_xlfn.CEILING.MATH(_xlfn.SWITCH(J79, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>13</v>
       </c>
@@ -4091,13 +4091,13 @@
         <f t="shared" si="23"/>
         <v>470</v>
       </c>
-      <c r="J79" s="72" t="s">
-        <v>168</v>
+      <c r="J79" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B80" s="40" t="s">
         <v>57</v>
@@ -4119,7 +4119,7 @@
       <c r="G80" s="39">
         <v>33.5</v>
       </c>
-      <c r="H80" s="68" cm="1">
+      <c r="H80" s="48" cm="1">
         <f t="array" ref="H80">_xlfn.CEILING.MATH(_xlfn.SWITCH(J80, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>13</v>
       </c>
@@ -4127,43 +4127,43 @@
         <f t="shared" si="23"/>
         <v>525</v>
       </c>
-      <c r="J80" s="72" t="s">
-        <v>168</v>
+      <c r="J80" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B81" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="53"/>
-      <c r="D81" s="53"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="53"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="54"/>
+        <v>138</v>
+      </c>
+      <c r="B81" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="66"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="B82" s="55"/>
-      <c r="C82" s="56"/>
-      <c r="D82" s="56"/>
-      <c r="E82" s="56"/>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="56"/>
-      <c r="I82" s="56"/>
-      <c r="J82" s="57"/>
+        <v>139</v>
+      </c>
+      <c r="B82" s="67"/>
+      <c r="C82" s="68"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="68"/>
+      <c r="I82" s="68"/>
+      <c r="J82" s="69"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B83" s="40" t="s">
         <v>57</v>
@@ -4185,7 +4185,7 @@
       <c r="G83" s="39">
         <v>10.5</v>
       </c>
-      <c r="H83" s="68" cm="1">
+      <c r="H83" s="48" cm="1">
         <f t="array" ref="H83">_xlfn.CEILING.MATH(_xlfn.SWITCH(J83, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4193,13 +4193,13 @@
         <f>2*F83*(G83+H83+6)</f>
         <v>621</v>
       </c>
-      <c r="J83" s="72" t="s">
-        <v>169</v>
+      <c r="J83" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B84" s="40" t="s">
         <v>57</v>
@@ -4221,7 +4221,7 @@
       <c r="G84" s="39">
         <v>17.5</v>
       </c>
-      <c r="H84" s="68" cm="1">
+      <c r="H84" s="48" cm="1">
         <f t="array" ref="H84">_xlfn.CEILING.MATH(_xlfn.SWITCH(J84, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4229,13 +4229,13 @@
         <f t="shared" ref="I84:I88" si="25">2*F84*(G84+H84+6)</f>
         <v>747</v>
       </c>
-      <c r="J84" s="72" t="s">
-        <v>169</v>
+      <c r="J84" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B85" s="40" t="s">
         <v>57</v>
@@ -4257,7 +4257,7 @@
       <c r="G85" s="39">
         <v>23.5</v>
       </c>
-      <c r="H85" s="68" cm="1">
+      <c r="H85" s="48" cm="1">
         <f t="array" ref="H85">_xlfn.CEILING.MATH(_xlfn.SWITCH(J85, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4265,13 +4265,13 @@
         <f t="shared" si="25"/>
         <v>665</v>
       </c>
-      <c r="J85" s="72" t="s">
-        <v>169</v>
+      <c r="J85" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B86" s="40" t="s">
         <v>57</v>
@@ -4293,7 +4293,7 @@
       <c r="G86" s="39">
         <v>29.5</v>
       </c>
-      <c r="H86" s="68" cm="1">
+      <c r="H86" s="48" cm="1">
         <f t="array" ref="H86">_xlfn.CEILING.MATH(_xlfn.SWITCH(J86, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4301,13 +4301,13 @@
         <f t="shared" si="25"/>
         <v>749</v>
       </c>
-      <c r="J86" s="72" t="s">
-        <v>169</v>
+      <c r="J86" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B87" s="40" t="s">
         <v>57</v>
@@ -4329,7 +4329,7 @@
       <c r="G87" s="39">
         <v>35.5</v>
       </c>
-      <c r="H87" s="68" cm="1">
+      <c r="H87" s="48" cm="1">
         <f t="array" ref="H87">_xlfn.CEILING.MATH(_xlfn.SWITCH(J87, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4337,13 +4337,13 @@
         <f t="shared" si="25"/>
         <v>833</v>
       </c>
-      <c r="J87" s="72" t="s">
-        <v>169</v>
+      <c r="J87" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B88" s="40" t="s">
         <v>57</v>
@@ -4365,7 +4365,7 @@
       <c r="G88" s="39">
         <v>41.5</v>
       </c>
-      <c r="H88" s="68" cm="1">
+      <c r="H88" s="48" cm="1">
         <f t="array" ref="H88">_xlfn.CEILING.MATH(_xlfn.SWITCH(J88, "A", 13.21, "B", 4.86, "C", 10.56, "D", 10.87, "E", 16.75, "F", 22, "G", 13.2, "H", 19.3, "I", 17.5, "J", 12.8, "K", 17.3, "L", 17, -1))</f>
         <v>18</v>
       </c>
@@ -4373,8 +4373,8 @@
         <f t="shared" si="25"/>
         <v>917</v>
       </c>
-      <c r="J88" s="72" t="s">
-        <v>169</v>
+      <c r="J88" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -4390,7 +4390,7 @@
         <v>123</v>
       </c>
       <c r="G89" s="29"/>
-      <c r="H89" s="67"/>
+      <c r="H89" s="47"/>
       <c r="I89" s="29">
         <f>SUM(I67:I88)</f>
         <v>11020.02</v>
@@ -4409,14 +4409,14 @@
         <v>537</v>
       </c>
       <c r="G91" s="37"/>
-      <c r="H91" s="69"/>
+      <c r="H91" s="49"/>
       <c r="I91" s="37">
         <f>I89+I65+I45+I20</f>
         <v>57307.380000000005</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H93" s="67" t="s">
+      <c r="H93" s="47" t="s">
         <v>68</v>
       </c>
       <c r="I93" s="29">
@@ -4425,7 +4425,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H94" s="67" t="s">
+      <c r="H94" s="47" t="s">
         <v>69</v>
       </c>
       <c r="I94" s="29">
@@ -4434,52 +4434,57 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="78" t="s">
         <v>70</v>
       </c>
+      <c r="B96" s="78"/>
       <c r="C96" s="37">
         <f>I91/(F91*2)</f>
         <v>53.358826815642459</v>
       </c>
-      <c r="E96" t="s">
+    </row>
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
+    </row>
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B99" s="55"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B100" s="56"/>
+    </row>
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="57" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="B98" s="74"/>
-      <c r="C98" s="74"/>
-      <c r="D98" s="74"/>
-      <c r="E98" s="74"/>
-      <c r="F98" s="74"/>
-      <c r="G98" s="74"/>
-      <c r="H98" s="74"/>
-    </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B99" s="75"/>
-    </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="76" t="s">
-        <v>73</v>
-      </c>
-      <c r="B100" s="76"/>
-    </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="B101" s="77"/>
-      <c r="C101" s="77"/>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B75:J75"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B37:J38"/>
     <mergeCell ref="A98:H98"/>
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="A100:B100"/>
@@ -4487,13 +4492,7 @@
     <mergeCell ref="B55:J56"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B81:J82"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B75:J75"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B37:J38"/>
+    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C96">
@@ -4554,7 +4553,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="76" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="10">
@@ -4573,12 +4572,12 @@
       <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="76" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="65"/>
+      <c r="A3" s="77"/>
       <c r="B3" s="10">
         <v>1</v>
       </c>
@@ -4593,10 +4592,10 @@
       <c r="G3" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="65"/>
+      <c r="H3" s="77"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
+      <c r="A4" s="77"/>
       <c r="B4" s="10">
         <v>1</v>
       </c>
@@ -4613,10 +4612,10 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="77"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="65"/>
+      <c r="A5" s="77"/>
       <c r="B5" s="10">
         <v>1</v>
       </c>
@@ -4627,10 +4626,10 @@
       <c r="G5" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="65"/>
+      <c r="H5" s="77"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="65"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="10">
         <v>1</v>
       </c>
@@ -4647,10 +4646,10 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="65"/>
+      <c r="H6" s="77"/>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="10">
         <v>1</v>
       </c>
@@ -4665,10 +4664,10 @@
       <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="65"/>
+      <c r="H7" s="77"/>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="65"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="24">
         <v>1</v>
       </c>
@@ -4685,10 +4684,10 @@
       <c r="G8" s="5">
         <v>50</v>
       </c>
-      <c r="H8" s="65"/>
+      <c r="H8" s="77"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="65"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -4698,10 +4697,10 @@
       <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="65"/>
+      <c r="H9" s="77"/>
     </row>
     <row r="10" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="65"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -4714,10 +4713,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="65"/>
+      <c r="H10" s="77"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="65"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="10">
         <v>1</v>
       </c>
@@ -4728,10 +4727,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="65"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="65"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="10">
         <v>1</v>
       </c>
@@ -4742,10 +4741,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="65"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="65"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="10">
         <v>1</v>
       </c>
@@ -4756,10 +4755,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="65"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="65"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="10">
         <v>1</v>
       </c>
@@ -4768,10 +4767,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="65"/>
+      <c r="H14" s="77"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="65"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="10">
         <v>1</v>
       </c>
@@ -4782,10 +4781,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="65"/>
+      <c r="H15" s="77"/>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="65"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="10">
         <v>1</v>
       </c>
@@ -4796,10 +4795,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="77"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="65"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="24">
         <v>7</v>
       </c>
@@ -4808,70 +4807,70 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="65"/>
+      <c r="H17" s="77"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="65"/>
+      <c r="A18" s="77"/>
       <c r="B18" s="24"/>
       <c r="C18" s="35"/>
       <c r="D18" s="10"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="65"/>
+      <c r="H18" s="77"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="65"/>
+      <c r="A19" s="77"/>
       <c r="B19" s="24"/>
       <c r="C19" s="35"/>
       <c r="D19" s="10"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="65"/>
+      <c r="H19" s="77"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="65"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="24"/>
       <c r="C20" s="35"/>
       <c r="D20" s="10"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="65"/>
+      <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="65"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="24"/>
       <c r="C21" s="35"/>
       <c r="D21" s="10"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="65"/>
+      <c r="H21" s="77"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="65"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="24"/>
       <c r="C22" s="35"/>
       <c r="D22" s="10"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="65"/>
+      <c r="H22" s="77"/>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="65"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="24"/>
       <c r="C23" s="36"/>
       <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="65"/>
+      <c r="H23" s="77"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="65"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="10">
         <v>1</v>
       </c>
@@ -4882,10 +4881,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="65"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="65"/>
+      <c r="A25" s="77"/>
       <c r="B25" s="10">
         <v>1</v>
       </c>
@@ -4896,10 +4895,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="65"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="65"/>
+      <c r="A26" s="77"/>
       <c r="B26" s="10">
         <v>1</v>
       </c>
@@ -4910,10 +4909,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="65"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="65"/>
+      <c r="A27" s="77"/>
       <c r="B27" s="10">
         <v>1</v>
       </c>
@@ -4922,10 +4921,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="65"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="65"/>
+      <c r="A28" s="77"/>
       <c r="B28" s="10">
         <v>1</v>
       </c>
@@ -4934,10 +4933,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="65"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="10">
         <v>1</v>
       </c>
@@ -4953,10 +4952,10 @@
       <c r="G29" s="5">
         <v>50</v>
       </c>
-      <c r="H29" s="65"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="65"/>
+      <c r="A30" s="77"/>
       <c r="B30" s="10">
         <v>6</v>
       </c>
@@ -4967,40 +4966,40 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="65"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="65"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="65"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="65"/>
+      <c r="A32" s="77"/>
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="65"/>
+      <c r="H32" s="77"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="65"/>
+      <c r="A33" s="77"/>
       <c r="B33" s="10"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="65"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="65"/>
+      <c r="A34" s="77"/>
       <c r="B34" s="10">
         <v>1</v>
       </c>
@@ -5013,10 +5012,10 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="65"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="65"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="10">
         <v>1</v>
       </c>
@@ -5027,10 +5026,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="65"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="65"/>
+      <c r="A36" s="77"/>
       <c r="B36" s="10">
         <v>1</v>
       </c>
@@ -5047,10 +5046,10 @@
       <c r="G36" s="5">
         <v>200</v>
       </c>
-      <c r="H36" s="65"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="65"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="10">
         <v>2</v>
       </c>
@@ -5061,10 +5060,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="65"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="65"/>
+      <c r="A38" s="77"/>
       <c r="B38" s="10">
         <v>4</v>
       </c>
@@ -5079,10 +5078,10 @@
       <c r="G38" s="5">
         <v>250</v>
       </c>
-      <c r="H38" s="65"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="65"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="10">
         <v>4</v>
       </c>
@@ -5097,37 +5096,37 @@
       <c r="G39" s="5">
         <v>250</v>
       </c>
-      <c r="H39" s="65"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="65"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="65"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="65"/>
+      <c r="A41" s="77"/>
       <c r="B41" s="10"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="65"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="65"/>
+      <c r="A42" s="77"/>
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="65"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
@@ -5354,21 +5353,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E4DE2CC379442A4D8483D9D7B1BA3E35" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3cbd871ac436bbcd94953c6f74650012">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b380a0-b262-4a13-9203-497a21b8eee5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f82e0ce2898406bfa558450728792a3e" ns2:_="">
     <xsd:import namespace="a1b380a0-b262-4a13-9203-497a21b8eee5"/>
@@ -5506,24 +5490,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F86897-A5B3-4CA1-BC45-17E92954BA24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5539,4 +5521,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160991D8-BA81-407D-9E91-473AD6B09576}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456E5AF3-7BBF-4763-B83A-9DB8001DA7F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0318409-9D07-4107-AD2E-444995DA1C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB177BD1-40F2-4C22-B1EC-1930EFF56AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="1" r:id="rId1"/>
     <sheet name="Fiber" sheetId="5" r:id="rId2"/>
-    <sheet name="MDF" sheetId="2" r:id="rId3"/>
-    <sheet name="IDF1" sheetId="3" r:id="rId4"/>
-    <sheet name="IDF..." sheetId="4" r:id="rId5"/>
+    <sheet name="Equipment" sheetId="6" r:id="rId3"/>
+    <sheet name="MDF" sheetId="2" r:id="rId4"/>
+    <sheet name="IDF1" sheetId="3" r:id="rId5"/>
+    <sheet name="IDF..." sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="189">
   <si>
     <t>Room Nr</t>
   </si>
@@ -658,13 +659,31 @@
   </si>
   <si>
     <t>Target</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Choice 2</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Choice 1 (CISCO)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +748,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -827,7 +853,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1529,11 +1555,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1595,6 +1706,93 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1606,8 +1804,6 @@
     <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1629,95 +1825,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2076,17 +2219,17 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="87"/>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -2272,31 +2415,31 @@
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="57"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="90"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2694,31 +2837,31 @@
       <c r="A24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="57"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="93"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -2904,17 +3047,17 @@
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="63"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -3100,31 +3243,31 @@
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="64" t="s">
+      <c r="B37" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="57"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="90"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="60"/>
+      <c r="B38" s="91"/>
+      <c r="C38" s="92"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="93"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -3450,17 +3593,17 @@
       <c r="A49" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="63"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="87"/>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -3646,31 +3789,31 @@
       <c r="A55" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="55" t="s">
+      <c r="B55" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="57"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="89"/>
+      <c r="J55" s="90"/>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="58"/>
-      <c r="C56" s="59"/>
-      <c r="D56" s="59"/>
-      <c r="E56" s="59"/>
-      <c r="F56" s="59"/>
-      <c r="G56" s="59"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="59"/>
-      <c r="J56" s="60"/>
+      <c r="B56" s="91"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="92"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="92"/>
+      <c r="J56" s="93"/>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -4068,31 +4211,31 @@
       <c r="A69" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="55" t="s">
+      <c r="B69" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="56"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="56"/>
-      <c r="F69" s="56"/>
-      <c r="G69" s="56"/>
-      <c r="H69" s="56"/>
-      <c r="I69" s="56"/>
-      <c r="J69" s="57"/>
+      <c r="C69" s="89"/>
+      <c r="D69" s="89"/>
+      <c r="E69" s="89"/>
+      <c r="F69" s="89"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="90"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="58"/>
-      <c r="C70" s="59"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="59"/>
-      <c r="F70" s="59"/>
-      <c r="G70" s="59"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="59"/>
-      <c r="J70" s="60"/>
+      <c r="B70" s="91"/>
+      <c r="C70" s="92"/>
+      <c r="D70" s="92"/>
+      <c r="E70" s="92"/>
+      <c r="F70" s="92"/>
+      <c r="G70" s="92"/>
+      <c r="H70" s="92"/>
+      <c r="I70" s="92"/>
+      <c r="J70" s="93"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
@@ -4242,17 +4385,17 @@
       <c r="A75" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="61" t="s">
+      <c r="B75" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="62"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="62"/>
-      <c r="G75" s="62"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="62"/>
-      <c r="J75" s="63"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="86"/>
+      <c r="F75" s="86"/>
+      <c r="G75" s="86"/>
+      <c r="H75" s="86"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="87"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
@@ -4438,31 +4581,31 @@
       <c r="A81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B81" s="64" t="s">
+      <c r="B81" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
-      <c r="E81" s="56"/>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="57"/>
+      <c r="C81" s="89"/>
+      <c r="D81" s="89"/>
+      <c r="E81" s="89"/>
+      <c r="F81" s="89"/>
+      <c r="G81" s="89"/>
+      <c r="H81" s="89"/>
+      <c r="I81" s="89"/>
+      <c r="J81" s="90"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="58"/>
-      <c r="C82" s="59"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="60"/>
+      <c r="B82" s="91"/>
+      <c r="C82" s="92"/>
+      <c r="D82" s="92"/>
+      <c r="E82" s="92"/>
+      <c r="F82" s="92"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
+      <c r="I82" s="92"/>
+      <c r="J82" s="93"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
@@ -4757,10 +4900,10 @@
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="71" t="s">
+      <c r="A97" s="102" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="72"/>
+      <c r="B97" s="103"/>
       <c r="C97" s="18">
         <f>I91/(F91*2)</f>
         <v>53.358826815642459</v>
@@ -4773,42 +4916,42 @@
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="70" t="s">
+      <c r="A99" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="66"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="67"/>
+      <c r="B99" s="97"/>
+      <c r="C99" s="97"/>
+      <c r="D99" s="97"/>
+      <c r="E99" s="97"/>
+      <c r="F99" s="97"/>
+      <c r="G99" s="97"/>
+      <c r="H99" s="98"/>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="69" t="s">
+      <c r="A100" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="67"/>
+      <c r="B100" s="98"/>
       <c r="H100" s="17"/>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="68" t="s">
+      <c r="A101" s="99" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="67"/>
+      <c r="B101" s="98"/>
       <c r="H101" s="17"/>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="65" t="s">
+      <c r="A102" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="66"/>
-      <c r="C102" s="66"/>
-      <c r="D102" s="66"/>
-      <c r="E102" s="67"/>
+      <c r="B102" s="97"/>
+      <c r="C102" s="97"/>
+      <c r="D102" s="97"/>
+      <c r="E102" s="98"/>
       <c r="H102" s="17"/>
       <c r="J102" s="15"/>
     </row>
@@ -8410,13 +8553,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B55:J56"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B37:J38"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B75:J75"/>
     <mergeCell ref="B81:J82"/>
@@ -8425,6 +8561,13 @@
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A97:B97"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
@@ -8447,228 +8590,229 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="78"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="77" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100" t="s">
+      <c r="B2" s="78"/>
+      <c r="C2" s="83" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102" t="s">
+      <c r="D2" s="84"/>
+      <c r="E2" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="103"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="78"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="94" t="s">
+      <c r="B3" s="80"/>
+      <c r="C3" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97">
+      <c r="D3" s="74"/>
+      <c r="E3" s="73">
         <v>35</v>
       </c>
-      <c r="F3" s="96"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="78"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="82" t="s">
+      <c r="B4" s="81"/>
+      <c r="C4" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="85"/>
-      <c r="E4" s="92">
+      <c r="D4" s="67"/>
+      <c r="E4" s="75">
         <v>85</v>
       </c>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="78"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="92">
+      <c r="D5" s="67"/>
+      <c r="E5" s="75">
         <v>35</v>
       </c>
-      <c r="F5" s="85"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="104" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="105"/>
-      <c r="E6" s="104">
+      <c r="D6" s="61"/>
+      <c r="E6" s="60">
         <v>85</v>
       </c>
-      <c r="F6" s="105"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="78"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="104" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104">
+      <c r="D7" s="61"/>
+      <c r="E7" s="60">
         <v>5</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="78"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="104" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="105"/>
-      <c r="E8" s="104">
+      <c r="D8" s="61"/>
+      <c r="E8" s="60">
         <v>5</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="78"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="104" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104">
+      <c r="D9" s="61"/>
+      <c r="E9" s="60">
         <v>5</v>
       </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="78"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="83" t="s">
+      <c r="B10" s="82"/>
+      <c r="C10" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="86"/>
-      <c r="E10" s="93">
+      <c r="D10" s="69"/>
+      <c r="E10" s="76">
         <v>5</v>
       </c>
-      <c r="F10" s="86"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="78"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="78"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="81">
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="62">
         <f>SUM(E3:F10)</f>
         <v>260</v>
       </c>
-      <c r="F12" s="81"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="78"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="76"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="78"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -8680,26 +8824,84 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="8.88671875" style="116"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="106" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="110" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="111"/>
+      <c r="D2" s="110" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="112"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="109"/>
+      <c r="B3" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="114" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="115" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="117"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8741,7 +8943,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="104" t="s">
         <v>138</v>
       </c>
       <c r="B2" s="23">
@@ -8760,12 +8962,12 @@
       <c r="G2" s="25">
         <v>0</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="104" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
+      <c r="A3" s="105"/>
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -8780,10 +8982,10 @@
       <c r="G3" s="25">
         <v>0</v>
       </c>
-      <c r="H3" s="75"/>
+      <c r="H3" s="105"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
+      <c r="A4" s="105"/>
       <c r="B4" s="23">
         <v>1</v>
       </c>
@@ -8800,10 +9002,10 @@
       <c r="G4" s="25">
         <v>200</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="105"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
+      <c r="A5" s="105"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -8814,10 +9016,10 @@
       <c r="G5" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="75"/>
+      <c r="H5" s="105"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
+      <c r="A6" s="105"/>
       <c r="B6" s="23">
         <v>1</v>
       </c>
@@ -8834,10 +9036,10 @@
       <c r="G6" s="25">
         <v>0</v>
       </c>
-      <c r="H6" s="75"/>
+      <c r="H6" s="105"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="23">
         <v>1</v>
       </c>
@@ -8852,10 +9054,10 @@
       <c r="G7" s="25">
         <v>0</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="105"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="27">
         <v>1</v>
       </c>
@@ -8872,10 +9074,10 @@
       <c r="G8" s="25">
         <v>50</v>
       </c>
-      <c r="H8" s="75"/>
+      <c r="H8" s="105"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
+      <c r="A9" s="105"/>
       <c r="B9" s="27">
         <v>1</v>
       </c>
@@ -8885,10 +9087,10 @@
       <c r="D9" s="23"/>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="75"/>
+      <c r="H9" s="105"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
+      <c r="A10" s="105"/>
       <c r="B10" s="27">
         <v>1</v>
       </c>
@@ -8901,10 +9103,10 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="25"/>
-      <c r="H10" s="75"/>
+      <c r="H10" s="105"/>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
+      <c r="A11" s="105"/>
       <c r="B11" s="23">
         <v>1</v>
       </c>
@@ -8915,10 +9117,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="75"/>
+      <c r="H11" s="105"/>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="23">
         <v>1</v>
       </c>
@@ -8929,10 +9131,10 @@
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="75"/>
+      <c r="H12" s="105"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="23">
         <v>1</v>
       </c>
@@ -8943,10 +9145,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="75"/>
+      <c r="H13" s="105"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
+      <c r="A14" s="105"/>
       <c r="B14" s="23">
         <v>1</v>
       </c>
@@ -8955,10 +9157,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="75"/>
+      <c r="H14" s="105"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -8969,10 +9171,10 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="75"/>
+      <c r="H15" s="105"/>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="23">
         <v>1</v>
       </c>
@@ -8983,10 +9185,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
-      <c r="H16" s="75"/>
+      <c r="H16" s="105"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="27">
         <v>7</v>
       </c>
@@ -8995,70 +9197,70 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="75"/>
+      <c r="H17" s="105"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
+      <c r="A18" s="105"/>
       <c r="B18" s="27"/>
       <c r="C18" s="33"/>
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="75"/>
+      <c r="H18" s="105"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="27"/>
       <c r="C19" s="33"/>
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="75"/>
+      <c r="H19" s="105"/>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="27"/>
       <c r="C20" s="33"/>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="75"/>
+      <c r="H20" s="105"/>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
+      <c r="A21" s="105"/>
       <c r="B21" s="27"/>
       <c r="C21" s="33"/>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="75"/>
+      <c r="H21" s="105"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
+      <c r="A22" s="105"/>
       <c r="B22" s="27"/>
       <c r="C22" s="33"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="75"/>
+      <c r="H22" s="105"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
+      <c r="A23" s="105"/>
       <c r="B23" s="27"/>
       <c r="C23" s="34"/>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="75"/>
+      <c r="H23" s="105"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="23">
         <v>1</v>
       </c>
@@ -9069,10 +9271,10 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25"/>
-      <c r="H24" s="75"/>
+      <c r="H24" s="105"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="23">
         <v>1</v>
       </c>
@@ -9083,10 +9285,10 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="25"/>
-      <c r="H25" s="75"/>
+      <c r="H25" s="105"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
+      <c r="A26" s="105"/>
       <c r="B26" s="23">
         <v>1</v>
       </c>
@@ -9097,10 +9299,10 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
-      <c r="H26" s="75"/>
+      <c r="H26" s="105"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
+      <c r="A27" s="105"/>
       <c r="B27" s="23">
         <v>1</v>
       </c>
@@ -9109,10 +9311,10 @@
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25"/>
-      <c r="H27" s="75"/>
+      <c r="H27" s="105"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="23">
         <v>1</v>
       </c>
@@ -9121,10 +9323,10 @@
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="75"/>
+      <c r="H28" s="105"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
+      <c r="A29" s="105"/>
       <c r="B29" s="23">
         <v>1</v>
       </c>
@@ -9140,10 +9342,10 @@
       <c r="G29" s="25">
         <v>50</v>
       </c>
-      <c r="H29" s="75"/>
+      <c r="H29" s="105"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
+      <c r="A30" s="105"/>
       <c r="B30" s="23">
         <v>6</v>
       </c>
@@ -9154,40 +9356,40 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25"/>
-      <c r="H30" s="75"/>
+      <c r="H30" s="105"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
+      <c r="A31" s="105"/>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="25"/>
-      <c r="H31" s="75"/>
+      <c r="H31" s="105"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
-      <c r="H32" s="75"/>
+      <c r="H32" s="105"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25"/>
-      <c r="H33" s="75"/>
+      <c r="H33" s="105"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
+      <c r="A34" s="105"/>
       <c r="B34" s="23">
         <v>1</v>
       </c>
@@ -9200,10 +9402,10 @@
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="75"/>
+      <c r="H34" s="105"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
+      <c r="A35" s="105"/>
       <c r="B35" s="23">
         <v>1</v>
       </c>
@@ -9214,10 +9416,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25"/>
-      <c r="H35" s="75"/>
+      <c r="H35" s="105"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="23">
         <v>1</v>
       </c>
@@ -9234,10 +9436,10 @@
       <c r="G36" s="25">
         <v>200</v>
       </c>
-      <c r="H36" s="75"/>
+      <c r="H36" s="105"/>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
+      <c r="A37" s="105"/>
       <c r="B37" s="23">
         <v>2</v>
       </c>
@@ -9248,10 +9450,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="75"/>
+      <c r="H37" s="105"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
+      <c r="A38" s="105"/>
       <c r="B38" s="23">
         <v>4</v>
       </c>
@@ -9266,10 +9468,10 @@
       <c r="G38" s="25">
         <v>250</v>
       </c>
-      <c r="H38" s="75"/>
+      <c r="H38" s="105"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
+      <c r="A39" s="105"/>
       <c r="B39" s="23">
         <v>4</v>
       </c>
@@ -9284,37 +9486,37 @@
       <c r="G39" s="25">
         <v>250</v>
       </c>
-      <c r="H39" s="75"/>
+      <c r="H39" s="105"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="75"/>
+      <c r="H40" s="105"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="75"/>
+      <c r="H41" s="105"/>
     </row>
     <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
+      <c r="A42" s="105"/>
       <c r="B42" s="36"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="75"/>
+      <c r="H42" s="105"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="38" t="s">
@@ -10458,7 +10660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11472,7 +11674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8981C4AF-D0EE-42AB-8143-04EA83E0C1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA59B0F6-AEBC-45F4-84B6-6B4FFC0ED210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4668" yWindow="2664" windowWidth="18192" windowHeight="8916" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="1" r:id="rId1"/>
-    <sheet name="Fiber" sheetId="5" r:id="rId2"/>
-    <sheet name="Equipment" sheetId="6" r:id="rId3"/>
-    <sheet name="MDF" sheetId="2" r:id="rId4"/>
-    <sheet name="IDF1" sheetId="3" r:id="rId5"/>
-    <sheet name="IDF..." sheetId="4" r:id="rId6"/>
+    <sheet name="Traffic Estimation" sheetId="7" r:id="rId2"/>
+    <sheet name="Fiber" sheetId="5" r:id="rId3"/>
+    <sheet name="Equipment" sheetId="6" r:id="rId4"/>
+    <sheet name="MDF" sheetId="2" r:id="rId5"/>
+    <sheet name="IDF1" sheetId="3" r:id="rId6"/>
+    <sheet name="IDF..." sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -110,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="205">
   <si>
     <t>Room Nr</t>
   </si>
@@ -677,6 +678,54 @@
   </si>
   <si>
     <t>Choice 1 (CISCO)</t>
+  </si>
+  <si>
+    <t>Number of workstations</t>
+  </si>
+  <si>
+    <t>Number of IP phones</t>
+  </si>
+  <si>
+    <t>Number of access points</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>Estimated Average Traffic</t>
+  </si>
+  <si>
+    <t>Workstation</t>
+  </si>
+  <si>
+    <t>IP phone</t>
+  </si>
+  <si>
+    <t>Access Point</t>
+  </si>
+  <si>
+    <t>Number of rooms</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>GROUND FLOOR</t>
+  </si>
+  <si>
+    <t>FIRST FLOOR</t>
+  </si>
+  <si>
+    <t>Total Estimated Traffic [Gbps]</t>
+  </si>
+  <si>
+    <t>Estimated Traffic/Room [Gbps]</t>
+  </si>
+  <si>
+    <t>Number of simple outlets</t>
+  </si>
+  <si>
+    <t>Total number of double outlets</t>
   </si>
 </sst>
 </file>
@@ -853,7 +902,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="80">
     <border>
       <left/>
       <right/>
@@ -1640,11 +1689,243 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1723,6 +2004,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1744,6 +2031,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1755,8 +2047,6 @@
     <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1778,34 +2068,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1817,10 +2098,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1835,6 +2113,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1844,22 +2125,97 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2218,17 +2574,17 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="79"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -2414,31 +2770,31 @@
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="73"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="76"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2836,31 +3192,31 @@
       <c r="A24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="73"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="78"/>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="76"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="81"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -3046,17 +3402,17 @@
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="79"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="75"/>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -3242,31 +3598,31 @@
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="80" t="s">
+      <c r="B37" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="73"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="78"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="74"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="76"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="81"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -3276,18 +3632,18 @@
         <v>39</v>
       </c>
       <c r="C39" s="7">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D39" s="7">
         <v>12.5</v>
       </c>
       <c r="E39" s="6">
         <f t="shared" ref="E39:E44" si="18">C39*D39</f>
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="F39" s="6">
         <f t="shared" ref="F39:F44" si="19">ROUNDUP(E39/10,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" s="7">
         <v>10.5</v>
@@ -3298,7 +3654,7 @@
       </c>
       <c r="I39" s="9">
         <f t="shared" ref="I39:I44" si="20">2*F39*(G39+H39+6)</f>
-        <v>552</v>
+        <v>483</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>60</v>
@@ -3494,13 +3850,13 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13">
         <f>SUM(F22:F44)</f>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="14"/>
       <c r="I45" s="13">
         <f>SUM(I22:I44)</f>
-        <v>12327.039999999999</v>
+        <v>12258.039999999999</v>
       </c>
       <c r="J45" s="15"/>
     </row>
@@ -3592,17 +3948,17 @@
       <c r="A49" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="89" t="s">
+      <c r="B49" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="78"/>
-      <c r="D49" s="78"/>
-      <c r="E49" s="78"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="78"/>
-      <c r="H49" s="78"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="79"/>
+      <c r="C49" s="74"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="75"/>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -3788,31 +4144,31 @@
       <c r="A55" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="71" t="s">
+      <c r="B55" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="72"/>
-      <c r="D55" s="72"/>
-      <c r="E55" s="72"/>
-      <c r="F55" s="72"/>
-      <c r="G55" s="72"/>
-      <c r="H55" s="72"/>
-      <c r="I55" s="72"/>
-      <c r="J55" s="73"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="77"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="77"/>
+      <c r="I55" s="77"/>
+      <c r="J55" s="78"/>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="74"/>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="75"/>
-      <c r="J56" s="76"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="80"/>
+      <c r="J56" s="81"/>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -4210,31 +4566,31 @@
       <c r="A69" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="71" t="s">
+      <c r="B69" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="72"/>
-      <c r="I69" s="72"/>
-      <c r="J69" s="73"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="77"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="77"/>
+      <c r="I69" s="77"/>
+      <c r="J69" s="78"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="74"/>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="76"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="80"/>
+      <c r="F70" s="80"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="81"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
@@ -4384,17 +4740,17 @@
       <c r="A75" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="77" t="s">
+      <c r="B75" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="78"/>
-      <c r="D75" s="78"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="78"/>
-      <c r="G75" s="78"/>
-      <c r="H75" s="78"/>
-      <c r="I75" s="78"/>
-      <c r="J75" s="79"/>
+      <c r="C75" s="74"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="74"/>
+      <c r="J75" s="75"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
@@ -4404,18 +4760,18 @@
         <v>88</v>
       </c>
       <c r="C76" s="7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D76" s="7">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="E76" s="6">
         <f t="shared" ref="E76:E80" si="36">C76*D76</f>
-        <v>16</v>
+        <v>42.75</v>
       </c>
       <c r="F76" s="6">
         <f t="shared" ref="F76:F80" si="37">ROUNDUP(E76/10,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G76" s="7">
         <v>11.5</v>
@@ -4426,7 +4782,7 @@
       </c>
       <c r="I76" s="9">
         <f t="shared" ref="I76:I80" si="38">2*F76*(G76+H76+6)</f>
-        <v>122</v>
+        <v>305</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>52</v>
@@ -4580,31 +4936,31 @@
       <c r="A81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B81" s="80" t="s">
+      <c r="B81" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="72"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="72"/>
-      <c r="J81" s="73"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="77"/>
+      <c r="G81" s="77"/>
+      <c r="H81" s="77"/>
+      <c r="I81" s="77"/>
+      <c r="J81" s="78"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="74"/>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="75"/>
-      <c r="F82" s="75"/>
-      <c r="G82" s="75"/>
-      <c r="H82" s="75"/>
-      <c r="I82" s="75"/>
-      <c r="J82" s="76"/>
+      <c r="B82" s="79"/>
+      <c r="C82" s="80"/>
+      <c r="D82" s="80"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="80"/>
+      <c r="G82" s="80"/>
+      <c r="H82" s="80"/>
+      <c r="I82" s="80"/>
+      <c r="J82" s="81"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
@@ -4614,18 +4970,18 @@
         <v>88</v>
       </c>
       <c r="C83" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D83" s="7">
         <v>12.5</v>
       </c>
       <c r="E83" s="6">
         <f t="shared" ref="E83:E88" si="39">C83*D83</f>
-        <v>81.25</v>
+        <v>68.75</v>
       </c>
       <c r="F83" s="6">
         <f t="shared" ref="F83:F88" si="40">ROUNDUP(E83/10,0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G83" s="7">
         <v>10.5</v>
@@ -4636,7 +4992,7 @@
       </c>
       <c r="I83" s="9">
         <f t="shared" ref="I83:I88" si="41">2*F83*(G83+H83+6)</f>
-        <v>621</v>
+        <v>483</v>
       </c>
       <c r="J83" s="10" t="s">
         <v>60</v>
@@ -4650,18 +5006,18 @@
         <v>88</v>
       </c>
       <c r="C84" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D84" s="7">
         <v>12.5</v>
       </c>
       <c r="E84" s="6">
         <f t="shared" si="39"/>
-        <v>81.25</v>
+        <v>68.75</v>
       </c>
       <c r="F84" s="6">
         <f t="shared" si="40"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G84" s="7">
         <v>17.5</v>
@@ -4672,7 +5028,7 @@
       </c>
       <c r="I84" s="9">
         <f t="shared" si="41"/>
-        <v>747</v>
+        <v>581</v>
       </c>
       <c r="J84" s="10" t="s">
         <v>60</v>
@@ -4832,13 +5188,13 @@
       <c r="E89" s="13"/>
       <c r="F89" s="13">
         <f>SUM(F67:F88)</f>
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G89" s="13"/>
       <c r="H89" s="14"/>
       <c r="I89" s="13">
         <f>SUM(I67:I88)</f>
-        <v>11020.02</v>
+        <v>10899.02</v>
       </c>
       <c r="J89" s="15"/>
     </row>
@@ -4856,13 +5212,13 @@
       <c r="E91" s="18"/>
       <c r="F91" s="18">
         <f>F89+F65+F45+F20</f>
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G91" s="18"/>
       <c r="H91" s="19"/>
       <c r="I91" s="18">
         <f>I89+I65+I45+I20</f>
-        <v>57307.380000000005</v>
+        <v>57117.380000000005</v>
       </c>
       <c r="J91" s="15"/>
     </row>
@@ -4899,13 +5255,13 @@
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="87" t="s">
+      <c r="A97" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="88"/>
+      <c r="B97" s="91"/>
       <c r="C97" s="18">
         <f>I91/(F91*2)</f>
-        <v>53.358826815642459</v>
+        <v>53.380728971962618</v>
       </c>
       <c r="H97" s="17"/>
       <c r="J97" s="15"/>
@@ -4915,42 +5271,42 @@
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="86" t="s">
+      <c r="A99" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="82"/>
-      <c r="C99" s="82"/>
-      <c r="D99" s="82"/>
-      <c r="E99" s="82"/>
-      <c r="F99" s="82"/>
-      <c r="G99" s="82"/>
-      <c r="H99" s="83"/>
+      <c r="B99" s="85"/>
+      <c r="C99" s="85"/>
+      <c r="D99" s="85"/>
+      <c r="E99" s="85"/>
+      <c r="F99" s="85"/>
+      <c r="G99" s="85"/>
+      <c r="H99" s="86"/>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="85" t="s">
+      <c r="A100" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="83"/>
+      <c r="B100" s="86"/>
       <c r="H100" s="17"/>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="84" t="s">
+      <c r="A101" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="83"/>
+      <c r="B101" s="86"/>
       <c r="H101" s="17"/>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="81" t="s">
+      <c r="A102" s="84" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="82"/>
-      <c r="C102" s="82"/>
-      <c r="D102" s="82"/>
-      <c r="E102" s="83"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="86"/>
       <c r="H102" s="17"/>
       <c r="J102" s="15"/>
     </row>
@@ -8552,13 +8908,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B55:J56"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B37:J38"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B75:J75"/>
     <mergeCell ref="B81:J82"/>
@@ -8567,6 +8916,13 @@
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A97:B97"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
@@ -8584,6 +8940,826 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6D2DF1-EEB7-4492-8A92-1BDE7B755239}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" style="119" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" style="119" customWidth="1"/>
+    <col min="3" max="4" width="26" style="119" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" style="119" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" style="119" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" style="119" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" style="119" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" style="119" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="119"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="129" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="120"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="127" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="128"/>
+      <c r="D2" s="120"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="122" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="125"/>
+      <c r="D3" s="120"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="123" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="126"/>
+      <c r="D4" s="120"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="130" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="131" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="130" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="131" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="130" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="138" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="132" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="121">
+        <v>1</v>
+      </c>
+      <c r="D10" s="124">
+        <f>E10*C10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="135">
+        <f>SUM($B$2*F10,$B$3*G10,$B$4*H10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="132">
+        <v>10</v>
+      </c>
+      <c r="G10" s="124">
+        <v>1</v>
+      </c>
+      <c r="H10" s="132">
+        <v>1</v>
+      </c>
+      <c r="I10" s="125">
+        <f>SUM(F10:H10)*C10</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="139"/>
+      <c r="B11" s="133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="122">
+        <v>1</v>
+      </c>
+      <c r="D11" s="125">
+        <f t="shared" ref="D11:D33" si="0">E11*C11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="136">
+        <f>SUM($B$2*F11,$B$3*G11,$B$4*H11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="133">
+        <v>10</v>
+      </c>
+      <c r="G11" s="125">
+        <v>1</v>
+      </c>
+      <c r="H11" s="133">
+        <v>1</v>
+      </c>
+      <c r="I11" s="125">
+        <f t="shared" ref="I11:I33" si="1">SUM(F11:H11)*C11</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="139"/>
+      <c r="B12" s="133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="122">
+        <v>5</v>
+      </c>
+      <c r="D12" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="136">
+        <f>SUM($B$2*F12,$B$3*G12,$B$4*H12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="133">
+        <v>8</v>
+      </c>
+      <c r="G12" s="125">
+        <v>1</v>
+      </c>
+      <c r="H12" s="133">
+        <v>1</v>
+      </c>
+      <c r="I12" s="125">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="139"/>
+      <c r="B13" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="122">
+        <v>1</v>
+      </c>
+      <c r="D13" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="136">
+        <f>SUM($B$2*F13,$B$3*G13,$B$4*H13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="133">
+        <v>16</v>
+      </c>
+      <c r="G13" s="125">
+        <v>2</v>
+      </c>
+      <c r="H13" s="133">
+        <v>2</v>
+      </c>
+      <c r="I13" s="125">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="139"/>
+      <c r="B14" s="133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="122">
+        <v>7</v>
+      </c>
+      <c r="D14" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="136">
+        <f>SUM($B$2*F14,$B$3*G14,$B$4*H14)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="133">
+        <v>14</v>
+      </c>
+      <c r="G14" s="125">
+        <v>1</v>
+      </c>
+      <c r="H14" s="133">
+        <v>1</v>
+      </c>
+      <c r="I14" s="125">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="139"/>
+      <c r="B15" s="133" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="122">
+        <v>1</v>
+      </c>
+      <c r="D15" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="136">
+        <f>SUM($B$2*F15,$B$3*G15,$B$4*H15)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="133">
+        <v>63</v>
+      </c>
+      <c r="G15" s="125">
+        <v>1</v>
+      </c>
+      <c r="H15" s="133">
+        <v>2</v>
+      </c>
+      <c r="I15" s="125">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="139"/>
+      <c r="B16" s="133" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="122">
+        <v>2</v>
+      </c>
+      <c r="D16" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="136">
+        <f>SUM($B$2*F16,$B$3*G16,$B$4*H16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="133">
+        <v>37</v>
+      </c>
+      <c r="G16" s="125">
+        <v>1</v>
+      </c>
+      <c r="H16" s="133">
+        <v>2</v>
+      </c>
+      <c r="I16" s="125">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="139"/>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="122">
+        <v>2</v>
+      </c>
+      <c r="D17" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="136">
+        <f>SUM($B$2*F17,$B$3*G17,$B$4*H17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="133">
+        <v>15</v>
+      </c>
+      <c r="G17" s="125">
+        <v>1</v>
+      </c>
+      <c r="H17" s="133">
+        <v>2</v>
+      </c>
+      <c r="I17" s="125">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="139"/>
+      <c r="B18" s="133" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="122">
+        <v>2</v>
+      </c>
+      <c r="D18" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="136">
+        <f>SUM($B$2*F18,$B$3*G18,$B$4*H18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="133">
+        <v>10</v>
+      </c>
+      <c r="G18" s="125">
+        <v>1</v>
+      </c>
+      <c r="H18" s="133">
+        <v>1</v>
+      </c>
+      <c r="I18" s="125">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="139"/>
+      <c r="B19" s="133" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="122">
+        <v>5</v>
+      </c>
+      <c r="D19" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="136">
+        <f>SUM($B$2*F19,$B$3*G19,$B$4*H19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="133">
+        <v>8</v>
+      </c>
+      <c r="G19" s="125">
+        <v>1</v>
+      </c>
+      <c r="H19" s="133">
+        <v>1</v>
+      </c>
+      <c r="I19" s="125">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="139"/>
+      <c r="B20" s="133" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="122">
+        <v>6</v>
+      </c>
+      <c r="D20" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="136">
+        <f>SUM($B$2*F20,$B$3*G20,$B$4*H20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="133">
+        <v>12</v>
+      </c>
+      <c r="G20" s="125">
+        <v>1</v>
+      </c>
+      <c r="H20" s="133">
+        <v>1</v>
+      </c>
+      <c r="I20" s="125">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="140"/>
+      <c r="B21" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="123">
+        <v>0</v>
+      </c>
+      <c r="D21" s="126">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="137">
+        <f>SUM($B$2*F21,$B$3*G21,$B$4*H21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="134">
+        <v>12</v>
+      </c>
+      <c r="G21" s="126">
+        <v>1</v>
+      </c>
+      <c r="H21" s="134">
+        <v>1</v>
+      </c>
+      <c r="I21" s="141">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="138" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="132" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="121">
+        <v>1</v>
+      </c>
+      <c r="D22" s="128">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="135">
+        <f>SUM($B$2*F22,$B$3*G22,$B$4*H22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="132">
+        <v>10</v>
+      </c>
+      <c r="G22" s="124">
+        <v>1</v>
+      </c>
+      <c r="H22" s="132">
+        <v>1</v>
+      </c>
+      <c r="I22" s="124">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="139"/>
+      <c r="B23" s="133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="122">
+        <v>1</v>
+      </c>
+      <c r="D23" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="136">
+        <f>SUM($B$2*F23,$B$3*G23,$B$4*H23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="133">
+        <v>10</v>
+      </c>
+      <c r="G23" s="125">
+        <v>1</v>
+      </c>
+      <c r="H23" s="133">
+        <v>1</v>
+      </c>
+      <c r="I23" s="125">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="139"/>
+      <c r="B24" s="133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="122">
+        <v>5</v>
+      </c>
+      <c r="D24" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="136">
+        <f>SUM($B$2*F24,$B$3*G24,$B$4*H24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="133">
+        <v>8</v>
+      </c>
+      <c r="G24" s="125">
+        <v>1</v>
+      </c>
+      <c r="H24" s="133">
+        <v>1</v>
+      </c>
+      <c r="I24" s="125">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="139"/>
+      <c r="B25" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="122">
+        <v>1</v>
+      </c>
+      <c r="D25" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="136">
+        <f>SUM($B$2*F25,$B$3*G25,$B$4*H25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="133">
+        <v>16</v>
+      </c>
+      <c r="G25" s="125">
+        <v>2</v>
+      </c>
+      <c r="H25" s="133">
+        <v>2</v>
+      </c>
+      <c r="I25" s="125">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="139"/>
+      <c r="B26" s="133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="122">
+        <v>7</v>
+      </c>
+      <c r="D26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="136">
+        <f>SUM($B$2*F26,$B$3*G26,$B$4*H26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="133">
+        <v>14</v>
+      </c>
+      <c r="G26" s="125">
+        <v>1</v>
+      </c>
+      <c r="H26" s="133">
+        <v>1</v>
+      </c>
+      <c r="I26" s="125">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="133" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="122">
+        <v>1</v>
+      </c>
+      <c r="D27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="136">
+        <f>SUM($B$2*F27,$B$3*G27,$B$4*H27)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="133">
+        <v>63</v>
+      </c>
+      <c r="G27" s="125">
+        <v>1</v>
+      </c>
+      <c r="H27" s="133">
+        <v>2</v>
+      </c>
+      <c r="I27" s="125">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="139"/>
+      <c r="B28" s="133" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="122">
+        <v>2</v>
+      </c>
+      <c r="D28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="136">
+        <f>SUM($B$2*F28,$B$3*G28,$B$4*H28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="133">
+        <v>37</v>
+      </c>
+      <c r="G28" s="125">
+        <v>1</v>
+      </c>
+      <c r="H28" s="133">
+        <v>2</v>
+      </c>
+      <c r="I28" s="125">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="139"/>
+      <c r="B29" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="122">
+        <v>0</v>
+      </c>
+      <c r="D29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="136">
+        <f>SUM($B$2*F29,$B$3*G29,$B$4*H29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="133">
+        <v>15</v>
+      </c>
+      <c r="G29" s="125">
+        <v>1</v>
+      </c>
+      <c r="H29" s="133">
+        <v>2</v>
+      </c>
+      <c r="I29" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="139"/>
+      <c r="B30" s="133" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="122">
+        <v>2</v>
+      </c>
+      <c r="D30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="136">
+        <f>SUM($B$2*F30,$B$3*G30,$B$4*H30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="133">
+        <v>10</v>
+      </c>
+      <c r="G30" s="125">
+        <v>1</v>
+      </c>
+      <c r="H30" s="133">
+        <v>1</v>
+      </c>
+      <c r="I30" s="125">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="139"/>
+      <c r="B31" s="133" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="122">
+        <v>5</v>
+      </c>
+      <c r="D31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="136">
+        <f>SUM($B$2*F31,$B$3*G31,$B$4*H31)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="133">
+        <v>8</v>
+      </c>
+      <c r="G31" s="125">
+        <v>1</v>
+      </c>
+      <c r="H31" s="133">
+        <v>1</v>
+      </c>
+      <c r="I31" s="125">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="139"/>
+      <c r="B32" s="133" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="122">
+        <v>6</v>
+      </c>
+      <c r="D32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="136">
+        <f>SUM($B$2*F32,$B$3*G32,$B$4*H32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="133">
+        <v>12</v>
+      </c>
+      <c r="G32" s="125">
+        <v>1</v>
+      </c>
+      <c r="H32" s="133">
+        <v>1</v>
+      </c>
+      <c r="I32" s="125">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="140"/>
+      <c r="B33" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="123">
+        <v>1</v>
+      </c>
+      <c r="D33" s="126">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="137">
+        <f>SUM($B$2*F33,$B$3*G33,$B$4*H33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="134">
+        <v>12</v>
+      </c>
+      <c r="G33" s="126">
+        <v>1</v>
+      </c>
+      <c r="H33" s="134">
+        <v>1</v>
+      </c>
+      <c r="I33" s="126">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G34" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="H34" s="70"/>
+      <c r="I34" s="119">
+        <f>SUM(I10:I33)/2</f>
+        <v>535</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A10:A21"/>
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="G34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752A381D-D99A-4B9C-A646-5E0BAE1C9D7E}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8607,158 +9783,158 @@
         <v>181</v>
       </c>
       <c r="B2" s="110"/>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="105" t="s">
+      <c r="D2" s="116"/>
+      <c r="E2" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="106"/>
+      <c r="F2" s="105"/>
       <c r="G2" s="58"/>
       <c r="H2" s="56"/>
       <c r="I2" s="55"/>
       <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="90" t="s">
+      <c r="B3" s="112"/>
+      <c r="C3" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="107">
+      <c r="D3" s="107"/>
+      <c r="E3" s="106">
         <v>35</v>
       </c>
-      <c r="F3" s="98"/>
+      <c r="F3" s="107"/>
       <c r="G3" s="58"/>
       <c r="H3" s="56"/>
       <c r="I3" s="55"/>
       <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="102" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="92" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="104"/>
+      <c r="D4" s="103"/>
       <c r="E4" s="108">
         <v>85</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="103"/>
       <c r="G4" s="58"/>
       <c r="H4" s="56"/>
       <c r="I4" s="55"/>
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="102" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="92" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="102" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="104"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="108">
         <v>35</v>
       </c>
-      <c r="F5" s="104"/>
+      <c r="F5" s="103"/>
       <c r="G5" s="58"/>
       <c r="H5" s="56"/>
       <c r="I5" s="55"/>
       <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="102" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="102">
+      <c r="D6" s="93"/>
+      <c r="E6" s="92">
         <v>85</v>
       </c>
-      <c r="F6" s="103"/>
+      <c r="F6" s="93"/>
       <c r="G6" s="58"/>
       <c r="H6" s="56"/>
       <c r="I6" s="55"/>
       <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="103"/>
-      <c r="C7" s="102" t="s">
+      <c r="B7" s="93"/>
+      <c r="C7" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="103"/>
-      <c r="E7" s="102">
+      <c r="D7" s="93"/>
+      <c r="E7" s="92">
         <v>5</v>
       </c>
-      <c r="F7" s="103"/>
+      <c r="F7" s="93"/>
       <c r="G7" s="58"/>
       <c r="H7" s="56"/>
       <c r="I7" s="55"/>
       <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="103"/>
-      <c r="C8" s="102" t="s">
+      <c r="B8" s="93"/>
+      <c r="C8" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="102">
+      <c r="D8" s="93"/>
+      <c r="E8" s="92">
         <v>5</v>
       </c>
-      <c r="F8" s="103"/>
+      <c r="F8" s="93"/>
       <c r="G8" s="58"/>
       <c r="H8" s="56"/>
       <c r="I8" s="55"/>
       <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="102" t="s">
+      <c r="A9" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="103"/>
-      <c r="C9" s="102" t="s">
+      <c r="B9" s="93"/>
+      <c r="C9" s="92" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="103"/>
-      <c r="E9" s="102">
+      <c r="D9" s="93"/>
+      <c r="E9" s="92">
         <v>5</v>
       </c>
-      <c r="F9" s="103"/>
+      <c r="F9" s="93"/>
       <c r="G9" s="58"/>
       <c r="H9" s="56"/>
       <c r="I9" s="55"/>
       <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="94" t="s">
+      <c r="B10" s="114"/>
+      <c r="C10" s="95" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="114">
+      <c r="D10" s="96"/>
+      <c r="E10" s="98">
         <v>5</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="96"/>
       <c r="G10" s="58"/>
       <c r="H10" s="56"/>
       <c r="I10" s="55"/>
@@ -8776,17 +9952,17 @@
       <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="113"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="111">
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="94">
         <f>SUM(E3:F10)</f>
         <v>260</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="94"/>
       <c r="G12" s="55"/>
       <c r="H12" s="56"/>
       <c r="I12" s="55"/>
@@ -8806,13 +9982,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -8829,47 +10005,47 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="69" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="71"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="69" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="66" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="66"/>
+      <c r="E2" s="68"/>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="70"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="60" t="s">
         <v>186</v>
       </c>
@@ -8897,7 +10073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8939,7 +10115,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="117" t="s">
         <v>138</v>
       </c>
       <c r="B2" s="23">
@@ -8958,12 +10134,12 @@
       <c r="G2" s="25">
         <v>0</v>
       </c>
-      <c r="H2" s="115" t="s">
+      <c r="H2" s="117" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="116"/>
+      <c r="A3" s="118"/>
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -8978,10 +10154,10 @@
       <c r="G3" s="25">
         <v>0</v>
       </c>
-      <c r="H3" s="116"/>
+      <c r="H3" s="118"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116"/>
+      <c r="A4" s="118"/>
       <c r="B4" s="23">
         <v>1</v>
       </c>
@@ -8998,10 +10174,10 @@
       <c r="G4" s="25">
         <v>200</v>
       </c>
-      <c r="H4" s="116"/>
+      <c r="H4" s="118"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -9012,10 +10188,10 @@
       <c r="G5" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="116"/>
+      <c r="H5" s="118"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="116"/>
+      <c r="A6" s="118"/>
       <c r="B6" s="23">
         <v>1</v>
       </c>
@@ -9032,10 +10208,10 @@
       <c r="G6" s="25">
         <v>0</v>
       </c>
-      <c r="H6" s="116"/>
+      <c r="H6" s="118"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="23">
         <v>1</v>
       </c>
@@ -9050,10 +10226,10 @@
       <c r="G7" s="25">
         <v>0</v>
       </c>
-      <c r="H7" s="116"/>
+      <c r="H7" s="118"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="27">
         <v>1</v>
       </c>
@@ -9070,10 +10246,10 @@
       <c r="G8" s="25">
         <v>50</v>
       </c>
-      <c r="H8" s="116"/>
+      <c r="H8" s="118"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="116"/>
+      <c r="A9" s="118"/>
       <c r="B9" s="27">
         <v>1</v>
       </c>
@@ -9083,10 +10259,10 @@
       <c r="D9" s="23"/>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="116"/>
+      <c r="H9" s="118"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="27">
         <v>1</v>
       </c>
@@ -9099,10 +10275,10 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="25"/>
-      <c r="H10" s="116"/>
+      <c r="H10" s="118"/>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="23">
         <v>1</v>
       </c>
@@ -9113,10 +10289,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="116"/>
+      <c r="H11" s="118"/>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="23">
         <v>1</v>
       </c>
@@ -9127,10 +10303,10 @@
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="116"/>
+      <c r="H12" s="118"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="116"/>
+      <c r="A13" s="118"/>
       <c r="B13" s="23">
         <v>1</v>
       </c>
@@ -9141,10 +10317,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="116"/>
+      <c r="H13" s="118"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="116"/>
+      <c r="A14" s="118"/>
       <c r="B14" s="23">
         <v>1</v>
       </c>
@@ -9153,10 +10329,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="116"/>
+      <c r="H14" s="118"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -9167,10 +10343,10 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="116"/>
+      <c r="H15" s="118"/>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="23">
         <v>1</v>
       </c>
@@ -9181,10 +10357,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
-      <c r="H16" s="116"/>
+      <c r="H16" s="118"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="116"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="27">
         <v>7</v>
       </c>
@@ -9193,70 +10369,70 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="116"/>
+      <c r="H17" s="118"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="116"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="27"/>
       <c r="C18" s="33"/>
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="116"/>
+      <c r="H18" s="118"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="27"/>
       <c r="C19" s="33"/>
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="116"/>
+      <c r="H19" s="118"/>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="27"/>
       <c r="C20" s="33"/>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="116"/>
+      <c r="H20" s="118"/>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="27"/>
       <c r="C21" s="33"/>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="116"/>
+      <c r="H21" s="118"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="116"/>
+      <c r="A22" s="118"/>
       <c r="B22" s="27"/>
       <c r="C22" s="33"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="116"/>
+      <c r="H22" s="118"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="116"/>
+      <c r="A23" s="118"/>
       <c r="B23" s="27"/>
       <c r="C23" s="34"/>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="116"/>
+      <c r="H23" s="118"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="116"/>
+      <c r="A24" s="118"/>
       <c r="B24" s="23">
         <v>1</v>
       </c>
@@ -9267,10 +10443,10 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25"/>
-      <c r="H24" s="116"/>
+      <c r="H24" s="118"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="116"/>
+      <c r="A25" s="118"/>
       <c r="B25" s="23">
         <v>1</v>
       </c>
@@ -9281,10 +10457,10 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="25"/>
-      <c r="H25" s="116"/>
+      <c r="H25" s="118"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="116"/>
+      <c r="A26" s="118"/>
       <c r="B26" s="23">
         <v>1</v>
       </c>
@@ -9295,10 +10471,10 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
-      <c r="H26" s="116"/>
+      <c r="H26" s="118"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="116"/>
+      <c r="A27" s="118"/>
       <c r="B27" s="23">
         <v>1</v>
       </c>
@@ -9307,10 +10483,10 @@
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25"/>
-      <c r="H27" s="116"/>
+      <c r="H27" s="118"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116"/>
+      <c r="A28" s="118"/>
       <c r="B28" s="23">
         <v>1</v>
       </c>
@@ -9319,10 +10495,10 @@
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="116"/>
+      <c r="H28" s="118"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="116"/>
+      <c r="A29" s="118"/>
       <c r="B29" s="23">
         <v>1</v>
       </c>
@@ -9338,10 +10514,10 @@
       <c r="G29" s="25">
         <v>50</v>
       </c>
-      <c r="H29" s="116"/>
+      <c r="H29" s="118"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="116"/>
+      <c r="A30" s="118"/>
       <c r="B30" s="23">
         <v>6</v>
       </c>
@@ -9352,40 +10528,40 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25"/>
-      <c r="H30" s="116"/>
+      <c r="H30" s="118"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="116"/>
+      <c r="A31" s="118"/>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="25"/>
-      <c r="H31" s="116"/>
+      <c r="H31" s="118"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="116"/>
+      <c r="A32" s="118"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
-      <c r="H32" s="116"/>
+      <c r="H32" s="118"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="116"/>
+      <c r="A33" s="118"/>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25"/>
-      <c r="H33" s="116"/>
+      <c r="H33" s="118"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="116"/>
+      <c r="A34" s="118"/>
       <c r="B34" s="23">
         <v>1</v>
       </c>
@@ -9398,10 +10574,10 @@
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="116"/>
+      <c r="H34" s="118"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="116"/>
+      <c r="A35" s="118"/>
       <c r="B35" s="23">
         <v>1</v>
       </c>
@@ -9412,10 +10588,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25"/>
-      <c r="H35" s="116"/>
+      <c r="H35" s="118"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116"/>
+      <c r="A36" s="118"/>
       <c r="B36" s="23">
         <v>1</v>
       </c>
@@ -9432,10 +10608,10 @@
       <c r="G36" s="25">
         <v>200</v>
       </c>
-      <c r="H36" s="116"/>
+      <c r="H36" s="118"/>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="116"/>
+      <c r="A37" s="118"/>
       <c r="B37" s="23">
         <v>2</v>
       </c>
@@ -9446,10 +10622,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="116"/>
+      <c r="H37" s="118"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="116"/>
+      <c r="A38" s="118"/>
       <c r="B38" s="23">
         <v>4</v>
       </c>
@@ -9464,10 +10640,10 @@
       <c r="G38" s="25">
         <v>250</v>
       </c>
-      <c r="H38" s="116"/>
+      <c r="H38" s="118"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="116"/>
+      <c r="A39" s="118"/>
       <c r="B39" s="23">
         <v>4</v>
       </c>
@@ -9482,37 +10658,37 @@
       <c r="G39" s="25">
         <v>250</v>
       </c>
-      <c r="H39" s="116"/>
+      <c r="H39" s="118"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="116"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="116"/>
+      <c r="H40" s="118"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="116"/>
+      <c r="A41" s="118"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="116"/>
+      <c r="H41" s="118"/>
     </row>
     <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="116"/>
+      <c r="A42" s="118"/>
       <c r="B42" s="36"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="116"/>
+      <c r="H42" s="118"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="38" t="s">
@@ -10656,7 +11832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11670,7 +12846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA59B0F6-AEBC-45F4-84B6-6B4FFC0ED210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962371DD-3EFD-469D-ABE9-A6D73125D0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="1" r:id="rId1"/>
-    <sheet name="Traffic Estimation" sheetId="7" r:id="rId2"/>
-    <sheet name="Fiber" sheetId="5" r:id="rId3"/>
-    <sheet name="Equipment" sheetId="6" r:id="rId4"/>
-    <sheet name="MDF" sheetId="2" r:id="rId5"/>
-    <sheet name="IDF1" sheetId="3" r:id="rId6"/>
-    <sheet name="IDF..." sheetId="4" r:id="rId7"/>
+    <sheet name="Fiber" sheetId="5" r:id="rId2"/>
+    <sheet name="MDF" sheetId="2" r:id="rId3"/>
+    <sheet name="IDF1" sheetId="3" r:id="rId4"/>
+    <sheet name="IDF..." sheetId="4" r:id="rId5"/>
+    <sheet name="Traffic Estimation" sheetId="7" r:id="rId6"/>
+    <sheet name="Equipment" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="224">
   <si>
     <t>Room Nr</t>
   </si>
@@ -692,9 +692,6 @@
     <t>Device</t>
   </si>
   <si>
-    <t>Estimated Average Traffic</t>
-  </si>
-  <si>
     <t>Workstation</t>
   </si>
   <si>
@@ -725,14 +722,74 @@
     <t>Number of simple outlets</t>
   </si>
   <si>
-    <t>Total number of double outlets</t>
+    <t>Estimated Average Traffic [Mpbs]</t>
+  </si>
+  <si>
+    <t>Concurrency factor</t>
+  </si>
+  <si>
+    <t>Estimated peak traffic value in network [Gbps]</t>
+  </si>
+  <si>
+    <t>Total number of simple outlets</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>Number of switch entries</t>
+  </si>
+  <si>
+    <t>ACCESS POINT</t>
+  </si>
+  <si>
+    <t>FIREWALL</t>
+  </si>
+  <si>
+    <t>CHASSIS</t>
+  </si>
+  <si>
+    <t>SUPERVISOR</t>
+  </si>
+  <si>
+    <t>LINE CARD</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Required number/DF</t>
+  </si>
+  <si>
+    <t>Total Number</t>
+  </si>
+  <si>
+    <t>Catalyst 9610R</t>
+  </si>
+  <si>
+    <t>Secure FW 3130</t>
+  </si>
+  <si>
+    <t>Catalyst 9178AXI</t>
+  </si>
+  <si>
+    <t>IP PHONES</t>
+  </si>
+  <si>
+    <t>CP-8851</t>
+  </si>
+  <si>
+    <t>C9610-SUP-2 (+ L3 switching)</t>
+  </si>
+  <si>
+    <t>C9600-LC-48TX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,6 +862,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -902,7 +974,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="81">
     <border>
       <left/>
       <right/>
@@ -1639,60 +1711,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1863,19 +1881,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1921,11 +1926,76 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1994,48 +2064,75 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2047,6 +2144,8 @@
     <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2068,25 +2167,40 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2097,9 +2211,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2113,9 +2224,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2125,99 +2233,87 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="79" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -2574,17 +2670,17 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -2770,31 +2866,31 @@
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="78"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="85"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="81"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -3192,31 +3288,31 @@
       <c r="A24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="78"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="85"/>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="81"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="88"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -3402,17 +3498,17 @@
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="75"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="91"/>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -3598,31 +3694,31 @@
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="78"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="85"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="79"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="81"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="88"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -3948,17 +4044,17 @@
       <c r="A49" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="75"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="90"/>
+      <c r="F49" s="90"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="91"/>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -4144,31 +4240,31 @@
       <c r="A55" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="76" t="s">
+      <c r="B55" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="77"/>
-      <c r="D55" s="77"/>
-      <c r="E55" s="77"/>
-      <c r="F55" s="77"/>
-      <c r="G55" s="77"/>
-      <c r="H55" s="77"/>
-      <c r="I55" s="77"/>
-      <c r="J55" s="78"/>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="85"/>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="79"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="80"/>
-      <c r="I56" s="80"/>
-      <c r="J56" s="81"/>
+      <c r="B56" s="86"/>
+      <c r="C56" s="87"/>
+      <c r="D56" s="87"/>
+      <c r="E56" s="87"/>
+      <c r="F56" s="87"/>
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="87"/>
+      <c r="J56" s="88"/>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -4566,31 +4662,31 @@
       <c r="A69" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="76" t="s">
+      <c r="B69" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="77"/>
-      <c r="G69" s="77"/>
-      <c r="H69" s="77"/>
-      <c r="I69" s="77"/>
-      <c r="J69" s="78"/>
+      <c r="C69" s="84"/>
+      <c r="D69" s="84"/>
+      <c r="E69" s="84"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="84"/>
+      <c r="H69" s="84"/>
+      <c r="I69" s="84"/>
+      <c r="J69" s="85"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
-      <c r="E70" s="80"/>
-      <c r="F70" s="80"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="80"/>
-      <c r="I70" s="80"/>
-      <c r="J70" s="81"/>
+      <c r="B70" s="86"/>
+      <c r="C70" s="87"/>
+      <c r="D70" s="87"/>
+      <c r="E70" s="87"/>
+      <c r="F70" s="87"/>
+      <c r="G70" s="87"/>
+      <c r="H70" s="87"/>
+      <c r="I70" s="87"/>
+      <c r="J70" s="88"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
@@ -4740,17 +4836,17 @@
       <c r="A75" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="82" t="s">
+      <c r="B75" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="75"/>
+      <c r="C75" s="90"/>
+      <c r="D75" s="90"/>
+      <c r="E75" s="90"/>
+      <c r="F75" s="90"/>
+      <c r="G75" s="90"/>
+      <c r="H75" s="90"/>
+      <c r="I75" s="90"/>
+      <c r="J75" s="91"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
@@ -4936,31 +5032,31 @@
       <c r="A81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B81" s="83" t="s">
+      <c r="B81" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="77"/>
-      <c r="H81" s="77"/>
-      <c r="I81" s="77"/>
-      <c r="J81" s="78"/>
+      <c r="C81" s="84"/>
+      <c r="D81" s="84"/>
+      <c r="E81" s="84"/>
+      <c r="F81" s="84"/>
+      <c r="G81" s="84"/>
+      <c r="H81" s="84"/>
+      <c r="I81" s="84"/>
+      <c r="J81" s="85"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="79"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="81"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="87"/>
+      <c r="D82" s="87"/>
+      <c r="E82" s="87"/>
+      <c r="F82" s="87"/>
+      <c r="G82" s="87"/>
+      <c r="H82" s="87"/>
+      <c r="I82" s="87"/>
+      <c r="J82" s="88"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
@@ -5255,10 +5351,10 @@
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="90" t="s">
+      <c r="A97" s="99" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="91"/>
+      <c r="B97" s="100"/>
       <c r="C97" s="18">
         <f>I91/(F91*2)</f>
         <v>53.380728971962618</v>
@@ -5271,42 +5367,42 @@
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="89" t="s">
+      <c r="A99" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="85"/>
-      <c r="C99" s="85"/>
-      <c r="D99" s="85"/>
-      <c r="E99" s="85"/>
-      <c r="F99" s="85"/>
-      <c r="G99" s="85"/>
-      <c r="H99" s="86"/>
+      <c r="B99" s="94"/>
+      <c r="C99" s="94"/>
+      <c r="D99" s="94"/>
+      <c r="E99" s="94"/>
+      <c r="F99" s="94"/>
+      <c r="G99" s="94"/>
+      <c r="H99" s="95"/>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="88" t="s">
+      <c r="A100" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="86"/>
+      <c r="B100" s="95"/>
       <c r="H100" s="17"/>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="87" t="s">
+      <c r="A101" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="86"/>
+      <c r="B101" s="95"/>
       <c r="H101" s="17"/>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="84" t="s">
+      <c r="A102" s="93" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="86"/>
+      <c r="B102" s="94"/>
+      <c r="C102" s="94"/>
+      <c r="D102" s="94"/>
+      <c r="E102" s="95"/>
       <c r="H102" s="17"/>
       <c r="J102" s="15"/>
     </row>
@@ -8908,6 +9004,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B37:J38"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B75:J75"/>
     <mergeCell ref="B81:J82"/>
@@ -8916,13 +9019,6 @@
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A97:B97"/>
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B55:J56"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
@@ -8940,1001 +9036,181 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6D2DF1-EEB7-4492-8A92-1BDE7B755239}">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22.33203125" style="119" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" style="119" customWidth="1"/>
-    <col min="3" max="4" width="26" style="119" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" style="119" customWidth="1"/>
-    <col min="6" max="6" width="24.21875" style="119" customWidth="1"/>
-    <col min="7" max="7" width="19.77734375" style="119" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" style="119" customWidth="1"/>
-    <col min="9" max="9" width="22.6640625" style="119" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="119"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="130" t="s">
-        <v>193</v>
-      </c>
-      <c r="D1" s="120"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="127" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="128"/>
-      <c r="D2" s="120"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="122" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="125"/>
-      <c r="D3" s="120"/>
-    </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="123" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="126"/>
-      <c r="D4" s="120"/>
-    </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="130" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="131" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="130" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="G9" s="131" t="s">
-        <v>190</v>
-      </c>
-      <c r="H9" s="65" t="s">
-        <v>191</v>
-      </c>
-      <c r="I9" s="130" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="138" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" s="132" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="121">
-        <v>1</v>
-      </c>
-      <c r="D10" s="124">
-        <f>E10*C10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="135">
-        <f>SUM($B$2*F10,$B$3*G10,$B$4*H10)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="132">
-        <v>10</v>
-      </c>
-      <c r="G10" s="124">
-        <v>1</v>
-      </c>
-      <c r="H10" s="132">
-        <v>1</v>
-      </c>
-      <c r="I10" s="125">
-        <f>SUM(F10:H10)*C10</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="139"/>
-      <c r="B11" s="133" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="122">
-        <v>1</v>
-      </c>
-      <c r="D11" s="125">
-        <f t="shared" ref="D11:D33" si="0">E11*C11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="136">
-        <f>SUM($B$2*F11,$B$3*G11,$B$4*H11)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="133">
-        <v>10</v>
-      </c>
-      <c r="G11" s="125">
-        <v>1</v>
-      </c>
-      <c r="H11" s="133">
-        <v>1</v>
-      </c>
-      <c r="I11" s="125">
-        <f t="shared" ref="I11:I33" si="1">SUM(F11:H11)*C11</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="139"/>
-      <c r="B12" s="133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="122">
-        <v>5</v>
-      </c>
-      <c r="D12" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="136">
-        <f>SUM($B$2*F12,$B$3*G12,$B$4*H12)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="133">
-        <v>8</v>
-      </c>
-      <c r="G12" s="125">
-        <v>1</v>
-      </c>
-      <c r="H12" s="133">
-        <v>1</v>
-      </c>
-      <c r="I12" s="125">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="139"/>
-      <c r="B13" s="133" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="122">
-        <v>1</v>
-      </c>
-      <c r="D13" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="136">
-        <f>SUM($B$2*F13,$B$3*G13,$B$4*H13)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="133">
-        <v>16</v>
-      </c>
-      <c r="G13" s="125">
-        <v>2</v>
-      </c>
-      <c r="H13" s="133">
-        <v>2</v>
-      </c>
-      <c r="I13" s="125">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="139"/>
-      <c r="B14" s="133" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="122">
-        <v>7</v>
-      </c>
-      <c r="D14" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="136">
-        <f>SUM($B$2*F14,$B$3*G14,$B$4*H14)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="133">
-        <v>14</v>
-      </c>
-      <c r="G14" s="125">
-        <v>1</v>
-      </c>
-      <c r="H14" s="133">
-        <v>1</v>
-      </c>
-      <c r="I14" s="125">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="139"/>
-      <c r="B15" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="122">
-        <v>1</v>
-      </c>
-      <c r="D15" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="136">
-        <f>SUM($B$2*F15,$B$3*G15,$B$4*H15)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="133">
-        <v>63</v>
-      </c>
-      <c r="G15" s="125">
-        <v>1</v>
-      </c>
-      <c r="H15" s="133">
-        <v>2</v>
-      </c>
-      <c r="I15" s="125">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="139"/>
-      <c r="B16" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="122">
-        <v>2</v>
-      </c>
-      <c r="D16" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="136">
-        <f>SUM($B$2*F16,$B$3*G16,$B$4*H16)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="133">
-        <v>37</v>
-      </c>
-      <c r="G16" s="125">
-        <v>1</v>
-      </c>
-      <c r="H16" s="133">
-        <v>2</v>
-      </c>
-      <c r="I16" s="125">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="139"/>
-      <c r="B17" s="133" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="122">
-        <v>2</v>
-      </c>
-      <c r="D17" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="136">
-        <f>SUM($B$2*F17,$B$3*G17,$B$4*H17)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="133">
-        <v>15</v>
-      </c>
-      <c r="G17" s="125">
-        <v>1</v>
-      </c>
-      <c r="H17" s="133">
-        <v>2</v>
-      </c>
-      <c r="I17" s="125">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="139"/>
-      <c r="B18" s="133" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="122">
-        <v>2</v>
-      </c>
-      <c r="D18" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="136">
-        <f>SUM($B$2*F18,$B$3*G18,$B$4*H18)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="133">
-        <v>10</v>
-      </c>
-      <c r="G18" s="125">
-        <v>1</v>
-      </c>
-      <c r="H18" s="133">
-        <v>1</v>
-      </c>
-      <c r="I18" s="125">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="139"/>
-      <c r="B19" s="133" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="122">
-        <v>5</v>
-      </c>
-      <c r="D19" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="136">
-        <f>SUM($B$2*F19,$B$3*G19,$B$4*H19)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="133">
-        <v>8</v>
-      </c>
-      <c r="G19" s="125">
-        <v>1</v>
-      </c>
-      <c r="H19" s="133">
-        <v>1</v>
-      </c>
-      <c r="I19" s="125">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="139"/>
-      <c r="B20" s="133" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="122">
-        <v>6</v>
-      </c>
-      <c r="D20" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="136">
-        <f>SUM($B$2*F20,$B$3*G20,$B$4*H20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="133">
-        <v>12</v>
-      </c>
-      <c r="G20" s="125">
-        <v>1</v>
-      </c>
-      <c r="H20" s="133">
-        <v>1</v>
-      </c>
-      <c r="I20" s="125">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="140"/>
-      <c r="B21" s="134" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="123">
-        <v>0</v>
-      </c>
-      <c r="D21" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="137">
-        <f>SUM($B$2*F21,$B$3*G21,$B$4*H21)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="134">
-        <v>12</v>
-      </c>
-      <c r="G21" s="126">
-        <v>1</v>
-      </c>
-      <c r="H21" s="134">
-        <v>1</v>
-      </c>
-      <c r="I21" s="141">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="138" t="s">
-        <v>200</v>
-      </c>
-      <c r="B22" s="132" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="121">
-        <v>1</v>
-      </c>
-      <c r="D22" s="128">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="135">
-        <f>SUM($B$2*F22,$B$3*G22,$B$4*H22)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="132">
-        <v>10</v>
-      </c>
-      <c r="G22" s="124">
-        <v>1</v>
-      </c>
-      <c r="H22" s="132">
-        <v>1</v>
-      </c>
-      <c r="I22" s="124">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="139"/>
-      <c r="B23" s="133" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="122">
-        <v>1</v>
-      </c>
-      <c r="D23" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="136">
-        <f>SUM($B$2*F23,$B$3*G23,$B$4*H23)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="133">
-        <v>10</v>
-      </c>
-      <c r="G23" s="125">
-        <v>1</v>
-      </c>
-      <c r="H23" s="133">
-        <v>1</v>
-      </c>
-      <c r="I23" s="125">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="139"/>
-      <c r="B24" s="133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="122">
-        <v>5</v>
-      </c>
-      <c r="D24" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="136">
-        <f>SUM($B$2*F24,$B$3*G24,$B$4*H24)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="133">
-        <v>8</v>
-      </c>
-      <c r="G24" s="125">
-        <v>1</v>
-      </c>
-      <c r="H24" s="133">
-        <v>1</v>
-      </c>
-      <c r="I24" s="125">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="139"/>
-      <c r="B25" s="133" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="122">
-        <v>1</v>
-      </c>
-      <c r="D25" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="136">
-        <f>SUM($B$2*F25,$B$3*G25,$B$4*H25)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="133">
-        <v>16</v>
-      </c>
-      <c r="G25" s="125">
-        <v>2</v>
-      </c>
-      <c r="H25" s="133">
-        <v>2</v>
-      </c>
-      <c r="I25" s="125">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="139"/>
-      <c r="B26" s="133" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="122">
-        <v>7</v>
-      </c>
-      <c r="D26" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="136">
-        <f>SUM($B$2*F26,$B$3*G26,$B$4*H26)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="133">
-        <v>14</v>
-      </c>
-      <c r="G26" s="125">
-        <v>1</v>
-      </c>
-      <c r="H26" s="133">
-        <v>1</v>
-      </c>
-      <c r="I26" s="125">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="139"/>
-      <c r="B27" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="122">
-        <v>1</v>
-      </c>
-      <c r="D27" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="136">
-        <f>SUM($B$2*F27,$B$3*G27,$B$4*H27)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="133">
-        <v>63</v>
-      </c>
-      <c r="G27" s="125">
-        <v>1</v>
-      </c>
-      <c r="H27" s="133">
-        <v>2</v>
-      </c>
-      <c r="I27" s="125">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="139"/>
-      <c r="B28" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="122">
-        <v>2</v>
-      </c>
-      <c r="D28" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="136">
-        <f>SUM($B$2*F28,$B$3*G28,$B$4*H28)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="133">
-        <v>37</v>
-      </c>
-      <c r="G28" s="125">
-        <v>1</v>
-      </c>
-      <c r="H28" s="133">
-        <v>2</v>
-      </c>
-      <c r="I28" s="125">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="139"/>
-      <c r="B29" s="133" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="122">
-        <v>0</v>
-      </c>
-      <c r="D29" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="136">
-        <f>SUM($B$2*F29,$B$3*G29,$B$4*H29)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="133">
-        <v>15</v>
-      </c>
-      <c r="G29" s="125">
-        <v>1</v>
-      </c>
-      <c r="H29" s="133">
-        <v>2</v>
-      </c>
-      <c r="I29" s="125">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="139"/>
-      <c r="B30" s="133" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="122">
-        <v>2</v>
-      </c>
-      <c r="D30" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="136">
-        <f>SUM($B$2*F30,$B$3*G30,$B$4*H30)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="133">
-        <v>10</v>
-      </c>
-      <c r="G30" s="125">
-        <v>1</v>
-      </c>
-      <c r="H30" s="133">
-        <v>1</v>
-      </c>
-      <c r="I30" s="125">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="139"/>
-      <c r="B31" s="133" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="122">
-        <v>5</v>
-      </c>
-      <c r="D31" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="136">
-        <f>SUM($B$2*F31,$B$3*G31,$B$4*H31)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="133">
-        <v>8</v>
-      </c>
-      <c r="G31" s="125">
-        <v>1</v>
-      </c>
-      <c r="H31" s="133">
-        <v>1</v>
-      </c>
-      <c r="I31" s="125">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="139"/>
-      <c r="B32" s="133" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="122">
-        <v>6</v>
-      </c>
-      <c r="D32" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="136">
-        <f>SUM($B$2*F32,$B$3*G32,$B$4*H32)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="133">
-        <v>12</v>
-      </c>
-      <c r="G32" s="125">
-        <v>1</v>
-      </c>
-      <c r="H32" s="133">
-        <v>1</v>
-      </c>
-      <c r="I32" s="125">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="140"/>
-      <c r="B33" s="134" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="123">
-        <v>1</v>
-      </c>
-      <c r="D33" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="137">
-        <f>SUM($B$2*F33,$B$3*G33,$B$4*H33)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="134">
-        <v>12</v>
-      </c>
-      <c r="G33" s="126">
-        <v>1</v>
-      </c>
-      <c r="H33" s="134">
-        <v>1</v>
-      </c>
-      <c r="I33" s="126">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G34" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="H34" s="70"/>
-      <c r="I34" s="119">
-        <f>SUM(I10:I33)/2</f>
-        <v>535</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:A21"/>
-    <mergeCell ref="A22:A33"/>
-    <mergeCell ref="G34:H34"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752A381D-D99A-4B9C-A646-5E0BAE1C9D7E}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="113" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="101"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="59"/>
       <c r="H1" s="56"/>
       <c r="I1" s="55"/>
       <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="115" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="108" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="116"/>
-      <c r="E2" s="104" t="s">
+      <c r="D2" s="109"/>
+      <c r="E2" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="105"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="58"/>
       <c r="H2" s="56"/>
       <c r="I2" s="55"/>
       <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="111" t="s">
+      <c r="B3" s="103"/>
+      <c r="C3" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="107"/>
-      <c r="E3" s="106">
+      <c r="D3" s="110"/>
+      <c r="E3" s="119">
         <v>35</v>
       </c>
-      <c r="F3" s="107"/>
+      <c r="F3" s="110"/>
       <c r="G3" s="58"/>
       <c r="H3" s="56"/>
       <c r="I3" s="55"/>
       <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="102" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="103"/>
-      <c r="E4" s="108">
+      <c r="D4" s="116"/>
+      <c r="E4" s="120">
         <v>85</v>
       </c>
-      <c r="F4" s="103"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="58"/>
       <c r="H4" s="56"/>
       <c r="I4" s="55"/>
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="104" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="102" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="103"/>
-      <c r="E5" s="108">
+      <c r="D5" s="116"/>
+      <c r="E5" s="120">
         <v>35</v>
       </c>
-      <c r="F5" s="103"/>
+      <c r="F5" s="116"/>
       <c r="G5" s="58"/>
       <c r="H5" s="56"/>
       <c r="I5" s="55"/>
       <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="111" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="92" t="s">
+      <c r="B6" s="112"/>
+      <c r="C6" s="111" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="93"/>
-      <c r="E6" s="92">
+      <c r="D6" s="112"/>
+      <c r="E6" s="111">
         <v>85</v>
       </c>
-      <c r="F6" s="93"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="58"/>
       <c r="H6" s="56"/>
       <c r="I6" s="55"/>
       <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="92" t="s">
+      <c r="B7" s="112"/>
+      <c r="C7" s="111" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="92">
+      <c r="D7" s="112"/>
+      <c r="E7" s="111">
         <v>5</v>
       </c>
-      <c r="F7" s="93"/>
+      <c r="F7" s="112"/>
       <c r="G7" s="58"/>
       <c r="H7" s="56"/>
       <c r="I7" s="55"/>
       <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="111" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="93"/>
-      <c r="C8" s="92" t="s">
+      <c r="B8" s="112"/>
+      <c r="C8" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="93"/>
-      <c r="E8" s="92">
+      <c r="D8" s="112"/>
+      <c r="E8" s="111">
         <v>5</v>
       </c>
-      <c r="F8" s="93"/>
+      <c r="F8" s="112"/>
       <c r="G8" s="58"/>
       <c r="H8" s="56"/>
       <c r="I8" s="55"/>
       <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="92" t="s">
+      <c r="B9" s="112"/>
+      <c r="C9" s="111" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="93"/>
-      <c r="E9" s="92">
+      <c r="D9" s="112"/>
+      <c r="E9" s="111">
         <v>5</v>
       </c>
-      <c r="F9" s="93"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="58"/>
       <c r="H9" s="56"/>
       <c r="I9" s="55"/>
       <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="114"/>
-      <c r="C10" s="95" t="s">
+      <c r="B10" s="107"/>
+      <c r="C10" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="98">
+      <c r="D10" s="124"/>
+      <c r="E10" s="126">
         <v>5</v>
       </c>
-      <c r="F10" s="96"/>
+      <c r="F10" s="124"/>
       <c r="G10" s="58"/>
       <c r="H10" s="56"/>
       <c r="I10" s="55"/>
@@ -9952,17 +9228,17 @@
       <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="125" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="94">
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="123">
         <f>SUM(E3:F10)</f>
         <v>260</v>
       </c>
-      <c r="F12" s="94"/>
+      <c r="F12" s="123"/>
       <c r="G12" s="55"/>
       <c r="H12" s="56"/>
       <c r="I12" s="55"/>
@@ -9982,13 +9258,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -10005,75 +9281,19 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="71"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="68"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="72"/>
-      <c r="B3" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="63"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10115,7 +9335,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="129" t="s">
         <v>138</v>
       </c>
       <c r="B2" s="23">
@@ -10134,12 +9354,12 @@
       <c r="G2" s="25">
         <v>0</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="H2" s="129" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="118"/>
+      <c r="A3" s="130"/>
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -10154,10 +9374,10 @@
       <c r="G3" s="25">
         <v>0</v>
       </c>
-      <c r="H3" s="118"/>
+      <c r="H3" s="130"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="118"/>
+      <c r="A4" s="130"/>
       <c r="B4" s="23">
         <v>1</v>
       </c>
@@ -10174,10 +9394,10 @@
       <c r="G4" s="25">
         <v>200</v>
       </c>
-      <c r="H4" s="118"/>
+      <c r="H4" s="130"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="118"/>
+      <c r="A5" s="130"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -10188,10 +9408,10 @@
       <c r="G5" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="118"/>
+      <c r="H5" s="130"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="118"/>
+      <c r="A6" s="130"/>
       <c r="B6" s="23">
         <v>1</v>
       </c>
@@ -10208,10 +9428,10 @@
       <c r="G6" s="25">
         <v>0</v>
       </c>
-      <c r="H6" s="118"/>
+      <c r="H6" s="130"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="118"/>
+      <c r="A7" s="130"/>
       <c r="B7" s="23">
         <v>1</v>
       </c>
@@ -10226,10 +9446,10 @@
       <c r="G7" s="25">
         <v>0</v>
       </c>
-      <c r="H7" s="118"/>
+      <c r="H7" s="130"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="118"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="27">
         <v>1</v>
       </c>
@@ -10246,10 +9466,10 @@
       <c r="G8" s="25">
         <v>50</v>
       </c>
-      <c r="H8" s="118"/>
+      <c r="H8" s="130"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="118"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="27">
         <v>1</v>
       </c>
@@ -10259,10 +9479,10 @@
       <c r="D9" s="23"/>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="118"/>
+      <c r="H9" s="130"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="118"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="27">
         <v>1</v>
       </c>
@@ -10275,10 +9495,10 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="25"/>
-      <c r="H10" s="118"/>
+      <c r="H10" s="130"/>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="118"/>
+      <c r="A11" s="130"/>
       <c r="B11" s="23">
         <v>1</v>
       </c>
@@ -10289,10 +9509,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="118"/>
+      <c r="H11" s="130"/>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="118"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="23">
         <v>1</v>
       </c>
@@ -10303,10 +9523,10 @@
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="118"/>
+      <c r="H12" s="130"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="118"/>
+      <c r="A13" s="130"/>
       <c r="B13" s="23">
         <v>1</v>
       </c>
@@ -10317,10 +9537,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="118"/>
+      <c r="H13" s="130"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="118"/>
+      <c r="A14" s="130"/>
       <c r="B14" s="23">
         <v>1</v>
       </c>
@@ -10329,10 +9549,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="118"/>
+      <c r="H14" s="130"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="118"/>
+      <c r="A15" s="130"/>
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -10343,10 +9563,10 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="118"/>
+      <c r="H15" s="130"/>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="118"/>
+      <c r="A16" s="130"/>
       <c r="B16" s="23">
         <v>1</v>
       </c>
@@ -10357,10 +9577,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
-      <c r="H16" s="118"/>
+      <c r="H16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="118"/>
+      <c r="A17" s="130"/>
       <c r="B17" s="27">
         <v>7</v>
       </c>
@@ -10369,70 +9589,70 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="118"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="118"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="27"/>
       <c r="C18" s="33"/>
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="118"/>
+      <c r="H18" s="130"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="118"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="27"/>
       <c r="C19" s="33"/>
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="118"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="118"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="27"/>
       <c r="C20" s="33"/>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="118"/>
+      <c r="H20" s="130"/>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="118"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="27"/>
       <c r="C21" s="33"/>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="118"/>
+      <c r="H21" s="130"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="118"/>
+      <c r="A22" s="130"/>
       <c r="B22" s="27"/>
       <c r="C22" s="33"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="118"/>
+      <c r="H22" s="130"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="118"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="27"/>
       <c r="C23" s="34"/>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="118"/>
+      <c r="H23" s="130"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="118"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="23">
         <v>1</v>
       </c>
@@ -10443,10 +9663,10 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25"/>
-      <c r="H24" s="118"/>
+      <c r="H24" s="130"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="118"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="23">
         <v>1</v>
       </c>
@@ -10457,10 +9677,10 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="25"/>
-      <c r="H25" s="118"/>
+      <c r="H25" s="130"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="118"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="23">
         <v>1</v>
       </c>
@@ -10471,10 +9691,10 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
-      <c r="H26" s="118"/>
+      <c r="H26" s="130"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="118"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="23">
         <v>1</v>
       </c>
@@ -10483,10 +9703,10 @@
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25"/>
-      <c r="H27" s="118"/>
+      <c r="H27" s="130"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="118"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="23">
         <v>1</v>
       </c>
@@ -10495,10 +9715,10 @@
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="118"/>
+      <c r="H28" s="130"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="118"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="23">
         <v>1</v>
       </c>
@@ -10514,10 +9734,10 @@
       <c r="G29" s="25">
         <v>50</v>
       </c>
-      <c r="H29" s="118"/>
+      <c r="H29" s="130"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="118"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="23">
         <v>6</v>
       </c>
@@ -10528,40 +9748,40 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25"/>
-      <c r="H30" s="118"/>
+      <c r="H30" s="130"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="118"/>
+      <c r="A31" s="130"/>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="25"/>
-      <c r="H31" s="118"/>
+      <c r="H31" s="130"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="118"/>
+      <c r="A32" s="130"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
-      <c r="H32" s="118"/>
+      <c r="H32" s="130"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="118"/>
+      <c r="A33" s="130"/>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25"/>
-      <c r="H33" s="118"/>
+      <c r="H33" s="130"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="118"/>
+      <c r="A34" s="130"/>
       <c r="B34" s="23">
         <v>1</v>
       </c>
@@ -10574,10 +9794,10 @@
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="118"/>
+      <c r="H34" s="130"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="118"/>
+      <c r="A35" s="130"/>
       <c r="B35" s="23">
         <v>1</v>
       </c>
@@ -10588,10 +9808,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25"/>
-      <c r="H35" s="118"/>
+      <c r="H35" s="130"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="118"/>
+      <c r="A36" s="130"/>
       <c r="B36" s="23">
         <v>1</v>
       </c>
@@ -10608,10 +9828,10 @@
       <c r="G36" s="25">
         <v>200</v>
       </c>
-      <c r="H36" s="118"/>
+      <c r="H36" s="130"/>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="118"/>
+      <c r="A37" s="130"/>
       <c r="B37" s="23">
         <v>2</v>
       </c>
@@ -10622,10 +9842,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="118"/>
+      <c r="H37" s="130"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="118"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="23">
         <v>4</v>
       </c>
@@ -10640,10 +9860,10 @@
       <c r="G38" s="25">
         <v>250</v>
       </c>
-      <c r="H38" s="118"/>
+      <c r="H38" s="130"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="118"/>
+      <c r="A39" s="130"/>
       <c r="B39" s="23">
         <v>4</v>
       </c>
@@ -10658,37 +9878,37 @@
       <c r="G39" s="25">
         <v>250</v>
       </c>
-      <c r="H39" s="118"/>
+      <c r="H39" s="130"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="118"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="118"/>
+      <c r="H40" s="130"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="118"/>
+      <c r="A41" s="130"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="118"/>
+      <c r="H41" s="130"/>
     </row>
     <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="118"/>
+      <c r="A42" s="130"/>
       <c r="B42" s="36"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="118"/>
+      <c r="H42" s="130"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="38" t="s">
@@ -11832,7 +11052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12846,7 +12066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -13858,4 +13078,1073 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6D2DF1-EEB7-4492-8A92-1BDE7B755239}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" style="62" customWidth="1"/>
+    <col min="3" max="4" width="26" style="62" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" style="62" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" style="62" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" style="62" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" style="62" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" style="62" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="63"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="71">
+        <v>25</v>
+      </c>
+      <c r="D2" s="63"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="68">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="63"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="66" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="69">
+        <v>300</v>
+      </c>
+      <c r="D4" s="63"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="62">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="73" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="73" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="64">
+        <v>1</v>
+      </c>
+      <c r="D10" s="64">
+        <f>E10*C10/1000</f>
+        <v>0.38506999999999997</v>
+      </c>
+      <c r="E10" s="67">
+        <f>SUM($B$2*F10,$B$3*G10,$B$4*H10)*$B$6</f>
+        <v>385.07</v>
+      </c>
+      <c r="F10" s="75">
+        <v>10</v>
+      </c>
+      <c r="G10" s="67">
+        <v>1</v>
+      </c>
+      <c r="H10" s="75">
+        <v>1</v>
+      </c>
+      <c r="I10" s="68">
+        <f>SUM(F10:H10)*C10</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="80"/>
+      <c r="B11" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="65">
+        <v>1</v>
+      </c>
+      <c r="D11" s="65">
+        <f t="shared" ref="D11:D33" si="0">E11*C11/1000</f>
+        <v>0.38506999999999997</v>
+      </c>
+      <c r="E11" s="68">
+        <f t="shared" ref="E11:E33" si="1">SUM($B$2*F11,$B$3*G11,$B$4*H11)*$B$6</f>
+        <v>385.07</v>
+      </c>
+      <c r="F11" s="76">
+        <v>10</v>
+      </c>
+      <c r="G11" s="68">
+        <v>1</v>
+      </c>
+      <c r="H11" s="76">
+        <v>1</v>
+      </c>
+      <c r="I11" s="68">
+        <f t="shared" ref="I11:I33" si="2">SUM(F11:H11)*C11</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="80"/>
+      <c r="B12" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="65">
+        <v>5</v>
+      </c>
+      <c r="D12" s="65">
+        <f t="shared" si="0"/>
+        <v>1.7503499999999999</v>
+      </c>
+      <c r="E12" s="68">
+        <f t="shared" si="1"/>
+        <v>350.07</v>
+      </c>
+      <c r="F12" s="76">
+        <v>8</v>
+      </c>
+      <c r="G12" s="68">
+        <v>1</v>
+      </c>
+      <c r="H12" s="76">
+        <v>1</v>
+      </c>
+      <c r="I12" s="68">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="80"/>
+      <c r="B13" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="65">
+        <v>1</v>
+      </c>
+      <c r="D13" s="65">
+        <f t="shared" si="0"/>
+        <v>0.70013999999999998</v>
+      </c>
+      <c r="E13" s="68">
+        <f t="shared" si="1"/>
+        <v>700.14</v>
+      </c>
+      <c r="F13" s="76">
+        <v>16</v>
+      </c>
+      <c r="G13" s="68">
+        <v>2</v>
+      </c>
+      <c r="H13" s="76">
+        <v>2</v>
+      </c>
+      <c r="I13" s="68">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="80"/>
+      <c r="B14" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="65">
+        <v>7</v>
+      </c>
+      <c r="D14" s="65">
+        <f t="shared" si="0"/>
+        <v>3.1854899999999997</v>
+      </c>
+      <c r="E14" s="68">
+        <f t="shared" si="1"/>
+        <v>455.07</v>
+      </c>
+      <c r="F14" s="76">
+        <v>14</v>
+      </c>
+      <c r="G14" s="68">
+        <v>1</v>
+      </c>
+      <c r="H14" s="76">
+        <v>1</v>
+      </c>
+      <c r="I14" s="68">
+        <f t="shared" si="2"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="80"/>
+      <c r="B15" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="65">
+        <v>1</v>
+      </c>
+      <c r="D15" s="65">
+        <f t="shared" si="0"/>
+        <v>1.52257</v>
+      </c>
+      <c r="E15" s="68">
+        <f t="shared" si="1"/>
+        <v>1522.57</v>
+      </c>
+      <c r="F15" s="76">
+        <v>63</v>
+      </c>
+      <c r="G15" s="68">
+        <v>1</v>
+      </c>
+      <c r="H15" s="76">
+        <v>2</v>
+      </c>
+      <c r="I15" s="68">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="80"/>
+      <c r="B16" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="65">
+        <v>2</v>
+      </c>
+      <c r="D16" s="65">
+        <f t="shared" si="0"/>
+        <v>2.1351399999999998</v>
+      </c>
+      <c r="E16" s="68">
+        <f t="shared" si="1"/>
+        <v>1067.57</v>
+      </c>
+      <c r="F16" s="76">
+        <v>37</v>
+      </c>
+      <c r="G16" s="68">
+        <v>1</v>
+      </c>
+      <c r="H16" s="76">
+        <v>2</v>
+      </c>
+      <c r="I16" s="68">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="80"/>
+      <c r="B17" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="65">
+        <v>2</v>
+      </c>
+      <c r="D17" s="65">
+        <f t="shared" si="0"/>
+        <v>1.3651399999999998</v>
+      </c>
+      <c r="E17" s="68">
+        <f t="shared" si="1"/>
+        <v>682.56999999999994</v>
+      </c>
+      <c r="F17" s="76">
+        <v>15</v>
+      </c>
+      <c r="G17" s="68">
+        <v>1</v>
+      </c>
+      <c r="H17" s="76">
+        <v>2</v>
+      </c>
+      <c r="I17" s="68">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="80"/>
+      <c r="B18" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="65">
+        <v>2</v>
+      </c>
+      <c r="D18" s="65">
+        <f t="shared" si="0"/>
+        <v>0.77013999999999994</v>
+      </c>
+      <c r="E18" s="68">
+        <f t="shared" si="1"/>
+        <v>385.07</v>
+      </c>
+      <c r="F18" s="76">
+        <v>10</v>
+      </c>
+      <c r="G18" s="68">
+        <v>1</v>
+      </c>
+      <c r="H18" s="76">
+        <v>1</v>
+      </c>
+      <c r="I18" s="68">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="80"/>
+      <c r="B19" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="65">
+        <v>5</v>
+      </c>
+      <c r="D19" s="65">
+        <f t="shared" si="0"/>
+        <v>1.7503499999999999</v>
+      </c>
+      <c r="E19" s="68">
+        <f t="shared" si="1"/>
+        <v>350.07</v>
+      </c>
+      <c r="F19" s="76">
+        <v>8</v>
+      </c>
+      <c r="G19" s="68">
+        <v>1</v>
+      </c>
+      <c r="H19" s="76">
+        <v>1</v>
+      </c>
+      <c r="I19" s="68">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="80"/>
+      <c r="B20" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="65">
+        <v>6</v>
+      </c>
+      <c r="D20" s="65">
+        <f t="shared" si="0"/>
+        <v>2.5204200000000001</v>
+      </c>
+      <c r="E20" s="68">
+        <f t="shared" si="1"/>
+        <v>420.07</v>
+      </c>
+      <c r="F20" s="76">
+        <v>12</v>
+      </c>
+      <c r="G20" s="68">
+        <v>1</v>
+      </c>
+      <c r="H20" s="76">
+        <v>1</v>
+      </c>
+      <c r="I20" s="68">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="81"/>
+      <c r="B21" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="66">
+        <v>0</v>
+      </c>
+      <c r="D21" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69">
+        <f t="shared" si="1"/>
+        <v>420.07</v>
+      </c>
+      <c r="F21" s="77">
+        <v>12</v>
+      </c>
+      <c r="G21" s="69">
+        <v>1</v>
+      </c>
+      <c r="H21" s="77">
+        <v>1</v>
+      </c>
+      <c r="I21" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="79" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="64">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70">
+        <f t="shared" si="0"/>
+        <v>0.38506999999999997</v>
+      </c>
+      <c r="E22" s="67">
+        <f>SUM($B$2*F22,$B$3*G22,$B$4*H22)*$B$6</f>
+        <v>385.07</v>
+      </c>
+      <c r="F22" s="75">
+        <v>10</v>
+      </c>
+      <c r="G22" s="67">
+        <v>1</v>
+      </c>
+      <c r="H22" s="75">
+        <v>1</v>
+      </c>
+      <c r="I22" s="67">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="80"/>
+      <c r="B23" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="65">
+        <v>1</v>
+      </c>
+      <c r="D23" s="65">
+        <f t="shared" si="0"/>
+        <v>0.38506999999999997</v>
+      </c>
+      <c r="E23" s="68">
+        <f t="shared" si="1"/>
+        <v>385.07</v>
+      </c>
+      <c r="F23" s="76">
+        <v>10</v>
+      </c>
+      <c r="G23" s="68">
+        <v>1</v>
+      </c>
+      <c r="H23" s="76">
+        <v>1</v>
+      </c>
+      <c r="I23" s="68">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="80"/>
+      <c r="B24" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="65">
+        <v>5</v>
+      </c>
+      <c r="D24" s="65">
+        <f t="shared" si="0"/>
+        <v>1.7503499999999999</v>
+      </c>
+      <c r="E24" s="68">
+        <f t="shared" si="1"/>
+        <v>350.07</v>
+      </c>
+      <c r="F24" s="76">
+        <v>8</v>
+      </c>
+      <c r="G24" s="68">
+        <v>1</v>
+      </c>
+      <c r="H24" s="76">
+        <v>1</v>
+      </c>
+      <c r="I24" s="68">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="80"/>
+      <c r="B25" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="65">
+        <v>1</v>
+      </c>
+      <c r="D25" s="65">
+        <f t="shared" si="0"/>
+        <v>0.70013999999999998</v>
+      </c>
+      <c r="E25" s="68">
+        <f t="shared" si="1"/>
+        <v>700.14</v>
+      </c>
+      <c r="F25" s="76">
+        <v>16</v>
+      </c>
+      <c r="G25" s="68">
+        <v>2</v>
+      </c>
+      <c r="H25" s="76">
+        <v>2</v>
+      </c>
+      <c r="I25" s="68">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="80"/>
+      <c r="B26" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="65">
+        <v>7</v>
+      </c>
+      <c r="D26" s="65">
+        <f t="shared" si="0"/>
+        <v>3.1854899999999997</v>
+      </c>
+      <c r="E26" s="68">
+        <f t="shared" si="1"/>
+        <v>455.07</v>
+      </c>
+      <c r="F26" s="76">
+        <v>14</v>
+      </c>
+      <c r="G26" s="68">
+        <v>1</v>
+      </c>
+      <c r="H26" s="76">
+        <v>1</v>
+      </c>
+      <c r="I26" s="68">
+        <f t="shared" si="2"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="80"/>
+      <c r="B27" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="65">
+        <v>1</v>
+      </c>
+      <c r="D27" s="65">
+        <f t="shared" si="0"/>
+        <v>1.52257</v>
+      </c>
+      <c r="E27" s="68">
+        <f t="shared" si="1"/>
+        <v>1522.57</v>
+      </c>
+      <c r="F27" s="76">
+        <v>63</v>
+      </c>
+      <c r="G27" s="68">
+        <v>1</v>
+      </c>
+      <c r="H27" s="76">
+        <v>2</v>
+      </c>
+      <c r="I27" s="68">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="80"/>
+      <c r="B28" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="65">
+        <v>2</v>
+      </c>
+      <c r="D28" s="65">
+        <f t="shared" si="0"/>
+        <v>2.1351399999999998</v>
+      </c>
+      <c r="E28" s="68">
+        <f t="shared" si="1"/>
+        <v>1067.57</v>
+      </c>
+      <c r="F28" s="76">
+        <v>37</v>
+      </c>
+      <c r="G28" s="68">
+        <v>1</v>
+      </c>
+      <c r="H28" s="76">
+        <v>2</v>
+      </c>
+      <c r="I28" s="68">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="80"/>
+      <c r="B29" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="65">
+        <v>0</v>
+      </c>
+      <c r="D29" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="68">
+        <f t="shared" si="1"/>
+        <v>682.56999999999994</v>
+      </c>
+      <c r="F29" s="76">
+        <v>15</v>
+      </c>
+      <c r="G29" s="68">
+        <v>1</v>
+      </c>
+      <c r="H29" s="76">
+        <v>2</v>
+      </c>
+      <c r="I29" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="80"/>
+      <c r="B30" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="65">
+        <v>2</v>
+      </c>
+      <c r="D30" s="65">
+        <f t="shared" si="0"/>
+        <v>0.77013999999999994</v>
+      </c>
+      <c r="E30" s="68">
+        <f t="shared" si="1"/>
+        <v>385.07</v>
+      </c>
+      <c r="F30" s="76">
+        <v>10</v>
+      </c>
+      <c r="G30" s="68">
+        <v>1</v>
+      </c>
+      <c r="H30" s="76">
+        <v>1</v>
+      </c>
+      <c r="I30" s="68">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="80"/>
+      <c r="B31" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="65">
+        <v>5</v>
+      </c>
+      <c r="D31" s="65">
+        <f t="shared" si="0"/>
+        <v>1.7503499999999999</v>
+      </c>
+      <c r="E31" s="68">
+        <f t="shared" si="1"/>
+        <v>350.07</v>
+      </c>
+      <c r="F31" s="76">
+        <v>8</v>
+      </c>
+      <c r="G31" s="68">
+        <v>1</v>
+      </c>
+      <c r="H31" s="76">
+        <v>1</v>
+      </c>
+      <c r="I31" s="68">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="80"/>
+      <c r="B32" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="65">
+        <v>6</v>
+      </c>
+      <c r="D32" s="65">
+        <f t="shared" si="0"/>
+        <v>2.5204200000000001</v>
+      </c>
+      <c r="E32" s="68">
+        <f t="shared" si="1"/>
+        <v>420.07</v>
+      </c>
+      <c r="F32" s="76">
+        <v>12</v>
+      </c>
+      <c r="G32" s="68">
+        <v>1</v>
+      </c>
+      <c r="H32" s="76">
+        <v>1</v>
+      </c>
+      <c r="I32" s="68">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="81"/>
+      <c r="B33" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="66">
+        <v>1</v>
+      </c>
+      <c r="D33" s="66">
+        <f t="shared" si="0"/>
+        <v>0.42007</v>
+      </c>
+      <c r="E33" s="69">
+        <f t="shared" si="1"/>
+        <v>420.07</v>
+      </c>
+      <c r="F33" s="77">
+        <v>12</v>
+      </c>
+      <c r="G33" s="69">
+        <v>1</v>
+      </c>
+      <c r="H33" s="77">
+        <v>1</v>
+      </c>
+      <c r="I33" s="69">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="82"/>
+      <c r="D34" s="62">
+        <f>_xlfn.CEILING.MATH(SUM(D10:D33))</f>
+        <v>32</v>
+      </c>
+      <c r="G34" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="62">
+        <f>SUM(I10:I33)</f>
+        <v>1070</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A10:A21"/>
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B34:C34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="71.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.21875" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="128"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="164"/>
+      <c r="D2" s="152" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="154"/>
+      <c r="F2" s="142" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="144" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="140"/>
+      <c r="B3" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="139"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="141"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="153" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="147" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="156" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="153"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="144" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="160"/>
+      <c r="H4" s="153"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="148" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="157" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="149" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="137"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="150"/>
+      <c r="H5" s="137"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="148" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="148" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="149" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="137"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="137"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="157" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="149" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="137"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="137"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="148" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="155" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="138"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="146"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="138"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="162" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="158" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="135"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="135"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="135" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="131" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="132">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="137" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="133">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="133">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="138" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="134">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F2:F3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{80B83815-A50D-46A4-BEA0-CF1A27585021}"/>
+    <hyperlink ref="C5:C6" r:id="rId2" display="link" xr:uid="{1266295D-E9A3-4E93-AD55-60C4C75F5D8F}"/>
+    <hyperlink ref="C8" r:id="rId3" xr:uid="{1FE0C054-3932-4DFB-A079-D528176C6357}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{86EE9E67-4350-42ED-BD92-B0D509FD78C0}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{84CA0A26-1C37-4DC1-82DB-E059761431F7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962371DD-3EFD-469D-ABE9-A6D73125D0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD1C274-3820-4CDD-8A8B-BE6F9D0E39B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cable" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="237">
   <si>
     <t>Room Nr</t>
   </si>
@@ -737,9 +737,6 @@
     <t>DF</t>
   </si>
   <si>
-    <t>Number of switch entries</t>
-  </si>
-  <si>
     <t>ACCESS POINT</t>
   </si>
   <si>
@@ -752,44 +749,86 @@
     <t>SUPERVISOR</t>
   </si>
   <si>
-    <t>LINE CARD</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
     <t>Required number/DF</t>
   </si>
   <si>
-    <t>Total Number</t>
-  </si>
-  <si>
-    <t>Catalyst 9610R</t>
-  </si>
-  <si>
-    <t>Secure FW 3130</t>
-  </si>
-  <si>
-    <t>Catalyst 9178AXI</t>
-  </si>
-  <si>
     <t>IP PHONES</t>
   </si>
   <si>
-    <t>CP-8851</t>
-  </si>
-  <si>
-    <t>C9610-SUP-2 (+ L3 switching)</t>
-  </si>
-  <si>
-    <t>C9600-LC-48TX</t>
+    <t>C9400-SUP-1XL</t>
+  </si>
+  <si>
+    <t>C9400-LC-48UXM</t>
+  </si>
+  <si>
+    <t>LINE CARD (AP)</t>
+  </si>
+  <si>
+    <t>LINE CARD (WS)</t>
+  </si>
+  <si>
+    <t>C9400-LC-48P</t>
+  </si>
+  <si>
+    <t>LINE CARD (IPPHONE)</t>
+  </si>
+  <si>
+    <t>Cisco Wireless 9179F</t>
+  </si>
+  <si>
+    <t>Cisco FirePower 4145</t>
+  </si>
+  <si>
+    <t>Cisco Catalyst 9410R</t>
+  </si>
+  <si>
+    <t>LINE CARD (OF)</t>
+  </si>
+  <si>
+    <t>C9400-LC-12QC</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Cisco IP Phone 8861</t>
+  </si>
+  <si>
+    <t>Total number of IP Phones</t>
+  </si>
+  <si>
+    <t>Total number of AP</t>
+  </si>
+  <si>
+    <t>Total number of WS</t>
+  </si>
+  <si>
+    <t>Cisco Wireless 9178</t>
+  </si>
+  <si>
+    <t>Number of WS</t>
+  </si>
+  <si>
+    <t>Number of AP</t>
+  </si>
+  <si>
+    <t>Number of IP Phones</t>
+  </si>
+  <si>
+    <t>Number of Room Types Covered</t>
+  </si>
+  <si>
+    <t>Total outlets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,14 +910,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -974,7 +1005,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="81">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1937,39 +1968,6 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1990,12 +1988,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2121,18 +2226,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2144,8 +2280,6 @@
     <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2167,40 +2301,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2211,6 +2330,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2224,6 +2346,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2233,83 +2358,178 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="79" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="74" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2670,17 +2890,17 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="91"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -2866,31 +3086,31 @@
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="85"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="103"/>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -3288,31 +3508,31 @@
       <c r="A24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="85"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="100"/>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="86"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="88"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="103"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -3498,17 +3718,17 @@
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="91"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="97"/>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -3694,31 +3914,31 @@
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="92" t="s">
+      <c r="B37" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="85"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="88"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="103"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -4044,17 +4264,17 @@
       <c r="A49" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="101" t="s">
+      <c r="B49" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90"/>
-      <c r="F49" s="90"/>
-      <c r="G49" s="90"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="91"/>
+      <c r="C49" s="96"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="97"/>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -4240,31 +4460,31 @@
       <c r="A55" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="83" t="s">
+      <c r="B55" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="84"/>
-      <c r="D55" s="84"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="84"/>
-      <c r="G55" s="84"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="84"/>
-      <c r="J55" s="85"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="100"/>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="86"/>
-      <c r="C56" s="87"/>
-      <c r="D56" s="87"/>
-      <c r="E56" s="87"/>
-      <c r="F56" s="87"/>
-      <c r="G56" s="87"/>
-      <c r="H56" s="87"/>
-      <c r="I56" s="87"/>
-      <c r="J56" s="88"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="102"/>
+      <c r="D56" s="102"/>
+      <c r="E56" s="102"/>
+      <c r="F56" s="102"/>
+      <c r="G56" s="102"/>
+      <c r="H56" s="102"/>
+      <c r="I56" s="102"/>
+      <c r="J56" s="103"/>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -4662,31 +4882,31 @@
       <c r="A69" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="83" t="s">
+      <c r="B69" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="84"/>
-      <c r="D69" s="84"/>
-      <c r="E69" s="84"/>
-      <c r="F69" s="84"/>
-      <c r="G69" s="84"/>
-      <c r="H69" s="84"/>
-      <c r="I69" s="84"/>
-      <c r="J69" s="85"/>
+      <c r="C69" s="99"/>
+      <c r="D69" s="99"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="99"/>
+      <c r="G69" s="99"/>
+      <c r="H69" s="99"/>
+      <c r="I69" s="99"/>
+      <c r="J69" s="100"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="86"/>
-      <c r="C70" s="87"/>
-      <c r="D70" s="87"/>
-      <c r="E70" s="87"/>
-      <c r="F70" s="87"/>
-      <c r="G70" s="87"/>
-      <c r="H70" s="87"/>
-      <c r="I70" s="87"/>
-      <c r="J70" s="88"/>
+      <c r="B70" s="101"/>
+      <c r="C70" s="102"/>
+      <c r="D70" s="102"/>
+      <c r="E70" s="102"/>
+      <c r="F70" s="102"/>
+      <c r="G70" s="102"/>
+      <c r="H70" s="102"/>
+      <c r="I70" s="102"/>
+      <c r="J70" s="103"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
@@ -4836,17 +5056,17 @@
       <c r="A75" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="89" t="s">
+      <c r="B75" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="90"/>
-      <c r="D75" s="90"/>
-      <c r="E75" s="90"/>
-      <c r="F75" s="90"/>
-      <c r="G75" s="90"/>
-      <c r="H75" s="90"/>
-      <c r="I75" s="90"/>
-      <c r="J75" s="91"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
+      <c r="F75" s="96"/>
+      <c r="G75" s="96"/>
+      <c r="H75" s="96"/>
+      <c r="I75" s="96"/>
+      <c r="J75" s="97"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
@@ -5032,31 +5252,31 @@
       <c r="A81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B81" s="92" t="s">
+      <c r="B81" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="84"/>
-      <c r="D81" s="84"/>
-      <c r="E81" s="84"/>
-      <c r="F81" s="84"/>
-      <c r="G81" s="84"/>
-      <c r="H81" s="84"/>
-      <c r="I81" s="84"/>
-      <c r="J81" s="85"/>
+      <c r="C81" s="99"/>
+      <c r="D81" s="99"/>
+      <c r="E81" s="99"/>
+      <c r="F81" s="99"/>
+      <c r="G81" s="99"/>
+      <c r="H81" s="99"/>
+      <c r="I81" s="99"/>
+      <c r="J81" s="100"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="87"/>
-      <c r="D82" s="87"/>
-      <c r="E82" s="87"/>
-      <c r="F82" s="87"/>
-      <c r="G82" s="87"/>
-      <c r="H82" s="87"/>
-      <c r="I82" s="87"/>
-      <c r="J82" s="88"/>
+      <c r="B82" s="101"/>
+      <c r="C82" s="102"/>
+      <c r="D82" s="102"/>
+      <c r="E82" s="102"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="102"/>
+      <c r="H82" s="102"/>
+      <c r="I82" s="102"/>
+      <c r="J82" s="103"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
@@ -5351,10 +5571,10 @@
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="99" t="s">
+      <c r="A97" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="100"/>
+      <c r="B97" s="113"/>
       <c r="C97" s="18">
         <f>I91/(F91*2)</f>
         <v>53.380728971962618</v>
@@ -5367,42 +5587,42 @@
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="98" t="s">
+      <c r="A99" s="111" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="94"/>
-      <c r="C99" s="94"/>
-      <c r="D99" s="94"/>
-      <c r="E99" s="94"/>
-      <c r="F99" s="94"/>
-      <c r="G99" s="94"/>
-      <c r="H99" s="95"/>
+      <c r="B99" s="107"/>
+      <c r="C99" s="107"/>
+      <c r="D99" s="107"/>
+      <c r="E99" s="107"/>
+      <c r="F99" s="107"/>
+      <c r="G99" s="107"/>
+      <c r="H99" s="108"/>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="97" t="s">
+      <c r="A100" s="110" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="95"/>
+      <c r="B100" s="108"/>
       <c r="H100" s="17"/>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="96" t="s">
+      <c r="A101" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="95"/>
+      <c r="B101" s="108"/>
       <c r="H101" s="17"/>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="93" t="s">
+      <c r="A102" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="94"/>
-      <c r="C102" s="94"/>
-      <c r="D102" s="94"/>
-      <c r="E102" s="95"/>
+      <c r="B102" s="107"/>
+      <c r="C102" s="107"/>
+      <c r="D102" s="107"/>
+      <c r="E102" s="108"/>
       <c r="H102" s="17"/>
       <c r="J102" s="15"/>
     </row>
@@ -9004,13 +9224,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B55:J56"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B37:J38"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B75:J75"/>
     <mergeCell ref="B81:J82"/>
@@ -9019,6 +9232,13 @@
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A97:B97"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
@@ -9041,176 +9261,176 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="115"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="123"/>
       <c r="G1" s="59"/>
       <c r="H1" s="56"/>
       <c r="I1" s="55"/>
       <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="108" t="s">
+      <c r="B2" s="132"/>
+      <c r="C2" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="109"/>
-      <c r="E2" s="117" t="s">
+      <c r="D2" s="138"/>
+      <c r="E2" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="118"/>
+      <c r="F2" s="127"/>
       <c r="G2" s="58"/>
       <c r="H2" s="56"/>
       <c r="I2" s="55"/>
       <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="133" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="102" t="s">
+      <c r="B3" s="134"/>
+      <c r="C3" s="133" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="110"/>
-      <c r="E3" s="119">
+      <c r="D3" s="129"/>
+      <c r="E3" s="128">
         <v>35</v>
       </c>
-      <c r="F3" s="110"/>
+      <c r="F3" s="129"/>
       <c r="G3" s="58"/>
       <c r="H3" s="56"/>
       <c r="I3" s="55"/>
       <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="124" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="105"/>
-      <c r="C4" s="104" t="s">
+      <c r="B4" s="135"/>
+      <c r="C4" s="124" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="120">
+      <c r="D4" s="125"/>
+      <c r="E4" s="130">
         <v>85</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="125"/>
       <c r="G4" s="58"/>
       <c r="H4" s="56"/>
       <c r="I4" s="55"/>
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="104" t="s">
+      <c r="B5" s="135"/>
+      <c r="C5" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="116"/>
-      <c r="E5" s="120">
+      <c r="D5" s="125"/>
+      <c r="E5" s="130">
         <v>35</v>
       </c>
-      <c r="F5" s="116"/>
+      <c r="F5" s="125"/>
       <c r="G5" s="58"/>
       <c r="H5" s="56"/>
       <c r="I5" s="55"/>
       <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="112"/>
-      <c r="C6" s="111" t="s">
+      <c r="B6" s="115"/>
+      <c r="C6" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="112"/>
-      <c r="E6" s="111">
+      <c r="D6" s="115"/>
+      <c r="E6" s="114">
         <v>85</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="115"/>
       <c r="G6" s="58"/>
       <c r="H6" s="56"/>
       <c r="I6" s="55"/>
       <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="112"/>
-      <c r="C7" s="111" t="s">
+      <c r="B7" s="115"/>
+      <c r="C7" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="112"/>
-      <c r="E7" s="111">
+      <c r="D7" s="115"/>
+      <c r="E7" s="114">
         <v>5</v>
       </c>
-      <c r="F7" s="112"/>
+      <c r="F7" s="115"/>
       <c r="G7" s="58"/>
       <c r="H7" s="56"/>
       <c r="I7" s="55"/>
       <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="111" t="s">
+      <c r="B8" s="115"/>
+      <c r="C8" s="114" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="111">
+      <c r="D8" s="115"/>
+      <c r="E8" s="114">
         <v>5</v>
       </c>
-      <c r="F8" s="112"/>
+      <c r="F8" s="115"/>
       <c r="G8" s="58"/>
       <c r="H8" s="56"/>
       <c r="I8" s="55"/>
       <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="111" t="s">
+      <c r="B9" s="115"/>
+      <c r="C9" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="111">
+      <c r="D9" s="115"/>
+      <c r="E9" s="114">
         <v>5</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="115"/>
       <c r="G9" s="58"/>
       <c r="H9" s="56"/>
       <c r="I9" s="55"/>
       <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="117" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="107"/>
-      <c r="C10" s="106" t="s">
+      <c r="B10" s="136"/>
+      <c r="C10" s="117" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="124"/>
-      <c r="E10" s="126">
+      <c r="D10" s="118"/>
+      <c r="E10" s="120">
         <v>5</v>
       </c>
-      <c r="F10" s="124"/>
+      <c r="F10" s="118"/>
       <c r="G10" s="58"/>
       <c r="H10" s="56"/>
       <c r="I10" s="55"/>
@@ -9228,17 +9448,17 @@
       <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="123">
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="116">
         <f>SUM(E3:F10)</f>
         <v>260</v>
       </c>
-      <c r="F12" s="123"/>
+      <c r="F12" s="116"/>
       <c r="G12" s="55"/>
       <c r="H12" s="56"/>
       <c r="I12" s="55"/>
@@ -9258,13 +9478,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -9281,13 +9501,13 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9335,7 +9555,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="139" t="s">
         <v>138</v>
       </c>
       <c r="B2" s="23">
@@ -9354,12 +9574,12 @@
       <c r="G2" s="25">
         <v>0</v>
       </c>
-      <c r="H2" s="129" t="s">
+      <c r="H2" s="139" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="130"/>
+      <c r="A3" s="140"/>
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -9374,10 +9594,10 @@
       <c r="G3" s="25">
         <v>0</v>
       </c>
-      <c r="H3" s="130"/>
+      <c r="H3" s="140"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="130"/>
+      <c r="A4" s="140"/>
       <c r="B4" s="23">
         <v>1</v>
       </c>
@@ -9394,10 +9614,10 @@
       <c r="G4" s="25">
         <v>200</v>
       </c>
-      <c r="H4" s="130"/>
+      <c r="H4" s="140"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="130"/>
+      <c r="A5" s="140"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -9408,10 +9628,10 @@
       <c r="G5" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="130"/>
+      <c r="H5" s="140"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="130"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="23">
         <v>1</v>
       </c>
@@ -9428,10 +9648,10 @@
       <c r="G6" s="25">
         <v>0</v>
       </c>
-      <c r="H6" s="130"/>
+      <c r="H6" s="140"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="130"/>
+      <c r="A7" s="140"/>
       <c r="B7" s="23">
         <v>1</v>
       </c>
@@ -9446,10 +9666,10 @@
       <c r="G7" s="25">
         <v>0</v>
       </c>
-      <c r="H7" s="130"/>
+      <c r="H7" s="140"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="130"/>
+      <c r="A8" s="140"/>
       <c r="B8" s="27">
         <v>1</v>
       </c>
@@ -9466,10 +9686,10 @@
       <c r="G8" s="25">
         <v>50</v>
       </c>
-      <c r="H8" s="130"/>
+      <c r="H8" s="140"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="130"/>
+      <c r="A9" s="140"/>
       <c r="B9" s="27">
         <v>1</v>
       </c>
@@ -9479,10 +9699,10 @@
       <c r="D9" s="23"/>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="130"/>
+      <c r="H9" s="140"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="130"/>
+      <c r="A10" s="140"/>
       <c r="B10" s="27">
         <v>1</v>
       </c>
@@ -9495,10 +9715,10 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="25"/>
-      <c r="H10" s="130"/>
+      <c r="H10" s="140"/>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="130"/>
+      <c r="A11" s="140"/>
       <c r="B11" s="23">
         <v>1</v>
       </c>
@@ -9509,10 +9729,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="130"/>
+      <c r="H11" s="140"/>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="130"/>
+      <c r="A12" s="140"/>
       <c r="B12" s="23">
         <v>1</v>
       </c>
@@ -9523,10 +9743,10 @@
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="130"/>
+      <c r="H12" s="140"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="130"/>
+      <c r="A13" s="140"/>
       <c r="B13" s="23">
         <v>1</v>
       </c>
@@ -9537,10 +9757,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="130"/>
+      <c r="H13" s="140"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="130"/>
+      <c r="A14" s="140"/>
       <c r="B14" s="23">
         <v>1</v>
       </c>
@@ -9549,10 +9769,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="130"/>
+      <c r="H14" s="140"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="130"/>
+      <c r="A15" s="140"/>
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -9563,10 +9783,10 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="130"/>
+      <c r="H15" s="140"/>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="130"/>
+      <c r="A16" s="140"/>
       <c r="B16" s="23">
         <v>1</v>
       </c>
@@ -9577,10 +9797,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
-      <c r="H16" s="130"/>
+      <c r="H16" s="140"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="130"/>
+      <c r="A17" s="140"/>
       <c r="B17" s="27">
         <v>7</v>
       </c>
@@ -9589,70 +9809,70 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="130"/>
+      <c r="H17" s="140"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="130"/>
+      <c r="A18" s="140"/>
       <c r="B18" s="27"/>
       <c r="C18" s="33"/>
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="130"/>
+      <c r="H18" s="140"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="130"/>
+      <c r="A19" s="140"/>
       <c r="B19" s="27"/>
       <c r="C19" s="33"/>
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="130"/>
+      <c r="H19" s="140"/>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="130"/>
+      <c r="A20" s="140"/>
       <c r="B20" s="27"/>
       <c r="C20" s="33"/>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="130"/>
+      <c r="H20" s="140"/>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="130"/>
+      <c r="A21" s="140"/>
       <c r="B21" s="27"/>
       <c r="C21" s="33"/>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="130"/>
+      <c r="H21" s="140"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="130"/>
+      <c r="A22" s="140"/>
       <c r="B22" s="27"/>
       <c r="C22" s="33"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="130"/>
+      <c r="H22" s="140"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="130"/>
+      <c r="A23" s="140"/>
       <c r="B23" s="27"/>
       <c r="C23" s="34"/>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="130"/>
+      <c r="H23" s="140"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="130"/>
+      <c r="A24" s="140"/>
       <c r="B24" s="23">
         <v>1</v>
       </c>
@@ -9663,10 +9883,10 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25"/>
-      <c r="H24" s="130"/>
+      <c r="H24" s="140"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="130"/>
+      <c r="A25" s="140"/>
       <c r="B25" s="23">
         <v>1</v>
       </c>
@@ -9677,10 +9897,10 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="25"/>
-      <c r="H25" s="130"/>
+      <c r="H25" s="140"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="130"/>
+      <c r="A26" s="140"/>
       <c r="B26" s="23">
         <v>1</v>
       </c>
@@ -9691,10 +9911,10 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
-      <c r="H26" s="130"/>
+      <c r="H26" s="140"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="130"/>
+      <c r="A27" s="140"/>
       <c r="B27" s="23">
         <v>1</v>
       </c>
@@ -9703,10 +9923,10 @@
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25"/>
-      <c r="H27" s="130"/>
+      <c r="H27" s="140"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="130"/>
+      <c r="A28" s="140"/>
       <c r="B28" s="23">
         <v>1</v>
       </c>
@@ -9715,10 +9935,10 @@
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="130"/>
+      <c r="H28" s="140"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="130"/>
+      <c r="A29" s="140"/>
       <c r="B29" s="23">
         <v>1</v>
       </c>
@@ -9734,10 +9954,10 @@
       <c r="G29" s="25">
         <v>50</v>
       </c>
-      <c r="H29" s="130"/>
+      <c r="H29" s="140"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="130"/>
+      <c r="A30" s="140"/>
       <c r="B30" s="23">
         <v>6</v>
       </c>
@@ -9748,40 +9968,40 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25"/>
-      <c r="H30" s="130"/>
+      <c r="H30" s="140"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="130"/>
+      <c r="A31" s="140"/>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="25"/>
-      <c r="H31" s="130"/>
+      <c r="H31" s="140"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="130"/>
+      <c r="A32" s="140"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
-      <c r="H32" s="130"/>
+      <c r="H32" s="140"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="130"/>
+      <c r="A33" s="140"/>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25"/>
-      <c r="H33" s="130"/>
+      <c r="H33" s="140"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="130"/>
+      <c r="A34" s="140"/>
       <c r="B34" s="23">
         <v>1</v>
       </c>
@@ -9794,10 +10014,10 @@
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="130"/>
+      <c r="H34" s="140"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="130"/>
+      <c r="A35" s="140"/>
       <c r="B35" s="23">
         <v>1</v>
       </c>
@@ -9808,10 +10028,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25"/>
-      <c r="H35" s="130"/>
+      <c r="H35" s="140"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="130"/>
+      <c r="A36" s="140"/>
       <c r="B36" s="23">
         <v>1</v>
       </c>
@@ -9828,10 +10048,10 @@
       <c r="G36" s="25">
         <v>200</v>
       </c>
-      <c r="H36" s="130"/>
+      <c r="H36" s="140"/>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="130"/>
+      <c r="A37" s="140"/>
       <c r="B37" s="23">
         <v>2</v>
       </c>
@@ -9842,10 +10062,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="130"/>
+      <c r="H37" s="140"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="130"/>
+      <c r="A38" s="140"/>
       <c r="B38" s="23">
         <v>4</v>
       </c>
@@ -9860,10 +10080,10 @@
       <c r="G38" s="25">
         <v>250</v>
       </c>
-      <c r="H38" s="130"/>
+      <c r="H38" s="140"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="130"/>
+      <c r="A39" s="140"/>
       <c r="B39" s="23">
         <v>4</v>
       </c>
@@ -9878,37 +10098,37 @@
       <c r="G39" s="25">
         <v>250</v>
       </c>
-      <c r="H39" s="130"/>
+      <c r="H39" s="140"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="130"/>
+      <c r="A40" s="140"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="130"/>
+      <c r="H40" s="140"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="130"/>
+      <c r="A41" s="140"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="130"/>
+      <c r="H41" s="140"/>
     </row>
     <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="130"/>
+      <c r="A42" s="140"/>
       <c r="B42" s="36"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="130"/>
+      <c r="H42" s="140"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="38" t="s">
@@ -13082,7 +13302,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6D2DF1-EEB7-4492-8A92-1BDE7B755239}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="62" customWidth="1"/>
@@ -13171,7 +13391,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="141" t="s">
         <v>198</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -13203,7 +13423,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="80"/>
+      <c r="A11" s="142"/>
       <c r="B11" s="76" t="s">
         <v>14</v>
       </c>
@@ -13233,7 +13453,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="80"/>
+      <c r="A12" s="142"/>
       <c r="B12" s="76" t="s">
         <v>17</v>
       </c>
@@ -13263,7 +13483,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="80"/>
+      <c r="A13" s="142"/>
       <c r="B13" s="76" t="s">
         <v>26</v>
       </c>
@@ -13293,7 +13513,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="80"/>
+      <c r="A14" s="142"/>
       <c r="B14" s="76" t="s">
         <v>30</v>
       </c>
@@ -13323,7 +13543,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="80"/>
+      <c r="A15" s="142"/>
       <c r="B15" s="76" t="s">
         <v>28</v>
       </c>
@@ -13353,7 +13573,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="80"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="76" t="s">
         <v>36</v>
       </c>
@@ -13383,7 +13603,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="80"/>
+      <c r="A17" s="142"/>
       <c r="B17" s="76" t="s">
         <v>45</v>
       </c>
@@ -13413,7 +13633,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="80"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="76" t="s">
         <v>48</v>
       </c>
@@ -13443,7 +13663,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="80"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="76" t="s">
         <v>52</v>
       </c>
@@ -13473,7 +13693,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="80"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="76" t="s">
         <v>60</v>
       </c>
@@ -13503,7 +13723,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="81"/>
+      <c r="A21" s="143"/>
       <c r="B21" s="77" t="s">
         <v>94</v>
       </c>
@@ -13533,7 +13753,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="141" t="s">
         <v>199</v>
       </c>
       <c r="B22" s="75" t="s">
@@ -13565,7 +13785,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="80"/>
+      <c r="A23" s="142"/>
       <c r="B23" s="76" t="s">
         <v>14</v>
       </c>
@@ -13595,7 +13815,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="80"/>
+      <c r="A24" s="142"/>
       <c r="B24" s="76" t="s">
         <v>17</v>
       </c>
@@ -13625,7 +13845,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="80"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="76" t="s">
         <v>26</v>
       </c>
@@ -13655,7 +13875,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="80"/>
+      <c r="A26" s="142"/>
       <c r="B26" s="76" t="s">
         <v>30</v>
       </c>
@@ -13685,7 +13905,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="80"/>
+      <c r="A27" s="142"/>
       <c r="B27" s="76" t="s">
         <v>28</v>
       </c>
@@ -13715,7 +13935,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="80"/>
+      <c r="A28" s="142"/>
       <c r="B28" s="76" t="s">
         <v>36</v>
       </c>
@@ -13745,7 +13965,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="80"/>
+      <c r="A29" s="142"/>
       <c r="B29" s="76" t="s">
         <v>45</v>
       </c>
@@ -13775,7 +13995,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
+      <c r="A30" s="142"/>
       <c r="B30" s="76" t="s">
         <v>48</v>
       </c>
@@ -13805,7 +14025,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="80"/>
+      <c r="A31" s="142"/>
       <c r="B31" s="76" t="s">
         <v>52</v>
       </c>
@@ -13835,7 +14055,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="80"/>
+      <c r="A32" s="142"/>
       <c r="B32" s="76" t="s">
         <v>60</v>
       </c>
@@ -13864,8 +14084,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="81"/>
+    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="143"/>
       <c r="B33" s="77" t="s">
         <v>94</v>
       </c>
@@ -13894,257 +14114,1174 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="82" t="s">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="82"/>
+      <c r="C34" s="88"/>
       <c r="D34" s="62">
         <f>_xlfn.CEILING.MATH(SUM(D10:D33))</f>
         <v>32</v>
       </c>
-      <c r="G34" s="82" t="s">
+      <c r="G34" s="88" t="s">
         <v>206</v>
       </c>
-      <c r="H34" s="82"/>
+      <c r="H34" s="88"/>
       <c r="I34" s="62">
         <f>SUM(I10:I33)</f>
         <v>1070</v>
       </c>
     </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G35" s="151" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="150"/>
+      <c r="I35" s="62">
+        <f>SUMPRODUCT(G10:G33,C10:C33)</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G36" s="151" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="150"/>
+      <c r="I36" s="62">
+        <f>SUMPRODUCT(H10:H33,C10:C33)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G37" s="151" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="150"/>
+      <c r="I37" s="62">
+        <f>SUMPRODUCT(F10:F33,C10:C33)</f>
+        <v>928</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="161" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="163" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="163" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="163" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="165" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="166"/>
+      <c r="G38" s="166"/>
+      <c r="H38" s="166"/>
+      <c r="I38" s="166"/>
+      <c r="J38" s="166"/>
+      <c r="K38" s="166"/>
+      <c r="L38" s="166"/>
+      <c r="M38" s="166"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="166"/>
+      <c r="P38" s="167"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="162"/>
+      <c r="B39" s="164"/>
+      <c r="C39" s="164"/>
+      <c r="D39" s="164"/>
+      <c r="E39" s="153" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="153" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="153" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39" s="153" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" s="153" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="153" t="s">
+        <v>48</v>
+      </c>
+      <c r="N39" s="153" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39" s="153" t="s">
+        <v>60</v>
+      </c>
+      <c r="P39" s="155" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="156" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="154" cm="1">
+        <f t="array" ref="B40">SUMPRODUCT(E40:P40,TRANSPOSE($F$10:$F$21))</f>
+        <v>246</v>
+      </c>
+      <c r="C40" s="154" cm="1">
+        <f t="array" ref="C40">SUMPRODUCT(E40:P40,TRANSPOSE($H$10:$H$21))</f>
+        <v>18</v>
+      </c>
+      <c r="D40" s="154" cm="1">
+        <f t="array" ref="D40">SUMPRODUCT(E40:P40,TRANSPOSE($G$10:$G$21))</f>
+        <v>16</v>
+      </c>
+      <c r="E40" s="154">
+        <v>1</v>
+      </c>
+      <c r="F40" s="154">
+        <v>1</v>
+      </c>
+      <c r="G40" s="154">
+        <v>5</v>
+      </c>
+      <c r="H40" s="154">
+        <v>1</v>
+      </c>
+      <c r="I40" s="154">
+        <v>5</v>
+      </c>
+      <c r="J40" s="154">
+        <v>1</v>
+      </c>
+      <c r="K40" s="154">
+        <v>1</v>
+      </c>
+      <c r="L40" s="154">
+        <v>0</v>
+      </c>
+      <c r="M40" s="154">
+        <v>0</v>
+      </c>
+      <c r="N40" s="154">
+        <v>0</v>
+      </c>
+      <c r="O40" s="154">
+        <v>0</v>
+      </c>
+      <c r="P40" s="157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="156" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="154" cm="1">
+        <f t="array" ref="B41">SUMPRODUCT(E41:P41,TRANSPOSE($F$10:$F$21))</f>
+        <v>227</v>
+      </c>
+      <c r="C41" s="154" cm="1">
+        <f t="array" ref="C41">SUMPRODUCT(E41:P41,TRANSPOSE($H$10:$H$21))</f>
+        <v>21</v>
+      </c>
+      <c r="D41" s="154" cm="1">
+        <f t="array" ref="D41">SUMPRODUCT(E41:P41,TRANSPOSE($G$10:$G$21))</f>
+        <v>18</v>
+      </c>
+      <c r="E41" s="154">
+        <v>0</v>
+      </c>
+      <c r="F41" s="154">
+        <v>0</v>
+      </c>
+      <c r="G41" s="154">
+        <v>0</v>
+      </c>
+      <c r="H41" s="154">
+        <v>0</v>
+      </c>
+      <c r="I41" s="154">
+        <v>2</v>
+      </c>
+      <c r="J41" s="154">
+        <v>0</v>
+      </c>
+      <c r="K41" s="154">
+        <v>1</v>
+      </c>
+      <c r="L41" s="154">
+        <v>2</v>
+      </c>
+      <c r="M41" s="154">
+        <v>2</v>
+      </c>
+      <c r="N41" s="154">
+        <v>5</v>
+      </c>
+      <c r="O41" s="154">
+        <v>6</v>
+      </c>
+      <c r="P41" s="157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="156" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="154" cm="1">
+        <f t="array" ref="B42">SUMPRODUCT(E42:P42,TRANSPOSE($F$10:$F$21))</f>
+        <v>246</v>
+      </c>
+      <c r="C42" s="154" cm="1">
+        <f t="array" ref="C42">SUMPRODUCT(E42:P42,TRANSPOSE($H$10:$H$21))</f>
+        <v>18</v>
+      </c>
+      <c r="D42" s="154" cm="1">
+        <f t="array" ref="D42">SUMPRODUCT(E42:P42,TRANSPOSE($G$10:$G$21))</f>
+        <v>16</v>
+      </c>
+      <c r="E42" s="154">
+        <v>1</v>
+      </c>
+      <c r="F42" s="154">
+        <v>1</v>
+      </c>
+      <c r="G42" s="154">
+        <v>5</v>
+      </c>
+      <c r="H42" s="154">
+        <v>1</v>
+      </c>
+      <c r="I42" s="154">
+        <v>5</v>
+      </c>
+      <c r="J42" s="154">
+        <v>1</v>
+      </c>
+      <c r="K42" s="154">
+        <v>1</v>
+      </c>
+      <c r="L42" s="154">
+        <v>0</v>
+      </c>
+      <c r="M42" s="154">
+        <v>0</v>
+      </c>
+      <c r="N42" s="154">
+        <v>0</v>
+      </c>
+      <c r="O42" s="154">
+        <v>0</v>
+      </c>
+      <c r="P42" s="157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="158" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="159" cm="1">
+        <f t="array" ref="B43">SUMPRODUCT(E43:P43,TRANSPOSE($F$10:$F$21))</f>
+        <v>209</v>
+      </c>
+      <c r="C43" s="159" cm="1">
+        <f t="array" ref="C43">SUMPRODUCT(E43:P43,TRANSPOSE($H$10:$H$21))</f>
+        <v>18</v>
+      </c>
+      <c r="D43" s="159" cm="1">
+        <f t="array" ref="D43">SUMPRODUCT(E43:P43,TRANSPOSE($G$10:$G$21))</f>
+        <v>17</v>
+      </c>
+      <c r="E43" s="159">
+        <v>0</v>
+      </c>
+      <c r="F43" s="159">
+        <v>0</v>
+      </c>
+      <c r="G43" s="159">
+        <v>0</v>
+      </c>
+      <c r="H43" s="159">
+        <v>0</v>
+      </c>
+      <c r="I43" s="159">
+        <v>2</v>
+      </c>
+      <c r="J43" s="159">
+        <v>0</v>
+      </c>
+      <c r="K43" s="159">
+        <v>1</v>
+      </c>
+      <c r="L43" s="159">
+        <v>0</v>
+      </c>
+      <c r="M43" s="159">
+        <v>2</v>
+      </c>
+      <c r="N43" s="159">
+        <v>5</v>
+      </c>
+      <c r="O43" s="159">
+        <v>6</v>
+      </c>
+      <c r="P43" s="160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="152" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" s="62">
+        <f>SUM(B40:D43)</f>
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="189" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" s="190"/>
+      <c r="C47" s="190"/>
+      <c r="D47" s="190"/>
+      <c r="E47" s="190"/>
+      <c r="F47" s="190"/>
+      <c r="G47" s="190"/>
+      <c r="H47" s="190"/>
+      <c r="I47" s="191"/>
+    </row>
+    <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="87" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="88"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="91"/>
+      <c r="G48" s="93" t="s">
+        <v>207</v>
+      </c>
+      <c r="H48" s="93" t="s">
+        <v>213</v>
+      </c>
+      <c r="I48" s="186"/>
+    </row>
+    <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="92"/>
+      <c r="B49" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="148" t="s">
+        <v>226</v>
+      </c>
+      <c r="D49" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="F49" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="94"/>
+      <c r="H49" s="94"/>
+      <c r="I49" s="186"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B50" s="174" t="s">
+        <v>223</v>
+      </c>
+      <c r="C50" s="175"/>
+      <c r="D50" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" s="177"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="147" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="64">
+        <v>1</v>
+      </c>
+      <c r="I50" s="187"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="178" t="s">
+        <v>211</v>
+      </c>
+      <c r="B51" s="174" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" s="175"/>
+      <c r="D51" s="179"/>
+      <c r="E51" s="180"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="145"/>
+      <c r="H51" s="65">
+        <v>1</v>
+      </c>
+      <c r="I51" s="187"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="178" t="s">
+        <v>218</v>
+      </c>
+      <c r="B52" s="168" t="s">
+        <v>219</v>
+      </c>
+      <c r="C52" s="175"/>
+      <c r="D52" s="172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="170"/>
+      <c r="F52" s="170"/>
+      <c r="G52" s="145"/>
+      <c r="H52" s="184">
+        <f>_xlfn.CEILING.MATH(SUM(B40,D40)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="I52" s="188"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="178" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" s="169"/>
+      <c r="C53" s="175"/>
+      <c r="D53" s="173"/>
+      <c r="E53" s="171"/>
+      <c r="F53" s="171"/>
+      <c r="G53" s="145"/>
+      <c r="H53" s="185"/>
+      <c r="I53" s="188"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="178" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54" s="175"/>
+      <c r="D54" s="179"/>
+      <c r="E54" s="180"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="145"/>
+      <c r="H54" s="65">
+        <v>1</v>
+      </c>
+      <c r="I54" s="187"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="178" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="181" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="178"/>
+      <c r="D55" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E55" s="180"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="145"/>
+      <c r="H55" s="65">
+        <f>_xlfn.CEILING.MATH(C40/48)</f>
+        <v>1</v>
+      </c>
+      <c r="I55" s="187"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" s="181" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56" s="178"/>
+      <c r="D56" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="180"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="145"/>
+      <c r="H56" s="65">
+        <f>C40</f>
+        <v>18</v>
+      </c>
+      <c r="I56" s="187"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="181" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" s="178"/>
+      <c r="D57" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E57" s="180"/>
+      <c r="F57" s="68"/>
+      <c r="G57" s="145"/>
+      <c r="H57" s="65">
+        <v>1</v>
+      </c>
+      <c r="I57" s="187"/>
+    </row>
+    <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" s="149" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="85"/>
+      <c r="D58" s="182"/>
+      <c r="E58" s="183"/>
+      <c r="F58" s="69"/>
+      <c r="G58" s="146"/>
+      <c r="H58" s="66">
+        <f>D40</f>
+        <v>16</v>
+      </c>
+      <c r="I58" s="187"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B59" s="174" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="175"/>
+      <c r="D59" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" s="177"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="147" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="64">
+        <v>1</v>
+      </c>
+      <c r="I59" s="187"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="178" t="s">
+        <v>211</v>
+      </c>
+      <c r="B60" s="174" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="175"/>
+      <c r="D60" s="179"/>
+      <c r="E60" s="180"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="145"/>
+      <c r="H60" s="65">
+        <v>1</v>
+      </c>
+      <c r="I60" s="187"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="178" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="168" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="168"/>
+      <c r="D61" s="172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" s="170"/>
+      <c r="F61" s="170"/>
+      <c r="G61" s="145"/>
+      <c r="H61" s="184">
+        <f>_xlfn.CEILING.MATH(SUM(B41,D41)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="I61" s="188"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="178" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62" s="169"/>
+      <c r="C62" s="169"/>
+      <c r="D62" s="173"/>
+      <c r="E62" s="171"/>
+      <c r="F62" s="171"/>
+      <c r="G62" s="145"/>
+      <c r="H62" s="185"/>
+      <c r="I62" s="188"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="178" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="C63" s="175"/>
+      <c r="D63" s="179"/>
+      <c r="E63" s="180"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="145"/>
+      <c r="H63" s="65">
+        <v>1</v>
+      </c>
+      <c r="I63" s="187"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="178" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" s="181" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="178"/>
+      <c r="D64" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E64" s="180"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="145"/>
+      <c r="H64" s="65">
+        <f>_xlfn.CEILING.MATH(C41/48)</f>
+        <v>1</v>
+      </c>
+      <c r="I64" s="187"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65" s="181" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" s="178"/>
+      <c r="D65" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E65" s="180"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="145"/>
+      <c r="H65" s="65">
+        <f>C41</f>
+        <v>21</v>
+      </c>
+      <c r="I65" s="187"/>
+    </row>
+    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B66" s="149" t="s">
+        <v>227</v>
+      </c>
+      <c r="C66" s="85"/>
+      <c r="D66" s="182"/>
+      <c r="E66" s="183"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="146"/>
+      <c r="H66" s="66">
+        <f>D41</f>
+        <v>18</v>
+      </c>
+      <c r="I66" s="187"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="174" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="175"/>
+      <c r="D67" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" s="177"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="147" t="s">
+        <v>68</v>
+      </c>
+      <c r="H67" s="64">
+        <v>1</v>
+      </c>
+      <c r="I67" s="187"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="178" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="174" t="s">
+        <v>215</v>
+      </c>
+      <c r="C68" s="175"/>
+      <c r="D68" s="179"/>
+      <c r="E68" s="180"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="145"/>
+      <c r="H68" s="65">
+        <v>1</v>
+      </c>
+      <c r="I68" s="187"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="178" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="168" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" s="168"/>
+      <c r="D69" s="172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E69" s="170"/>
+      <c r="F69" s="170"/>
+      <c r="G69" s="145"/>
+      <c r="H69" s="184">
+        <f>_xlfn.CEILING.MATH(SUM(B42,D42)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="I69" s="187"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="178" t="s">
+        <v>220</v>
+      </c>
+      <c r="B70" s="169"/>
+      <c r="C70" s="169"/>
+      <c r="D70" s="173"/>
+      <c r="E70" s="171"/>
+      <c r="F70" s="171"/>
+      <c r="G70" s="145"/>
+      <c r="H70" s="185"/>
+      <c r="I70" s="187"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="178" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="C71" s="175"/>
+      <c r="D71" s="179"/>
+      <c r="E71" s="180"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="145"/>
+      <c r="H71" s="65">
+        <v>1</v>
+      </c>
+      <c r="I71" s="187"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="178" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="181" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" s="178"/>
+      <c r="D72" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E72" s="180"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="145"/>
+      <c r="H72" s="65">
+        <f>_xlfn.CEILING.MATH(C42/48)</f>
+        <v>1</v>
+      </c>
+      <c r="I72" s="187"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B73" s="181" t="s">
+        <v>221</v>
+      </c>
+      <c r="C73" s="178"/>
+      <c r="D73" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E73" s="180"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="145"/>
+      <c r="H73" s="65">
+        <f>C42</f>
+        <v>18</v>
+      </c>
+      <c r="I73" s="187"/>
+    </row>
+    <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B74" s="149" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="85"/>
+      <c r="D74" s="182"/>
+      <c r="E74" s="183"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="146"/>
+      <c r="H74" s="66">
+        <f>D42</f>
+        <v>16</v>
+      </c>
+      <c r="I74" s="187"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B75" s="174" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="175"/>
+      <c r="D75" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E75" s="177"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="147" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" s="64">
+        <v>1</v>
+      </c>
+      <c r="I75" s="187"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="178" t="s">
+        <v>211</v>
+      </c>
+      <c r="B76" s="174" t="s">
+        <v>215</v>
+      </c>
+      <c r="C76" s="175"/>
+      <c r="D76" s="179"/>
+      <c r="E76" s="180"/>
+      <c r="F76" s="68"/>
+      <c r="G76" s="145"/>
+      <c r="H76" s="65">
+        <v>1</v>
+      </c>
+      <c r="I76" s="187"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="178" t="s">
+        <v>218</v>
+      </c>
+      <c r="B77" s="168" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="168"/>
+      <c r="D77" s="172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" s="170"/>
+      <c r="F77" s="170"/>
+      <c r="G77" s="145"/>
+      <c r="H77" s="184">
+        <f>_xlfn.CEILING.MATH(SUM(B43,D43)/48)</f>
+        <v>5</v>
+      </c>
+      <c r="I77" s="187"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="178" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="169"/>
+      <c r="C78" s="169"/>
+      <c r="D78" s="173"/>
+      <c r="E78" s="171"/>
+      <c r="F78" s="171"/>
+      <c r="G78" s="145"/>
+      <c r="H78" s="185"/>
+      <c r="I78" s="187"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="178" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" s="175"/>
+      <c r="D79" s="179"/>
+      <c r="E79" s="180"/>
+      <c r="F79" s="68"/>
+      <c r="G79" s="145"/>
+      <c r="H79" s="65">
+        <v>1</v>
+      </c>
+      <c r="I79" s="187"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="178" t="s">
+        <v>217</v>
+      </c>
+      <c r="B80" s="181" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="178"/>
+      <c r="D80" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" s="180"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="145"/>
+      <c r="H80" s="65">
+        <f>_xlfn.CEILING.MATH(C43/48)</f>
+        <v>1</v>
+      </c>
+      <c r="I80" s="187"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="181" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" s="178"/>
+      <c r="D81" s="176" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="180"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="145"/>
+      <c r="H81" s="65">
+        <f>C43</f>
+        <v>18</v>
+      </c>
+      <c r="I81" s="187"/>
+    </row>
+    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="B82" s="149" t="s">
+        <v>227</v>
+      </c>
+      <c r="C82" s="85"/>
+      <c r="D82" s="182"/>
+      <c r="E82" s="183"/>
+      <c r="F82" s="69"/>
+      <c r="G82" s="146"/>
+      <c r="H82" s="66">
+        <f>D43</f>
+        <v>17</v>
+      </c>
+      <c r="I82" s="187"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+    </row>
+    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="144">
+        <v>280</v>
+      </c>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="81">
+        <v>266</v>
+      </c>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B87" s="81">
+        <v>280</v>
+      </c>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+    </row>
+    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="82">
+        <v>244</v>
+      </c>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="48">
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:P38"/>
+    <mergeCell ref="G50:G58"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="G59:G66"/>
+    <mergeCell ref="G67:G74"/>
+    <mergeCell ref="G75:G82"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A10:A21"/>
     <mergeCell ref="A22:A33"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="G35:H35"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D57" r:id="rId1" xr:uid="{A029F0E9-C9D1-4CD2-ADE0-4784660C9D97}"/>
+    <hyperlink ref="D56" r:id="rId2" xr:uid="{857B9BB1-3282-4DA1-96F1-AAF639475A2D}"/>
+    <hyperlink ref="D55" r:id="rId3" xr:uid="{F6634F98-8A1B-4296-BD90-DA744A704792}"/>
+    <hyperlink ref="D52" r:id="rId4" xr:uid="{4EB1002D-512E-490E-8CE7-EC79EF9020B5}"/>
+    <hyperlink ref="D50" r:id="rId5" xr:uid="{883103FA-02FE-4CB6-A102-CF901C48D85E}"/>
+    <hyperlink ref="D59" r:id="rId6" xr:uid="{D897E3EA-4B88-4B07-8E04-9BC62AA8DE11}"/>
+    <hyperlink ref="D65" r:id="rId7" xr:uid="{881D9D2F-DA17-40C4-AA3C-EF0106248703}"/>
+    <hyperlink ref="D64" r:id="rId8" xr:uid="{AA809D2B-FA2E-4C7A-A7B7-4832F6E4D09E}"/>
+    <hyperlink ref="D61" r:id="rId9" xr:uid="{C8C2BF74-BEEC-4D78-81DC-1C5EAC1A63DA}"/>
+    <hyperlink ref="D67" r:id="rId10" xr:uid="{D2753667-397D-495A-9EFF-B90CDE17CC24}"/>
+    <hyperlink ref="D73" r:id="rId11" xr:uid="{509B4E63-2B9B-4B39-AE71-EC1816BD00CA}"/>
+    <hyperlink ref="D72" r:id="rId12" xr:uid="{A9DD4DFE-201F-431D-BB40-6EDD85971C07}"/>
+    <hyperlink ref="D69" r:id="rId13" xr:uid="{7056E575-1D4F-4EF2-89C3-BBB0B9A6A6BD}"/>
+    <hyperlink ref="D75" r:id="rId14" xr:uid="{339D2A8A-3C61-4946-8E27-FBC09434974D}"/>
+    <hyperlink ref="D81" r:id="rId15" xr:uid="{CE0123D6-F228-4B48-B3A9-3B41355BD82C}"/>
+    <hyperlink ref="D80" r:id="rId16" xr:uid="{ADA3AFEC-EFC1-4367-AF19-DAEAF49BD26A}"/>
+    <hyperlink ref="D77" r:id="rId17" xr:uid="{4C3B922A-447E-41C3-9BF0-53BEF1EE6AA2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="71.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.21875" customWidth="1"/>
-    <col min="7" max="7" width="24.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="128"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="127" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="164"/>
-      <c r="D2" s="152" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="154"/>
-      <c r="F2" s="142" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="144" t="s">
-        <v>215</v>
-      </c>
-      <c r="H2" s="143" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="140"/>
-      <c r="B3" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="139"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="141"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="153" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="147" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="156" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="153"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="144" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="160"/>
-      <c r="H4" s="153"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="157" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="149" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="137"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="137"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="148" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="148" t="s">
-        <v>223</v>
-      </c>
-      <c r="C6" s="149" t="s">
-        <v>214</v>
-      </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="137"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="161" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="157" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="149" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="137"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="137"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="135" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="148" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="155" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="138"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="146"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="138"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="162" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="158" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="135"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="135"/>
-    </row>
-    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="135" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="131" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="136" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="132">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="137" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="133">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="137" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="133">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="138" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="134">
-        <v>244</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:F3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{80B83815-A50D-46A4-BEA0-CF1A27585021}"/>
-    <hyperlink ref="C5:C6" r:id="rId2" display="link" xr:uid="{1266295D-E9A3-4E93-AD55-60C4C75F5D8F}"/>
-    <hyperlink ref="C8" r:id="rId3" xr:uid="{1FE0C054-3932-4DFB-A079-D528176C6357}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{86EE9E67-4350-42ED-BD92-B0D509FD78C0}"/>
-    <hyperlink ref="C9" r:id="rId5" xr:uid="{84CA0A26-1C37-4DC1-82DB-E059761431F7}"/>
-  </hyperlinks>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/calc_and_rack.xlsx
+++ b/calc_and_rack.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l7aur\Desktop\CND\CNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD1C274-3820-4CDD-8A8B-BE6F9D0E39B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30673C26-9998-47A5-BDF3-73F3AB649FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="IDF1" sheetId="3" r:id="rId4"/>
     <sheet name="IDF..." sheetId="4" r:id="rId5"/>
     <sheet name="Traffic Estimation" sheetId="7" r:id="rId6"/>
-    <sheet name="Equipment" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +88,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="237">
   <si>
     <t>Room Nr</t>
   </si>
@@ -1005,7 +1004,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="87">
+  <borders count="95">
     <border>
       <left/>
       <right/>
@@ -1989,21 +1988,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -2053,11 +2037,132 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2066,33 +2171,13 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2100,7 +2185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2232,43 +2317,114 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="74" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2280,6 +2436,8 @@
     <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2301,25 +2459,40 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2330,9 +2503,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2346,9 +2516,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2358,178 +2525,141 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="74" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2890,17 +3020,17 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -3086,31 +3216,31 @@
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="119"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="103"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -3508,31 +3638,31 @@
       <c r="A24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="98" t="s">
+      <c r="B24" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="100"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="119"/>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="103"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="122"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -3718,17 +3848,17 @@
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="104" t="s">
+      <c r="B31" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="97"/>
+      <c r="C31" s="124"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="124"/>
+      <c r="I31" s="124"/>
+      <c r="J31" s="125"/>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -3914,31 +4044,31 @@
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="105" t="s">
+      <c r="B37" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="119"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="101"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
-      <c r="J38" s="103"/>
+      <c r="B38" s="120"/>
+      <c r="C38" s="121"/>
+      <c r="D38" s="121"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="121"/>
+      <c r="H38" s="121"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="122"/>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -4264,17 +4394,17 @@
       <c r="A49" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="95" t="s">
+      <c r="B49" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="96"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="96"/>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="97"/>
+      <c r="C49" s="124"/>
+      <c r="D49" s="124"/>
+      <c r="E49" s="124"/>
+      <c r="F49" s="124"/>
+      <c r="G49" s="124"/>
+      <c r="H49" s="124"/>
+      <c r="I49" s="124"/>
+      <c r="J49" s="125"/>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
@@ -4460,31 +4590,31 @@
       <c r="A55" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="98" t="s">
+      <c r="B55" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="99"/>
-      <c r="D55" s="99"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="100"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="119"/>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="101"/>
-      <c r="C56" s="102"/>
-      <c r="D56" s="102"/>
-      <c r="E56" s="102"/>
-      <c r="F56" s="102"/>
-      <c r="G56" s="102"/>
-      <c r="H56" s="102"/>
-      <c r="I56" s="102"/>
-      <c r="J56" s="103"/>
+      <c r="B56" s="120"/>
+      <c r="C56" s="121"/>
+      <c r="D56" s="121"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="121"/>
+      <c r="H56" s="121"/>
+      <c r="I56" s="121"/>
+      <c r="J56" s="122"/>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -4882,31 +5012,31 @@
       <c r="A69" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="98" t="s">
+      <c r="B69" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="99"/>
-      <c r="D69" s="99"/>
-      <c r="E69" s="99"/>
-      <c r="F69" s="99"/>
-      <c r="G69" s="99"/>
-      <c r="H69" s="99"/>
-      <c r="I69" s="99"/>
-      <c r="J69" s="100"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="118"/>
+      <c r="F69" s="118"/>
+      <c r="G69" s="118"/>
+      <c r="H69" s="118"/>
+      <c r="I69" s="118"/>
+      <c r="J69" s="119"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="101"/>
-      <c r="C70" s="102"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="102"/>
-      <c r="F70" s="102"/>
-      <c r="G70" s="102"/>
-      <c r="H70" s="102"/>
-      <c r="I70" s="102"/>
-      <c r="J70" s="103"/>
+      <c r="B70" s="120"/>
+      <c r="C70" s="121"/>
+      <c r="D70" s="121"/>
+      <c r="E70" s="121"/>
+      <c r="F70" s="121"/>
+      <c r="G70" s="121"/>
+      <c r="H70" s="121"/>
+      <c r="I70" s="121"/>
+      <c r="J70" s="122"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
@@ -5056,17 +5186,17 @@
       <c r="A75" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="104" t="s">
+      <c r="B75" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="96"/>
-      <c r="D75" s="96"/>
-      <c r="E75" s="96"/>
-      <c r="F75" s="96"/>
-      <c r="G75" s="96"/>
-      <c r="H75" s="96"/>
-      <c r="I75" s="96"/>
-      <c r="J75" s="97"/>
+      <c r="C75" s="124"/>
+      <c r="D75" s="124"/>
+      <c r="E75" s="124"/>
+      <c r="F75" s="124"/>
+      <c r="G75" s="124"/>
+      <c r="H75" s="124"/>
+      <c r="I75" s="124"/>
+      <c r="J75" s="125"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
@@ -5252,31 +5382,31 @@
       <c r="A81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B81" s="105" t="s">
+      <c r="B81" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="99"/>
-      <c r="D81" s="99"/>
-      <c r="E81" s="99"/>
-      <c r="F81" s="99"/>
-      <c r="G81" s="99"/>
-      <c r="H81" s="99"/>
-      <c r="I81" s="99"/>
-      <c r="J81" s="100"/>
+      <c r="C81" s="118"/>
+      <c r="D81" s="118"/>
+      <c r="E81" s="118"/>
+      <c r="F81" s="118"/>
+      <c r="G81" s="118"/>
+      <c r="H81" s="118"/>
+      <c r="I81" s="118"/>
+      <c r="J81" s="119"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B82" s="101"/>
-      <c r="C82" s="102"/>
-      <c r="D82" s="102"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="102"/>
-      <c r="I82" s="102"/>
-      <c r="J82" s="103"/>
+      <c r="B82" s="120"/>
+      <c r="C82" s="121"/>
+      <c r="D82" s="121"/>
+      <c r="E82" s="121"/>
+      <c r="F82" s="121"/>
+      <c r="G82" s="121"/>
+      <c r="H82" s="121"/>
+      <c r="I82" s="121"/>
+      <c r="J82" s="122"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
@@ -5571,10 +5701,10 @@
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="112" t="s">
+      <c r="A97" s="133" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="113"/>
+      <c r="B97" s="134"/>
       <c r="C97" s="18">
         <f>I91/(F91*2)</f>
         <v>53.380728971962618</v>
@@ -5587,42 +5717,42 @@
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="111" t="s">
+      <c r="A99" s="132" t="s">
         <v>127</v>
       </c>
-      <c r="B99" s="107"/>
-      <c r="C99" s="107"/>
-      <c r="D99" s="107"/>
-      <c r="E99" s="107"/>
-      <c r="F99" s="107"/>
-      <c r="G99" s="107"/>
-      <c r="H99" s="108"/>
+      <c r="B99" s="128"/>
+      <c r="C99" s="128"/>
+      <c r="D99" s="128"/>
+      <c r="E99" s="128"/>
+      <c r="F99" s="128"/>
+      <c r="G99" s="128"/>
+      <c r="H99" s="129"/>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="110" t="s">
+      <c r="A100" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="108"/>
+      <c r="B100" s="129"/>
       <c r="H100" s="17"/>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="109" t="s">
+      <c r="A101" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="108"/>
+      <c r="B101" s="129"/>
       <c r="H101" s="17"/>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="106" t="s">
+      <c r="A102" s="127" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="107"/>
-      <c r="C102" s="107"/>
-      <c r="D102" s="107"/>
-      <c r="E102" s="108"/>
+      <c r="B102" s="128"/>
+      <c r="C102" s="128"/>
+      <c r="D102" s="128"/>
+      <c r="E102" s="129"/>
       <c r="H102" s="17"/>
       <c r="J102" s="15"/>
     </row>
@@ -9224,6 +9354,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B37:J38"/>
     <mergeCell ref="B69:J70"/>
     <mergeCell ref="B75:J75"/>
     <mergeCell ref="B81:J82"/>
@@ -9232,13 +9369,6 @@
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A97:B97"/>
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B55:J56"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B37:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
@@ -9261,176 +9391,176 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="147" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="123"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149"/>
       <c r="G1" s="59"/>
       <c r="H1" s="56"/>
       <c r="I1" s="55"/>
       <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="137" t="s">
+      <c r="B2" s="156"/>
+      <c r="C2" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="138"/>
-      <c r="E2" s="126" t="s">
+      <c r="D2" s="143"/>
+      <c r="E2" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="127"/>
+      <c r="F2" s="152"/>
       <c r="G2" s="58"/>
       <c r="H2" s="56"/>
       <c r="I2" s="55"/>
       <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="133" t="s">
+      <c r="A3" s="136" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="133" t="s">
+      <c r="B3" s="137"/>
+      <c r="C3" s="136" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="128">
+      <c r="D3" s="144"/>
+      <c r="E3" s="153">
         <v>35</v>
       </c>
-      <c r="F3" s="129"/>
+      <c r="F3" s="144"/>
       <c r="G3" s="58"/>
       <c r="H3" s="56"/>
       <c r="I3" s="55"/>
       <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="138" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="124" t="s">
+      <c r="B4" s="139"/>
+      <c r="C4" s="138" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="130">
+      <c r="D4" s="150"/>
+      <c r="E4" s="154">
         <v>85</v>
       </c>
-      <c r="F4" s="125"/>
+      <c r="F4" s="150"/>
       <c r="G4" s="58"/>
       <c r="H4" s="56"/>
       <c r="I4" s="55"/>
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="124" t="s">
+      <c r="A5" s="138" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="124" t="s">
+      <c r="B5" s="139"/>
+      <c r="C5" s="138" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="130">
+      <c r="D5" s="150"/>
+      <c r="E5" s="154">
         <v>35</v>
       </c>
-      <c r="F5" s="125"/>
+      <c r="F5" s="150"/>
       <c r="G5" s="58"/>
       <c r="H5" s="56"/>
       <c r="I5" s="55"/>
       <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="145" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="114" t="s">
+      <c r="B6" s="146"/>
+      <c r="C6" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="114">
+      <c r="D6" s="146"/>
+      <c r="E6" s="145">
         <v>85</v>
       </c>
-      <c r="F6" s="115"/>
+      <c r="F6" s="146"/>
       <c r="G6" s="58"/>
       <c r="H6" s="56"/>
       <c r="I6" s="55"/>
       <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="145" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="115"/>
-      <c r="C7" s="114" t="s">
+      <c r="B7" s="146"/>
+      <c r="C7" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="115"/>
-      <c r="E7" s="114">
+      <c r="D7" s="146"/>
+      <c r="E7" s="145">
         <v>5</v>
       </c>
-      <c r="F7" s="115"/>
+      <c r="F7" s="146"/>
       <c r="G7" s="58"/>
       <c r="H7" s="56"/>
       <c r="I7" s="55"/>
       <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="145" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="115"/>
-      <c r="C8" s="114" t="s">
+      <c r="B8" s="146"/>
+      <c r="C8" s="145" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="114">
+      <c r="D8" s="146"/>
+      <c r="E8" s="145">
         <v>5</v>
       </c>
-      <c r="F8" s="115"/>
+      <c r="F8" s="146"/>
       <c r="G8" s="58"/>
       <c r="H8" s="56"/>
       <c r="I8" s="55"/>
       <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="115"/>
-      <c r="C9" s="114" t="s">
+      <c r="B9" s="146"/>
+      <c r="C9" s="145" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="115"/>
-      <c r="E9" s="114">
+      <c r="D9" s="146"/>
+      <c r="E9" s="145">
         <v>5</v>
       </c>
-      <c r="F9" s="115"/>
+      <c r="F9" s="146"/>
       <c r="G9" s="58"/>
       <c r="H9" s="56"/>
       <c r="I9" s="55"/>
       <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="117" t="s">
+      <c r="A10" s="140" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="136"/>
-      <c r="C10" s="117" t="s">
+      <c r="B10" s="141"/>
+      <c r="C10" s="140" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="120">
+      <c r="D10" s="158"/>
+      <c r="E10" s="160">
         <v>5</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="158"/>
       <c r="G10" s="58"/>
       <c r="H10" s="56"/>
       <c r="I10" s="55"/>
@@ -9448,17 +9578,17 @@
       <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="119" t="s">
+      <c r="A12" s="159" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="116">
+      <c r="B12" s="159"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="157">
         <f>SUM(E3:F10)</f>
         <v>260</v>
       </c>
-      <c r="F12" s="116"/>
+      <c r="F12" s="157"/>
       <c r="G12" s="55"/>
       <c r="H12" s="56"/>
       <c r="I12" s="55"/>
@@ -9478,13 +9608,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -9501,13 +9631,13 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9555,7 +9685,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="161" t="s">
         <v>138</v>
       </c>
       <c r="B2" s="23">
@@ -9574,12 +9704,12 @@
       <c r="G2" s="25">
         <v>0</v>
       </c>
-      <c r="H2" s="139" t="s">
+      <c r="H2" s="161" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="140"/>
+      <c r="A3" s="162"/>
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -9594,10 +9724,10 @@
       <c r="G3" s="25">
         <v>0</v>
       </c>
-      <c r="H3" s="140"/>
+      <c r="H3" s="162"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="140"/>
+      <c r="A4" s="162"/>
       <c r="B4" s="23">
         <v>1</v>
       </c>
@@ -9614,10 +9744,10 @@
       <c r="G4" s="25">
         <v>200</v>
       </c>
-      <c r="H4" s="140"/>
+      <c r="H4" s="162"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="140"/>
+      <c r="A5" s="162"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -9628,10 +9758,10 @@
       <c r="G5" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="140"/>
+      <c r="H5" s="162"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="140"/>
+      <c r="A6" s="162"/>
       <c r="B6" s="23">
         <v>1</v>
       </c>
@@ -9648,10 +9778,10 @@
       <c r="G6" s="25">
         <v>0</v>
       </c>
-      <c r="H6" s="140"/>
+      <c r="H6" s="162"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="140"/>
+      <c r="A7" s="162"/>
       <c r="B7" s="23">
         <v>1</v>
       </c>
@@ -9666,10 +9796,10 @@
       <c r="G7" s="25">
         <v>0</v>
       </c>
-      <c r="H7" s="140"/>
+      <c r="H7" s="162"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="140"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="27">
         <v>1</v>
       </c>
@@ -9686,10 +9816,10 @@
       <c r="G8" s="25">
         <v>50</v>
       </c>
-      <c r="H8" s="140"/>
+      <c r="H8" s="162"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="140"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="27">
         <v>1</v>
       </c>
@@ -9699,10 +9829,10 @@
       <c r="D9" s="23"/>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="140"/>
+      <c r="H9" s="162"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="140"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="27">
         <v>1</v>
       </c>
@@ -9715,10 +9845,10 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="25"/>
-      <c r="H10" s="140"/>
+      <c r="H10" s="162"/>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="140"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="23">
         <v>1</v>
       </c>
@@ -9729,10 +9859,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="140"/>
+      <c r="H11" s="162"/>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="140"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="23">
         <v>1</v>
       </c>
@@ -9743,10 +9873,10 @@
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="140"/>
+      <c r="H12" s="162"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="140"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="23">
         <v>1</v>
       </c>
@@ -9757,10 +9887,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="140"/>
+      <c r="H13" s="162"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="140"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="23">
         <v>1</v>
       </c>
@@ -9769,10 +9899,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="140"/>
+      <c r="H14" s="162"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="140"/>
+      <c r="A15" s="162"/>
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -9783,10 +9913,10 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="140"/>
+      <c r="H15" s="162"/>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="140"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="23">
         <v>1</v>
       </c>
@@ -9797,10 +9927,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25"/>
-      <c r="H16" s="140"/>
+      <c r="H16" s="162"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="140"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="27">
         <v>7</v>
       </c>
@@ -9809,70 +9939,70 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="140"/>
+      <c r="H17" s="162"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="140"/>
+      <c r="A18" s="162"/>
       <c r="B18" s="27"/>
       <c r="C18" s="33"/>
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="140"/>
+      <c r="H18" s="162"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="140"/>
+      <c r="A19" s="162"/>
       <c r="B19" s="27"/>
       <c r="C19" s="33"/>
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="140"/>
+      <c r="H19" s="162"/>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="140"/>
+      <c r="A20" s="162"/>
       <c r="B20" s="27"/>
       <c r="C20" s="33"/>
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="140"/>
+      <c r="H20" s="162"/>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="140"/>
+      <c r="A21" s="162"/>
       <c r="B21" s="27"/>
       <c r="C21" s="33"/>
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="140"/>
+      <c r="H21" s="162"/>
     </row>
     <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="140"/>
+      <c r="A22" s="162"/>
       <c r="B22" s="27"/>
       <c r="C22" s="33"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="140"/>
+      <c r="H22" s="162"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="140"/>
+      <c r="A23" s="162"/>
       <c r="B23" s="27"/>
       <c r="C23" s="34"/>
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="140"/>
+      <c r="H23" s="162"/>
     </row>
     <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="140"/>
+      <c r="A24" s="162"/>
       <c r="B24" s="23">
         <v>1</v>
       </c>
@@ -9883,10 +10013,10 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25"/>
-      <c r="H24" s="140"/>
+      <c r="H24" s="162"/>
     </row>
     <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="140"/>
+      <c r="A25" s="162"/>
       <c r="B25" s="23">
         <v>1</v>
       </c>
@@ -9897,10 +10027,10 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="25"/>
-      <c r="H25" s="140"/>
+      <c r="H25" s="162"/>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="140"/>
+      <c r="A26" s="162"/>
       <c r="B26" s="23">
         <v>1</v>
       </c>
@@ -9911,10 +10041,10 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25"/>
-      <c r="H26" s="140"/>
+      <c r="H26" s="162"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="140"/>
+      <c r="A27" s="162"/>
       <c r="B27" s="23">
         <v>1</v>
       </c>
@@ -9923,10 +10053,10 @@
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25"/>
-      <c r="H27" s="140"/>
+      <c r="H27" s="162"/>
     </row>
     <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="140"/>
+      <c r="A28" s="162"/>
       <c r="B28" s="23">
         <v>1</v>
       </c>
@@ -9935,10 +10065,10 @@
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="140"/>
+      <c r="H28" s="162"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="140"/>
+      <c r="A29" s="162"/>
       <c r="B29" s="23">
         <v>1</v>
       </c>
@@ -9954,10 +10084,10 @@
       <c r="G29" s="25">
         <v>50</v>
       </c>
-      <c r="H29" s="140"/>
+      <c r="H29" s="162"/>
     </row>
     <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="140"/>
+      <c r="A30" s="162"/>
       <c r="B30" s="23">
         <v>6</v>
       </c>
@@ -9968,40 +10098,40 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25"/>
-      <c r="H30" s="140"/>
+      <c r="H30" s="162"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="140"/>
+      <c r="A31" s="162"/>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="25"/>
-      <c r="H31" s="140"/>
+      <c r="H31" s="162"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="140"/>
+      <c r="A32" s="162"/>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25"/>
-      <c r="H32" s="140"/>
+      <c r="H32" s="162"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="140"/>
+      <c r="A33" s="162"/>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25"/>
-      <c r="H33" s="140"/>
+      <c r="H33" s="162"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="140"/>
+      <c r="A34" s="162"/>
       <c r="B34" s="23">
         <v>1</v>
       </c>
@@ -10014,10 +10144,10 @@
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="140"/>
+      <c r="H34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="140"/>
+      <c r="A35" s="162"/>
       <c r="B35" s="23">
         <v>1</v>
       </c>
@@ -10028,10 +10158,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25"/>
-      <c r="H35" s="140"/>
+      <c r="H35" s="162"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="140"/>
+      <c r="A36" s="162"/>
       <c r="B36" s="23">
         <v>1</v>
       </c>
@@ -10048,10 +10178,10 @@
       <c r="G36" s="25">
         <v>200</v>
       </c>
-      <c r="H36" s="140"/>
+      <c r="H36" s="162"/>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="140"/>
+      <c r="A37" s="162"/>
       <c r="B37" s="23">
         <v>2</v>
       </c>
@@ -10062,10 +10192,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="140"/>
+      <c r="H37" s="162"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="140"/>
+      <c r="A38" s="162"/>
       <c r="B38" s="23">
         <v>4</v>
       </c>
@@ -10080,10 +10210,10 @@
       <c r="G38" s="25">
         <v>250</v>
       </c>
-      <c r="H38" s="140"/>
+      <c r="H38" s="162"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="140"/>
+      <c r="A39" s="162"/>
       <c r="B39" s="23">
         <v>4</v>
       </c>
@@ -10098,37 +10228,37 @@
       <c r="G39" s="25">
         <v>250</v>
       </c>
-      <c r="H39" s="140"/>
+      <c r="H39" s="162"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="140"/>
+      <c r="A40" s="162"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="140"/>
+      <c r="H40" s="162"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="140"/>
+      <c r="A41" s="162"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="140"/>
+      <c r="H41" s="162"/>
     </row>
     <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="140"/>
+      <c r="A42" s="162"/>
       <c r="B42" s="36"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="140"/>
+      <c r="H42" s="162"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="38" t="s">
@@ -13302,57 +13432,62 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6D2DF1-EEB7-4492-8A92-1BDE7B755239}">
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="62" customWidth="1"/>
     <col min="2" max="2" width="29.21875" style="62" customWidth="1"/>
-    <col min="3" max="4" width="26" style="62" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" style="62" customWidth="1"/>
-    <col min="6" max="6" width="24.21875" style="62" customWidth="1"/>
-    <col min="7" max="7" width="19.77734375" style="62" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" style="62" customWidth="1"/>
-    <col min="9" max="9" width="22.6640625" style="62" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="62"/>
+    <col min="3" max="3" width="19.88671875" style="62" customWidth="1"/>
+    <col min="4" max="5" width="26" style="62" customWidth="1"/>
+    <col min="6" max="6" width="27.6640625" style="62" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" style="62" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" style="62" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" style="62" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" style="62" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="72" t="s">
         <v>192</v>
       </c>
       <c r="B1" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="63"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C1" s="63"/>
+      <c r="E1" s="63"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="70" t="s">
         <v>193</v>
       </c>
       <c r="B2" s="71">
         <v>25</v>
       </c>
-      <c r="D2" s="63"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C2" s="63"/>
+      <c r="E2" s="63"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="65" t="s">
         <v>194</v>
       </c>
       <c r="B3" s="68">
         <v>0.1</v>
       </c>
-      <c r="D3" s="63"/>
-    </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="63"/>
+      <c r="E3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="66" t="s">
         <v>195</v>
       </c>
       <c r="B4" s="69">
         <v>300</v>
       </c>
-      <c r="D4" s="63"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="63"/>
+      <c r="E4" s="63"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>204</v>
       </c>
@@ -13360,1928 +13495,1954 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="E9" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="F9" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="G9" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="H9" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="I9" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="I9" s="73" t="s">
+      <c r="J9" s="73" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="141" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="114" t="s">
         <v>198</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="175"/>
+      <c r="D10" s="64">
         <v>1</v>
       </c>
-      <c r="D10" s="64">
-        <f>E10*C10/1000</f>
+      <c r="E10" s="64">
+        <f>F10*D10/1000</f>
         <v>0.38506999999999997</v>
       </c>
-      <c r="E10" s="67">
-        <f>SUM($B$2*F10,$B$3*G10,$B$4*H10)*$B$6</f>
+      <c r="F10" s="67">
+        <f>SUM($B$2*G10,$B$3*H10,$B$4*I10)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F10" s="75">
+      <c r="G10" s="75">
         <v>10</v>
       </c>
-      <c r="G10" s="67">
+      <c r="H10" s="67">
         <v>1</v>
       </c>
-      <c r="H10" s="75">
+      <c r="I10" s="75">
         <v>1</v>
       </c>
-      <c r="I10" s="68">
-        <f>SUM(F10:H10)*C10</f>
+      <c r="J10" s="68">
+        <f>SUM(G10:I10)*D10</f>
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="142"/>
-      <c r="B11" s="76" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="115"/>
+      <c r="B11" s="172" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="173"/>
+      <c r="D11" s="65">
         <v>1</v>
       </c>
-      <c r="D11" s="65">
-        <f t="shared" ref="D11:D33" si="0">E11*C11/1000</f>
+      <c r="E11" s="65">
+        <f t="shared" ref="E11:E33" si="0">F11*D11/1000</f>
         <v>0.38506999999999997</v>
       </c>
-      <c r="E11" s="68">
-        <f t="shared" ref="E11:E33" si="1">SUM($B$2*F11,$B$3*G11,$B$4*H11)*$B$6</f>
+      <c r="F11" s="68">
+        <f>SUM($B$2*G11,$B$3*H11,$B$4*I11)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F11" s="76">
+      <c r="G11" s="76">
         <v>10</v>
       </c>
-      <c r="G11" s="68">
+      <c r="H11" s="68">
         <v>1</v>
       </c>
-      <c r="H11" s="76">
+      <c r="I11" s="76">
         <v>1</v>
       </c>
-      <c r="I11" s="68">
-        <f t="shared" ref="I11:I33" si="2">SUM(F11:H11)*C11</f>
+      <c r="J11" s="68">
+        <f>SUM(G11:I11)*D11</f>
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="142"/>
-      <c r="B12" s="76" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="115"/>
+      <c r="B12" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="173"/>
+      <c r="D12" s="65">
         <v>5</v>
       </c>
-      <c r="D12" s="65">
+      <c r="E12" s="65">
         <f t="shared" si="0"/>
         <v>1.7503499999999999</v>
       </c>
-      <c r="E12" s="68">
-        <f t="shared" si="1"/>
+      <c r="F12" s="68">
+        <f>SUM($B$2*G12,$B$3*H12,$B$4*I12)*$B$6</f>
         <v>350.07</v>
       </c>
-      <c r="F12" s="76">
+      <c r="G12" s="76">
         <v>8</v>
       </c>
-      <c r="G12" s="68">
+      <c r="H12" s="68">
         <v>1</v>
       </c>
-      <c r="H12" s="76">
+      <c r="I12" s="76">
         <v>1</v>
       </c>
-      <c r="I12" s="68">
-        <f t="shared" si="2"/>
+      <c r="J12" s="68">
+        <f>SUM(G12:I12)*D12</f>
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="142"/>
-      <c r="B13" s="76" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="115"/>
+      <c r="B13" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="173"/>
+      <c r="D13" s="65">
         <v>1</v>
       </c>
-      <c r="D13" s="65">
+      <c r="E13" s="65">
         <f t="shared" si="0"/>
         <v>0.70013999999999998</v>
       </c>
-      <c r="E13" s="68">
-        <f t="shared" si="1"/>
+      <c r="F13" s="68">
+        <f>SUM($B$2*G13,$B$3*H13,$B$4*I13)*$B$6</f>
         <v>700.14</v>
       </c>
-      <c r="F13" s="76">
+      <c r="G13" s="76">
         <v>16</v>
       </c>
-      <c r="G13" s="68">
+      <c r="H13" s="68">
         <v>2</v>
       </c>
-      <c r="H13" s="76">
+      <c r="I13" s="76">
         <v>2</v>
       </c>
-      <c r="I13" s="68">
-        <f t="shared" si="2"/>
+      <c r="J13" s="68">
+        <f>SUM(G13:I13)*D13</f>
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="142"/>
-      <c r="B14" s="76" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="115"/>
+      <c r="B14" s="172" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="173"/>
+      <c r="D14" s="65">
         <v>7</v>
       </c>
-      <c r="D14" s="65">
+      <c r="E14" s="65">
         <f t="shared" si="0"/>
         <v>3.1854899999999997</v>
       </c>
-      <c r="E14" s="68">
-        <f t="shared" si="1"/>
+      <c r="F14" s="68">
+        <f>SUM($B$2*G14,$B$3*H14,$B$4*I14)*$B$6</f>
         <v>455.07</v>
       </c>
-      <c r="F14" s="76">
+      <c r="G14" s="76">
         <v>14</v>
       </c>
-      <c r="G14" s="68">
+      <c r="H14" s="68">
         <v>1</v>
       </c>
-      <c r="H14" s="76">
+      <c r="I14" s="76">
         <v>1</v>
       </c>
-      <c r="I14" s="68">
-        <f t="shared" si="2"/>
+      <c r="J14" s="68">
+        <f>SUM(G14:I14)*D14</f>
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="142"/>
-      <c r="B15" s="76" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="115"/>
+      <c r="B15" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="173"/>
+      <c r="D15" s="65">
         <v>1</v>
       </c>
-      <c r="D15" s="65">
+      <c r="E15" s="65">
         <f t="shared" si="0"/>
         <v>1.52257</v>
       </c>
-      <c r="E15" s="68">
-        <f t="shared" si="1"/>
+      <c r="F15" s="68">
+        <f>SUM($B$2*G15,$B$3*H15,$B$4*I15)*$B$6</f>
         <v>1522.57</v>
       </c>
-      <c r="F15" s="76">
+      <c r="G15" s="76">
         <v>63</v>
       </c>
-      <c r="G15" s="68">
+      <c r="H15" s="68">
         <v>1</v>
       </c>
-      <c r="H15" s="76">
+      <c r="I15" s="76">
         <v>2</v>
       </c>
-      <c r="I15" s="68">
-        <f t="shared" si="2"/>
+      <c r="J15" s="68">
+        <f>SUM(G15:I15)*D15</f>
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="142"/>
-      <c r="B16" s="76" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="115"/>
+      <c r="B16" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="173"/>
+      <c r="D16" s="65">
         <v>2</v>
       </c>
-      <c r="D16" s="65">
+      <c r="E16" s="65">
         <f t="shared" si="0"/>
         <v>2.1351399999999998</v>
       </c>
-      <c r="E16" s="68">
-        <f t="shared" si="1"/>
+      <c r="F16" s="68">
+        <f>SUM($B$2*G16,$B$3*H16,$B$4*I16)*$B$6</f>
         <v>1067.57</v>
       </c>
-      <c r="F16" s="76">
+      <c r="G16" s="76">
         <v>37</v>
       </c>
-      <c r="G16" s="68">
+      <c r="H16" s="68">
         <v>1</v>
       </c>
-      <c r="H16" s="76">
+      <c r="I16" s="76">
         <v>2</v>
       </c>
-      <c r="I16" s="68">
-        <f t="shared" si="2"/>
+      <c r="J16" s="68">
+        <f>SUM(G16:I16)*D16</f>
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="142"/>
-      <c r="B17" s="76" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="115"/>
+      <c r="B17" s="172" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="173"/>
+      <c r="D17" s="65">
         <v>2</v>
       </c>
-      <c r="D17" s="65">
+      <c r="E17" s="65">
         <f t="shared" si="0"/>
         <v>1.3651399999999998</v>
       </c>
-      <c r="E17" s="68">
-        <f t="shared" si="1"/>
+      <c r="F17" s="68">
+        <f>SUM($B$2*G17,$B$3*H17,$B$4*I17)*$B$6</f>
         <v>682.56999999999994</v>
       </c>
-      <c r="F17" s="76">
+      <c r="G17" s="76">
         <v>15</v>
       </c>
-      <c r="G17" s="68">
+      <c r="H17" s="68">
         <v>1</v>
       </c>
-      <c r="H17" s="76">
+      <c r="I17" s="76">
         <v>2</v>
       </c>
-      <c r="I17" s="68">
-        <f t="shared" si="2"/>
+      <c r="J17" s="68">
+        <f>SUM(G17:I17)*D17</f>
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="142"/>
-      <c r="B18" s="76" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="115"/>
+      <c r="B18" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="173"/>
+      <c r="D18" s="65">
         <v>2</v>
       </c>
-      <c r="D18" s="65">
+      <c r="E18" s="65">
         <f t="shared" si="0"/>
         <v>0.77013999999999994</v>
       </c>
-      <c r="E18" s="68">
-        <f t="shared" si="1"/>
+      <c r="F18" s="68">
+        <f>SUM($B$2*G18,$B$3*H18,$B$4*I18)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F18" s="76">
+      <c r="G18" s="76">
         <v>10</v>
       </c>
-      <c r="G18" s="68">
+      <c r="H18" s="68">
         <v>1</v>
       </c>
-      <c r="H18" s="76">
+      <c r="I18" s="76">
         <v>1</v>
       </c>
-      <c r="I18" s="68">
-        <f t="shared" si="2"/>
+      <c r="J18" s="68">
+        <f>SUM(G18:I18)*D18</f>
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="142"/>
-      <c r="B19" s="76" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="115"/>
+      <c r="B19" s="172" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="173"/>
+      <c r="D19" s="65">
         <v>5</v>
       </c>
-      <c r="D19" s="65">
+      <c r="E19" s="65">
         <f t="shared" si="0"/>
         <v>1.7503499999999999</v>
       </c>
-      <c r="E19" s="68">
-        <f t="shared" si="1"/>
+      <c r="F19" s="68">
+        <f>SUM($B$2*G19,$B$3*H19,$B$4*I19)*$B$6</f>
         <v>350.07</v>
       </c>
-      <c r="F19" s="76">
+      <c r="G19" s="76">
         <v>8</v>
       </c>
-      <c r="G19" s="68">
+      <c r="H19" s="68">
         <v>1</v>
       </c>
-      <c r="H19" s="76">
+      <c r="I19" s="76">
         <v>1</v>
       </c>
-      <c r="I19" s="68">
-        <f t="shared" si="2"/>
+      <c r="J19" s="68">
+        <f>SUM(G19:I19)*D19</f>
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="142"/>
-      <c r="B20" s="76" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="115"/>
+      <c r="B20" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="173"/>
+      <c r="D20" s="65">
         <v>6</v>
       </c>
-      <c r="D20" s="65">
+      <c r="E20" s="65">
         <f t="shared" si="0"/>
         <v>2.5204200000000001</v>
       </c>
-      <c r="E20" s="68">
-        <f t="shared" si="1"/>
+      <c r="F20" s="68">
+        <f>SUM($B$2*G20,$B$3*H20,$B$4*I20)*$B$6</f>
         <v>420.07</v>
       </c>
-      <c r="F20" s="76">
+      <c r="G20" s="76">
         <v>12</v>
       </c>
-      <c r="G20" s="68">
+      <c r="H20" s="68">
         <v>1</v>
       </c>
-      <c r="H20" s="76">
+      <c r="I20" s="76">
         <v>1</v>
       </c>
-      <c r="I20" s="68">
-        <f t="shared" si="2"/>
+      <c r="J20" s="68">
+        <f>SUM(G20:I20)*D20</f>
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="143"/>
-      <c r="B21" s="77" t="s">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="116"/>
+      <c r="B21" s="179" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="180"/>
+      <c r="D21" s="66">
         <v>0</v>
       </c>
-      <c r="D21" s="66">
+      <c r="E21" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="69">
-        <f t="shared" si="1"/>
+      <c r="F21" s="69">
+        <f>SUM($B$2*G21,$B$3*H21,$B$4*I21)*$B$6</f>
         <v>420.07</v>
       </c>
-      <c r="F21" s="77">
+      <c r="G21" s="77">
         <v>12</v>
       </c>
-      <c r="G21" s="69">
+      <c r="H21" s="69">
         <v>1</v>
       </c>
-      <c r="H21" s="77">
+      <c r="I21" s="77">
         <v>1</v>
       </c>
-      <c r="I21" s="78">
-        <f t="shared" si="2"/>
+      <c r="J21" s="78">
+        <f>SUM(G21:I21)*D21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="141" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="114" t="s">
         <v>199</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="64">
+      <c r="C22" s="175"/>
+      <c r="D22" s="64">
         <v>1</v>
       </c>
-      <c r="D22" s="70">
+      <c r="E22" s="70">
         <f t="shared" si="0"/>
         <v>0.38506999999999997</v>
       </c>
-      <c r="E22" s="67">
-        <f>SUM($B$2*F22,$B$3*G22,$B$4*H22)*$B$6</f>
+      <c r="F22" s="67">
+        <f>SUM($B$2*G22,$B$3*H22,$B$4*I22)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F22" s="75">
+      <c r="G22" s="75">
         <v>10</v>
       </c>
-      <c r="G22" s="67">
+      <c r="H22" s="67">
         <v>1</v>
       </c>
-      <c r="H22" s="75">
+      <c r="I22" s="75">
         <v>1</v>
       </c>
-      <c r="I22" s="67">
-        <f t="shared" si="2"/>
+      <c r="J22" s="67">
+        <f>SUM(G22:I22)*D22</f>
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="142"/>
-      <c r="B23" s="76" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="115"/>
+      <c r="B23" s="172" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="173"/>
+      <c r="D23" s="65">
         <v>1</v>
       </c>
-      <c r="D23" s="65">
+      <c r="E23" s="65">
         <f t="shared" si="0"/>
         <v>0.38506999999999997</v>
       </c>
-      <c r="E23" s="68">
-        <f t="shared" si="1"/>
+      <c r="F23" s="68">
+        <f>SUM($B$2*G23,$B$3*H23,$B$4*I23)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F23" s="76">
+      <c r="G23" s="76">
         <v>10</v>
       </c>
-      <c r="G23" s="68">
+      <c r="H23" s="68">
         <v>1</v>
       </c>
-      <c r="H23" s="76">
+      <c r="I23" s="76">
         <v>1</v>
       </c>
-      <c r="I23" s="68">
-        <f t="shared" si="2"/>
+      <c r="J23" s="68">
+        <f>SUM(G23:I23)*D23</f>
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="142"/>
-      <c r="B24" s="76" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="115"/>
+      <c r="B24" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="173"/>
+      <c r="D24" s="65">
         <v>5</v>
       </c>
-      <c r="D24" s="65">
+      <c r="E24" s="65">
         <f t="shared" si="0"/>
         <v>1.7503499999999999</v>
       </c>
-      <c r="E24" s="68">
-        <f t="shared" si="1"/>
+      <c r="F24" s="68">
+        <f>SUM($B$2*G24,$B$3*H24,$B$4*I24)*$B$6</f>
         <v>350.07</v>
       </c>
-      <c r="F24" s="76">
+      <c r="G24" s="76">
         <v>8</v>
       </c>
-      <c r="G24" s="68">
+      <c r="H24" s="68">
         <v>1</v>
       </c>
-      <c r="H24" s="76">
+      <c r="I24" s="76">
         <v>1</v>
       </c>
-      <c r="I24" s="68">
-        <f t="shared" si="2"/>
+      <c r="J24" s="68">
+        <f>SUM(G24:I24)*D24</f>
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="142"/>
-      <c r="B25" s="76" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="115"/>
+      <c r="B25" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="173"/>
+      <c r="D25" s="65">
         <v>1</v>
       </c>
-      <c r="D25" s="65">
+      <c r="E25" s="65">
         <f t="shared" si="0"/>
         <v>0.70013999999999998</v>
       </c>
-      <c r="E25" s="68">
-        <f t="shared" si="1"/>
+      <c r="F25" s="68">
+        <f>SUM($B$2*G25,$B$3*H25,$B$4*I25)*$B$6</f>
         <v>700.14</v>
       </c>
-      <c r="F25" s="76">
+      <c r="G25" s="76">
         <v>16</v>
       </c>
-      <c r="G25" s="68">
+      <c r="H25" s="68">
         <v>2</v>
       </c>
-      <c r="H25" s="76">
+      <c r="I25" s="76">
         <v>2</v>
       </c>
-      <c r="I25" s="68">
-        <f t="shared" si="2"/>
+      <c r="J25" s="68">
+        <f>SUM(G25:I25)*D25</f>
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="142"/>
-      <c r="B26" s="76" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="115"/>
+      <c r="B26" s="172" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="173"/>
+      <c r="D26" s="65">
         <v>7</v>
       </c>
-      <c r="D26" s="65">
+      <c r="E26" s="65">
         <f t="shared" si="0"/>
         <v>3.1854899999999997</v>
       </c>
-      <c r="E26" s="68">
-        <f t="shared" si="1"/>
+      <c r="F26" s="68">
+        <f>SUM($B$2*G26,$B$3*H26,$B$4*I26)*$B$6</f>
         <v>455.07</v>
       </c>
-      <c r="F26" s="76">
+      <c r="G26" s="76">
         <v>14</v>
       </c>
-      <c r="G26" s="68">
+      <c r="H26" s="68">
         <v>1</v>
       </c>
-      <c r="H26" s="76">
+      <c r="I26" s="76">
         <v>1</v>
       </c>
-      <c r="I26" s="68">
-        <f t="shared" si="2"/>
+      <c r="J26" s="68">
+        <f>SUM(G26:I26)*D26</f>
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="142"/>
-      <c r="B27" s="76" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="115"/>
+      <c r="B27" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="65">
+      <c r="C27" s="173"/>
+      <c r="D27" s="65">
         <v>1</v>
       </c>
-      <c r="D27" s="65">
+      <c r="E27" s="65">
         <f t="shared" si="0"/>
         <v>1.52257</v>
       </c>
-      <c r="E27" s="68">
-        <f t="shared" si="1"/>
+      <c r="F27" s="68">
+        <f>SUM($B$2*G27,$B$3*H27,$B$4*I27)*$B$6</f>
         <v>1522.57</v>
       </c>
-      <c r="F27" s="76">
+      <c r="G27" s="76">
         <v>63</v>
       </c>
-      <c r="G27" s="68">
+      <c r="H27" s="68">
         <v>1</v>
       </c>
-      <c r="H27" s="76">
+      <c r="I27" s="76">
         <v>2</v>
       </c>
-      <c r="I27" s="68">
-        <f t="shared" si="2"/>
+      <c r="J27" s="68">
+        <f>SUM(G27:I27)*D27</f>
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="142"/>
-      <c r="B28" s="76" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="115"/>
+      <c r="B28" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="65">
+      <c r="C28" s="173"/>
+      <c r="D28" s="65">
         <v>2</v>
       </c>
-      <c r="D28" s="65">
+      <c r="E28" s="65">
         <f t="shared" si="0"/>
         <v>2.1351399999999998</v>
       </c>
-      <c r="E28" s="68">
-        <f t="shared" si="1"/>
+      <c r="F28" s="68">
+        <f>SUM($B$2*G28,$B$3*H28,$B$4*I28)*$B$6</f>
         <v>1067.57</v>
       </c>
-      <c r="F28" s="76">
+      <c r="G28" s="76">
         <v>37</v>
       </c>
-      <c r="G28" s="68">
+      <c r="H28" s="68">
         <v>1</v>
       </c>
-      <c r="H28" s="76">
+      <c r="I28" s="76">
         <v>2</v>
       </c>
-      <c r="I28" s="68">
-        <f t="shared" si="2"/>
+      <c r="J28" s="68">
+        <f>SUM(G28:I28)*D28</f>
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
-      <c r="B29" s="76" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="115"/>
+      <c r="B29" s="172" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="65">
+      <c r="C29" s="173"/>
+      <c r="D29" s="65">
         <v>0</v>
       </c>
-      <c r="D29" s="65">
+      <c r="E29" s="65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="68">
-        <f t="shared" si="1"/>
+      <c r="F29" s="68">
+        <f>SUM($B$2*G29,$B$3*H29,$B$4*I29)*$B$6</f>
         <v>682.56999999999994</v>
       </c>
-      <c r="F29" s="76">
+      <c r="G29" s="76">
         <v>15</v>
       </c>
-      <c r="G29" s="68">
+      <c r="H29" s="68">
         <v>1</v>
       </c>
-      <c r="H29" s="76">
+      <c r="I29" s="76">
         <v>2</v>
       </c>
-      <c r="I29" s="68">
-        <f t="shared" si="2"/>
+      <c r="J29" s="68">
+        <f>SUM(G29:I29)*D29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="142"/>
-      <c r="B30" s="76" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="115"/>
+      <c r="B30" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="173"/>
+      <c r="D30" s="65">
         <v>2</v>
       </c>
-      <c r="D30" s="65">
+      <c r="E30" s="65">
         <f t="shared" si="0"/>
         <v>0.77013999999999994</v>
       </c>
-      <c r="E30" s="68">
-        <f t="shared" si="1"/>
+      <c r="F30" s="68">
+        <f>SUM($B$2*G30,$B$3*H30,$B$4*I30)*$B$6</f>
         <v>385.07</v>
       </c>
-      <c r="F30" s="76">
+      <c r="G30" s="76">
         <v>10</v>
       </c>
-      <c r="G30" s="68">
+      <c r="H30" s="68">
         <v>1</v>
       </c>
-      <c r="H30" s="76">
+      <c r="I30" s="76">
         <v>1</v>
       </c>
-      <c r="I30" s="68">
-        <f t="shared" si="2"/>
+      <c r="J30" s="68">
+        <f>SUM(G30:I30)*D30</f>
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
-      <c r="B31" s="76" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="115"/>
+      <c r="B31" s="172" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="65">
+      <c r="C31" s="173"/>
+      <c r="D31" s="65">
         <v>5</v>
       </c>
-      <c r="D31" s="65">
+      <c r="E31" s="65">
         <f t="shared" si="0"/>
         <v>1.7503499999999999</v>
       </c>
-      <c r="E31" s="68">
-        <f t="shared" si="1"/>
+      <c r="F31" s="68">
+        <f>SUM($B$2*G31,$B$3*H31,$B$4*I31)*$B$6</f>
         <v>350.07</v>
       </c>
-      <c r="F31" s="76">
+      <c r="G31" s="76">
         <v>8</v>
       </c>
-      <c r="G31" s="68">
+      <c r="H31" s="68">
         <v>1</v>
       </c>
-      <c r="H31" s="76">
+      <c r="I31" s="76">
         <v>1</v>
       </c>
-      <c r="I31" s="68">
-        <f t="shared" si="2"/>
+      <c r="J31" s="68">
+        <f>SUM(G31:I31)*D31</f>
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
-      <c r="B32" s="76" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="115"/>
+      <c r="B32" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="65">
+      <c r="C32" s="173"/>
+      <c r="D32" s="65">
         <v>6</v>
       </c>
-      <c r="D32" s="65">
+      <c r="E32" s="65">
         <f t="shared" si="0"/>
         <v>2.5204200000000001</v>
       </c>
-      <c r="E32" s="68">
-        <f t="shared" si="1"/>
+      <c r="F32" s="68">
+        <f>SUM($B$2*G32,$B$3*H32,$B$4*I32)*$B$6</f>
         <v>420.07</v>
       </c>
-      <c r="F32" s="76">
+      <c r="G32" s="76">
         <v>12</v>
       </c>
-      <c r="G32" s="68">
+      <c r="H32" s="68">
         <v>1</v>
       </c>
-      <c r="H32" s="76">
+      <c r="I32" s="76">
         <v>1</v>
       </c>
-      <c r="I32" s="68">
-        <f t="shared" si="2"/>
+      <c r="J32" s="68">
+        <f>SUM(G32:I32)*D32</f>
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="143"/>
-      <c r="B33" s="77" t="s">
+    <row r="33" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="116"/>
+      <c r="B33" s="179" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="66">
+      <c r="C33" s="180"/>
+      <c r="D33" s="66">
         <v>1</v>
       </c>
-      <c r="D33" s="66">
+      <c r="E33" s="66">
         <f t="shared" si="0"/>
         <v>0.42007</v>
       </c>
-      <c r="E33" s="69">
-        <f t="shared" si="1"/>
+      <c r="F33" s="69">
+        <f>SUM($B$2*G33,$B$3*H33,$B$4*I33)*$B$6</f>
         <v>420.07</v>
       </c>
-      <c r="F33" s="77">
+      <c r="G33" s="77">
         <v>12</v>
       </c>
-      <c r="G33" s="69">
+      <c r="H33" s="69">
         <v>1</v>
       </c>
-      <c r="H33" s="77">
+      <c r="I33" s="77">
         <v>1</v>
       </c>
-      <c r="I33" s="69">
-        <f t="shared" si="2"/>
+      <c r="J33" s="69">
+        <f>SUM(G33:I33)*D33</f>
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B34" s="108" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="88"/>
-      <c r="D34" s="62">
-        <f>_xlfn.CEILING.MATH(SUM(D10:D33))</f>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="62">
+        <f>_xlfn.CEILING.MATH(SUM(E10:E33))</f>
         <v>32</v>
       </c>
-      <c r="G34" s="88" t="s">
+      <c r="H34" s="108" t="s">
         <v>206</v>
       </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="62">
-        <f>SUM(I10:I33)</f>
+      <c r="I34" s="108"/>
+      <c r="J34" s="62">
+        <f>SUM(J10:J33)</f>
         <v>1070</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G35" s="151" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H35" s="112" t="s">
         <v>228</v>
       </c>
-      <c r="H35" s="150"/>
-      <c r="I35" s="62">
-        <f>SUMPRODUCT(G10:G33,C10:C33)</f>
+      <c r="I35" s="113"/>
+      <c r="J35" s="62">
+        <f>SUMPRODUCT(H10:H33,D10:D33)</f>
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G36" s="151" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H36" s="112" t="s">
         <v>229</v>
       </c>
-      <c r="H36" s="150"/>
-      <c r="I36" s="62">
-        <f>SUMPRODUCT(H10:H33,C10:C33)</f>
+      <c r="I36" s="113"/>
+      <c r="J36" s="62">
+        <f>SUMPRODUCT(I10:I33,D10:D33)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G37" s="151" t="s">
+    <row r="37" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H37" s="112" t="s">
         <v>230</v>
       </c>
-      <c r="H37" s="150"/>
-      <c r="I37" s="62">
-        <f>SUMPRODUCT(F10:F33,C10:C33)</f>
+      <c r="I37" s="113"/>
+      <c r="J37" s="62">
+        <f>SUMPRODUCT(G10:G33,D10:D33)</f>
         <v>928</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="161" t="s">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="163" t="s">
+      <c r="B38" s="176" t="s">
         <v>232</v>
       </c>
-      <c r="C38" s="163" t="s">
+      <c r="C38" s="177"/>
+      <c r="D38" s="103" t="s">
         <v>233</v>
       </c>
-      <c r="D38" s="163" t="s">
+      <c r="E38" s="103" t="s">
         <v>234</v>
       </c>
-      <c r="E38" s="165" t="s">
+      <c r="F38" s="104" t="s">
         <v>235</v>
       </c>
-      <c r="F38" s="166"/>
-      <c r="G38" s="166"/>
-      <c r="H38" s="166"/>
-      <c r="I38" s="166"/>
-      <c r="J38" s="166"/>
-      <c r="K38" s="166"/>
-      <c r="L38" s="166"/>
-      <c r="M38" s="166"/>
-      <c r="N38" s="166"/>
-      <c r="O38" s="166"/>
-      <c r="P38" s="167"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="162"/>
-      <c r="B39" s="164"/>
-      <c r="C39" s="164"/>
-      <c r="D39" s="164"/>
-      <c r="E39" s="153" t="s">
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="105"/>
+      <c r="J38" s="105"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="105"/>
+      <c r="M38" s="105"/>
+      <c r="N38" s="105"/>
+      <c r="O38" s="105"/>
+      <c r="P38" s="105"/>
+      <c r="Q38" s="106"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="194"/>
+      <c r="B39" s="195"/>
+      <c r="C39" s="196"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="198" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="153" t="s">
+      <c r="G39" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="153" t="s">
+      <c r="H39" s="198" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="153" t="s">
+      <c r="I39" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="I39" s="153" t="s">
+      <c r="J39" s="198" t="s">
         <v>30</v>
       </c>
-      <c r="J39" s="153" t="s">
+      <c r="K39" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="K39" s="153" t="s">
+      <c r="L39" s="198" t="s">
         <v>36</v>
       </c>
-      <c r="L39" s="153" t="s">
+      <c r="M39" s="198" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="153" t="s">
+      <c r="N39" s="198" t="s">
         <v>48</v>
       </c>
-      <c r="N39" s="153" t="s">
+      <c r="O39" s="198" t="s">
         <v>52</v>
       </c>
-      <c r="O39" s="153" t="s">
+      <c r="P39" s="198" t="s">
         <v>60</v>
       </c>
-      <c r="P39" s="155" t="s">
+      <c r="Q39" s="199" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="156" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="154" cm="1">
-        <f t="array" ref="B40">SUMPRODUCT(E40:P40,TRANSPOSE($F$10:$F$21))</f>
+      <c r="B40" s="174" cm="1">
+        <f t="array" ref="B40">SUMPRODUCT(F40:Q40,TRANSPOSE($G$10:$G$21))</f>
         <v>246</v>
       </c>
-      <c r="C40" s="154" cm="1">
-        <f t="array" ref="C40">SUMPRODUCT(E40:P40,TRANSPOSE($H$10:$H$21))</f>
+      <c r="C40" s="175"/>
+      <c r="D40" s="188" cm="1">
+        <f t="array" ref="D40">SUMPRODUCT(F40:Q40,TRANSPOSE($I$10:$I$21))</f>
         <v>18</v>
       </c>
-      <c r="D40" s="154" cm="1">
-        <f t="array" ref="D40">SUMPRODUCT(E40:P40,TRANSPOSE($G$10:$G$21))</f>
+      <c r="E40" s="74" cm="1">
+        <f t="array" ref="E40">SUMPRODUCT(F40:Q40,TRANSPOSE($H$10:$H$21))</f>
         <v>16</v>
       </c>
-      <c r="E40" s="154">
+      <c r="F40" s="188">
         <v>1</v>
       </c>
-      <c r="F40" s="154">
+      <c r="G40" s="67">
         <v>1</v>
       </c>
-      <c r="G40" s="154">
+      <c r="H40" s="188">
         <v>5</v>
       </c>
-      <c r="H40" s="154">
+      <c r="I40" s="67">
         <v>1</v>
       </c>
-      <c r="I40" s="154">
+      <c r="J40" s="188">
         <v>5</v>
       </c>
-      <c r="J40" s="154">
+      <c r="K40" s="67">
         <v>1</v>
       </c>
-      <c r="K40" s="154">
+      <c r="L40" s="188">
         <v>1</v>
       </c>
-      <c r="L40" s="154">
+      <c r="M40" s="67">
         <v>0</v>
       </c>
-      <c r="M40" s="154">
+      <c r="N40" s="188">
         <v>0</v>
       </c>
-      <c r="N40" s="154">
+      <c r="O40" s="67">
         <v>0</v>
       </c>
-      <c r="O40" s="154">
+      <c r="P40" s="188">
         <v>0</v>
       </c>
-      <c r="P40" s="157">
+      <c r="Q40" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="156" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="154" cm="1">
-        <f t="array" ref="B41">SUMPRODUCT(E41:P41,TRANSPOSE($F$10:$F$21))</f>
+      <c r="B41" s="172" cm="1">
+        <f t="array" ref="B41">SUMPRODUCT(F41:Q41,TRANSPOSE($G$10:$G$21))</f>
         <v>227</v>
       </c>
-      <c r="C41" s="154" cm="1">
-        <f t="array" ref="C41">SUMPRODUCT(E41:P41,TRANSPOSE($H$10:$H$21))</f>
+      <c r="C41" s="173"/>
+      <c r="D41" s="76" cm="1">
+        <f t="array" ref="D41">SUMPRODUCT(F41:Q41,TRANSPOSE($I$10:$I$21))</f>
         <v>21</v>
       </c>
-      <c r="D41" s="154" cm="1">
-        <f t="array" ref="D41">SUMPRODUCT(E41:P41,TRANSPOSE($G$10:$G$21))</f>
+      <c r="E41" s="68" cm="1">
+        <f t="array" ref="E41">SUMPRODUCT(F41:Q41,TRANSPOSE($H$10:$H$21))</f>
         <v>18</v>
       </c>
-      <c r="E41" s="154">
+      <c r="F41" s="76">
         <v>0</v>
       </c>
-      <c r="F41" s="154">
+      <c r="G41" s="68">
         <v>0</v>
       </c>
-      <c r="G41" s="154">
+      <c r="H41" s="76">
         <v>0</v>
       </c>
-      <c r="H41" s="154">
+      <c r="I41" s="68">
         <v>0</v>
       </c>
-      <c r="I41" s="154">
+      <c r="J41" s="76">
         <v>2</v>
       </c>
-      <c r="J41" s="154">
+      <c r="K41" s="68">
         <v>0</v>
       </c>
-      <c r="K41" s="154">
+      <c r="L41" s="76">
         <v>1</v>
       </c>
-      <c r="L41" s="154">
+      <c r="M41" s="68">
         <v>2</v>
       </c>
-      <c r="M41" s="154">
+      <c r="N41" s="76">
         <v>2</v>
       </c>
-      <c r="N41" s="154">
+      <c r="O41" s="68">
         <v>5</v>
       </c>
-      <c r="O41" s="154">
+      <c r="P41" s="76">
         <v>6</v>
       </c>
-      <c r="P41" s="157">
+      <c r="Q41" s="68">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="156" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="201" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="154" cm="1">
-        <f t="array" ref="B42">SUMPRODUCT(E42:P42,TRANSPOSE($F$10:$F$21))</f>
+      <c r="B42" s="172" cm="1">
+        <f t="array" ref="B42">SUMPRODUCT(F42:Q42,TRANSPOSE($G$10:$G$21))</f>
         <v>246</v>
       </c>
-      <c r="C42" s="154" cm="1">
-        <f t="array" ref="C42">SUMPRODUCT(E42:P42,TRANSPOSE($H$10:$H$21))</f>
+      <c r="C42" s="173"/>
+      <c r="D42" s="76" cm="1">
+        <f t="array" ref="D42">SUMPRODUCT(F42:Q42,TRANSPOSE($I$10:$I$21))</f>
         <v>18</v>
       </c>
-      <c r="D42" s="154" cm="1">
-        <f t="array" ref="D42">SUMPRODUCT(E42:P42,TRANSPOSE($G$10:$G$21))</f>
+      <c r="E42" s="71" cm="1">
+        <f t="array" ref="E42">SUMPRODUCT(F42:Q42,TRANSPOSE($H$10:$H$21))</f>
         <v>16</v>
       </c>
-      <c r="E42" s="154">
+      <c r="F42" s="76">
         <v>1</v>
       </c>
-      <c r="F42" s="154">
+      <c r="G42" s="68">
         <v>1</v>
       </c>
-      <c r="G42" s="154">
+      <c r="H42" s="76">
         <v>5</v>
       </c>
-      <c r="H42" s="154">
+      <c r="I42" s="68">
         <v>1</v>
       </c>
-      <c r="I42" s="154">
+      <c r="J42" s="76">
         <v>5</v>
       </c>
-      <c r="J42" s="154">
+      <c r="K42" s="68">
         <v>1</v>
       </c>
-      <c r="K42" s="154">
+      <c r="L42" s="76">
         <v>1</v>
       </c>
-      <c r="L42" s="154">
+      <c r="M42" s="68">
         <v>0</v>
       </c>
-      <c r="M42" s="154">
+      <c r="N42" s="76">
         <v>0</v>
       </c>
-      <c r="N42" s="154">
+      <c r="O42" s="68">
         <v>0</v>
       </c>
-      <c r="O42" s="154">
+      <c r="P42" s="76">
         <v>0</v>
       </c>
-      <c r="P42" s="157">
+      <c r="Q42" s="68">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="158" t="s">
+    <row r="43" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="159" cm="1">
-        <f t="array" ref="B43">SUMPRODUCT(E43:P43,TRANSPOSE($F$10:$F$21))</f>
+      <c r="B43" s="179" cm="1">
+        <f t="array" ref="B43">SUMPRODUCT(F43:Q43,TRANSPOSE($G$10:$G$21))</f>
         <v>209</v>
       </c>
-      <c r="C43" s="159" cm="1">
-        <f t="array" ref="C43">SUMPRODUCT(E43:P43,TRANSPOSE($H$10:$H$21))</f>
+      <c r="C43" s="180"/>
+      <c r="D43" s="77" cm="1">
+        <f t="array" ref="D43">SUMPRODUCT(F43:Q43,TRANSPOSE($I$10:$I$21))</f>
         <v>18</v>
       </c>
-      <c r="D43" s="159" cm="1">
-        <f t="array" ref="D43">SUMPRODUCT(E43:P43,TRANSPOSE($G$10:$G$21))</f>
+      <c r="E43" s="69" cm="1">
+        <f t="array" ref="E43">SUMPRODUCT(F43:Q43,TRANSPOSE($H$10:$H$21))</f>
         <v>17</v>
       </c>
-      <c r="E43" s="159">
+      <c r="F43" s="77">
         <v>0</v>
       </c>
-      <c r="F43" s="159">
+      <c r="G43" s="69">
         <v>0</v>
       </c>
-      <c r="G43" s="159">
+      <c r="H43" s="77">
         <v>0</v>
       </c>
-      <c r="H43" s="159">
+      <c r="I43" s="69">
         <v>0</v>
       </c>
-      <c r="I43" s="159">
+      <c r="J43" s="77">
         <v>2</v>
       </c>
-      <c r="J43" s="159">
+      <c r="K43" s="69">
         <v>0</v>
       </c>
-      <c r="K43" s="159">
+      <c r="L43" s="77">
         <v>1</v>
       </c>
-      <c r="L43" s="159">
+      <c r="M43" s="69">
         <v>0</v>
       </c>
-      <c r="M43" s="159">
+      <c r="N43" s="77">
         <v>2</v>
       </c>
-      <c r="N43" s="159">
+      <c r="O43" s="69">
         <v>5</v>
       </c>
-      <c r="O43" s="159">
+      <c r="P43" s="77">
         <v>6</v>
       </c>
-      <c r="P43" s="160">
+      <c r="Q43" s="69">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="152" t="s">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="82" t="s">
         <v>236</v>
       </c>
       <c r="B44" s="62">
-        <f>SUM(B40:D43)</f>
+        <f>SUM(B40:E43)</f>
         <v>1070</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="189" t="s">
+    <row r="46" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="190"/>
-      <c r="C47" s="190"/>
-      <c r="D47" s="190"/>
-      <c r="E47" s="190"/>
-      <c r="F47" s="190"/>
-      <c r="G47" s="190"/>
-      <c r="H47" s="190"/>
-      <c r="I47" s="191"/>
-    </row>
-    <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="87" t="s">
+      <c r="B47" s="108"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="108"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="108"/>
+      <c r="G47" s="108"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="108"/>
+      <c r="J47" s="181"/>
+    </row>
+    <row r="48" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="89" t="s">
+      <c r="B48" s="107" t="s">
         <v>188</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="89" t="s">
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="109"/>
+      <c r="F48" s="96" t="s">
         <v>184</v>
       </c>
-      <c r="F48" s="91"/>
-      <c r="G48" s="93" t="s">
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
+      <c r="I48" s="171"/>
+      <c r="J48" s="182" t="s">
         <v>207</v>
       </c>
-      <c r="H48" s="93" t="s">
-        <v>213</v>
-      </c>
-      <c r="I48" s="186"/>
-    </row>
-    <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="92"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="111"/>
       <c r="B49" s="72" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="148" t="s">
+      <c r="C49" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="D49" s="165" t="s">
         <v>226</v>
       </c>
-      <c r="D49" s="74" t="s">
+      <c r="E49" s="73" t="s">
         <v>187</v>
       </c>
-      <c r="E49" s="80" t="s">
+      <c r="F49" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="F49" s="73" t="s">
+      <c r="G49" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="H49" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="I49" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="G49" s="94"/>
-      <c r="H49" s="94"/>
-      <c r="I49" s="186"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" s="183"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="B50" s="174" t="s">
+      <c r="B50" s="84" t="s">
         <v>223</v>
       </c>
-      <c r="C50" s="175"/>
-      <c r="D50" s="176" t="s">
+      <c r="C50" s="71">
+        <v>1</v>
+      </c>
+      <c r="D50" s="166"/>
+      <c r="E50" s="83" t="s">
         <v>212</v>
       </c>
-      <c r="E50" s="177"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="147" t="s">
+      <c r="F50" s="86"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="188"/>
+      <c r="J50" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="64">
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B51" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" s="68">
         <v>1</v>
       </c>
-      <c r="I50" s="187"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="178" t="s">
-        <v>211</v>
-      </c>
-      <c r="B51" s="174" t="s">
-        <v>215</v>
-      </c>
-      <c r="C51" s="175"/>
-      <c r="D51" s="179"/>
-      <c r="E51" s="180"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="145"/>
-      <c r="H51" s="65">
+      <c r="D51" s="166"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="68"/>
+      <c r="I51" s="76"/>
+      <c r="J51" s="183"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="87" t="s">
+        <v>218</v>
+      </c>
+      <c r="B52" s="163" t="s">
+        <v>219</v>
+      </c>
+      <c r="C52" s="178">
+        <f>_xlfn.CEILING.MATH(SUM(B40,E40)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="D52" s="92"/>
+      <c r="E52" s="98" t="s">
+        <v>212</v>
+      </c>
+      <c r="F52" s="100"/>
+      <c r="G52" s="94"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="189"/>
+      <c r="J52" s="183"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" s="164"/>
+      <c r="C53" s="178"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="99"/>
+      <c r="F53" s="101"/>
+      <c r="G53" s="95"/>
+      <c r="H53" s="101"/>
+      <c r="I53" s="190"/>
+      <c r="J53" s="183"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="87" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54" s="68">
         <v>1</v>
       </c>
-      <c r="I51" s="187"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="178" t="s">
-        <v>218</v>
-      </c>
-      <c r="B52" s="168" t="s">
-        <v>219</v>
-      </c>
-      <c r="C52" s="175"/>
-      <c r="D52" s="172" t="s">
+      <c r="D54" s="166"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="76"/>
+      <c r="J54" s="183"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="68">
+        <f>_xlfn.CEILING.MATH(D40/48)</f>
+        <v>1</v>
+      </c>
+      <c r="D55" s="167"/>
+      <c r="E55" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E52" s="170"/>
-      <c r="F52" s="170"/>
-      <c r="G52" s="145"/>
-      <c r="H52" s="184">
-        <f>_xlfn.CEILING.MATH(SUM(B40,D40)/48)</f>
-        <v>6</v>
-      </c>
-      <c r="I52" s="188"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="178" t="s">
-        <v>220</v>
-      </c>
-      <c r="B53" s="169"/>
-      <c r="C53" s="175"/>
-      <c r="D53" s="173"/>
-      <c r="E53" s="171"/>
-      <c r="F53" s="171"/>
-      <c r="G53" s="145"/>
-      <c r="H53" s="185"/>
-      <c r="I53" s="188"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="178" t="s">
-        <v>224</v>
-      </c>
-      <c r="B54" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="C54" s="175"/>
-      <c r="D54" s="179"/>
-      <c r="E54" s="180"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="145"/>
-      <c r="H54" s="65">
-        <v>1</v>
-      </c>
-      <c r="I54" s="187"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="178" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="181" t="s">
-        <v>216</v>
-      </c>
-      <c r="C55" s="178"/>
-      <c r="D55" s="176" t="s">
-        <v>212</v>
-      </c>
-      <c r="E55" s="180"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="145"/>
-      <c r="H55" s="65">
-        <f>_xlfn.CEILING.MATH(C40/48)</f>
-        <v>1</v>
-      </c>
-      <c r="I55" s="187"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F55" s="88"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="76"/>
+      <c r="J55" s="183"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="181" t="s">
+      <c r="B56" s="89" t="s">
         <v>231</v>
       </c>
-      <c r="C56" s="178"/>
-      <c r="D56" s="176" t="s">
+      <c r="C56" s="68">
+        <f>D40</f>
+        <v>18</v>
+      </c>
+      <c r="D56" s="167"/>
+      <c r="E56" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E56" s="180"/>
-      <c r="F56" s="68"/>
-      <c r="G56" s="145"/>
-      <c r="H56" s="65">
-        <f>C40</f>
-        <v>18</v>
-      </c>
-      <c r="I56" s="187"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F56" s="88"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="68"/>
+      <c r="I56" s="76"/>
+      <c r="J56" s="183"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="B57" s="181" t="s">
+      <c r="B57" s="89" t="s">
         <v>222</v>
       </c>
-      <c r="C57" s="178"/>
-      <c r="D57" s="176" t="s">
+      <c r="C57" s="68">
+        <v>1</v>
+      </c>
+      <c r="D57" s="167"/>
+      <c r="E57" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E57" s="180"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="145"/>
-      <c r="H57" s="65">
-        <v>1</v>
-      </c>
-      <c r="I57" s="187"/>
-    </row>
-    <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F57" s="88"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="68"/>
+      <c r="I57" s="76"/>
+      <c r="J57" s="183"/>
+    </row>
+    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="79" t="s">
         <v>214</v>
       </c>
-      <c r="B58" s="149" t="s">
+      <c r="B58" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="C58" s="85"/>
-      <c r="D58" s="182"/>
-      <c r="E58" s="183"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="146"/>
-      <c r="H58" s="66">
-        <f>D40</f>
+      <c r="C58" s="78">
+        <f>E40</f>
         <v>16</v>
       </c>
-      <c r="I58" s="187"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D58" s="168"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="78"/>
+      <c r="I58" s="191"/>
+      <c r="J58" s="187"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="B59" s="174" t="s">
+      <c r="B59" s="84" t="s">
         <v>223</v>
       </c>
-      <c r="C59" s="175"/>
-      <c r="D59" s="176" t="s">
+      <c r="C59" s="67">
+        <v>1</v>
+      </c>
+      <c r="D59" s="166"/>
+      <c r="E59" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E59" s="177"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="147" t="s">
+      <c r="F59" s="86"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="67"/>
+      <c r="I59" s="86"/>
+      <c r="J59" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="H59" s="64">
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B60" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="68">
         <v>1</v>
       </c>
-      <c r="I59" s="187"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="178" t="s">
-        <v>211</v>
-      </c>
-      <c r="B60" s="174" t="s">
-        <v>215</v>
-      </c>
-      <c r="C60" s="175"/>
-      <c r="D60" s="179"/>
-      <c r="E60" s="180"/>
-      <c r="F60" s="68"/>
-      <c r="G60" s="145"/>
-      <c r="H60" s="65">
+      <c r="D60" s="166"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="68"/>
+      <c r="I60" s="88"/>
+      <c r="J60" s="185"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="87" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="163" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="178">
+        <f>_xlfn.CEILING.MATH(SUM(B41,E41)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="D61" s="169"/>
+      <c r="E61" s="98" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" s="100"/>
+      <c r="G61" s="94"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="192"/>
+      <c r="J61" s="185"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62" s="164"/>
+      <c r="C62" s="178"/>
+      <c r="D62" s="170"/>
+      <c r="E62" s="99"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="95"/>
+      <c r="H62" s="101"/>
+      <c r="I62" s="193"/>
+      <c r="J62" s="185"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="87" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="C63" s="68">
         <v>1</v>
       </c>
-      <c r="I60" s="187"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="178" t="s">
-        <v>218</v>
-      </c>
-      <c r="B61" s="168" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="168"/>
-      <c r="D61" s="172" t="s">
+      <c r="D63" s="166"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="88"/>
+      <c r="J63" s="185"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" s="89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="68">
+        <f>_xlfn.CEILING.MATH(D41/48)</f>
+        <v>1</v>
+      </c>
+      <c r="D64" s="167"/>
+      <c r="E64" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E61" s="170"/>
-      <c r="F61" s="170"/>
-      <c r="G61" s="145"/>
-      <c r="H61" s="184">
-        <f>_xlfn.CEILING.MATH(SUM(B41,D41)/48)</f>
-        <v>6</v>
-      </c>
-      <c r="I61" s="188"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="178" t="s">
-        <v>220</v>
-      </c>
-      <c r="B62" s="169"/>
-      <c r="C62" s="169"/>
-      <c r="D62" s="173"/>
-      <c r="E62" s="171"/>
-      <c r="F62" s="171"/>
-      <c r="G62" s="145"/>
-      <c r="H62" s="185"/>
-      <c r="I62" s="188"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="178" t="s">
-        <v>224</v>
-      </c>
-      <c r="B63" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="C63" s="175"/>
-      <c r="D63" s="179"/>
-      <c r="E63" s="180"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="145"/>
-      <c r="H63" s="65">
-        <v>1</v>
-      </c>
-      <c r="I63" s="187"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="178" t="s">
-        <v>217</v>
-      </c>
-      <c r="B64" s="181" t="s">
-        <v>216</v>
-      </c>
-      <c r="C64" s="178"/>
-      <c r="D64" s="176" t="s">
-        <v>212</v>
-      </c>
-      <c r="E64" s="180"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="145"/>
-      <c r="H64" s="65">
-        <f>_xlfn.CEILING.MATH(C41/48)</f>
-        <v>1</v>
-      </c>
-      <c r="I64" s="187"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F64" s="88"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="68"/>
+      <c r="I64" s="88"/>
+      <c r="J64" s="185"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="181" t="s">
+      <c r="B65" s="89" t="s">
         <v>221</v>
       </c>
-      <c r="C65" s="178"/>
-      <c r="D65" s="176" t="s">
+      <c r="C65" s="68">
+        <f>D41</f>
+        <v>21</v>
+      </c>
+      <c r="D65" s="167"/>
+      <c r="E65" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E65" s="180"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="145"/>
-      <c r="H65" s="65">
-        <f>C41</f>
-        <v>21</v>
-      </c>
-      <c r="I65" s="187"/>
-    </row>
-    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F65" s="88"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="68"/>
+      <c r="I65" s="88"/>
+      <c r="J65" s="185"/>
+    </row>
+    <row r="66" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="79" t="s">
         <v>214</v>
       </c>
-      <c r="B66" s="149" t="s">
+      <c r="B66" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="C66" s="85"/>
-      <c r="D66" s="182"/>
-      <c r="E66" s="183"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="146"/>
-      <c r="H66" s="66">
-        <f>D41</f>
+      <c r="C66" s="69">
+        <f>E41</f>
         <v>18</v>
       </c>
-      <c r="I66" s="187"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D66" s="168"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="91"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="91"/>
+      <c r="J66" s="186"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="B67" s="174" t="s">
+      <c r="B67" s="84" t="s">
         <v>223</v>
       </c>
-      <c r="C67" s="175"/>
-      <c r="D67" s="176" t="s">
+      <c r="C67" s="67">
+        <v>1</v>
+      </c>
+      <c r="D67" s="166"/>
+      <c r="E67" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E67" s="177"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="147" t="s">
+      <c r="F67" s="86"/>
+      <c r="G67" s="64"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="188"/>
+      <c r="J67" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="H67" s="64">
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C68" s="68">
         <v>1</v>
       </c>
-      <c r="I67" s="187"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="178" t="s">
-        <v>211</v>
-      </c>
-      <c r="B68" s="174" t="s">
-        <v>215</v>
-      </c>
-      <c r="C68" s="175"/>
-      <c r="D68" s="179"/>
-      <c r="E68" s="180"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="145"/>
-      <c r="H68" s="65">
+      <c r="D68" s="166"/>
+      <c r="E68" s="83"/>
+      <c r="F68" s="88"/>
+      <c r="G68" s="65"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="76"/>
+      <c r="J68" s="183"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="87" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="163" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" s="178">
+        <f>_xlfn.CEILING.MATH(SUM(B42,E42)/48)</f>
+        <v>6</v>
+      </c>
+      <c r="D69" s="169"/>
+      <c r="E69" s="98" t="s">
+        <v>212</v>
+      </c>
+      <c r="F69" s="100"/>
+      <c r="G69" s="94"/>
+      <c r="H69" s="100"/>
+      <c r="I69" s="189"/>
+      <c r="J69" s="183"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B70" s="164"/>
+      <c r="C70" s="178"/>
+      <c r="D70" s="170"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="95"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="190"/>
+      <c r="J70" s="183"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="87" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="C71" s="68">
         <v>1</v>
       </c>
-      <c r="I68" s="187"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="178" t="s">
-        <v>218</v>
-      </c>
-      <c r="B69" s="168" t="s">
-        <v>219</v>
-      </c>
-      <c r="C69" s="168"/>
-      <c r="D69" s="172" t="s">
+      <c r="D71" s="166"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="88"/>
+      <c r="G71" s="65"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="76"/>
+      <c r="J71" s="183"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" s="68">
+        <f>_xlfn.CEILING.MATH(D42/48)</f>
+        <v>1</v>
+      </c>
+      <c r="D72" s="167"/>
+      <c r="E72" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E69" s="170"/>
-      <c r="F69" s="170"/>
-      <c r="G69" s="145"/>
-      <c r="H69" s="184">
-        <f>_xlfn.CEILING.MATH(SUM(B42,D42)/48)</f>
-        <v>6</v>
-      </c>
-      <c r="I69" s="187"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="178" t="s">
-        <v>220</v>
-      </c>
-      <c r="B70" s="169"/>
-      <c r="C70" s="169"/>
-      <c r="D70" s="173"/>
-      <c r="E70" s="171"/>
-      <c r="F70" s="171"/>
-      <c r="G70" s="145"/>
-      <c r="H70" s="185"/>
-      <c r="I70" s="187"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="178" t="s">
-        <v>224</v>
-      </c>
-      <c r="B71" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="C71" s="175"/>
-      <c r="D71" s="179"/>
-      <c r="E71" s="180"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="145"/>
-      <c r="H71" s="65">
-        <v>1</v>
-      </c>
-      <c r="I71" s="187"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="178" t="s">
-        <v>217</v>
-      </c>
-      <c r="B72" s="181" t="s">
-        <v>216</v>
-      </c>
-      <c r="C72" s="178"/>
-      <c r="D72" s="176" t="s">
-        <v>212</v>
-      </c>
-      <c r="E72" s="180"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="145"/>
-      <c r="H72" s="65">
-        <f>_xlfn.CEILING.MATH(C42/48)</f>
-        <v>1</v>
-      </c>
-      <c r="I72" s="187"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F72" s="88"/>
+      <c r="G72" s="65"/>
+      <c r="H72" s="68"/>
+      <c r="I72" s="76"/>
+      <c r="J72" s="183"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="B73" s="181" t="s">
+      <c r="B73" s="89" t="s">
         <v>221</v>
       </c>
-      <c r="C73" s="178"/>
-      <c r="D73" s="176" t="s">
+      <c r="C73" s="68">
+        <f>D42</f>
+        <v>18</v>
+      </c>
+      <c r="D73" s="167"/>
+      <c r="E73" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E73" s="180"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="145"/>
-      <c r="H73" s="65">
-        <f>C42</f>
-        <v>18</v>
-      </c>
-      <c r="I73" s="187"/>
-    </row>
-    <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F73" s="88"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="76"/>
+      <c r="J73" s="183"/>
+    </row>
+    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="79" t="s">
         <v>214</v>
       </c>
-      <c r="B74" s="149" t="s">
+      <c r="B74" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="C74" s="85"/>
-      <c r="D74" s="182"/>
-      <c r="E74" s="183"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="146"/>
-      <c r="H74" s="66">
-        <f>D42</f>
+      <c r="C74" s="69">
+        <f>E42</f>
         <v>16</v>
       </c>
-      <c r="I74" s="187"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D74" s="168"/>
+      <c r="E74" s="90"/>
+      <c r="F74" s="91"/>
+      <c r="G74" s="66"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="191"/>
+      <c r="J74" s="187"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="B75" s="174" t="s">
+      <c r="B75" s="84" t="s">
         <v>223</v>
       </c>
-      <c r="C75" s="175"/>
-      <c r="D75" s="176" t="s">
+      <c r="C75" s="71">
+        <v>1</v>
+      </c>
+      <c r="D75" s="166"/>
+      <c r="E75" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E75" s="177"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="147" t="s">
+      <c r="F75" s="86"/>
+      <c r="G75" s="64"/>
+      <c r="H75" s="67"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="184" t="s">
         <v>88</v>
       </c>
-      <c r="H75" s="64">
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B76" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C76" s="68">
         <v>1</v>
       </c>
-      <c r="I75" s="187"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="178" t="s">
-        <v>211</v>
-      </c>
-      <c r="B76" s="174" t="s">
-        <v>215</v>
-      </c>
-      <c r="C76" s="175"/>
-      <c r="D76" s="179"/>
-      <c r="E76" s="180"/>
-      <c r="F76" s="68"/>
-      <c r="G76" s="145"/>
-      <c r="H76" s="65">
+      <c r="D76" s="166"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="88"/>
+      <c r="J76" s="185"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="87" t="s">
+        <v>218</v>
+      </c>
+      <c r="B77" s="163" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="178">
+        <f>_xlfn.CEILING.MATH(SUM(B43,E43)/48)</f>
+        <v>5</v>
+      </c>
+      <c r="D77" s="169"/>
+      <c r="E77" s="98" t="s">
+        <v>212</v>
+      </c>
+      <c r="F77" s="100"/>
+      <c r="G77" s="94"/>
+      <c r="H77" s="100"/>
+      <c r="I77" s="192"/>
+      <c r="J77" s="185"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="164"/>
+      <c r="C78" s="178"/>
+      <c r="D78" s="170"/>
+      <c r="E78" s="99"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="95"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="193"/>
+      <c r="J78" s="185"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="87" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" s="68">
         <v>1</v>
       </c>
-      <c r="I76" s="187"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="178" t="s">
-        <v>218</v>
-      </c>
-      <c r="B77" s="168" t="s">
-        <v>219</v>
-      </c>
-      <c r="C77" s="168"/>
-      <c r="D77" s="172" t="s">
+      <c r="D79" s="166"/>
+      <c r="E79" s="83"/>
+      <c r="F79" s="88"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="88"/>
+      <c r="J79" s="185"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B80" s="89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="68">
+        <f>_xlfn.CEILING.MATH(D43/48)</f>
+        <v>1</v>
+      </c>
+      <c r="D80" s="167"/>
+      <c r="E80" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E77" s="170"/>
-      <c r="F77" s="170"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="184">
-        <f>_xlfn.CEILING.MATH(SUM(B43,D43)/48)</f>
-        <v>5</v>
-      </c>
-      <c r="I77" s="187"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="178" t="s">
-        <v>220</v>
-      </c>
-      <c r="B78" s="169"/>
-      <c r="C78" s="169"/>
-      <c r="D78" s="173"/>
-      <c r="E78" s="171"/>
-      <c r="F78" s="171"/>
-      <c r="G78" s="145"/>
-      <c r="H78" s="185"/>
-      <c r="I78" s="187"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="178" t="s">
-        <v>224</v>
-      </c>
-      <c r="B79" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="C79" s="175"/>
-      <c r="D79" s="179"/>
-      <c r="E79" s="180"/>
-      <c r="F79" s="68"/>
-      <c r="G79" s="145"/>
-      <c r="H79" s="65">
-        <v>1</v>
-      </c>
-      <c r="I79" s="187"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="178" t="s">
-        <v>217</v>
-      </c>
-      <c r="B80" s="181" t="s">
-        <v>216</v>
-      </c>
-      <c r="C80" s="178"/>
-      <c r="D80" s="176" t="s">
-        <v>212</v>
-      </c>
-      <c r="E80" s="180"/>
-      <c r="F80" s="68"/>
-      <c r="G80" s="145"/>
-      <c r="H80" s="65">
-        <f>_xlfn.CEILING.MATH(C43/48)</f>
-        <v>1</v>
-      </c>
-      <c r="I80" s="187"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F80" s="88"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="88"/>
+      <c r="J80" s="185"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="B81" s="181" t="s">
+      <c r="B81" s="89" t="s">
         <v>221</v>
       </c>
-      <c r="C81" s="178"/>
-      <c r="D81" s="176" t="s">
+      <c r="C81" s="68">
+        <f>D43</f>
+        <v>18</v>
+      </c>
+      <c r="D81" s="167"/>
+      <c r="E81" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="E81" s="180"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="145"/>
-      <c r="H81" s="65">
-        <f>C43</f>
-        <v>18</v>
-      </c>
-      <c r="I81" s="187"/>
-    </row>
-    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F81" s="88"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="68"/>
+      <c r="I81" s="88"/>
+      <c r="J81" s="185"/>
+    </row>
+    <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="79" t="s">
         <v>214</v>
       </c>
-      <c r="B82" s="149" t="s">
+      <c r="B82" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="C82" s="85"/>
-      <c r="D82" s="182"/>
-      <c r="E82" s="183"/>
-      <c r="F82" s="69"/>
-      <c r="G82" s="146"/>
-      <c r="H82" s="66">
-        <f>D43</f>
+      <c r="C82" s="69">
+        <f>E43</f>
         <v>17</v>
       </c>
-      <c r="I82" s="187"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-    </row>
-    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B85" s="144">
-        <v>280</v>
-      </c>
-      <c r="C85"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
-      <c r="I85"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="83" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" s="81">
-        <v>266</v>
-      </c>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="B87" s="81">
-        <v>280</v>
-      </c>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-    </row>
-    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="84" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" s="82">
-        <v>244</v>
-      </c>
-      <c r="C88"/>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
+      <c r="D82" s="168"/>
+      <c r="E82" s="90"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="66"/>
+      <c r="H82" s="69"/>
+      <c r="I82" s="91"/>
+      <c r="J82" s="186"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="63"/>
+      <c r="B85" s="63"/>
+      <c r="C85" s="63"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="63"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="63"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="63"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="63"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="82">
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A10:A21"/>
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J75:J82"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="J59:J66"/>
+    <mergeCell ref="J67:J74"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="J50:J58"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
     <mergeCell ref="B61:B62"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="C77:C78"/>
     <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
     <mergeCell ref="D77:D78"/>
     <mergeCell ref="E77:E78"/>
     <mergeCell ref="F77:F78"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G69:G70"/>
     <mergeCell ref="F69:F70"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="D69:D70"/>
-    <mergeCell ref="C69:C70"/>
     <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C61:C62"/>
     <mergeCell ref="D61:D62"/>
     <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:P38"/>
-    <mergeCell ref="G50:G58"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="G59:G66"/>
-    <mergeCell ref="G67:G74"/>
-    <mergeCell ref="G75:G82"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A10:A21"/>
-    <mergeCell ref="A22:A33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="G35:H35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D57" r:id="rId1" xr:uid="{A029F0E9-C9D1-4CD2-ADE0-4784660C9D97}"/>
-    <hyperlink ref="D56" r:id="rId2" xr:uid="{857B9BB1-3282-4DA1-96F1-AAF639475A2D}"/>
-    <hyperlink ref="D55" r:id="rId3" xr:uid="{F6634F98-8A1B-4296-BD90-DA744A704792}"/>
-    <hyperlink ref="D52" r:id="rId4" xr:uid="{4EB1002D-512E-490E-8CE7-EC79EF9020B5}"/>
-    <hyperlink ref="D50" r:id="rId5" xr:uid="{883103FA-02FE-4CB6-A102-CF901C48D85E}"/>
-    <hyperlink ref="D59" r:id="rId6" xr:uid="{D897E3EA-4B88-4B07-8E04-9BC62AA8DE11}"/>
-    <hyperlink ref="D65" r:id="rId7" xr:uid="{881D9D2F-DA17-40C4-AA3C-EF0106248703}"/>
-    <hyperlink ref="D64" r:id="rId8" xr:uid="{AA809D2B-FA2E-4C7A-A7B7-4832F6E4D09E}"/>
-    <hyperlink ref="D61" r:id="rId9" xr:uid="{C8C2BF74-BEEC-4D78-81DC-1C5EAC1A63DA}"/>
-    <hyperlink ref="D67" r:id="rId10" xr:uid="{D2753667-397D-495A-9EFF-B90CDE17CC24}"/>
-    <hyperlink ref="D73" r:id="rId11" xr:uid="{509B4E63-2B9B-4B39-AE71-EC1816BD00CA}"/>
-    <hyperlink ref="D72" r:id="rId12" xr:uid="{A9DD4DFE-201F-431D-BB40-6EDD85971C07}"/>
-    <hyperlink ref="D69" r:id="rId13" xr:uid="{7056E575-1D4F-4EF2-89C3-BBB0B9A6A6BD}"/>
-    <hyperlink ref="D75" r:id="rId14" xr:uid="{339D2A8A-3C61-4946-8E27-FBC09434974D}"/>
-    <hyperlink ref="D81" r:id="rId15" xr:uid="{CE0123D6-F228-4B48-B3A9-3B41355BD82C}"/>
-    <hyperlink ref="D80" r:id="rId16" xr:uid="{ADA3AFEC-EFC1-4367-AF19-DAEAF49BD26A}"/>
-    <hyperlink ref="D77" r:id="rId17" xr:uid="{4C3B922A-447E-41C3-9BF0-53BEF1EE6AA2}"/>
+    <hyperlink ref="E57" r:id="rId1" xr:uid="{A029F0E9-C9D1-4CD2-ADE0-4784660C9D97}"/>
+    <hyperlink ref="E56" r:id="rId2" xr:uid="{857B9BB1-3282-4DA1-96F1-AAF639475A2D}"/>
+    <hyperlink ref="E55" r:id="rId3" xr:uid="{F6634F98-8A1B-4296-BD90-DA744A704792}"/>
+    <hyperlink ref="E52" r:id="rId4" xr:uid="{4EB1002D-512E-490E-8CE7-EC79EF9020B5}"/>
+    <hyperlink ref="E50" r:id="rId5" xr:uid="{883103FA-02FE-4CB6-A102-CF901C48D85E}"/>
+    <hyperlink ref="E59" r:id="rId6" xr:uid="{D897E3EA-4B88-4B07-8E04-9BC62AA8DE11}"/>
+    <hyperlink ref="E65" r:id="rId7" xr:uid="{881D9D2F-DA17-40C4-AA3C-EF0106248703}"/>
+    <hyperlink ref="E64" r:id="rId8" xr:uid="{AA809D2B-FA2E-4C7A-A7B7-4832F6E4D09E}"/>
+    <hyperlink ref="E61" r:id="rId9" xr:uid="{C8C2BF74-BEEC-4D78-81DC-1C5EAC1A63DA}"/>
+    <hyperlink ref="E67" r:id="rId10" xr:uid="{D2753667-397D-495A-9EFF-B90CDE17CC24}"/>
+    <hyperlink ref="E73" r:id="rId11" xr:uid="{509B4E63-2B9B-4B39-AE71-EC1816BD00CA}"/>
+    <hyperlink ref="E72" r:id="rId12" xr:uid="{A9DD4DFE-201F-431D-BB40-6EDD85971C07}"/>
+    <hyperlink ref="E69" r:id="rId13" xr:uid="{7056E575-1D4F-4EF2-89C3-BBB0B9A6A6BD}"/>
+    <hyperlink ref="E75" r:id="rId14" xr:uid="{339D2A8A-3C61-4946-8E27-FBC09434974D}"/>
+    <hyperlink ref="E81" r:id="rId15" xr:uid="{CE0123D6-F228-4B48-B3A9-3B41355BD82C}"/>
+    <hyperlink ref="E80" r:id="rId16" xr:uid="{ADA3AFEC-EFC1-4367-AF19-DAEAF49BD26A}"/>
+    <hyperlink ref="E77" r:id="rId17" xr:uid="{4C3B922A-447E-41C3-9BF0-53BEF1EE6AA2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A52946-D4CE-40B0-A487-FBC087A60333}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="26.44140625" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>